--- a/data/flat/model_ledgers/mlb-moneyline-elo-trend-lr.xlsx
+++ b/data/flat/model_ledgers/mlb-moneyline-elo-trend-lr.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ48"/>
+  <dimension ref="A1:AJ76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5762,14 +5762,34 @@
       <c r="W48" s="2" t="inlineStr"/>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y48" s="2" t="inlineStr"/>
-      <c r="Z48" s="2" t="inlineStr"/>
-      <c r="AA48" s="2" t="inlineStr"/>
-      <c r="AB48" s="2" t="inlineStr"/>
-      <c r="AC48" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>0.515000</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>0.000437</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:15:17.663386Z</t>
+        </is>
+      </c>
       <c r="AD48" s="2" t="inlineStr"/>
       <c r="AE48" s="2" t="inlineStr"/>
       <c r="AF48" s="2" t="inlineStr"/>
@@ -5778,8 +5798,2976 @@
       <c r="AI48" s="2" t="inlineStr"/>
       <c r="AJ48" s="2" t="inlineStr"/>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>f81c2723b5ba4b32</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>05c3756bf75b5965</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>401816384</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>0.608376</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>0.577114</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>0.028544067226890846</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:15:51.012225Z</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:35:00-0400</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr"/>
+      <c r="W49" s="2" t="inlineStr"/>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr"/>
+      <c r="Z49" s="2" t="inlineStr"/>
+      <c r="AA49" s="2" t="inlineStr"/>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr"/>
+      <c r="AE49" s="2" t="inlineStr"/>
+      <c r="AF49" s="2" t="inlineStr"/>
+      <c r="AG49" s="2" t="inlineStr"/>
+      <c r="AH49" s="2" t="inlineStr"/>
+      <c r="AI49" s="2" t="inlineStr"/>
+      <c r="AJ49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>54638b7f302b453f</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>347d61eb57e3bb0a</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>401816385</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>0.537985</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>0.557214</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>-0.02148636563876649</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:15:52.049827Z</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr"/>
+      <c r="W50" s="2" t="inlineStr"/>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr"/>
+      <c r="Z50" s="2" t="inlineStr"/>
+      <c r="AA50" s="2" t="inlineStr"/>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr"/>
+      <c r="AE50" s="2" t="inlineStr"/>
+      <c r="AF50" s="2" t="inlineStr"/>
+      <c r="AG50" s="2" t="inlineStr"/>
+      <c r="AH50" s="2" t="inlineStr"/>
+      <c r="AI50" s="2" t="inlineStr"/>
+      <c r="AJ50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>1fd264f5b5994ea9</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>f82e26d9838dadee</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>401816388</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>0.566359</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>0.577114</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>-0.013472932773109236</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:15:51.519520Z</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr"/>
+      <c r="W51" s="2" t="inlineStr"/>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr"/>
+      <c r="Z51" s="2" t="inlineStr"/>
+      <c r="AA51" s="2" t="inlineStr"/>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr"/>
+      <c r="AE51" s="2" t="inlineStr"/>
+      <c r="AF51" s="2" t="inlineStr"/>
+      <c r="AG51" s="2" t="inlineStr"/>
+      <c r="AH51" s="2" t="inlineStr"/>
+      <c r="AI51" s="2" t="inlineStr"/>
+      <c r="AJ51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>4c442a4ff3fe4e4f</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>2d2157753549fa43</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>401816390</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>0.585425</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>0.696517</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>-0.11427469969969972</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:15:52.562607Z</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr"/>
+      <c r="W52" s="2" t="inlineStr"/>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr"/>
+      <c r="Z52" s="2" t="inlineStr"/>
+      <c r="AA52" s="2" t="inlineStr"/>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr"/>
+      <c r="AE52" s="2" t="inlineStr"/>
+      <c r="AF52" s="2" t="inlineStr"/>
+      <c r="AG52" s="2" t="inlineStr"/>
+      <c r="AH52" s="2" t="inlineStr"/>
+      <c r="AI52" s="2" t="inlineStr"/>
+      <c r="AJ52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>e31402483e47496b</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>46e5091ac002d857</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>401816389</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>0.585595</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>0.606965</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>-0.023780000000000023</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:15:53.080118Z</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr"/>
+      <c r="W53" s="2" t="inlineStr"/>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr"/>
+      <c r="Z53" s="2" t="inlineStr"/>
+      <c r="AA53" s="2" t="inlineStr"/>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr"/>
+      <c r="AE53" s="2" t="inlineStr"/>
+      <c r="AF53" s="2" t="inlineStr"/>
+      <c r="AG53" s="2" t="inlineStr"/>
+      <c r="AH53" s="2" t="inlineStr"/>
+      <c r="AI53" s="2" t="inlineStr"/>
+      <c r="AJ53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>eadd59cf8b6f46b8</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>6d8c7e3df64a59e5</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>401816386</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>0.589425</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>0.5454545454545454</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>0.542289</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>0.04397045454545456</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:15:53.458241Z</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr"/>
+      <c r="W54" s="2" t="inlineStr"/>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr"/>
+      <c r="Z54" s="2" t="inlineStr"/>
+      <c r="AA54" s="2" t="inlineStr"/>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr"/>
+      <c r="AE54" s="2" t="inlineStr"/>
+      <c r="AF54" s="2" t="inlineStr"/>
+      <c r="AG54" s="2" t="inlineStr"/>
+      <c r="AH54" s="2" t="inlineStr"/>
+      <c r="AI54" s="2" t="inlineStr"/>
+      <c r="AJ54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>01ec88a7a3e94b00</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>a848ce53b859a7af</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>401816387</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>0.589807</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>0.567164</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>0.01899154935622316</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:15:54.013055Z</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr"/>
+      <c r="W55" s="2" t="inlineStr"/>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr"/>
+      <c r="Z55" s="2" t="inlineStr"/>
+      <c r="AA55" s="2" t="inlineStr"/>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr"/>
+      <c r="AE55" s="2" t="inlineStr"/>
+      <c r="AF55" s="2" t="inlineStr"/>
+      <c r="AG55" s="2" t="inlineStr"/>
+      <c r="AH55" s="2" t="inlineStr"/>
+      <c r="AI55" s="2" t="inlineStr"/>
+      <c r="AJ55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>d0cbaf732e354647</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>38faa34e09dfd0e3</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>401816392</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>0.540164</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>0.425531914893617</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>0.422886</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>0.11463208510638295</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:15:55.219356Z</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr"/>
+      <c r="W56" s="2" t="inlineStr"/>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr"/>
+      <c r="Z56" s="2" t="inlineStr"/>
+      <c r="AA56" s="2" t="inlineStr"/>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="2" t="inlineStr"/>
+      <c r="AE56" s="2" t="inlineStr"/>
+      <c r="AF56" s="2" t="inlineStr"/>
+      <c r="AG56" s="2" t="inlineStr"/>
+      <c r="AH56" s="2" t="inlineStr"/>
+      <c r="AI56" s="2" t="inlineStr"/>
+      <c r="AJ56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>d74a52d1e5c64bed</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>2f5664ed9b7f4a0c</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>401816393</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>0.605446</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>0.5951417004048584</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>0.59204</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>0.010304299595141675</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:15:54.957859Z</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr"/>
+      <c r="W57" s="2" t="inlineStr"/>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr"/>
+      <c r="Z57" s="2" t="inlineStr"/>
+      <c r="AA57" s="2" t="inlineStr"/>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr"/>
+      <c r="AE57" s="2" t="inlineStr"/>
+      <c r="AF57" s="2" t="inlineStr"/>
+      <c r="AG57" s="2" t="inlineStr"/>
+      <c r="AH57" s="2" t="inlineStr"/>
+      <c r="AI57" s="2" t="inlineStr"/>
+      <c r="AJ57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2e886755b3314adb</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>035178b95253fb5f</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>401816391</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>0.509251</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>0.35460992907801414</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>0.353234</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>0.15464107092198587</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:15:55.825867Z</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr"/>
+      <c r="W58" s="2" t="inlineStr"/>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr"/>
+      <c r="Z58" s="2" t="inlineStr"/>
+      <c r="AA58" s="2" t="inlineStr"/>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr"/>
+      <c r="AE58" s="2" t="inlineStr"/>
+      <c r="AF58" s="2" t="inlineStr"/>
+      <c r="AG58" s="2" t="inlineStr"/>
+      <c r="AH58" s="2" t="inlineStr"/>
+      <c r="AI58" s="2" t="inlineStr"/>
+      <c r="AJ58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>d400a40e32b84978</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>2e6e6abc0bc66052</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>401816394</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>0.584674</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>0.6453900709219857</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>0.641791</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>-0.06071607092198572</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:15:56.533366Z</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr"/>
+      <c r="W59" s="2" t="inlineStr"/>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr"/>
+      <c r="Z59" s="2" t="inlineStr"/>
+      <c r="AA59" s="2" t="inlineStr"/>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr"/>
+      <c r="AE59" s="2" t="inlineStr"/>
+      <c r="AF59" s="2" t="inlineStr"/>
+      <c r="AG59" s="2" t="inlineStr"/>
+      <c r="AH59" s="2" t="inlineStr"/>
+      <c r="AI59" s="2" t="inlineStr"/>
+      <c r="AJ59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>19c433ed86a7418b</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>fb9456890e2413ab</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>401816395</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>0.542548</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>0.547264</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>-0.007001549549549457</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:15:56.938647Z</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr"/>
+      <c r="W60" s="2" t="inlineStr"/>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr"/>
+      <c r="Z60" s="2" t="inlineStr"/>
+      <c r="AA60" s="2" t="inlineStr"/>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr"/>
+      <c r="AE60" s="2" t="inlineStr"/>
+      <c r="AF60" s="2" t="inlineStr"/>
+      <c r="AG60" s="2" t="inlineStr"/>
+      <c r="AH60" s="2" t="inlineStr"/>
+      <c r="AI60" s="2" t="inlineStr"/>
+      <c r="AJ60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>14811eea9c554efd</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>8de15563949fe1fc</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>401816396</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>0.651882</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>0.577114</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>0.07205006722689078</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:15:57.314287Z</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr"/>
+      <c r="W61" s="2" t="inlineStr"/>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr"/>
+      <c r="Z61" s="2" t="inlineStr"/>
+      <c r="AA61" s="2" t="inlineStr"/>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr"/>
+      <c r="AE61" s="2" t="inlineStr"/>
+      <c r="AF61" s="2" t="inlineStr"/>
+      <c r="AG61" s="2" t="inlineStr"/>
+      <c r="AH61" s="2" t="inlineStr"/>
+      <c r="AI61" s="2" t="inlineStr"/>
+      <c r="AJ61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>74c3388b3d3e4f43</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>e98fc4952bf08d0c</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>401816397</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>0.561649</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>0.574468085106383</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>0.572139</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>-0.012819085106383077</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:15:58.414494Z</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr"/>
+      <c r="W62" s="2" t="inlineStr"/>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr"/>
+      <c r="Z62" s="2" t="inlineStr"/>
+      <c r="AA62" s="2" t="inlineStr"/>
+      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr"/>
+      <c r="AE62" s="2" t="inlineStr"/>
+      <c r="AF62" s="2" t="inlineStr"/>
+      <c r="AG62" s="2" t="inlineStr"/>
+      <c r="AH62" s="2" t="inlineStr"/>
+      <c r="AI62" s="2" t="inlineStr"/>
+      <c r="AJ62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>34cb9d1d3b414ec4</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>2f493ff6e1e8d90a</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>401816398</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>0.501668</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>0.5454545454545454</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>0.542289</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>-0.04378654545454541</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:15:57.859055Z</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr"/>
+      <c r="W63" s="2" t="inlineStr"/>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr"/>
+      <c r="Z63" s="2" t="inlineStr"/>
+      <c r="AA63" s="2" t="inlineStr"/>
+      <c r="AB63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr"/>
+      <c r="AE63" s="2" t="inlineStr"/>
+      <c r="AF63" s="2" t="inlineStr"/>
+      <c r="AG63" s="2" t="inlineStr"/>
+      <c r="AH63" s="2" t="inlineStr"/>
+      <c r="AI63" s="2" t="inlineStr"/>
+      <c r="AJ63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>ac516d5700ef4d94</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>3c0db2a442210ede</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>401816385</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>0.538033</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>0.5555555555555556</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>0.552239</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>-0.017522555555555597</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:19.498539Z</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr"/>
+      <c r="W64" s="2" t="inlineStr"/>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr"/>
+      <c r="Z64" s="2" t="inlineStr"/>
+      <c r="AA64" s="2" t="inlineStr"/>
+      <c r="AB64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr"/>
+      <c r="AE64" s="2" t="inlineStr"/>
+      <c r="AF64" s="2" t="inlineStr"/>
+      <c r="AG64" s="2" t="inlineStr"/>
+      <c r="AH64" s="2" t="inlineStr"/>
+      <c r="AI64" s="2" t="inlineStr"/>
+      <c r="AJ64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>b28687da002f49b7</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>f82bfe398cfb233d</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>401816388</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>0.56639</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>0.587065</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>-0.023773934426229548</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:18.856760Z</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr"/>
+      <c r="W65" s="2" t="inlineStr"/>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr"/>
+      <c r="Z65" s="2" t="inlineStr"/>
+      <c r="AA65" s="2" t="inlineStr"/>
+      <c r="AB65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr"/>
+      <c r="AE65" s="2" t="inlineStr"/>
+      <c r="AF65" s="2" t="inlineStr"/>
+      <c r="AG65" s="2" t="inlineStr"/>
+      <c r="AH65" s="2" t="inlineStr"/>
+      <c r="AI65" s="2" t="inlineStr"/>
+      <c r="AJ65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>85f6835169e74f8e</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>093993194689ed4e</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>401816390</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>0.585456</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>0.696517</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>-0.11424369969969972</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:19.941279Z</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr"/>
+      <c r="W66" s="2" t="inlineStr"/>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr"/>
+      <c r="Z66" s="2" t="inlineStr"/>
+      <c r="AA66" s="2" t="inlineStr"/>
+      <c r="AB66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr"/>
+      <c r="AE66" s="2" t="inlineStr"/>
+      <c r="AF66" s="2" t="inlineStr"/>
+      <c r="AG66" s="2" t="inlineStr"/>
+      <c r="AH66" s="2" t="inlineStr"/>
+      <c r="AI66" s="2" t="inlineStr"/>
+      <c r="AJ66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2c13314a91234ed0</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>288f404cbb2ac94a</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>401816389</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>0.585641</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>0.606965</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>-0.023734000000000033</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:20.462463Z</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr"/>
+      <c r="W67" s="2" t="inlineStr"/>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr"/>
+      <c r="Z67" s="2" t="inlineStr"/>
+      <c r="AA67" s="2" t="inlineStr"/>
+      <c r="AB67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr"/>
+      <c r="AE67" s="2" t="inlineStr"/>
+      <c r="AF67" s="2" t="inlineStr"/>
+      <c r="AG67" s="2" t="inlineStr"/>
+      <c r="AH67" s="2" t="inlineStr"/>
+      <c r="AI67" s="2" t="inlineStr"/>
+      <c r="AJ67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>568eeae3effa4f2d</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>067d8daffda52912</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>401816386</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>0.589466</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>0.547264</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>0.03991645045045056</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:20.885688Z</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr"/>
+      <c r="W68" s="2" t="inlineStr"/>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr"/>
+      <c r="Z68" s="2" t="inlineStr"/>
+      <c r="AA68" s="2" t="inlineStr"/>
+      <c r="AB68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr"/>
+      <c r="AE68" s="2" t="inlineStr"/>
+      <c r="AF68" s="2" t="inlineStr"/>
+      <c r="AG68" s="2" t="inlineStr"/>
+      <c r="AH68" s="2" t="inlineStr"/>
+      <c r="AI68" s="2" t="inlineStr"/>
+      <c r="AJ68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>71bc80f82a57405f</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>dbeb91f17a9268bb</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>401816387</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>0.589535</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>0.567164</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>0.01871954935622322</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:21.412725Z</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr"/>
+      <c r="W69" s="2" t="inlineStr"/>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr"/>
+      <c r="Z69" s="2" t="inlineStr"/>
+      <c r="AA69" s="2" t="inlineStr"/>
+      <c r="AB69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr"/>
+      <c r="AE69" s="2" t="inlineStr"/>
+      <c r="AF69" s="2" t="inlineStr"/>
+      <c r="AG69" s="2" t="inlineStr"/>
+      <c r="AH69" s="2" t="inlineStr"/>
+      <c r="AI69" s="2" t="inlineStr"/>
+      <c r="AJ69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>6667e8d50324493f</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>c38b45d4af23d8e9</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>401816392</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>0.540201</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>0.425531914893617</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>0.422886</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>0.11466908510638302</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:22.244590Z</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr"/>
+      <c r="W70" s="2" t="inlineStr"/>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr"/>
+      <c r="Z70" s="2" t="inlineStr"/>
+      <c r="AA70" s="2" t="inlineStr"/>
+      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr"/>
+      <c r="AE70" s="2" t="inlineStr"/>
+      <c r="AF70" s="2" t="inlineStr"/>
+      <c r="AG70" s="2" t="inlineStr"/>
+      <c r="AH70" s="2" t="inlineStr"/>
+      <c r="AI70" s="2" t="inlineStr"/>
+      <c r="AJ70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>70c47b18ad90439d</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>2f5664ed9b7f4a0c</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>401816393</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>0.605446</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>0.597015</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>0.005445999999999951</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:21.899733Z</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr"/>
+      <c r="W71" s="2" t="inlineStr"/>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr"/>
+      <c r="Z71" s="2" t="inlineStr"/>
+      <c r="AA71" s="2" t="inlineStr"/>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr"/>
+      <c r="AE71" s="2" t="inlineStr"/>
+      <c r="AF71" s="2" t="inlineStr"/>
+      <c r="AG71" s="2" t="inlineStr"/>
+      <c r="AH71" s="2" t="inlineStr"/>
+      <c r="AI71" s="2" t="inlineStr"/>
+      <c r="AJ71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>a468f3d3b6654324</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>f68ee4f138d232dd</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>401816391</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>0.509325</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>0.35460992907801414</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>0.353234</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>0.1547150709219859</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:22.695517Z</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr"/>
+      <c r="W72" s="2" t="inlineStr"/>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr"/>
+      <c r="Z72" s="2" t="inlineStr"/>
+      <c r="AA72" s="2" t="inlineStr"/>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr"/>
+      <c r="AE72" s="2" t="inlineStr"/>
+      <c r="AF72" s="2" t="inlineStr"/>
+      <c r="AG72" s="2" t="inlineStr"/>
+      <c r="AH72" s="2" t="inlineStr"/>
+      <c r="AI72" s="2" t="inlineStr"/>
+      <c r="AJ72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>ef84fb14e3d24716</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>2e6e6abc0bc66052</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>401816394</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>0.584674</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>0.6453900709219857</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>0.641791</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>-0.06071607092198572</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:23.300225Z</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr"/>
+      <c r="W73" s="2" t="inlineStr"/>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr"/>
+      <c r="Z73" s="2" t="inlineStr"/>
+      <c r="AA73" s="2" t="inlineStr"/>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr"/>
+      <c r="AE73" s="2" t="inlineStr"/>
+      <c r="AF73" s="2" t="inlineStr"/>
+      <c r="AG73" s="2" t="inlineStr"/>
+      <c r="AH73" s="2" t="inlineStr"/>
+      <c r="AI73" s="2" t="inlineStr"/>
+      <c r="AJ73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>c3912a3273ae4eeb</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>fb9456890e2413ab</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>401816395</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>0.542548</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>0.547264</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>-0.007001549549549457</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:23.770086Z</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr"/>
+      <c r="W74" s="2" t="inlineStr"/>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr"/>
+      <c r="Z74" s="2" t="inlineStr"/>
+      <c r="AA74" s="2" t="inlineStr"/>
+      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="inlineStr"/>
+      <c r="AE74" s="2" t="inlineStr"/>
+      <c r="AF74" s="2" t="inlineStr"/>
+      <c r="AG74" s="2" t="inlineStr"/>
+      <c r="AH74" s="2" t="inlineStr"/>
+      <c r="AI74" s="2" t="inlineStr"/>
+      <c r="AJ74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>9ab76c47a3eb4b1b</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>aa1550043d30dddf</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>401816396</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>0.651997</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>0.577114</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>0.07216506722689087</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:24.205568Z</t>
+        </is>
+      </c>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr"/>
+      <c r="W75" s="2" t="inlineStr"/>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr"/>
+      <c r="Z75" s="2" t="inlineStr"/>
+      <c r="AA75" s="2" t="inlineStr"/>
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr"/>
+      <c r="AE75" s="2" t="inlineStr"/>
+      <c r="AF75" s="2" t="inlineStr"/>
+      <c r="AG75" s="2" t="inlineStr"/>
+      <c r="AH75" s="2" t="inlineStr"/>
+      <c r="AI75" s="2" t="inlineStr"/>
+      <c r="AJ75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>b5f7c8efc3844851</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>2f493ff6e1e8d90a</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>401816398</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>0.501668</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>0.547264</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>-0.047881549549549485</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:24.768428Z</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr"/>
+      <c r="W76" s="2" t="inlineStr"/>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr"/>
+      <c r="Z76" s="2" t="inlineStr"/>
+      <c r="AA76" s="2" t="inlineStr"/>
+      <c r="AB76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr"/>
+      <c r="AE76" s="2" t="inlineStr"/>
+      <c r="AF76" s="2" t="inlineStr"/>
+      <c r="AG76" s="2" t="inlineStr"/>
+      <c r="AH76" s="2" t="inlineStr"/>
+      <c r="AI76" s="2" t="inlineStr"/>
+      <c r="AJ76" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ48"/>
+  <autoFilter ref="A1:AJ76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/flat/model_ledgers/mlb-moneyline-elo-trend-lr.xlsx
+++ b/data/flat/model_ledgers/mlb-moneyline-elo-trend-lr.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$115</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ76"/>
+  <dimension ref="A1:AJ115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -8766,8 +8766,4142 @@
       <c r="AI76" s="2" t="inlineStr"/>
       <c r="AJ76" s="2" t="inlineStr"/>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>36d2e98709b84f90</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>34955e0e36f59533</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>401816385</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>0.544091</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>0.5555555555555556</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>0.552239</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>-0.011464555555555589</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:58:40.965299Z</t>
+        </is>
+      </c>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr"/>
+      <c r="W77" s="2" t="inlineStr"/>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr"/>
+      <c r="Z77" s="2" t="inlineStr"/>
+      <c r="AA77" s="2" t="inlineStr"/>
+      <c r="AB77" s="2" t="inlineStr"/>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr"/>
+      <c r="AE77" s="2" t="inlineStr"/>
+      <c r="AF77" s="2" t="inlineStr"/>
+      <c r="AG77" s="2" t="inlineStr"/>
+      <c r="AH77" s="2" t="inlineStr"/>
+      <c r="AI77" s="2" t="inlineStr"/>
+      <c r="AJ77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>951e6166475d4649</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>b2e497c2488bcef9</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>401816388</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>0.583727</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>0.587065</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>-0.006436934426229501</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:58:40.454964Z</t>
+        </is>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr"/>
+      <c r="W78" s="2" t="inlineStr"/>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr"/>
+      <c r="Z78" s="2" t="inlineStr"/>
+      <c r="AA78" s="2" t="inlineStr"/>
+      <c r="AB78" s="2" t="inlineStr"/>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr"/>
+      <c r="AE78" s="2" t="inlineStr"/>
+      <c r="AF78" s="2" t="inlineStr"/>
+      <c r="AG78" s="2" t="inlineStr"/>
+      <c r="AH78" s="2" t="inlineStr"/>
+      <c r="AI78" s="2" t="inlineStr"/>
+      <c r="AJ78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>ba39c5d6cae8428d</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>2fcd9de1f1d03810</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>401816390</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>0.576593</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>0.696517</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>-0.12310669969969967</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:58:41.501894Z</t>
+        </is>
+      </c>
+      <c r="S79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr"/>
+      <c r="W79" s="2" t="inlineStr"/>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr"/>
+      <c r="Z79" s="2" t="inlineStr"/>
+      <c r="AA79" s="2" t="inlineStr"/>
+      <c r="AB79" s="2" t="inlineStr"/>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr"/>
+      <c r="AE79" s="2" t="inlineStr"/>
+      <c r="AF79" s="2" t="inlineStr"/>
+      <c r="AG79" s="2" t="inlineStr"/>
+      <c r="AH79" s="2" t="inlineStr"/>
+      <c r="AI79" s="2" t="inlineStr"/>
+      <c r="AJ79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>5dfa83d7ff634fb1</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>85e7671cf3d1699f</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>401816389</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>0.60719</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>0.606965</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>-0.0021849999999999925</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:58:41.988100Z</t>
+        </is>
+      </c>
+      <c r="S80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr"/>
+      <c r="W80" s="2" t="inlineStr"/>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr"/>
+      <c r="Z80" s="2" t="inlineStr"/>
+      <c r="AA80" s="2" t="inlineStr"/>
+      <c r="AB80" s="2" t="inlineStr"/>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr"/>
+      <c r="AE80" s="2" t="inlineStr"/>
+      <c r="AF80" s="2" t="inlineStr"/>
+      <c r="AG80" s="2" t="inlineStr"/>
+      <c r="AH80" s="2" t="inlineStr"/>
+      <c r="AI80" s="2" t="inlineStr"/>
+      <c r="AJ80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>f0baad31cb4c4ad4</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>909655e627d77f4a</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>401816386</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>0.575422</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>0.547264</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>0.0258724504504505</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:58:42.399303Z</t>
+        </is>
+      </c>
+      <c r="S81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr"/>
+      <c r="W81" s="2" t="inlineStr"/>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr"/>
+      <c r="Z81" s="2" t="inlineStr"/>
+      <c r="AA81" s="2" t="inlineStr"/>
+      <c r="AB81" s="2" t="inlineStr"/>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr"/>
+      <c r="AE81" s="2" t="inlineStr"/>
+      <c r="AF81" s="2" t="inlineStr"/>
+      <c r="AG81" s="2" t="inlineStr"/>
+      <c r="AH81" s="2" t="inlineStr"/>
+      <c r="AI81" s="2" t="inlineStr"/>
+      <c r="AJ81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>5997efb563c1496e</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>2a54030000f61ee9</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>401816387</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>0.592763</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>0.567164</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>0.021947549356223228</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:58:42.923436Z</t>
+        </is>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr"/>
+      <c r="W82" s="2" t="inlineStr"/>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr"/>
+      <c r="Z82" s="2" t="inlineStr"/>
+      <c r="AA82" s="2" t="inlineStr"/>
+      <c r="AB82" s="2" t="inlineStr"/>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr"/>
+      <c r="AE82" s="2" t="inlineStr"/>
+      <c r="AF82" s="2" t="inlineStr"/>
+      <c r="AG82" s="2" t="inlineStr"/>
+      <c r="AH82" s="2" t="inlineStr"/>
+      <c r="AI82" s="2" t="inlineStr"/>
+      <c r="AJ82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>9860ebd4cc514dc7</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>56b070c4691a81c1</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>401816392</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>0.548621</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>0.4291845493562232</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>0.427861</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>0.11943645064377684</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:58:43.879168Z</t>
+        </is>
+      </c>
+      <c r="S83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr"/>
+      <c r="W83" s="2" t="inlineStr"/>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr"/>
+      <c r="Z83" s="2" t="inlineStr"/>
+      <c r="AA83" s="2" t="inlineStr"/>
+      <c r="AB83" s="2" t="inlineStr"/>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr"/>
+      <c r="AE83" s="2" t="inlineStr"/>
+      <c r="AF83" s="2" t="inlineStr"/>
+      <c r="AG83" s="2" t="inlineStr"/>
+      <c r="AH83" s="2" t="inlineStr"/>
+      <c r="AI83" s="2" t="inlineStr"/>
+      <c r="AJ83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>257369ff6838440f</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>13e97fbe35b98e79</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>401816393</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>0.602762</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>0.597015</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>0.002761999999999931</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:58:43.461909Z</t>
+        </is>
+      </c>
+      <c r="S84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr"/>
+      <c r="W84" s="2" t="inlineStr"/>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr"/>
+      <c r="Z84" s="2" t="inlineStr"/>
+      <c r="AA84" s="2" t="inlineStr"/>
+      <c r="AB84" s="2" t="inlineStr"/>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr"/>
+      <c r="AE84" s="2" t="inlineStr"/>
+      <c r="AF84" s="2" t="inlineStr"/>
+      <c r="AG84" s="2" t="inlineStr"/>
+      <c r="AH84" s="2" t="inlineStr"/>
+      <c r="AI84" s="2" t="inlineStr"/>
+      <c r="AJ84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>88400c0f6aed4aa4</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>fc3023603b019a4d</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>401816391</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>0.521815</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>0.35460992907801414</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>0.353234</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>0.1672050709219859</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:58:44.331297Z</t>
+        </is>
+      </c>
+      <c r="S85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr"/>
+      <c r="W85" s="2" t="inlineStr"/>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr"/>
+      <c r="Z85" s="2" t="inlineStr"/>
+      <c r="AA85" s="2" t="inlineStr"/>
+      <c r="AB85" s="2" t="inlineStr"/>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr"/>
+      <c r="AE85" s="2" t="inlineStr"/>
+      <c r="AF85" s="2" t="inlineStr"/>
+      <c r="AG85" s="2" t="inlineStr"/>
+      <c r="AH85" s="2" t="inlineStr"/>
+      <c r="AI85" s="2" t="inlineStr"/>
+      <c r="AJ85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>22e4d65bbfa642a0</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>99e74cbbb81a6f38</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>401816394</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>0.598469</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>0.646766</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>-0.05188065034965028</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:58:45.046032Z</t>
+        </is>
+      </c>
+      <c r="S86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr"/>
+      <c r="W86" s="2" t="inlineStr"/>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr"/>
+      <c r="Z86" s="2" t="inlineStr"/>
+      <c r="AA86" s="2" t="inlineStr"/>
+      <c r="AB86" s="2" t="inlineStr"/>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr"/>
+      <c r="AE86" s="2" t="inlineStr"/>
+      <c r="AF86" s="2" t="inlineStr"/>
+      <c r="AG86" s="2" t="inlineStr"/>
+      <c r="AH86" s="2" t="inlineStr"/>
+      <c r="AI86" s="2" t="inlineStr"/>
+      <c r="AJ86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>cc904cbd5ef444c1</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>9031aa134a98c176</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>401816395</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>0.533882</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>0.547264</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>-0.01566754954954952</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:58:45.328977Z</t>
+        </is>
+      </c>
+      <c r="S87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr"/>
+      <c r="W87" s="2" t="inlineStr"/>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr"/>
+      <c r="Z87" s="2" t="inlineStr"/>
+      <c r="AA87" s="2" t="inlineStr"/>
+      <c r="AB87" s="2" t="inlineStr"/>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr"/>
+      <c r="AE87" s="2" t="inlineStr"/>
+      <c r="AF87" s="2" t="inlineStr"/>
+      <c r="AG87" s="2" t="inlineStr"/>
+      <c r="AH87" s="2" t="inlineStr"/>
+      <c r="AI87" s="2" t="inlineStr"/>
+      <c r="AJ87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02db69317b5542d4</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>4c080866fb111bff</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>401816396</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>0.619718</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>0.577114</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>0.03988606722689081</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:58:45.808478Z</t>
+        </is>
+      </c>
+      <c r="S88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr"/>
+      <c r="W88" s="2" t="inlineStr"/>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr"/>
+      <c r="Z88" s="2" t="inlineStr"/>
+      <c r="AA88" s="2" t="inlineStr"/>
+      <c r="AB88" s="2" t="inlineStr"/>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr"/>
+      <c r="AE88" s="2" t="inlineStr"/>
+      <c r="AF88" s="2" t="inlineStr"/>
+      <c r="AG88" s="2" t="inlineStr"/>
+      <c r="AH88" s="2" t="inlineStr"/>
+      <c r="AI88" s="2" t="inlineStr"/>
+      <c r="AJ88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>35f791690bec487a</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>3a529a8e501822ee</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>401816398</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>0.503922</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>0.547264</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>-0.045627549549549506</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:58:46.340446Z</t>
+        </is>
+      </c>
+      <c r="S89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr"/>
+      <c r="W89" s="2" t="inlineStr"/>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr"/>
+      <c r="Z89" s="2" t="inlineStr"/>
+      <c r="AA89" s="2" t="inlineStr"/>
+      <c r="AB89" s="2" t="inlineStr"/>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr"/>
+      <c r="AE89" s="2" t="inlineStr"/>
+      <c r="AF89" s="2" t="inlineStr"/>
+      <c r="AG89" s="2" t="inlineStr"/>
+      <c r="AH89" s="2" t="inlineStr"/>
+      <c r="AI89" s="2" t="inlineStr"/>
+      <c r="AJ89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>be046dc5a138433d</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>b94b2f1337120d9f</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>401816385</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>0.542811</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>0.5555555555555556</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>0.552239</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>-0.012744555555555537</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:04:23.602388Z</t>
+        </is>
+      </c>
+      <c r="S90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr"/>
+      <c r="W90" s="2" t="inlineStr"/>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr"/>
+      <c r="Z90" s="2" t="inlineStr"/>
+      <c r="AA90" s="2" t="inlineStr"/>
+      <c r="AB90" s="2" t="inlineStr"/>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr"/>
+      <c r="AE90" s="2" t="inlineStr"/>
+      <c r="AF90" s="2" t="inlineStr"/>
+      <c r="AG90" s="2" t="inlineStr"/>
+      <c r="AH90" s="2" t="inlineStr"/>
+      <c r="AI90" s="2" t="inlineStr"/>
+      <c r="AJ90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>46f4de3be9034426</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>0b49cd84a0231454</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>401816388</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>0.583155</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>0.5850622406639003</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>0.58209</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>-0.0019072406639003558</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:04:23.116066Z</t>
+        </is>
+      </c>
+      <c r="S91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr"/>
+      <c r="W91" s="2" t="inlineStr"/>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr"/>
+      <c r="Z91" s="2" t="inlineStr"/>
+      <c r="AA91" s="2" t="inlineStr"/>
+      <c r="AB91" s="2" t="inlineStr"/>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr"/>
+      <c r="AE91" s="2" t="inlineStr"/>
+      <c r="AF91" s="2" t="inlineStr"/>
+      <c r="AG91" s="2" t="inlineStr"/>
+      <c r="AH91" s="2" t="inlineStr"/>
+      <c r="AI91" s="2" t="inlineStr"/>
+      <c r="AJ91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>30f83de3069147da</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>9ee0310cde0f84fa</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>401816390</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>0.576615</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>0.7198879551820728</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>0.716418</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>-0.14327295518207284</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:04:24.213112Z</t>
+        </is>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr"/>
+      <c r="W92" s="2" t="inlineStr"/>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr"/>
+      <c r="Z92" s="2" t="inlineStr"/>
+      <c r="AA92" s="2" t="inlineStr"/>
+      <c r="AB92" s="2" t="inlineStr"/>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr"/>
+      <c r="AE92" s="2" t="inlineStr"/>
+      <c r="AF92" s="2" t="inlineStr"/>
+      <c r="AG92" s="2" t="inlineStr"/>
+      <c r="AH92" s="2" t="inlineStr"/>
+      <c r="AI92" s="2" t="inlineStr"/>
+      <c r="AJ92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>9f4a6ba5aae1411d</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>63ce416cd671aa81</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>401816389</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>0.606778</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>0.6453900709219857</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>0.641791</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>-0.03861207092198571</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:04:24.750087Z</t>
+        </is>
+      </c>
+      <c r="S93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr"/>
+      <c r="W93" s="2" t="inlineStr"/>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr"/>
+      <c r="Z93" s="2" t="inlineStr"/>
+      <c r="AA93" s="2" t="inlineStr"/>
+      <c r="AB93" s="2" t="inlineStr"/>
+      <c r="AC93" s="2" t="inlineStr"/>
+      <c r="AD93" s="2" t="inlineStr"/>
+      <c r="AE93" s="2" t="inlineStr"/>
+      <c r="AF93" s="2" t="inlineStr"/>
+      <c r="AG93" s="2" t="inlineStr"/>
+      <c r="AH93" s="2" t="inlineStr"/>
+      <c r="AI93" s="2" t="inlineStr"/>
+      <c r="AJ93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>27c9ddb8ec3e43d0</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>8e5d770c4943ab65</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>401816386</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>0.574715</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>0.5555555555555556</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>0.552239</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>0.019159444444444396</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:04:25.169651Z</t>
+        </is>
+      </c>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr"/>
+      <c r="W94" s="2" t="inlineStr"/>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr"/>
+      <c r="Z94" s="2" t="inlineStr"/>
+      <c r="AA94" s="2" t="inlineStr"/>
+      <c r="AB94" s="2" t="inlineStr"/>
+      <c r="AC94" s="2" t="inlineStr"/>
+      <c r="AD94" s="2" t="inlineStr"/>
+      <c r="AE94" s="2" t="inlineStr"/>
+      <c r="AF94" s="2" t="inlineStr"/>
+      <c r="AG94" s="2" t="inlineStr"/>
+      <c r="AH94" s="2" t="inlineStr"/>
+      <c r="AI94" s="2" t="inlineStr"/>
+      <c r="AJ94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>f7666a0a22984b8c</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>3a98c46b1feb5dff</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>401816387</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>0.592828</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>0.574468085106383</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>0.572139</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>0.01835991489361699</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:04:25.692850Z</t>
+        </is>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr"/>
+      <c r="W95" s="2" t="inlineStr"/>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr"/>
+      <c r="Z95" s="2" t="inlineStr"/>
+      <c r="AA95" s="2" t="inlineStr"/>
+      <c r="AB95" s="2" t="inlineStr"/>
+      <c r="AC95" s="2" t="inlineStr"/>
+      <c r="AD95" s="2" t="inlineStr"/>
+      <c r="AE95" s="2" t="inlineStr"/>
+      <c r="AF95" s="2" t="inlineStr"/>
+      <c r="AG95" s="2" t="inlineStr"/>
+      <c r="AH95" s="2" t="inlineStr"/>
+      <c r="AI95" s="2" t="inlineStr"/>
+      <c r="AJ95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>67b5e15307c743bd</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>8502bc8bb5e15229</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>401816392</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>0.548577</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>0.425531914893617</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>0.422886</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>0.12304508510638296</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:04:26.480856Z</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr"/>
+      <c r="W96" s="2" t="inlineStr"/>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr"/>
+      <c r="Z96" s="2" t="inlineStr"/>
+      <c r="AA96" s="2" t="inlineStr"/>
+      <c r="AB96" s="2" t="inlineStr"/>
+      <c r="AC96" s="2" t="inlineStr"/>
+      <c r="AD96" s="2" t="inlineStr"/>
+      <c r="AE96" s="2" t="inlineStr"/>
+      <c r="AF96" s="2" t="inlineStr"/>
+      <c r="AG96" s="2" t="inlineStr"/>
+      <c r="AH96" s="2" t="inlineStr"/>
+      <c r="AI96" s="2" t="inlineStr"/>
+      <c r="AJ96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>ef631ab85d9443e2</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>13e97fbe35b98e79</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>401816393</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>0.602762</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>0.597015</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>0.002761999999999931</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:04:26.210194Z</t>
+        </is>
+      </c>
+      <c r="S97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr"/>
+      <c r="W97" s="2" t="inlineStr"/>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr"/>
+      <c r="Z97" s="2" t="inlineStr"/>
+      <c r="AA97" s="2" t="inlineStr"/>
+      <c r="AB97" s="2" t="inlineStr"/>
+      <c r="AC97" s="2" t="inlineStr"/>
+      <c r="AD97" s="2" t="inlineStr"/>
+      <c r="AE97" s="2" t="inlineStr"/>
+      <c r="AF97" s="2" t="inlineStr"/>
+      <c r="AG97" s="2" t="inlineStr"/>
+      <c r="AH97" s="2" t="inlineStr"/>
+      <c r="AI97" s="2" t="inlineStr"/>
+      <c r="AJ97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>a9c013f024f341f7</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>60a3d5d3de62be38</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>401816391</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>0.521495</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>0.34965034965034963</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>0.348259</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>0.1718446503496504</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:04:26.943601Z</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr"/>
+      <c r="W98" s="2" t="inlineStr"/>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr"/>
+      <c r="Z98" s="2" t="inlineStr"/>
+      <c r="AA98" s="2" t="inlineStr"/>
+      <c r="AB98" s="2" t="inlineStr"/>
+      <c r="AC98" s="2" t="inlineStr"/>
+      <c r="AD98" s="2" t="inlineStr"/>
+      <c r="AE98" s="2" t="inlineStr"/>
+      <c r="AF98" s="2" t="inlineStr"/>
+      <c r="AG98" s="2" t="inlineStr"/>
+      <c r="AH98" s="2" t="inlineStr"/>
+      <c r="AI98" s="2" t="inlineStr"/>
+      <c r="AJ98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>b6e57d2be9e24135</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>99e74cbbb81a6f38</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>401816394</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>0.598469</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>0.6453900709219857</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>0.641791</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>-0.04692107092198572</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:04:27.537417Z</t>
+        </is>
+      </c>
+      <c r="S99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr"/>
+      <c r="W99" s="2" t="inlineStr"/>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr"/>
+      <c r="Z99" s="2" t="inlineStr"/>
+      <c r="AA99" s="2" t="inlineStr"/>
+      <c r="AB99" s="2" t="inlineStr"/>
+      <c r="AC99" s="2" t="inlineStr"/>
+      <c r="AD99" s="2" t="inlineStr"/>
+      <c r="AE99" s="2" t="inlineStr"/>
+      <c r="AF99" s="2" t="inlineStr"/>
+      <c r="AG99" s="2" t="inlineStr"/>
+      <c r="AH99" s="2" t="inlineStr"/>
+      <c r="AI99" s="2" t="inlineStr"/>
+      <c r="AJ99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>1e0a43d51e634c2e</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>9031aa134a98c176</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>401816395</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>0.533882</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>0.547264</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>-0.01566754954954952</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:04:28.059474Z</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr"/>
+      <c r="W100" s="2" t="inlineStr"/>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr"/>
+      <c r="Z100" s="2" t="inlineStr"/>
+      <c r="AA100" s="2" t="inlineStr"/>
+      <c r="AB100" s="2" t="inlineStr"/>
+      <c r="AC100" s="2" t="inlineStr"/>
+      <c r="AD100" s="2" t="inlineStr"/>
+      <c r="AE100" s="2" t="inlineStr"/>
+      <c r="AF100" s="2" t="inlineStr"/>
+      <c r="AG100" s="2" t="inlineStr"/>
+      <c r="AH100" s="2" t="inlineStr"/>
+      <c r="AI100" s="2" t="inlineStr"/>
+      <c r="AJ100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>608c2e5e9e3c48c2</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>16464949e4fc5515</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>401816396</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>0.61964</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>0.6047430830039526</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>0.60199</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>0.014896916996047338</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:04:28.471419Z</t>
+        </is>
+      </c>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr"/>
+      <c r="W101" s="2" t="inlineStr"/>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr"/>
+      <c r="Z101" s="2" t="inlineStr"/>
+      <c r="AA101" s="2" t="inlineStr"/>
+      <c r="AB101" s="2" t="inlineStr"/>
+      <c r="AC101" s="2" t="inlineStr"/>
+      <c r="AD101" s="2" t="inlineStr"/>
+      <c r="AE101" s="2" t="inlineStr"/>
+      <c r="AF101" s="2" t="inlineStr"/>
+      <c r="AG101" s="2" t="inlineStr"/>
+      <c r="AH101" s="2" t="inlineStr"/>
+      <c r="AI101" s="2" t="inlineStr"/>
+      <c r="AJ101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>4a91e3140dd04cff</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>3a529a8e501822ee</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>401816398</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>0.503922</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>0.5454545454545454</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>0.542289</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>-0.04153254545454543</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:04:28.986672Z</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr"/>
+      <c r="W102" s="2" t="inlineStr"/>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr"/>
+      <c r="Z102" s="2" t="inlineStr"/>
+      <c r="AA102" s="2" t="inlineStr"/>
+      <c r="AB102" s="2" t="inlineStr"/>
+      <c r="AC102" s="2" t="inlineStr"/>
+      <c r="AD102" s="2" t="inlineStr"/>
+      <c r="AE102" s="2" t="inlineStr"/>
+      <c r="AF102" s="2" t="inlineStr"/>
+      <c r="AG102" s="2" t="inlineStr"/>
+      <c r="AH102" s="2" t="inlineStr"/>
+      <c r="AI102" s="2" t="inlineStr"/>
+      <c r="AJ102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>ffde9e55359e4f16</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>b94b2f1337120d9f</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>401816385</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>0.542811</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>0.5555555555555556</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>0.552239</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>-0.012744555555555537</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:23:06.428271Z</t>
+        </is>
+      </c>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr"/>
+      <c r="W103" s="2" t="inlineStr"/>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr"/>
+      <c r="Z103" s="2" t="inlineStr"/>
+      <c r="AA103" s="2" t="inlineStr"/>
+      <c r="AB103" s="2" t="inlineStr"/>
+      <c r="AC103" s="2" t="inlineStr"/>
+      <c r="AD103" s="2" t="inlineStr"/>
+      <c r="AE103" s="2" t="inlineStr"/>
+      <c r="AF103" s="2" t="inlineStr"/>
+      <c r="AG103" s="2" t="inlineStr"/>
+      <c r="AH103" s="2" t="inlineStr"/>
+      <c r="AI103" s="2" t="inlineStr"/>
+      <c r="AJ103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>51b2b87d9d8e4400</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>0b49cd84a0231454</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>401816388</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>0.583155</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>0.5850622406639003</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>0.58209</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>-0.0019072406639003558</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:23:05.946346Z</t>
+        </is>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr"/>
+      <c r="V104" s="2" t="inlineStr"/>
+      <c r="W104" s="2" t="inlineStr"/>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr"/>
+      <c r="Z104" s="2" t="inlineStr"/>
+      <c r="AA104" s="2" t="inlineStr"/>
+      <c r="AB104" s="2" t="inlineStr"/>
+      <c r="AC104" s="2" t="inlineStr"/>
+      <c r="AD104" s="2" t="inlineStr"/>
+      <c r="AE104" s="2" t="inlineStr"/>
+      <c r="AF104" s="2" t="inlineStr"/>
+      <c r="AG104" s="2" t="inlineStr"/>
+      <c r="AH104" s="2" t="inlineStr"/>
+      <c r="AI104" s="2" t="inlineStr"/>
+      <c r="AJ104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>33cef8821d4e4d75</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>9ee0310cde0f84fa</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>401816390</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>0.576615</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr"/>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>0.7198879551820728</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>0.716418</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>-0.14327295518207284</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:23:07.075526Z</t>
+        </is>
+      </c>
+      <c r="S105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr"/>
+      <c r="V105" s="2" t="inlineStr"/>
+      <c r="W105" s="2" t="inlineStr"/>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr"/>
+      <c r="Z105" s="2" t="inlineStr"/>
+      <c r="AA105" s="2" t="inlineStr"/>
+      <c r="AB105" s="2" t="inlineStr"/>
+      <c r="AC105" s="2" t="inlineStr"/>
+      <c r="AD105" s="2" t="inlineStr"/>
+      <c r="AE105" s="2" t="inlineStr"/>
+      <c r="AF105" s="2" t="inlineStr"/>
+      <c r="AG105" s="2" t="inlineStr"/>
+      <c r="AH105" s="2" t="inlineStr"/>
+      <c r="AI105" s="2" t="inlineStr"/>
+      <c r="AJ105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>c711cc4e98ae492e</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>63ce416cd671aa81</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>401816389</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>0.606778</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr"/>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>0.6453900709219857</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>0.641791</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>-0.03861207092198571</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:23:07.959215Z</t>
+        </is>
+      </c>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr"/>
+      <c r="V106" s="2" t="inlineStr"/>
+      <c r="W106" s="2" t="inlineStr"/>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr"/>
+      <c r="Z106" s="2" t="inlineStr"/>
+      <c r="AA106" s="2" t="inlineStr"/>
+      <c r="AB106" s="2" t="inlineStr"/>
+      <c r="AC106" s="2" t="inlineStr"/>
+      <c r="AD106" s="2" t="inlineStr"/>
+      <c r="AE106" s="2" t="inlineStr"/>
+      <c r="AF106" s="2" t="inlineStr"/>
+      <c r="AG106" s="2" t="inlineStr"/>
+      <c r="AH106" s="2" t="inlineStr"/>
+      <c r="AI106" s="2" t="inlineStr"/>
+      <c r="AJ106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>b1d7a24520294440</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>8e5d770c4943ab65</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>401816386</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>0.574715</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr"/>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>0.5555555555555556</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>0.552239</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>0.019159444444444396</t>
+        </is>
+      </c>
+      <c r="R107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:23:08.559833Z</t>
+        </is>
+      </c>
+      <c r="S107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr"/>
+      <c r="V107" s="2" t="inlineStr"/>
+      <c r="W107" s="2" t="inlineStr"/>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr"/>
+      <c r="Z107" s="2" t="inlineStr"/>
+      <c r="AA107" s="2" t="inlineStr"/>
+      <c r="AB107" s="2" t="inlineStr"/>
+      <c r="AC107" s="2" t="inlineStr"/>
+      <c r="AD107" s="2" t="inlineStr"/>
+      <c r="AE107" s="2" t="inlineStr"/>
+      <c r="AF107" s="2" t="inlineStr"/>
+      <c r="AG107" s="2" t="inlineStr"/>
+      <c r="AH107" s="2" t="inlineStr"/>
+      <c r="AI107" s="2" t="inlineStr"/>
+      <c r="AJ107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>711e9b660faf4d03</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>3a98c46b1feb5dff</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>401816387</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>0.592828</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>0.577114</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>0.01299606722689084</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:23:09.398190Z</t>
+        </is>
+      </c>
+      <c r="S108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr"/>
+      <c r="V108" s="2" t="inlineStr"/>
+      <c r="W108" s="2" t="inlineStr"/>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr"/>
+      <c r="Z108" s="2" t="inlineStr"/>
+      <c r="AA108" s="2" t="inlineStr"/>
+      <c r="AB108" s="2" t="inlineStr"/>
+      <c r="AC108" s="2" t="inlineStr"/>
+      <c r="AD108" s="2" t="inlineStr"/>
+      <c r="AE108" s="2" t="inlineStr"/>
+      <c r="AF108" s="2" t="inlineStr"/>
+      <c r="AG108" s="2" t="inlineStr"/>
+      <c r="AH108" s="2" t="inlineStr"/>
+      <c r="AI108" s="2" t="inlineStr"/>
+      <c r="AJ108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>9c21d1d118704e98</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>8502bc8bb5e15229</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>401816392</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>0.548577</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr"/>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>0.425531914893617</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>0.422886</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>0.12304508510638296</t>
+        </is>
+      </c>
+      <c r="R109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:23:10.651606Z</t>
+        </is>
+      </c>
+      <c r="S109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr"/>
+      <c r="V109" s="2" t="inlineStr"/>
+      <c r="W109" s="2" t="inlineStr"/>
+      <c r="X109" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr"/>
+      <c r="Z109" s="2" t="inlineStr"/>
+      <c r="AA109" s="2" t="inlineStr"/>
+      <c r="AB109" s="2" t="inlineStr"/>
+      <c r="AC109" s="2" t="inlineStr"/>
+      <c r="AD109" s="2" t="inlineStr"/>
+      <c r="AE109" s="2" t="inlineStr"/>
+      <c r="AF109" s="2" t="inlineStr"/>
+      <c r="AG109" s="2" t="inlineStr"/>
+      <c r="AH109" s="2" t="inlineStr"/>
+      <c r="AI109" s="2" t="inlineStr"/>
+      <c r="AJ109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>3e4da1e3444b4fda</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>13e97fbe35b98e79</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>401816393</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>0.602762</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr"/>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>0.597015</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>0.002761999999999931</t>
+        </is>
+      </c>
+      <c r="R110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:23:10.125761Z</t>
+        </is>
+      </c>
+      <c r="S110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="inlineStr"/>
+      <c r="V110" s="2" t="inlineStr"/>
+      <c r="W110" s="2" t="inlineStr"/>
+      <c r="X110" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y110" s="2" t="inlineStr"/>
+      <c r="Z110" s="2" t="inlineStr"/>
+      <c r="AA110" s="2" t="inlineStr"/>
+      <c r="AB110" s="2" t="inlineStr"/>
+      <c r="AC110" s="2" t="inlineStr"/>
+      <c r="AD110" s="2" t="inlineStr"/>
+      <c r="AE110" s="2" t="inlineStr"/>
+      <c r="AF110" s="2" t="inlineStr"/>
+      <c r="AG110" s="2" t="inlineStr"/>
+      <c r="AH110" s="2" t="inlineStr"/>
+      <c r="AI110" s="2" t="inlineStr"/>
+      <c r="AJ110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>0d59fe526d34459b</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>60a3d5d3de62be38</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>401816391</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>0.521495</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr"/>
+      <c r="N111" s="2" t="inlineStr"/>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>0.3448275862068966</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>0.343284</t>
+        </is>
+      </c>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>0.17666741379310347</t>
+        </is>
+      </c>
+      <c r="R111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:23:11.051384Z</t>
+        </is>
+      </c>
+      <c r="S111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T111" s="2" t="inlineStr"/>
+      <c r="U111" s="2" t="inlineStr"/>
+      <c r="V111" s="2" t="inlineStr"/>
+      <c r="W111" s="2" t="inlineStr"/>
+      <c r="X111" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y111" s="2" t="inlineStr"/>
+      <c r="Z111" s="2" t="inlineStr"/>
+      <c r="AA111" s="2" t="inlineStr"/>
+      <c r="AB111" s="2" t="inlineStr"/>
+      <c r="AC111" s="2" t="inlineStr"/>
+      <c r="AD111" s="2" t="inlineStr"/>
+      <c r="AE111" s="2" t="inlineStr"/>
+      <c r="AF111" s="2" t="inlineStr"/>
+      <c r="AG111" s="2" t="inlineStr"/>
+      <c r="AH111" s="2" t="inlineStr"/>
+      <c r="AI111" s="2" t="inlineStr"/>
+      <c r="AJ111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>74840c4dfa364a1a</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>99e74cbbb81a6f38</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>401816394</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>0.598469</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr"/>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>0.6453900709219857</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>0.641791</t>
+        </is>
+      </c>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>-0.04692107092198572</t>
+        </is>
+      </c>
+      <c r="R112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:23:34.287233Z</t>
+        </is>
+      </c>
+      <c r="S112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T112" s="2" t="inlineStr"/>
+      <c r="U112" s="2" t="inlineStr"/>
+      <c r="V112" s="2" t="inlineStr"/>
+      <c r="W112" s="2" t="inlineStr"/>
+      <c r="X112" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y112" s="2" t="inlineStr"/>
+      <c r="Z112" s="2" t="inlineStr"/>
+      <c r="AA112" s="2" t="inlineStr"/>
+      <c r="AB112" s="2" t="inlineStr"/>
+      <c r="AC112" s="2" t="inlineStr"/>
+      <c r="AD112" s="2" t="inlineStr"/>
+      <c r="AE112" s="2" t="inlineStr"/>
+      <c r="AF112" s="2" t="inlineStr"/>
+      <c r="AG112" s="2" t="inlineStr"/>
+      <c r="AH112" s="2" t="inlineStr"/>
+      <c r="AI112" s="2" t="inlineStr"/>
+      <c r="AJ112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>67b03fdcaaef4727</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>9031aa134a98c176</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>401816395</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>0.533882</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr"/>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>0.547264</t>
+        </is>
+      </c>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>-0.01566754954954952</t>
+        </is>
+      </c>
+      <c r="R113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:23:12.528117Z</t>
+        </is>
+      </c>
+      <c r="S113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T113" s="2" t="inlineStr"/>
+      <c r="U113" s="2" t="inlineStr"/>
+      <c r="V113" s="2" t="inlineStr"/>
+      <c r="W113" s="2" t="inlineStr"/>
+      <c r="X113" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y113" s="2" t="inlineStr"/>
+      <c r="Z113" s="2" t="inlineStr"/>
+      <c r="AA113" s="2" t="inlineStr"/>
+      <c r="AB113" s="2" t="inlineStr"/>
+      <c r="AC113" s="2" t="inlineStr"/>
+      <c r="AD113" s="2" t="inlineStr"/>
+      <c r="AE113" s="2" t="inlineStr"/>
+      <c r="AF113" s="2" t="inlineStr"/>
+      <c r="AG113" s="2" t="inlineStr"/>
+      <c r="AH113" s="2" t="inlineStr"/>
+      <c r="AI113" s="2" t="inlineStr"/>
+      <c r="AJ113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>7c673b83887246a8</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>16464949e4fc5515</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>401816396</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>0.61964</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr"/>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>0.6047430830039526</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>0.60199</t>
+        </is>
+      </c>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>0.014896916996047338</t>
+        </is>
+      </c>
+      <c r="R114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:23:13.184791Z</t>
+        </is>
+      </c>
+      <c r="S114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T114" s="2" t="inlineStr"/>
+      <c r="U114" s="2" t="inlineStr"/>
+      <c r="V114" s="2" t="inlineStr"/>
+      <c r="W114" s="2" t="inlineStr"/>
+      <c r="X114" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y114" s="2" t="inlineStr"/>
+      <c r="Z114" s="2" t="inlineStr"/>
+      <c r="AA114" s="2" t="inlineStr"/>
+      <c r="AB114" s="2" t="inlineStr"/>
+      <c r="AC114" s="2" t="inlineStr"/>
+      <c r="AD114" s="2" t="inlineStr"/>
+      <c r="AE114" s="2" t="inlineStr"/>
+      <c r="AF114" s="2" t="inlineStr"/>
+      <c r="AG114" s="2" t="inlineStr"/>
+      <c r="AH114" s="2" t="inlineStr"/>
+      <c r="AI114" s="2" t="inlineStr"/>
+      <c r="AJ114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>bafd79589a824270</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>3a529a8e501822ee</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>401816398</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>0.503922</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr"/>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="inlineStr">
+        <is>
+          <t>0.537313</t>
+        </is>
+      </c>
+      <c r="Q115" s="2" t="inlineStr">
+        <is>
+          <t>-0.03524850691244241</t>
+        </is>
+      </c>
+      <c r="R115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:23:14.034829Z</t>
+        </is>
+      </c>
+      <c r="S115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T115" s="2" t="inlineStr"/>
+      <c r="U115" s="2" t="inlineStr"/>
+      <c r="V115" s="2" t="inlineStr"/>
+      <c r="W115" s="2" t="inlineStr"/>
+      <c r="X115" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y115" s="2" t="inlineStr"/>
+      <c r="Z115" s="2" t="inlineStr"/>
+      <c r="AA115" s="2" t="inlineStr"/>
+      <c r="AB115" s="2" t="inlineStr"/>
+      <c r="AC115" s="2" t="inlineStr"/>
+      <c r="AD115" s="2" t="inlineStr"/>
+      <c r="AE115" s="2" t="inlineStr"/>
+      <c r="AF115" s="2" t="inlineStr"/>
+      <c r="AG115" s="2" t="inlineStr"/>
+      <c r="AH115" s="2" t="inlineStr"/>
+      <c r="AI115" s="2" t="inlineStr"/>
+      <c r="AJ115" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ76"/>
+  <autoFilter ref="A1:AJ115"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/flat/model_ledgers/mlb-moneyline-elo-trend-lr.xlsx
+++ b/data/flat/model_ledgers/mlb-moneyline-elo-trend-lr.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$187</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ115"/>
+  <dimension ref="A1:AJ187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -12900,8 +12900,7676 @@
       <c r="AI115" s="2" t="inlineStr"/>
       <c r="AJ115" s="2" t="inlineStr"/>
     </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>dcce4df565c64e90</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>c2ecfa697e21708b</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>401816385</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>0.542818</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr"/>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>0.5555555555555556</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>0.552239</t>
+        </is>
+      </c>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>-0.012737555555555558</t>
+        </is>
+      </c>
+      <c r="R116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:43.180928Z</t>
+        </is>
+      </c>
+      <c r="S116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T116" s="2" t="inlineStr"/>
+      <c r="U116" s="2" t="inlineStr"/>
+      <c r="V116" s="2" t="inlineStr"/>
+      <c r="W116" s="2" t="inlineStr"/>
+      <c r="X116" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y116" s="2" t="inlineStr"/>
+      <c r="Z116" s="2" t="inlineStr"/>
+      <c r="AA116" s="2" t="inlineStr"/>
+      <c r="AB116" s="2" t="inlineStr"/>
+      <c r="AC116" s="2" t="inlineStr"/>
+      <c r="AD116" s="2" t="inlineStr"/>
+      <c r="AE116" s="2" t="inlineStr"/>
+      <c r="AF116" s="2" t="inlineStr"/>
+      <c r="AG116" s="2" t="inlineStr"/>
+      <c r="AH116" s="2" t="inlineStr"/>
+      <c r="AI116" s="2" t="inlineStr"/>
+      <c r="AJ116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>fb450ee460f446b8</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>ada77d6a6dbb9e1e</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>401816388</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>0.583183</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr"/>
+      <c r="N117" s="2" t="inlineStr"/>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>0.5850622406639003</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>0.58209</t>
+        </is>
+      </c>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
+          <t>-0.0018792406639003278</t>
+        </is>
+      </c>
+      <c r="R117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:42.633470Z</t>
+        </is>
+      </c>
+      <c r="S117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T117" s="2" t="inlineStr"/>
+      <c r="U117" s="2" t="inlineStr"/>
+      <c r="V117" s="2" t="inlineStr"/>
+      <c r="W117" s="2" t="inlineStr"/>
+      <c r="X117" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y117" s="2" t="inlineStr"/>
+      <c r="Z117" s="2" t="inlineStr"/>
+      <c r="AA117" s="2" t="inlineStr"/>
+      <c r="AB117" s="2" t="inlineStr"/>
+      <c r="AC117" s="2" t="inlineStr"/>
+      <c r="AD117" s="2" t="inlineStr"/>
+      <c r="AE117" s="2" t="inlineStr"/>
+      <c r="AF117" s="2" t="inlineStr"/>
+      <c r="AG117" s="2" t="inlineStr"/>
+      <c r="AH117" s="2" t="inlineStr"/>
+      <c r="AI117" s="2" t="inlineStr"/>
+      <c r="AJ117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>f05b696170794f83</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>bba6f5ecd242bdce</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>401816390</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>0.576688</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr"/>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>0.7198879551820728</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="inlineStr">
+        <is>
+          <t>0.716418</t>
+        </is>
+      </c>
+      <c r="Q118" s="2" t="inlineStr">
+        <is>
+          <t>-0.14319995518207285</t>
+        </is>
+      </c>
+      <c r="R118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:43.842263Z</t>
+        </is>
+      </c>
+      <c r="S118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T118" s="2" t="inlineStr"/>
+      <c r="U118" s="2" t="inlineStr"/>
+      <c r="V118" s="2" t="inlineStr"/>
+      <c r="W118" s="2" t="inlineStr"/>
+      <c r="X118" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y118" s="2" t="inlineStr"/>
+      <c r="Z118" s="2" t="inlineStr"/>
+      <c r="AA118" s="2" t="inlineStr"/>
+      <c r="AB118" s="2" t="inlineStr"/>
+      <c r="AC118" s="2" t="inlineStr"/>
+      <c r="AD118" s="2" t="inlineStr"/>
+      <c r="AE118" s="2" t="inlineStr"/>
+      <c r="AF118" s="2" t="inlineStr"/>
+      <c r="AG118" s="2" t="inlineStr"/>
+      <c r="AH118" s="2" t="inlineStr"/>
+      <c r="AI118" s="2" t="inlineStr"/>
+      <c r="AJ118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>5a43c12ddf634968</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>e352456760d683cf</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>401816389</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>0.606685</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr"/>
+      <c r="N119" s="2" t="inlineStr"/>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>0.6453900709219857</t>
+        </is>
+      </c>
+      <c r="P119" s="2" t="inlineStr">
+        <is>
+          <t>0.641791</t>
+        </is>
+      </c>
+      <c r="Q119" s="2" t="inlineStr">
+        <is>
+          <t>-0.03870507092198572</t>
+        </is>
+      </c>
+      <c r="R119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:44.452379Z</t>
+        </is>
+      </c>
+      <c r="S119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T119" s="2" t="inlineStr"/>
+      <c r="U119" s="2" t="inlineStr"/>
+      <c r="V119" s="2" t="inlineStr"/>
+      <c r="W119" s="2" t="inlineStr"/>
+      <c r="X119" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y119" s="2" t="inlineStr"/>
+      <c r="Z119" s="2" t="inlineStr"/>
+      <c r="AA119" s="2" t="inlineStr"/>
+      <c r="AB119" s="2" t="inlineStr"/>
+      <c r="AC119" s="2" t="inlineStr"/>
+      <c r="AD119" s="2" t="inlineStr"/>
+      <c r="AE119" s="2" t="inlineStr"/>
+      <c r="AF119" s="2" t="inlineStr"/>
+      <c r="AG119" s="2" t="inlineStr"/>
+      <c r="AH119" s="2" t="inlineStr"/>
+      <c r="AI119" s="2" t="inlineStr"/>
+      <c r="AJ119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>db9583cc1f2e4615</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>f4babf58e61e7a1d</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>401816386</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>0.574737</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr"/>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>0.5555555555555556</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="inlineStr">
+        <is>
+          <t>0.552239</t>
+        </is>
+      </c>
+      <c r="Q120" s="2" t="inlineStr">
+        <is>
+          <t>0.019181444444444473</t>
+        </is>
+      </c>
+      <c r="R120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:44.913944Z</t>
+        </is>
+      </c>
+      <c r="S120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T120" s="2" t="inlineStr"/>
+      <c r="U120" s="2" t="inlineStr"/>
+      <c r="V120" s="2" t="inlineStr"/>
+      <c r="W120" s="2" t="inlineStr"/>
+      <c r="X120" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y120" s="2" t="inlineStr"/>
+      <c r="Z120" s="2" t="inlineStr"/>
+      <c r="AA120" s="2" t="inlineStr"/>
+      <c r="AB120" s="2" t="inlineStr"/>
+      <c r="AC120" s="2" t="inlineStr"/>
+      <c r="AD120" s="2" t="inlineStr"/>
+      <c r="AE120" s="2" t="inlineStr"/>
+      <c r="AF120" s="2" t="inlineStr"/>
+      <c r="AG120" s="2" t="inlineStr"/>
+      <c r="AH120" s="2" t="inlineStr"/>
+      <c r="AI120" s="2" t="inlineStr"/>
+      <c r="AJ120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>eabbe639ffb54fb7</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>9b94d2e4730897d8</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>401816387</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>0.592871</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr"/>
+      <c r="N121" s="2" t="inlineStr"/>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="inlineStr">
+        <is>
+          <t>0.577114</t>
+        </is>
+      </c>
+      <c r="Q121" s="2" t="inlineStr">
+        <is>
+          <t>0.013039067226890855</t>
+        </is>
+      </c>
+      <c r="R121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:45.524068Z</t>
+        </is>
+      </c>
+      <c r="S121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T121" s="2" t="inlineStr"/>
+      <c r="U121" s="2" t="inlineStr"/>
+      <c r="V121" s="2" t="inlineStr"/>
+      <c r="W121" s="2" t="inlineStr"/>
+      <c r="X121" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y121" s="2" t="inlineStr"/>
+      <c r="Z121" s="2" t="inlineStr"/>
+      <c r="AA121" s="2" t="inlineStr"/>
+      <c r="AB121" s="2" t="inlineStr"/>
+      <c r="AC121" s="2" t="inlineStr"/>
+      <c r="AD121" s="2" t="inlineStr"/>
+      <c r="AE121" s="2" t="inlineStr"/>
+      <c r="AF121" s="2" t="inlineStr"/>
+      <c r="AG121" s="2" t="inlineStr"/>
+      <c r="AH121" s="2" t="inlineStr"/>
+      <c r="AI121" s="2" t="inlineStr"/>
+      <c r="AJ121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>6b51adf331c4489e</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>b3c88c5caf95695e</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>401816392</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>0.548636</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr"/>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>0.425531914893617</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="inlineStr">
+        <is>
+          <t>0.422886</t>
+        </is>
+      </c>
+      <c r="Q122" s="2" t="inlineStr">
+        <is>
+          <t>0.12310408510638299</t>
+        </is>
+      </c>
+      <c r="R122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:46.635088Z</t>
+        </is>
+      </c>
+      <c r="S122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T122" s="2" t="inlineStr"/>
+      <c r="U122" s="2" t="inlineStr"/>
+      <c r="V122" s="2" t="inlineStr"/>
+      <c r="W122" s="2" t="inlineStr"/>
+      <c r="X122" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y122" s="2" t="inlineStr"/>
+      <c r="Z122" s="2" t="inlineStr"/>
+      <c r="AA122" s="2" t="inlineStr"/>
+      <c r="AB122" s="2" t="inlineStr"/>
+      <c r="AC122" s="2" t="inlineStr"/>
+      <c r="AD122" s="2" t="inlineStr"/>
+      <c r="AE122" s="2" t="inlineStr"/>
+      <c r="AF122" s="2" t="inlineStr"/>
+      <c r="AG122" s="2" t="inlineStr"/>
+      <c r="AH122" s="2" t="inlineStr"/>
+      <c r="AI122" s="2" t="inlineStr"/>
+      <c r="AJ122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>314b1719a87549e4</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>13e97fbe35b98e79</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>401816393</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>0.602762</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr"/>
+      <c r="N123" s="2" t="inlineStr"/>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P123" s="2" t="inlineStr">
+        <is>
+          <t>0.587065</t>
+        </is>
+      </c>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>0.012598065573770523</t>
+        </is>
+      </c>
+      <c r="R123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:46.017881Z</t>
+        </is>
+      </c>
+      <c r="S123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T123" s="2" t="inlineStr"/>
+      <c r="U123" s="2" t="inlineStr"/>
+      <c r="V123" s="2" t="inlineStr"/>
+      <c r="W123" s="2" t="inlineStr"/>
+      <c r="X123" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y123" s="2" t="inlineStr"/>
+      <c r="Z123" s="2" t="inlineStr"/>
+      <c r="AA123" s="2" t="inlineStr"/>
+      <c r="AB123" s="2" t="inlineStr"/>
+      <c r="AC123" s="2" t="inlineStr"/>
+      <c r="AD123" s="2" t="inlineStr"/>
+      <c r="AE123" s="2" t="inlineStr"/>
+      <c r="AF123" s="2" t="inlineStr"/>
+      <c r="AG123" s="2" t="inlineStr"/>
+      <c r="AH123" s="2" t="inlineStr"/>
+      <c r="AI123" s="2" t="inlineStr"/>
+      <c r="AJ123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>9ef53fd1fd39443f</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>8e6c1112d71450b7</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>401816391</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>0.521554</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr"/>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>0.3448275862068966</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>0.343284</t>
+        </is>
+      </c>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>0.1767264137931034</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:47.078718Z</t>
+        </is>
+      </c>
+      <c r="S124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T124" s="2" t="inlineStr"/>
+      <c r="U124" s="2" t="inlineStr"/>
+      <c r="V124" s="2" t="inlineStr"/>
+      <c r="W124" s="2" t="inlineStr"/>
+      <c r="X124" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y124" s="2" t="inlineStr"/>
+      <c r="Z124" s="2" t="inlineStr"/>
+      <c r="AA124" s="2" t="inlineStr"/>
+      <c r="AB124" s="2" t="inlineStr"/>
+      <c r="AC124" s="2" t="inlineStr"/>
+      <c r="AD124" s="2" t="inlineStr"/>
+      <c r="AE124" s="2" t="inlineStr"/>
+      <c r="AF124" s="2" t="inlineStr"/>
+      <c r="AG124" s="2" t="inlineStr"/>
+      <c r="AH124" s="2" t="inlineStr"/>
+      <c r="AI124" s="2" t="inlineStr"/>
+      <c r="AJ124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>0ff1f2361bde4709</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>99e74cbbb81a6f38</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>401816394</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>0.598469</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="2" t="inlineStr"/>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>0.6453900709219857</t>
+        </is>
+      </c>
+      <c r="P125" s="2" t="inlineStr">
+        <is>
+          <t>0.641791</t>
+        </is>
+      </c>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>-0.04692107092198572</t>
+        </is>
+      </c>
+      <c r="R125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:47.802340Z</t>
+        </is>
+      </c>
+      <c r="S125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T125" s="2" t="inlineStr"/>
+      <c r="U125" s="2" t="inlineStr"/>
+      <c r="V125" s="2" t="inlineStr"/>
+      <c r="W125" s="2" t="inlineStr"/>
+      <c r="X125" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y125" s="2" t="inlineStr"/>
+      <c r="Z125" s="2" t="inlineStr"/>
+      <c r="AA125" s="2" t="inlineStr"/>
+      <c r="AB125" s="2" t="inlineStr"/>
+      <c r="AC125" s="2" t="inlineStr"/>
+      <c r="AD125" s="2" t="inlineStr"/>
+      <c r="AE125" s="2" t="inlineStr"/>
+      <c r="AF125" s="2" t="inlineStr"/>
+      <c r="AG125" s="2" t="inlineStr"/>
+      <c r="AH125" s="2" t="inlineStr"/>
+      <c r="AI125" s="2" t="inlineStr"/>
+      <c r="AJ125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>6d34cd9c3dd24a6c</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>9031aa134a98c176</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>401816395</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>0.533882</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr"/>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P126" s="2" t="inlineStr">
+        <is>
+          <t>0.547264</t>
+        </is>
+      </c>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>-0.01566754954954952</t>
+        </is>
+      </c>
+      <c r="R126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:48.151019Z</t>
+        </is>
+      </c>
+      <c r="S126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T126" s="2" t="inlineStr"/>
+      <c r="U126" s="2" t="inlineStr"/>
+      <c r="V126" s="2" t="inlineStr"/>
+      <c r="W126" s="2" t="inlineStr"/>
+      <c r="X126" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y126" s="2" t="inlineStr"/>
+      <c r="Z126" s="2" t="inlineStr"/>
+      <c r="AA126" s="2" t="inlineStr"/>
+      <c r="AB126" s="2" t="inlineStr"/>
+      <c r="AC126" s="2" t="inlineStr"/>
+      <c r="AD126" s="2" t="inlineStr"/>
+      <c r="AE126" s="2" t="inlineStr"/>
+      <c r="AF126" s="2" t="inlineStr"/>
+      <c r="AG126" s="2" t="inlineStr"/>
+      <c r="AH126" s="2" t="inlineStr"/>
+      <c r="AI126" s="2" t="inlineStr"/>
+      <c r="AJ126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>d6263f1c7140497d</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>6300dd580bdeea6d</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>401816396</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>0.619591</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="2" t="inlineStr"/>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>0.6153846153846154</t>
+        </is>
+      </c>
+      <c r="P127" s="2" t="inlineStr">
+        <is>
+          <t>0.61194</t>
+        </is>
+      </c>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>0.004206384615384584</t>
+        </is>
+      </c>
+      <c r="R127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:48.731784Z</t>
+        </is>
+      </c>
+      <c r="S127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T127" s="2" t="inlineStr"/>
+      <c r="U127" s="2" t="inlineStr"/>
+      <c r="V127" s="2" t="inlineStr"/>
+      <c r="W127" s="2" t="inlineStr"/>
+      <c r="X127" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y127" s="2" t="inlineStr"/>
+      <c r="Z127" s="2" t="inlineStr"/>
+      <c r="AA127" s="2" t="inlineStr"/>
+      <c r="AB127" s="2" t="inlineStr"/>
+      <c r="AC127" s="2" t="inlineStr"/>
+      <c r="AD127" s="2" t="inlineStr"/>
+      <c r="AE127" s="2" t="inlineStr"/>
+      <c r="AF127" s="2" t="inlineStr"/>
+      <c r="AG127" s="2" t="inlineStr"/>
+      <c r="AH127" s="2" t="inlineStr"/>
+      <c r="AI127" s="2" t="inlineStr"/>
+      <c r="AJ127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>28182b518361435f</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>3a529a8e501822ee</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>401816398</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>0.503922</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr"/>
+      <c r="N128" s="2" t="inlineStr"/>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="inlineStr">
+        <is>
+          <t>0.527363</t>
+        </is>
+      </c>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
+          <t>-0.026594431924882644</t>
+        </is>
+      </c>
+      <c r="R128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:49.301935Z</t>
+        </is>
+      </c>
+      <c r="S128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T128" s="2" t="inlineStr"/>
+      <c r="U128" s="2" t="inlineStr"/>
+      <c r="V128" s="2" t="inlineStr"/>
+      <c r="W128" s="2" t="inlineStr"/>
+      <c r="X128" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y128" s="2" t="inlineStr"/>
+      <c r="Z128" s="2" t="inlineStr"/>
+      <c r="AA128" s="2" t="inlineStr"/>
+      <c r="AB128" s="2" t="inlineStr"/>
+      <c r="AC128" s="2" t="inlineStr"/>
+      <c r="AD128" s="2" t="inlineStr"/>
+      <c r="AE128" s="2" t="inlineStr"/>
+      <c r="AF128" s="2" t="inlineStr"/>
+      <c r="AG128" s="2" t="inlineStr"/>
+      <c r="AH128" s="2" t="inlineStr"/>
+      <c r="AI128" s="2" t="inlineStr"/>
+      <c r="AJ128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>ee1424babc7d49fe</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>3e807b27cf4b5cde</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>401816385</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>0.542833</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr"/>
+      <c r="N129" s="2" t="inlineStr"/>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>0.5555555555555556</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr">
+        <is>
+          <t>0.552239</t>
+        </is>
+      </c>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>-0.01272255555555557</t>
+        </is>
+      </c>
+      <c r="R129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:50:13.028548Z</t>
+        </is>
+      </c>
+      <c r="S129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T129" s="2" t="inlineStr"/>
+      <c r="U129" s="2" t="inlineStr"/>
+      <c r="V129" s="2" t="inlineStr"/>
+      <c r="W129" s="2" t="inlineStr"/>
+      <c r="X129" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y129" s="2" t="inlineStr"/>
+      <c r="Z129" s="2" t="inlineStr"/>
+      <c r="AA129" s="2" t="inlineStr"/>
+      <c r="AB129" s="2" t="inlineStr"/>
+      <c r="AC129" s="2" t="inlineStr"/>
+      <c r="AD129" s="2" t="inlineStr"/>
+      <c r="AE129" s="2" t="inlineStr"/>
+      <c r="AF129" s="2" t="inlineStr"/>
+      <c r="AG129" s="2" t="inlineStr"/>
+      <c r="AH129" s="2" t="inlineStr"/>
+      <c r="AI129" s="2" t="inlineStr"/>
+      <c r="AJ129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>3baa9f9e04c94241</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>35a2bc4aecd7eec7</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>401816388</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>0.583191</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr"/>
+      <c r="N130" s="2" t="inlineStr"/>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>0.5850622406639003</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="inlineStr">
+        <is>
+          <t>0.58209</t>
+        </is>
+      </c>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>-0.0018712406639003198</t>
+        </is>
+      </c>
+      <c r="R130" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:50:12.501399Z</t>
+        </is>
+      </c>
+      <c r="S130" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T130" s="2" t="inlineStr"/>
+      <c r="U130" s="2" t="inlineStr"/>
+      <c r="V130" s="2" t="inlineStr"/>
+      <c r="W130" s="2" t="inlineStr"/>
+      <c r="X130" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y130" s="2" t="inlineStr"/>
+      <c r="Z130" s="2" t="inlineStr"/>
+      <c r="AA130" s="2" t="inlineStr"/>
+      <c r="AB130" s="2" t="inlineStr"/>
+      <c r="AC130" s="2" t="inlineStr"/>
+      <c r="AD130" s="2" t="inlineStr"/>
+      <c r="AE130" s="2" t="inlineStr"/>
+      <c r="AF130" s="2" t="inlineStr"/>
+      <c r="AG130" s="2" t="inlineStr"/>
+      <c r="AH130" s="2" t="inlineStr"/>
+      <c r="AI130" s="2" t="inlineStr"/>
+      <c r="AJ130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>7a43f3f237be4007</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>9ee0310cde0f84fa</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>401816390</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>0.576615</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr"/>
+      <c r="N131" s="2" t="inlineStr"/>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>0.7198879551820728</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="inlineStr">
+        <is>
+          <t>0.716418</t>
+        </is>
+      </c>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
+          <t>-0.14327295518207284</t>
+        </is>
+      </c>
+      <c r="R131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:50:13.669519Z</t>
+        </is>
+      </c>
+      <c r="S131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T131" s="2" t="inlineStr"/>
+      <c r="U131" s="2" t="inlineStr"/>
+      <c r="V131" s="2" t="inlineStr"/>
+      <c r="W131" s="2" t="inlineStr"/>
+      <c r="X131" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y131" s="2" t="inlineStr"/>
+      <c r="Z131" s="2" t="inlineStr"/>
+      <c r="AA131" s="2" t="inlineStr"/>
+      <c r="AB131" s="2" t="inlineStr"/>
+      <c r="AC131" s="2" t="inlineStr"/>
+      <c r="AD131" s="2" t="inlineStr"/>
+      <c r="AE131" s="2" t="inlineStr"/>
+      <c r="AF131" s="2" t="inlineStr"/>
+      <c r="AG131" s="2" t="inlineStr"/>
+      <c r="AH131" s="2" t="inlineStr"/>
+      <c r="AI131" s="2" t="inlineStr"/>
+      <c r="AJ131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>d5ca16086b0845ad</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>a8d0aab335b1e445</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>401816389</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>0.606664</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr"/>
+      <c r="N132" s="2" t="inlineStr"/>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>0.6453900709219857</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>0.641791</t>
+        </is>
+      </c>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>-0.03872607092198577</t>
+        </is>
+      </c>
+      <c r="R132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:50:14.342694Z</t>
+        </is>
+      </c>
+      <c r="S132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T132" s="2" t="inlineStr"/>
+      <c r="U132" s="2" t="inlineStr"/>
+      <c r="V132" s="2" t="inlineStr"/>
+      <c r="W132" s="2" t="inlineStr"/>
+      <c r="X132" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y132" s="2" t="inlineStr"/>
+      <c r="Z132" s="2" t="inlineStr"/>
+      <c r="AA132" s="2" t="inlineStr"/>
+      <c r="AB132" s="2" t="inlineStr"/>
+      <c r="AC132" s="2" t="inlineStr"/>
+      <c r="AD132" s="2" t="inlineStr"/>
+      <c r="AE132" s="2" t="inlineStr"/>
+      <c r="AF132" s="2" t="inlineStr"/>
+      <c r="AG132" s="2" t="inlineStr"/>
+      <c r="AH132" s="2" t="inlineStr"/>
+      <c r="AI132" s="2" t="inlineStr"/>
+      <c r="AJ132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>26534740a8ec454e</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>fd3882303c2010b8</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>401816386</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>0.574795</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr"/>
+      <c r="N133" s="2" t="inlineStr"/>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>0.5555555555555556</t>
+        </is>
+      </c>
+      <c r="P133" s="2" t="inlineStr">
+        <is>
+          <t>0.552239</t>
+        </is>
+      </c>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
+          <t>0.019239444444444365</t>
+        </is>
+      </c>
+      <c r="R133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:50:14.933076Z</t>
+        </is>
+      </c>
+      <c r="S133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T133" s="2" t="inlineStr"/>
+      <c r="U133" s="2" t="inlineStr"/>
+      <c r="V133" s="2" t="inlineStr"/>
+      <c r="W133" s="2" t="inlineStr"/>
+      <c r="X133" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y133" s="2" t="inlineStr"/>
+      <c r="Z133" s="2" t="inlineStr"/>
+      <c r="AA133" s="2" t="inlineStr"/>
+      <c r="AB133" s="2" t="inlineStr"/>
+      <c r="AC133" s="2" t="inlineStr"/>
+      <c r="AD133" s="2" t="inlineStr"/>
+      <c r="AE133" s="2" t="inlineStr"/>
+      <c r="AF133" s="2" t="inlineStr"/>
+      <c r="AG133" s="2" t="inlineStr"/>
+      <c r="AH133" s="2" t="inlineStr"/>
+      <c r="AI133" s="2" t="inlineStr"/>
+      <c r="AJ133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>d05c353f4fa749c7</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>6ac4a84f3fe182bc</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>401816387</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>0.592857</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr"/>
+      <c r="N134" s="2" t="inlineStr"/>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>0.574468085106383</t>
+        </is>
+      </c>
+      <c r="P134" s="2" t="inlineStr">
+        <is>
+          <t>0.572139</t>
+        </is>
+      </c>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>0.018388914893616937</t>
+        </is>
+      </c>
+      <c r="R134" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:50:15.492815Z</t>
+        </is>
+      </c>
+      <c r="S134" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T134" s="2" t="inlineStr"/>
+      <c r="U134" s="2" t="inlineStr"/>
+      <c r="V134" s="2" t="inlineStr"/>
+      <c r="W134" s="2" t="inlineStr"/>
+      <c r="X134" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y134" s="2" t="inlineStr"/>
+      <c r="Z134" s="2" t="inlineStr"/>
+      <c r="AA134" s="2" t="inlineStr"/>
+      <c r="AB134" s="2" t="inlineStr"/>
+      <c r="AC134" s="2" t="inlineStr"/>
+      <c r="AD134" s="2" t="inlineStr"/>
+      <c r="AE134" s="2" t="inlineStr"/>
+      <c r="AF134" s="2" t="inlineStr"/>
+      <c r="AG134" s="2" t="inlineStr"/>
+      <c r="AH134" s="2" t="inlineStr"/>
+      <c r="AI134" s="2" t="inlineStr"/>
+      <c r="AJ134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>82bac7da4e514832</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>fd407060ec940636</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>401816392</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>0.548673</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr"/>
+      <c r="N135" s="2" t="inlineStr"/>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>0.425531914893617</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="inlineStr">
+        <is>
+          <t>0.422886</t>
+        </is>
+      </c>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>0.12314108510638294</t>
+        </is>
+      </c>
+      <c r="R135" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:50:16.431306Z</t>
+        </is>
+      </c>
+      <c r="S135" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T135" s="2" t="inlineStr"/>
+      <c r="U135" s="2" t="inlineStr"/>
+      <c r="V135" s="2" t="inlineStr"/>
+      <c r="W135" s="2" t="inlineStr"/>
+      <c r="X135" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y135" s="2" t="inlineStr"/>
+      <c r="Z135" s="2" t="inlineStr"/>
+      <c r="AA135" s="2" t="inlineStr"/>
+      <c r="AB135" s="2" t="inlineStr"/>
+      <c r="AC135" s="2" t="inlineStr"/>
+      <c r="AD135" s="2" t="inlineStr"/>
+      <c r="AE135" s="2" t="inlineStr"/>
+      <c r="AF135" s="2" t="inlineStr"/>
+      <c r="AG135" s="2" t="inlineStr"/>
+      <c r="AH135" s="2" t="inlineStr"/>
+      <c r="AI135" s="2" t="inlineStr"/>
+      <c r="AJ135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>0044f766d6ca4353</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>13e97fbe35b98e79</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>401816393</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>0.602762</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr"/>
+      <c r="N136" s="2" t="inlineStr"/>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>0.5850622406639003</t>
+        </is>
+      </c>
+      <c r="P136" s="2" t="inlineStr">
+        <is>
+          <t>0.58209</t>
+        </is>
+      </c>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>0.017699759336099685</t>
+        </is>
+      </c>
+      <c r="R136" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:50:15.906759Z</t>
+        </is>
+      </c>
+      <c r="S136" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T136" s="2" t="inlineStr"/>
+      <c r="U136" s="2" t="inlineStr"/>
+      <c r="V136" s="2" t="inlineStr"/>
+      <c r="W136" s="2" t="inlineStr"/>
+      <c r="X136" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y136" s="2" t="inlineStr"/>
+      <c r="Z136" s="2" t="inlineStr"/>
+      <c r="AA136" s="2" t="inlineStr"/>
+      <c r="AB136" s="2" t="inlineStr"/>
+      <c r="AC136" s="2" t="inlineStr"/>
+      <c r="AD136" s="2" t="inlineStr"/>
+      <c r="AE136" s="2" t="inlineStr"/>
+      <c r="AF136" s="2" t="inlineStr"/>
+      <c r="AG136" s="2" t="inlineStr"/>
+      <c r="AH136" s="2" t="inlineStr"/>
+      <c r="AI136" s="2" t="inlineStr"/>
+      <c r="AJ136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>fe030b72d7b04ac2</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>41b4cee9c4165095</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>401816391</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>0.521547</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr"/>
+      <c r="N137" s="2" t="inlineStr"/>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>0.3448275862068966</t>
+        </is>
+      </c>
+      <c r="P137" s="2" t="inlineStr">
+        <is>
+          <t>0.343284</t>
+        </is>
+      </c>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
+          <t>0.1767194137931034</t>
+        </is>
+      </c>
+      <c r="R137" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:50:17.129354Z</t>
+        </is>
+      </c>
+      <c r="S137" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T137" s="2" t="inlineStr"/>
+      <c r="U137" s="2" t="inlineStr"/>
+      <c r="V137" s="2" t="inlineStr"/>
+      <c r="W137" s="2" t="inlineStr"/>
+      <c r="X137" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y137" s="2" t="inlineStr"/>
+      <c r="Z137" s="2" t="inlineStr"/>
+      <c r="AA137" s="2" t="inlineStr"/>
+      <c r="AB137" s="2" t="inlineStr"/>
+      <c r="AC137" s="2" t="inlineStr"/>
+      <c r="AD137" s="2" t="inlineStr"/>
+      <c r="AE137" s="2" t="inlineStr"/>
+      <c r="AF137" s="2" t="inlineStr"/>
+      <c r="AG137" s="2" t="inlineStr"/>
+      <c r="AH137" s="2" t="inlineStr"/>
+      <c r="AI137" s="2" t="inlineStr"/>
+      <c r="AJ137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>bac1cbc8799d4b41</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>99e74cbbb81a6f38</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>401816394</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>0.598469</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr"/>
+      <c r="N138" s="2" t="inlineStr"/>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>0.6453900709219857</t>
+        </is>
+      </c>
+      <c r="P138" s="2" t="inlineStr">
+        <is>
+          <t>0.641791</t>
+        </is>
+      </c>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>-0.04692107092198572</t>
+        </is>
+      </c>
+      <c r="R138" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:50:17.809691Z</t>
+        </is>
+      </c>
+      <c r="S138" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T138" s="2" t="inlineStr"/>
+      <c r="U138" s="2" t="inlineStr"/>
+      <c r="V138" s="2" t="inlineStr"/>
+      <c r="W138" s="2" t="inlineStr"/>
+      <c r="X138" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y138" s="2" t="inlineStr"/>
+      <c r="Z138" s="2" t="inlineStr"/>
+      <c r="AA138" s="2" t="inlineStr"/>
+      <c r="AB138" s="2" t="inlineStr"/>
+      <c r="AC138" s="2" t="inlineStr"/>
+      <c r="AD138" s="2" t="inlineStr"/>
+      <c r="AE138" s="2" t="inlineStr"/>
+      <c r="AF138" s="2" t="inlineStr"/>
+      <c r="AG138" s="2" t="inlineStr"/>
+      <c r="AH138" s="2" t="inlineStr"/>
+      <c r="AI138" s="2" t="inlineStr"/>
+      <c r="AJ138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>48c77ddc13fd46d0</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>9031aa134a98c176</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>401816395</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>0.533882</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr"/>
+      <c r="N139" s="2" t="inlineStr"/>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P139" s="2" t="inlineStr">
+        <is>
+          <t>0.547264</t>
+        </is>
+      </c>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>-0.01566754954954952</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:50:18.695721Z</t>
+        </is>
+      </c>
+      <c r="S139" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T139" s="2" t="inlineStr"/>
+      <c r="U139" s="2" t="inlineStr"/>
+      <c r="V139" s="2" t="inlineStr"/>
+      <c r="W139" s="2" t="inlineStr"/>
+      <c r="X139" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y139" s="2" t="inlineStr"/>
+      <c r="Z139" s="2" t="inlineStr"/>
+      <c r="AA139" s="2" t="inlineStr"/>
+      <c r="AB139" s="2" t="inlineStr"/>
+      <c r="AC139" s="2" t="inlineStr"/>
+      <c r="AD139" s="2" t="inlineStr"/>
+      <c r="AE139" s="2" t="inlineStr"/>
+      <c r="AF139" s="2" t="inlineStr"/>
+      <c r="AG139" s="2" t="inlineStr"/>
+      <c r="AH139" s="2" t="inlineStr"/>
+      <c r="AI139" s="2" t="inlineStr"/>
+      <c r="AJ139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>5704eeb6ce1c46fa</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>14d8a2af224d986f</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>401816396</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>0.619626</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr"/>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>0.6153846153846154</t>
+        </is>
+      </c>
+      <c r="P140" s="2" t="inlineStr">
+        <is>
+          <t>0.61194</t>
+        </is>
+      </c>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>0.004241384615384591</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:50:19.077140Z</t>
+        </is>
+      </c>
+      <c r="S140" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T140" s="2" t="inlineStr"/>
+      <c r="U140" s="2" t="inlineStr"/>
+      <c r="V140" s="2" t="inlineStr"/>
+      <c r="W140" s="2" t="inlineStr"/>
+      <c r="X140" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y140" s="2" t="inlineStr"/>
+      <c r="Z140" s="2" t="inlineStr"/>
+      <c r="AA140" s="2" t="inlineStr"/>
+      <c r="AB140" s="2" t="inlineStr"/>
+      <c r="AC140" s="2" t="inlineStr"/>
+      <c r="AD140" s="2" t="inlineStr"/>
+      <c r="AE140" s="2" t="inlineStr"/>
+      <c r="AF140" s="2" t="inlineStr"/>
+      <c r="AG140" s="2" t="inlineStr"/>
+      <c r="AH140" s="2" t="inlineStr"/>
+      <c r="AI140" s="2" t="inlineStr"/>
+      <c r="AJ140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>a6c366a7b352454a</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>3a529a8e501822ee</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>401816398</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>0.503922</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr"/>
+      <c r="N141" s="2" t="inlineStr"/>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>0.5260663507109005</t>
+        </is>
+      </c>
+      <c r="P141" s="2" t="inlineStr">
+        <is>
+          <t>0.522388</t>
+        </is>
+      </c>
+      <c r="Q141" s="2" t="inlineStr">
+        <is>
+          <t>-0.022144350710900484</t>
+        </is>
+      </c>
+      <c r="R141" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:50:20.017471Z</t>
+        </is>
+      </c>
+      <c r="S141" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T141" s="2" t="inlineStr"/>
+      <c r="U141" s="2" t="inlineStr"/>
+      <c r="V141" s="2" t="inlineStr"/>
+      <c r="W141" s="2" t="inlineStr"/>
+      <c r="X141" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y141" s="2" t="inlineStr"/>
+      <c r="Z141" s="2" t="inlineStr"/>
+      <c r="AA141" s="2" t="inlineStr"/>
+      <c r="AB141" s="2" t="inlineStr"/>
+      <c r="AC141" s="2" t="inlineStr"/>
+      <c r="AD141" s="2" t="inlineStr"/>
+      <c r="AE141" s="2" t="inlineStr"/>
+      <c r="AF141" s="2" t="inlineStr"/>
+      <c r="AG141" s="2" t="inlineStr"/>
+      <c r="AH141" s="2" t="inlineStr"/>
+      <c r="AI141" s="2" t="inlineStr"/>
+      <c r="AJ141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>b01bb982279344ec</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>e06e823a6bdbd1d9</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>401816385</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>0.542826</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr"/>
+      <c r="N142" s="2" t="inlineStr"/>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>0.5555555555555556</t>
+        </is>
+      </c>
+      <c r="P142" s="2" t="inlineStr">
+        <is>
+          <t>0.552239</t>
+        </is>
+      </c>
+      <c r="Q142" s="2" t="inlineStr">
+        <is>
+          <t>-0.01272955555555555</t>
+        </is>
+      </c>
+      <c r="R142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:05:10.639577Z</t>
+        </is>
+      </c>
+      <c r="S142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T142" s="2" t="inlineStr"/>
+      <c r="U142" s="2" t="inlineStr"/>
+      <c r="V142" s="2" t="inlineStr"/>
+      <c r="W142" s="2" t="inlineStr"/>
+      <c r="X142" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y142" s="2" t="inlineStr"/>
+      <c r="Z142" s="2" t="inlineStr"/>
+      <c r="AA142" s="2" t="inlineStr"/>
+      <c r="AB142" s="2" t="inlineStr"/>
+      <c r="AC142" s="2" t="inlineStr"/>
+      <c r="AD142" s="2" t="inlineStr"/>
+      <c r="AE142" s="2" t="inlineStr"/>
+      <c r="AF142" s="2" t="inlineStr"/>
+      <c r="AG142" s="2" t="inlineStr"/>
+      <c r="AH142" s="2" t="inlineStr"/>
+      <c r="AI142" s="2" t="inlineStr"/>
+      <c r="AJ142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>222c163a16cb4560</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>0b49cd84a0231454</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>401816388</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>0.583155</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr"/>
+      <c r="N143" s="2" t="inlineStr"/>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>0.5850622406639003</t>
+        </is>
+      </c>
+      <c r="P143" s="2" t="inlineStr">
+        <is>
+          <t>0.58209</t>
+        </is>
+      </c>
+      <c r="Q143" s="2" t="inlineStr">
+        <is>
+          <t>-0.0019072406639003558</t>
+        </is>
+      </c>
+      <c r="R143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:05:09.805172Z</t>
+        </is>
+      </c>
+      <c r="S143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T143" s="2" t="inlineStr"/>
+      <c r="U143" s="2" t="inlineStr"/>
+      <c r="V143" s="2" t="inlineStr"/>
+      <c r="W143" s="2" t="inlineStr"/>
+      <c r="X143" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y143" s="2" t="inlineStr"/>
+      <c r="Z143" s="2" t="inlineStr"/>
+      <c r="AA143" s="2" t="inlineStr"/>
+      <c r="AB143" s="2" t="inlineStr"/>
+      <c r="AC143" s="2" t="inlineStr"/>
+      <c r="AD143" s="2" t="inlineStr"/>
+      <c r="AE143" s="2" t="inlineStr"/>
+      <c r="AF143" s="2" t="inlineStr"/>
+      <c r="AG143" s="2" t="inlineStr"/>
+      <c r="AH143" s="2" t="inlineStr"/>
+      <c r="AI143" s="2" t="inlineStr"/>
+      <c r="AJ143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>5d454a46b9994f54</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>369d1536ae304e1e</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>401816390</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>0.57668</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr"/>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>0.7198879551820728</t>
+        </is>
+      </c>
+      <c r="P144" s="2" t="inlineStr">
+        <is>
+          <t>0.716418</t>
+        </is>
+      </c>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>-0.14320795518207285</t>
+        </is>
+      </c>
+      <c r="R144" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:05:11.521989Z</t>
+        </is>
+      </c>
+      <c r="S144" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T144" s="2" t="inlineStr"/>
+      <c r="U144" s="2" t="inlineStr"/>
+      <c r="V144" s="2" t="inlineStr"/>
+      <c r="W144" s="2" t="inlineStr"/>
+      <c r="X144" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y144" s="2" t="inlineStr"/>
+      <c r="Z144" s="2" t="inlineStr"/>
+      <c r="AA144" s="2" t="inlineStr"/>
+      <c r="AB144" s="2" t="inlineStr"/>
+      <c r="AC144" s="2" t="inlineStr"/>
+      <c r="AD144" s="2" t="inlineStr"/>
+      <c r="AE144" s="2" t="inlineStr"/>
+      <c r="AF144" s="2" t="inlineStr"/>
+      <c r="AG144" s="2" t="inlineStr"/>
+      <c r="AH144" s="2" t="inlineStr"/>
+      <c r="AI144" s="2" t="inlineStr"/>
+      <c r="AJ144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>560ca57098484b8b</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>7d5fd29c13735fcf</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>401816389</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr"/>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>0.606635</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr"/>
+      <c r="N145" s="2" t="inlineStr"/>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>0.6453900709219857</t>
+        </is>
+      </c>
+      <c r="P145" s="2" t="inlineStr">
+        <is>
+          <t>0.641791</t>
+        </is>
+      </c>
+      <c r="Q145" s="2" t="inlineStr">
+        <is>
+          <t>-0.03875507092198571</t>
+        </is>
+      </c>
+      <c r="R145" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:05:12.327010Z</t>
+        </is>
+      </c>
+      <c r="S145" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T145" s="2" t="inlineStr"/>
+      <c r="U145" s="2" t="inlineStr"/>
+      <c r="V145" s="2" t="inlineStr"/>
+      <c r="W145" s="2" t="inlineStr"/>
+      <c r="X145" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y145" s="2" t="inlineStr"/>
+      <c r="Z145" s="2" t="inlineStr"/>
+      <c r="AA145" s="2" t="inlineStr"/>
+      <c r="AB145" s="2" t="inlineStr"/>
+      <c r="AC145" s="2" t="inlineStr"/>
+      <c r="AD145" s="2" t="inlineStr"/>
+      <c r="AE145" s="2" t="inlineStr"/>
+      <c r="AF145" s="2" t="inlineStr"/>
+      <c r="AG145" s="2" t="inlineStr"/>
+      <c r="AH145" s="2" t="inlineStr"/>
+      <c r="AI145" s="2" t="inlineStr"/>
+      <c r="AJ145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>1ff8bea1f41049a9</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>da04afeb8405a951</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>401816386</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>0.574686</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr"/>
+      <c r="N146" s="2" t="inlineStr"/>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>0.5555555555555556</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="inlineStr">
+        <is>
+          <t>0.552239</t>
+        </is>
+      </c>
+      <c r="Q146" s="2" t="inlineStr">
+        <is>
+          <t>0.01913044444444445</t>
+        </is>
+      </c>
+      <c r="R146" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:05:13.146482Z</t>
+        </is>
+      </c>
+      <c r="S146" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T146" s="2" t="inlineStr"/>
+      <c r="U146" s="2" t="inlineStr"/>
+      <c r="V146" s="2" t="inlineStr"/>
+      <c r="W146" s="2" t="inlineStr"/>
+      <c r="X146" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y146" s="2" t="inlineStr"/>
+      <c r="Z146" s="2" t="inlineStr"/>
+      <c r="AA146" s="2" t="inlineStr"/>
+      <c r="AB146" s="2" t="inlineStr"/>
+      <c r="AC146" s="2" t="inlineStr"/>
+      <c r="AD146" s="2" t="inlineStr"/>
+      <c r="AE146" s="2" t="inlineStr"/>
+      <c r="AF146" s="2" t="inlineStr"/>
+      <c r="AG146" s="2" t="inlineStr"/>
+      <c r="AH146" s="2" t="inlineStr"/>
+      <c r="AI146" s="2" t="inlineStr"/>
+      <c r="AJ146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>4a9661e5b91f46cf</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>1f8d5c12ee61fe3c</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>401816387</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>0.593058</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr"/>
+      <c r="N147" s="2" t="inlineStr"/>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>0.574468085106383</t>
+        </is>
+      </c>
+      <c r="P147" s="2" t="inlineStr">
+        <is>
+          <t>0.572139</t>
+        </is>
+      </c>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>0.018589914893616943</t>
+        </is>
+      </c>
+      <c r="R147" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:05:14.015740Z</t>
+        </is>
+      </c>
+      <c r="S147" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T147" s="2" t="inlineStr"/>
+      <c r="U147" s="2" t="inlineStr"/>
+      <c r="V147" s="2" t="inlineStr"/>
+      <c r="W147" s="2" t="inlineStr"/>
+      <c r="X147" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y147" s="2" t="inlineStr"/>
+      <c r="Z147" s="2" t="inlineStr"/>
+      <c r="AA147" s="2" t="inlineStr"/>
+      <c r="AB147" s="2" t="inlineStr"/>
+      <c r="AC147" s="2" t="inlineStr"/>
+      <c r="AD147" s="2" t="inlineStr"/>
+      <c r="AE147" s="2" t="inlineStr"/>
+      <c r="AF147" s="2" t="inlineStr"/>
+      <c r="AG147" s="2" t="inlineStr"/>
+      <c r="AH147" s="2" t="inlineStr"/>
+      <c r="AI147" s="2" t="inlineStr"/>
+      <c r="AJ147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>0918bd10eaec4b26</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>87a4fb354fbed7f5</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>401816392</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>0.54868</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr"/>
+      <c r="N148" s="2" t="inlineStr"/>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>0.425531914893617</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="inlineStr">
+        <is>
+          <t>0.422886</t>
+        </is>
+      </c>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>0.12314808510638292</t>
+        </is>
+      </c>
+      <c r="R148" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:05:15.592826Z</t>
+        </is>
+      </c>
+      <c r="S148" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T148" s="2" t="inlineStr"/>
+      <c r="U148" s="2" t="inlineStr"/>
+      <c r="V148" s="2" t="inlineStr"/>
+      <c r="W148" s="2" t="inlineStr"/>
+      <c r="X148" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y148" s="2" t="inlineStr"/>
+      <c r="Z148" s="2" t="inlineStr"/>
+      <c r="AA148" s="2" t="inlineStr"/>
+      <c r="AB148" s="2" t="inlineStr"/>
+      <c r="AC148" s="2" t="inlineStr"/>
+      <c r="AD148" s="2" t="inlineStr"/>
+      <c r="AE148" s="2" t="inlineStr"/>
+      <c r="AF148" s="2" t="inlineStr"/>
+      <c r="AG148" s="2" t="inlineStr"/>
+      <c r="AH148" s="2" t="inlineStr"/>
+      <c r="AI148" s="2" t="inlineStr"/>
+      <c r="AJ148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>841ae63cee354e55</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>13e97fbe35b98e79</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>401816393</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>0.602762</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr"/>
+      <c r="N149" s="2" t="inlineStr"/>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P149" s="2" t="inlineStr">
+        <is>
+          <t>0.577114</t>
+        </is>
+      </c>
+      <c r="Q149" s="2" t="inlineStr">
+        <is>
+          <t>0.022930067226890838</t>
+        </is>
+      </c>
+      <c r="R149" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:05:14.823383Z</t>
+        </is>
+      </c>
+      <c r="S149" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T149" s="2" t="inlineStr"/>
+      <c r="U149" s="2" t="inlineStr"/>
+      <c r="V149" s="2" t="inlineStr"/>
+      <c r="W149" s="2" t="inlineStr"/>
+      <c r="X149" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y149" s="2" t="inlineStr"/>
+      <c r="Z149" s="2" t="inlineStr"/>
+      <c r="AA149" s="2" t="inlineStr"/>
+      <c r="AB149" s="2" t="inlineStr"/>
+      <c r="AC149" s="2" t="inlineStr"/>
+      <c r="AD149" s="2" t="inlineStr"/>
+      <c r="AE149" s="2" t="inlineStr"/>
+      <c r="AF149" s="2" t="inlineStr"/>
+      <c r="AG149" s="2" t="inlineStr"/>
+      <c r="AH149" s="2" t="inlineStr"/>
+      <c r="AI149" s="2" t="inlineStr"/>
+      <c r="AJ149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>b13d1769936c458c</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>8e6c1112d71450b7</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>401816391</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>0.521554</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr"/>
+      <c r="N150" s="2" t="inlineStr"/>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>0.35460992907801414</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="inlineStr">
+        <is>
+          <t>0.353234</t>
+        </is>
+      </c>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
+          <t>0.16694407092198582</t>
+        </is>
+      </c>
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:05:16.327300Z</t>
+        </is>
+      </c>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T150" s="2" t="inlineStr"/>
+      <c r="U150" s="2" t="inlineStr"/>
+      <c r="V150" s="2" t="inlineStr"/>
+      <c r="W150" s="2" t="inlineStr"/>
+      <c r="X150" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y150" s="2" t="inlineStr"/>
+      <c r="Z150" s="2" t="inlineStr"/>
+      <c r="AA150" s="2" t="inlineStr"/>
+      <c r="AB150" s="2" t="inlineStr"/>
+      <c r="AC150" s="2" t="inlineStr"/>
+      <c r="AD150" s="2" t="inlineStr"/>
+      <c r="AE150" s="2" t="inlineStr"/>
+      <c r="AF150" s="2" t="inlineStr"/>
+      <c r="AG150" s="2" t="inlineStr"/>
+      <c r="AH150" s="2" t="inlineStr"/>
+      <c r="AI150" s="2" t="inlineStr"/>
+      <c r="AJ150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>84c3b05456544f72</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>99e74cbbb81a6f38</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>401816394</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>0.598469</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr"/>
+      <c r="N151" s="2" t="inlineStr"/>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>0.6453900709219857</t>
+        </is>
+      </c>
+      <c r="P151" s="2" t="inlineStr">
+        <is>
+          <t>0.641791</t>
+        </is>
+      </c>
+      <c r="Q151" s="2" t="inlineStr">
+        <is>
+          <t>-0.04692107092198572</t>
+        </is>
+      </c>
+      <c r="R151" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:05:17.129462Z</t>
+        </is>
+      </c>
+      <c r="S151" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T151" s="2" t="inlineStr"/>
+      <c r="U151" s="2" t="inlineStr"/>
+      <c r="V151" s="2" t="inlineStr"/>
+      <c r="W151" s="2" t="inlineStr"/>
+      <c r="X151" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y151" s="2" t="inlineStr"/>
+      <c r="Z151" s="2" t="inlineStr"/>
+      <c r="AA151" s="2" t="inlineStr"/>
+      <c r="AB151" s="2" t="inlineStr"/>
+      <c r="AC151" s="2" t="inlineStr"/>
+      <c r="AD151" s="2" t="inlineStr"/>
+      <c r="AE151" s="2" t="inlineStr"/>
+      <c r="AF151" s="2" t="inlineStr"/>
+      <c r="AG151" s="2" t="inlineStr"/>
+      <c r="AH151" s="2" t="inlineStr"/>
+      <c r="AI151" s="2" t="inlineStr"/>
+      <c r="AJ151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>449d12b39b974ee1</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>9031aa134a98c176</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>401816395</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>0.533882</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr"/>
+      <c r="N152" s="2" t="inlineStr"/>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>0.5555555555555556</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="inlineStr">
+        <is>
+          <t>0.552239</t>
+        </is>
+      </c>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>-0.021673555555555613</t>
+        </is>
+      </c>
+      <c r="R152" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:05:17.895753Z</t>
+        </is>
+      </c>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="inlineStr"/>
+      <c r="U152" s="2" t="inlineStr"/>
+      <c r="V152" s="2" t="inlineStr"/>
+      <c r="W152" s="2" t="inlineStr"/>
+      <c r="X152" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y152" s="2" t="inlineStr"/>
+      <c r="Z152" s="2" t="inlineStr"/>
+      <c r="AA152" s="2" t="inlineStr"/>
+      <c r="AB152" s="2" t="inlineStr"/>
+      <c r="AC152" s="2" t="inlineStr"/>
+      <c r="AD152" s="2" t="inlineStr"/>
+      <c r="AE152" s="2" t="inlineStr"/>
+      <c r="AF152" s="2" t="inlineStr"/>
+      <c r="AG152" s="2" t="inlineStr"/>
+      <c r="AH152" s="2" t="inlineStr"/>
+      <c r="AI152" s="2" t="inlineStr"/>
+      <c r="AJ152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>7bec637b5d924c43</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>c26d1a6c79f0f9d1</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>401816396</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr"/>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>0.619563</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr"/>
+      <c r="N153" s="2" t="inlineStr"/>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>0.6153846153846154</t>
+        </is>
+      </c>
+      <c r="P153" s="2" t="inlineStr">
+        <is>
+          <t>0.61194</t>
+        </is>
+      </c>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t>0.004178384615384556</t>
+        </is>
+      </c>
+      <c r="R153" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:05:18.620557Z</t>
+        </is>
+      </c>
+      <c r="S153" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T153" s="2" t="inlineStr"/>
+      <c r="U153" s="2" t="inlineStr"/>
+      <c r="V153" s="2" t="inlineStr"/>
+      <c r="W153" s="2" t="inlineStr"/>
+      <c r="X153" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y153" s="2" t="inlineStr"/>
+      <c r="Z153" s="2" t="inlineStr"/>
+      <c r="AA153" s="2" t="inlineStr"/>
+      <c r="AB153" s="2" t="inlineStr"/>
+      <c r="AC153" s="2" t="inlineStr"/>
+      <c r="AD153" s="2" t="inlineStr"/>
+      <c r="AE153" s="2" t="inlineStr"/>
+      <c r="AF153" s="2" t="inlineStr"/>
+      <c r="AG153" s="2" t="inlineStr"/>
+      <c r="AH153" s="2" t="inlineStr"/>
+      <c r="AI153" s="2" t="inlineStr"/>
+      <c r="AJ153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>987c72f9069748af</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>74edfb020976515b</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>401816397</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>0.545643</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr"/>
+      <c r="N154" s="2" t="inlineStr"/>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>0.5348837209302326</t>
+        </is>
+      </c>
+      <c r="P154" s="2" t="inlineStr">
+        <is>
+          <t>0.532338</t>
+        </is>
+      </c>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>0.010759279069767369</t>
+        </is>
+      </c>
+      <c r="R154" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:05:20.060966Z</t>
+        </is>
+      </c>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T154" s="2" t="inlineStr"/>
+      <c r="U154" s="2" t="inlineStr"/>
+      <c r="V154" s="2" t="inlineStr"/>
+      <c r="W154" s="2" t="inlineStr"/>
+      <c r="X154" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y154" s="2" t="inlineStr"/>
+      <c r="Z154" s="2" t="inlineStr"/>
+      <c r="AA154" s="2" t="inlineStr"/>
+      <c r="AB154" s="2" t="inlineStr"/>
+      <c r="AC154" s="2" t="inlineStr"/>
+      <c r="AD154" s="2" t="inlineStr"/>
+      <c r="AE154" s="2" t="inlineStr"/>
+      <c r="AF154" s="2" t="inlineStr"/>
+      <c r="AG154" s="2" t="inlineStr"/>
+      <c r="AH154" s="2" t="inlineStr"/>
+      <c r="AI154" s="2" t="inlineStr"/>
+      <c r="AJ154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>c4b5485bf30d4fc0</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>3a529a8e501822ee</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>401816398</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>0.503922</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr"/>
+      <c r="N155" s="2" t="inlineStr"/>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>0.5260663507109005</t>
+        </is>
+      </c>
+      <c r="P155" s="2" t="inlineStr">
+        <is>
+          <t>0.522388</t>
+        </is>
+      </c>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>-0.022144350710900484</t>
+        </is>
+      </c>
+      <c r="R155" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:05:19.397122Z</t>
+        </is>
+      </c>
+      <c r="S155" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T155" s="2" t="inlineStr"/>
+      <c r="U155" s="2" t="inlineStr"/>
+      <c r="V155" s="2" t="inlineStr"/>
+      <c r="W155" s="2" t="inlineStr"/>
+      <c r="X155" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y155" s="2" t="inlineStr"/>
+      <c r="Z155" s="2" t="inlineStr"/>
+      <c r="AA155" s="2" t="inlineStr"/>
+      <c r="AB155" s="2" t="inlineStr"/>
+      <c r="AC155" s="2" t="inlineStr"/>
+      <c r="AD155" s="2" t="inlineStr"/>
+      <c r="AE155" s="2" t="inlineStr"/>
+      <c r="AF155" s="2" t="inlineStr"/>
+      <c r="AG155" s="2" t="inlineStr"/>
+      <c r="AH155" s="2" t="inlineStr"/>
+      <c r="AI155" s="2" t="inlineStr"/>
+      <c r="AJ155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>f38dcdee07ca4df4</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>74edfb020976515b</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>401816397</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr"/>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>0.545643</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr"/>
+      <c r="N156" s="2" t="inlineStr"/>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>0.5348837209302326</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="inlineStr">
+        <is>
+          <t>0.532338</t>
+        </is>
+      </c>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>0.010759279069767369</t>
+        </is>
+      </c>
+      <c r="R156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T01:07:10.847192Z</t>
+        </is>
+      </c>
+      <c r="S156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T156" s="2" t="inlineStr"/>
+      <c r="U156" s="2" t="inlineStr"/>
+      <c r="V156" s="2" t="inlineStr"/>
+      <c r="W156" s="2" t="inlineStr"/>
+      <c r="X156" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y156" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z156" s="2" t="inlineStr">
+        <is>
+          <t>0.535000</t>
+        </is>
+      </c>
+      <c r="AA156" s="2" t="inlineStr">
+        <is>
+          <t>0.000116</t>
+        </is>
+      </c>
+      <c r="AB156" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:21:31.889479Z</t>
+        </is>
+      </c>
+      <c r="AD156" s="2" t="inlineStr"/>
+      <c r="AE156" s="2" t="inlineStr"/>
+      <c r="AF156" s="2" t="inlineStr"/>
+      <c r="AG156" s="2" t="inlineStr"/>
+      <c r="AH156" s="2" t="inlineStr"/>
+      <c r="AI156" s="2" t="inlineStr"/>
+      <c r="AJ156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>3d5a82c3e21c4d55</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>3a529a8e501822ee</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>401816398</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>0.503922</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr"/>
+      <c r="N157" s="2" t="inlineStr"/>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>0.5260663507109005</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="inlineStr">
+        <is>
+          <t>0.522388</t>
+        </is>
+      </c>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>-0.022144350710900484</t>
+        </is>
+      </c>
+      <c r="R157" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T01:07:10.040602Z</t>
+        </is>
+      </c>
+      <c r="S157" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T157" s="2" t="inlineStr"/>
+      <c r="U157" s="2" t="inlineStr"/>
+      <c r="V157" s="2" t="inlineStr"/>
+      <c r="W157" s="2" t="inlineStr"/>
+      <c r="X157" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y157" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z157" s="2" t="inlineStr">
+        <is>
+          <t>0.525000</t>
+        </is>
+      </c>
+      <c r="AA157" s="2" t="inlineStr">
+        <is>
+          <t>-0.001066</t>
+        </is>
+      </c>
+      <c r="AB157" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC157" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:33:05.565371Z</t>
+        </is>
+      </c>
+      <c r="AD157" s="2" t="inlineStr"/>
+      <c r="AE157" s="2" t="inlineStr"/>
+      <c r="AF157" s="2" t="inlineStr"/>
+      <c r="AG157" s="2" t="inlineStr"/>
+      <c r="AH157" s="2" t="inlineStr"/>
+      <c r="AI157" s="2" t="inlineStr"/>
+      <c r="AJ157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>67c3970c9eb44d3e</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>7363e92b2bdde372</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>401816410</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>0.543314</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr"/>
+      <c r="N158" s="2" t="inlineStr"/>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>0.5238095238095238</t>
+        </is>
+      </c>
+      <c r="P158" s="2" t="inlineStr"/>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>0.019504476190476128</t>
+        </is>
+      </c>
+      <c r="R158" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:24:48.305759Z</t>
+        </is>
+      </c>
+      <c r="S158" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T158" s="2" t="inlineStr"/>
+      <c r="U158" s="2" t="inlineStr"/>
+      <c r="V158" s="2" t="inlineStr"/>
+      <c r="W158" s="2" t="inlineStr"/>
+      <c r="X158" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y158" s="2" t="inlineStr"/>
+      <c r="Z158" s="2" t="inlineStr"/>
+      <c r="AA158" s="2" t="inlineStr"/>
+      <c r="AB158" s="2" t="inlineStr"/>
+      <c r="AC158" s="2" t="inlineStr"/>
+      <c r="AD158" s="2" t="inlineStr"/>
+      <c r="AE158" s="2" t="inlineStr"/>
+      <c r="AF158" s="2" t="inlineStr"/>
+      <c r="AG158" s="2" t="inlineStr"/>
+      <c r="AH158" s="2" t="inlineStr"/>
+      <c r="AI158" s="2" t="inlineStr"/>
+      <c r="AJ158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>f9d50bd1e61a45d7</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>cd121ba990e73d6d</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>401816406</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>0.522292</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr"/>
+      <c r="N159" s="2" t="inlineStr"/>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>0.5348837209302326</t>
+        </is>
+      </c>
+      <c r="P159" s="2" t="inlineStr">
+        <is>
+          <t>0.532338</t>
+        </is>
+      </c>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
+          <t>-0.012591720930232642</t>
+        </is>
+      </c>
+      <c r="R159" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:22:59.031777Z</t>
+        </is>
+      </c>
+      <c r="S159" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:20:00-0400</t>
+        </is>
+      </c>
+      <c r="T159" s="2" t="inlineStr"/>
+      <c r="U159" s="2" t="inlineStr"/>
+      <c r="V159" s="2" t="inlineStr"/>
+      <c r="W159" s="2" t="inlineStr"/>
+      <c r="X159" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y159" s="2" t="inlineStr"/>
+      <c r="Z159" s="2" t="inlineStr"/>
+      <c r="AA159" s="2" t="inlineStr"/>
+      <c r="AB159" s="2" t="inlineStr"/>
+      <c r="AC159" s="2" t="inlineStr"/>
+      <c r="AD159" s="2" t="inlineStr"/>
+      <c r="AE159" s="2" t="inlineStr"/>
+      <c r="AF159" s="2" t="inlineStr"/>
+      <c r="AG159" s="2" t="inlineStr"/>
+      <c r="AH159" s="2" t="inlineStr"/>
+      <c r="AI159" s="2" t="inlineStr"/>
+      <c r="AJ159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>f659045e87a04336</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>b14707c8a9267bdd</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>401816409</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>0.585182</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr"/>
+      <c r="N160" s="2" t="inlineStr"/>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>0.6254681647940076</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr">
+        <is>
+          <t>0.621891</t>
+        </is>
+      </c>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>-0.040286164794007595</t>
+        </is>
+      </c>
+      <c r="R160" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:23:01.021649Z</t>
+        </is>
+      </c>
+      <c r="S160" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:35:00-0400</t>
+        </is>
+      </c>
+      <c r="T160" s="2" t="inlineStr"/>
+      <c r="U160" s="2" t="inlineStr"/>
+      <c r="V160" s="2" t="inlineStr"/>
+      <c r="W160" s="2" t="inlineStr"/>
+      <c r="X160" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y160" s="2" t="inlineStr"/>
+      <c r="Z160" s="2" t="inlineStr"/>
+      <c r="AA160" s="2" t="inlineStr"/>
+      <c r="AB160" s="2" t="inlineStr"/>
+      <c r="AC160" s="2" t="inlineStr"/>
+      <c r="AD160" s="2" t="inlineStr"/>
+      <c r="AE160" s="2" t="inlineStr"/>
+      <c r="AF160" s="2" t="inlineStr"/>
+      <c r="AG160" s="2" t="inlineStr"/>
+      <c r="AH160" s="2" t="inlineStr"/>
+      <c r="AI160" s="2" t="inlineStr"/>
+      <c r="AJ160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>9fb1d4f75a534ff5</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>afbdfea2d660f7f9</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>401816411</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>0.651419</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr"/>
+      <c r="N161" s="2" t="inlineStr"/>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>0.5951417004048584</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="inlineStr">
+        <is>
+          <t>0.59204</t>
+        </is>
+      </c>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>0.056277299595141606</t>
+        </is>
+      </c>
+      <c r="R161" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:23:02.060960Z</t>
+        </is>
+      </c>
+      <c r="S161" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T15:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T161" s="2" t="inlineStr"/>
+      <c r="U161" s="2" t="inlineStr"/>
+      <c r="V161" s="2" t="inlineStr"/>
+      <c r="W161" s="2" t="inlineStr"/>
+      <c r="X161" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y161" s="2" t="inlineStr"/>
+      <c r="Z161" s="2" t="inlineStr"/>
+      <c r="AA161" s="2" t="inlineStr"/>
+      <c r="AB161" s="2" t="inlineStr"/>
+      <c r="AC161" s="2" t="inlineStr"/>
+      <c r="AD161" s="2" t="inlineStr"/>
+      <c r="AE161" s="2" t="inlineStr"/>
+      <c r="AF161" s="2" t="inlineStr"/>
+      <c r="AG161" s="2" t="inlineStr"/>
+      <c r="AH161" s="2" t="inlineStr"/>
+      <c r="AI161" s="2" t="inlineStr"/>
+      <c r="AJ161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>ac8d3010e3a6413f</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>0c5ef877e6b12160</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>401816399</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>0.620283</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr"/>
+      <c r="N162" s="2" t="inlineStr"/>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>0.5652173913043479</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="inlineStr">
+        <is>
+          <t>0.562189</t>
+        </is>
+      </c>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>0.055065608695652135</t>
+        </is>
+      </c>
+      <c r="R162" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:23:03.919523Z</t>
+        </is>
+      </c>
+      <c r="S162" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:35:00-0400</t>
+        </is>
+      </c>
+      <c r="T162" s="2" t="inlineStr"/>
+      <c r="U162" s="2" t="inlineStr"/>
+      <c r="V162" s="2" t="inlineStr"/>
+      <c r="W162" s="2" t="inlineStr"/>
+      <c r="X162" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y162" s="2" t="inlineStr"/>
+      <c r="Z162" s="2" t="inlineStr"/>
+      <c r="AA162" s="2" t="inlineStr"/>
+      <c r="AB162" s="2" t="inlineStr"/>
+      <c r="AC162" s="2" t="inlineStr"/>
+      <c r="AD162" s="2" t="inlineStr"/>
+      <c r="AE162" s="2" t="inlineStr"/>
+      <c r="AF162" s="2" t="inlineStr"/>
+      <c r="AG162" s="2" t="inlineStr"/>
+      <c r="AH162" s="2" t="inlineStr"/>
+      <c r="AI162" s="2" t="inlineStr"/>
+      <c r="AJ162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>f058a610de53472c</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>117cc3945a0a3429</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>401816400</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>0.531988</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr"/>
+      <c r="N163" s="2" t="inlineStr"/>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>0.5652173913043479</t>
+        </is>
+      </c>
+      <c r="P163" s="2" t="inlineStr">
+        <is>
+          <t>0.562189</t>
+        </is>
+      </c>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>-0.03322939130434788</t>
+        </is>
+      </c>
+      <c r="R163" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:23:07.202644Z</t>
+        </is>
+      </c>
+      <c r="S163" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T163" s="2" t="inlineStr"/>
+      <c r="U163" s="2" t="inlineStr"/>
+      <c r="V163" s="2" t="inlineStr"/>
+      <c r="W163" s="2" t="inlineStr"/>
+      <c r="X163" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y163" s="2" t="inlineStr"/>
+      <c r="Z163" s="2" t="inlineStr"/>
+      <c r="AA163" s="2" t="inlineStr"/>
+      <c r="AB163" s="2" t="inlineStr"/>
+      <c r="AC163" s="2" t="inlineStr"/>
+      <c r="AD163" s="2" t="inlineStr"/>
+      <c r="AE163" s="2" t="inlineStr"/>
+      <c r="AF163" s="2" t="inlineStr"/>
+      <c r="AG163" s="2" t="inlineStr"/>
+      <c r="AH163" s="2" t="inlineStr"/>
+      <c r="AI163" s="2" t="inlineStr"/>
+      <c r="AJ163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>e112b9d3891d4715</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>e56570441b5f5cf2</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>401816403</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>0.570001</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr"/>
+      <c r="N164" s="2" t="inlineStr"/>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>0.4854368932038835</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="inlineStr">
+        <is>
+          <t>0.482587</t>
+        </is>
+      </c>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>0.08456410679611648</t>
+        </is>
+      </c>
+      <c r="R164" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:23:05.888046Z</t>
+        </is>
+      </c>
+      <c r="S164" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T164" s="2" t="inlineStr"/>
+      <c r="U164" s="2" t="inlineStr"/>
+      <c r="V164" s="2" t="inlineStr"/>
+      <c r="W164" s="2" t="inlineStr"/>
+      <c r="X164" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y164" s="2" t="inlineStr"/>
+      <c r="Z164" s="2" t="inlineStr"/>
+      <c r="AA164" s="2" t="inlineStr"/>
+      <c r="AB164" s="2" t="inlineStr"/>
+      <c r="AC164" s="2" t="inlineStr"/>
+      <c r="AD164" s="2" t="inlineStr"/>
+      <c r="AE164" s="2" t="inlineStr"/>
+      <c r="AF164" s="2" t="inlineStr"/>
+      <c r="AG164" s="2" t="inlineStr"/>
+      <c r="AH164" s="2" t="inlineStr"/>
+      <c r="AI164" s="2" t="inlineStr"/>
+      <c r="AJ164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>8af45a0ee3d341f6</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>cc0cc1936c4cd2d0</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>401816405</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>0.568075</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr"/>
+      <c r="N165" s="2" t="inlineStr"/>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>0.6153846153846154</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="inlineStr">
+        <is>
+          <t>0.61194</t>
+        </is>
+      </c>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>-0.04730961538461542</t>
+        </is>
+      </c>
+      <c r="R165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:23:04.982467Z</t>
+        </is>
+      </c>
+      <c r="S165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T165" s="2" t="inlineStr"/>
+      <c r="U165" s="2" t="inlineStr"/>
+      <c r="V165" s="2" t="inlineStr"/>
+      <c r="W165" s="2" t="inlineStr"/>
+      <c r="X165" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y165" s="2" t="inlineStr"/>
+      <c r="Z165" s="2" t="inlineStr"/>
+      <c r="AA165" s="2" t="inlineStr"/>
+      <c r="AB165" s="2" t="inlineStr"/>
+      <c r="AC165" s="2" t="inlineStr"/>
+      <c r="AD165" s="2" t="inlineStr"/>
+      <c r="AE165" s="2" t="inlineStr"/>
+      <c r="AF165" s="2" t="inlineStr"/>
+      <c r="AG165" s="2" t="inlineStr"/>
+      <c r="AH165" s="2" t="inlineStr"/>
+      <c r="AI165" s="2" t="inlineStr"/>
+      <c r="AJ165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>d67460fa374d489f</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>5e4023ab8bd19cc5</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>401816404</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>0.585723</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr"/>
+      <c r="N166" s="2" t="inlineStr"/>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>0.587065</t>
+        </is>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>-0.004440934426229504</t>
+        </is>
+      </c>
+      <c r="R166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:23:08.454965Z</t>
+        </is>
+      </c>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="inlineStr"/>
+      <c r="U166" s="2" t="inlineStr"/>
+      <c r="V166" s="2" t="inlineStr"/>
+      <c r="W166" s="2" t="inlineStr"/>
+      <c r="X166" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y166" s="2" t="inlineStr"/>
+      <c r="Z166" s="2" t="inlineStr"/>
+      <c r="AA166" s="2" t="inlineStr"/>
+      <c r="AB166" s="2" t="inlineStr"/>
+      <c r="AC166" s="2" t="inlineStr"/>
+      <c r="AD166" s="2" t="inlineStr"/>
+      <c r="AE166" s="2" t="inlineStr"/>
+      <c r="AF166" s="2" t="inlineStr"/>
+      <c r="AG166" s="2" t="inlineStr"/>
+      <c r="AH166" s="2" t="inlineStr"/>
+      <c r="AI166" s="2" t="inlineStr"/>
+      <c r="AJ166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>e3b61d36d39249d7</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>b747944f91650fd4</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>401816401</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>0.5761</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr"/>
+      <c r="N167" s="2" t="inlineStr"/>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>0.5348837209302326</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="inlineStr">
+        <is>
+          <t>0.532338</t>
+        </is>
+      </c>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>0.041216279069767325</t>
+        </is>
+      </c>
+      <c r="R167" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:23:09.418660Z</t>
+        </is>
+      </c>
+      <c r="S167" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T167" s="2" t="inlineStr"/>
+      <c r="U167" s="2" t="inlineStr"/>
+      <c r="V167" s="2" t="inlineStr"/>
+      <c r="W167" s="2" t="inlineStr"/>
+      <c r="X167" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y167" s="2" t="inlineStr"/>
+      <c r="Z167" s="2" t="inlineStr"/>
+      <c r="AA167" s="2" t="inlineStr"/>
+      <c r="AB167" s="2" t="inlineStr"/>
+      <c r="AC167" s="2" t="inlineStr"/>
+      <c r="AD167" s="2" t="inlineStr"/>
+      <c r="AE167" s="2" t="inlineStr"/>
+      <c r="AF167" s="2" t="inlineStr"/>
+      <c r="AG167" s="2" t="inlineStr"/>
+      <c r="AH167" s="2" t="inlineStr"/>
+      <c r="AI167" s="2" t="inlineStr"/>
+      <c r="AJ167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>4eb8811b02264f66</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>bb6f41cb5975b5bb</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>401816402</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr"/>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>0.59089</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr"/>
+      <c r="N168" s="2" t="inlineStr"/>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>0.5454545454545454</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="inlineStr">
+        <is>
+          <t>0.542289</t>
+        </is>
+      </c>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>0.04543545454545461</t>
+        </is>
+      </c>
+      <c r="R168" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:23:10.543433Z</t>
+        </is>
+      </c>
+      <c r="S168" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="inlineStr"/>
+      <c r="U168" s="2" t="inlineStr"/>
+      <c r="V168" s="2" t="inlineStr"/>
+      <c r="W168" s="2" t="inlineStr"/>
+      <c r="X168" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y168" s="2" t="inlineStr"/>
+      <c r="Z168" s="2" t="inlineStr"/>
+      <c r="AA168" s="2" t="inlineStr"/>
+      <c r="AB168" s="2" t="inlineStr"/>
+      <c r="AC168" s="2" t="inlineStr"/>
+      <c r="AD168" s="2" t="inlineStr"/>
+      <c r="AE168" s="2" t="inlineStr"/>
+      <c r="AF168" s="2" t="inlineStr"/>
+      <c r="AG168" s="2" t="inlineStr"/>
+      <c r="AH168" s="2" t="inlineStr"/>
+      <c r="AI168" s="2" t="inlineStr"/>
+      <c r="AJ168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>eb6a95c3c0b14e81</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>23aa584b6028ab97</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>401816408</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>0.615508</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr"/>
+      <c r="N169" s="2" t="inlineStr"/>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="inlineStr">
+        <is>
+          <t>0.547264</t>
+        </is>
+      </c>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>0.06595845045045057</t>
+        </is>
+      </c>
+      <c r="R169" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:23:11.123662Z</t>
+        </is>
+      </c>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="inlineStr"/>
+      <c r="U169" s="2" t="inlineStr"/>
+      <c r="V169" s="2" t="inlineStr"/>
+      <c r="W169" s="2" t="inlineStr"/>
+      <c r="X169" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y169" s="2" t="inlineStr"/>
+      <c r="Z169" s="2" t="inlineStr"/>
+      <c r="AA169" s="2" t="inlineStr"/>
+      <c r="AB169" s="2" t="inlineStr"/>
+      <c r="AC169" s="2" t="inlineStr"/>
+      <c r="AD169" s="2" t="inlineStr"/>
+      <c r="AE169" s="2" t="inlineStr"/>
+      <c r="AF169" s="2" t="inlineStr"/>
+      <c r="AG169" s="2" t="inlineStr"/>
+      <c r="AH169" s="2" t="inlineStr"/>
+      <c r="AI169" s="2" t="inlineStr"/>
+      <c r="AJ169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>7953f0f5ec1d40ef</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>f8ae77f69b137e22</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>401816407</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>0.525121</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr"/>
+      <c r="N170" s="2" t="inlineStr"/>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="inlineStr">
+        <is>
+          <t>0.514851</t>
+        </is>
+      </c>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>0.0058902307692307865</t>
+        </is>
+      </c>
+      <c r="R170" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:23:12.053164Z</t>
+        </is>
+      </c>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="inlineStr"/>
+      <c r="U170" s="2" t="inlineStr"/>
+      <c r="V170" s="2" t="inlineStr"/>
+      <c r="W170" s="2" t="inlineStr"/>
+      <c r="X170" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y170" s="2" t="inlineStr"/>
+      <c r="Z170" s="2" t="inlineStr"/>
+      <c r="AA170" s="2" t="inlineStr"/>
+      <c r="AB170" s="2" t="inlineStr"/>
+      <c r="AC170" s="2" t="inlineStr"/>
+      <c r="AD170" s="2" t="inlineStr"/>
+      <c r="AE170" s="2" t="inlineStr"/>
+      <c r="AF170" s="2" t="inlineStr"/>
+      <c r="AG170" s="2" t="inlineStr"/>
+      <c r="AH170" s="2" t="inlineStr"/>
+      <c r="AI170" s="2" t="inlineStr"/>
+      <c r="AJ170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>ebcb9060146c490b</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>1869d7c91b8ee576</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>401816412</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>0.550053</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr"/>
+      <c r="N171" s="2" t="inlineStr"/>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P171" s="2" t="inlineStr">
+        <is>
+          <t>0.577114</t>
+        </is>
+      </c>
+      <c r="Q171" s="2" t="inlineStr">
+        <is>
+          <t>-0.029778932773109168</t>
+        </is>
+      </c>
+      <c r="R171" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:23:13.112032Z</t>
+        </is>
+      </c>
+      <c r="S171" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T171" s="2" t="inlineStr"/>
+      <c r="U171" s="2" t="inlineStr"/>
+      <c r="V171" s="2" t="inlineStr"/>
+      <c r="W171" s="2" t="inlineStr"/>
+      <c r="X171" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y171" s="2" t="inlineStr"/>
+      <c r="Z171" s="2" t="inlineStr"/>
+      <c r="AA171" s="2" t="inlineStr"/>
+      <c r="AB171" s="2" t="inlineStr"/>
+      <c r="AC171" s="2" t="inlineStr"/>
+      <c r="AD171" s="2" t="inlineStr"/>
+      <c r="AE171" s="2" t="inlineStr"/>
+      <c r="AF171" s="2" t="inlineStr"/>
+      <c r="AG171" s="2" t="inlineStr"/>
+      <c r="AH171" s="2" t="inlineStr"/>
+      <c r="AI171" s="2" t="inlineStr"/>
+      <c r="AJ171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>3d1061506ea748d0</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>1245bd5bb2d9bde3</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>401816413</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>0.509506</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr"/>
+      <c r="N172" s="2" t="inlineStr"/>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="inlineStr">
+        <is>
+          <t>0.517413</t>
+        </is>
+      </c>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>-0.009724769230769148</t>
+        </is>
+      </c>
+      <c r="R172" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:23:14.088657Z</t>
+        </is>
+      </c>
+      <c r="S172" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="inlineStr"/>
+      <c r="U172" s="2" t="inlineStr"/>
+      <c r="V172" s="2" t="inlineStr"/>
+      <c r="W172" s="2" t="inlineStr"/>
+      <c r="X172" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y172" s="2" t="inlineStr"/>
+      <c r="Z172" s="2" t="inlineStr"/>
+      <c r="AA172" s="2" t="inlineStr"/>
+      <c r="AB172" s="2" t="inlineStr"/>
+      <c r="AC172" s="2" t="inlineStr"/>
+      <c r="AD172" s="2" t="inlineStr"/>
+      <c r="AE172" s="2" t="inlineStr"/>
+      <c r="AF172" s="2" t="inlineStr"/>
+      <c r="AG172" s="2" t="inlineStr"/>
+      <c r="AH172" s="2" t="inlineStr"/>
+      <c r="AI172" s="2" t="inlineStr"/>
+      <c r="AJ172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>fd63c963afec46e6</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>7363e92b2bdde372</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>401816410</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>0.543314</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr"/>
+      <c r="N173" s="2" t="inlineStr"/>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="inlineStr">
+        <is>
+          <t>0.606965</t>
+        </is>
+      </c>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>-0.06606100000000004</t>
+        </is>
+      </c>
+      <c r="R173" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:33:50.122845Z</t>
+        </is>
+      </c>
+      <c r="S173" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T173" s="2" t="inlineStr"/>
+      <c r="U173" s="2" t="inlineStr"/>
+      <c r="V173" s="2" t="inlineStr"/>
+      <c r="W173" s="2" t="inlineStr"/>
+      <c r="X173" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y173" s="2" t="inlineStr"/>
+      <c r="Z173" s="2" t="inlineStr"/>
+      <c r="AA173" s="2" t="inlineStr"/>
+      <c r="AB173" s="2" t="inlineStr"/>
+      <c r="AC173" s="2" t="inlineStr"/>
+      <c r="AD173" s="2" t="inlineStr"/>
+      <c r="AE173" s="2" t="inlineStr"/>
+      <c r="AF173" s="2" t="inlineStr"/>
+      <c r="AG173" s="2" t="inlineStr"/>
+      <c r="AH173" s="2" t="inlineStr"/>
+      <c r="AI173" s="2" t="inlineStr"/>
+      <c r="AJ173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>4ccca5830a3b456d</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>cd121ba990e73d6d</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>401816406</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>0.522292</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr"/>
+      <c r="N174" s="2" t="inlineStr"/>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>0.5348837209302326</t>
+        </is>
+      </c>
+      <c r="P174" s="2" t="inlineStr">
+        <is>
+          <t>0.532338</t>
+        </is>
+      </c>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>-0.012591720930232642</t>
+        </is>
+      </c>
+      <c r="R174" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:33:50.628303Z</t>
+        </is>
+      </c>
+      <c r="S174" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:20:00-0400</t>
+        </is>
+      </c>
+      <c r="T174" s="2" t="inlineStr"/>
+      <c r="U174" s="2" t="inlineStr"/>
+      <c r="V174" s="2" t="inlineStr"/>
+      <c r="W174" s="2" t="inlineStr"/>
+      <c r="X174" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y174" s="2" t="inlineStr"/>
+      <c r="Z174" s="2" t="inlineStr"/>
+      <c r="AA174" s="2" t="inlineStr"/>
+      <c r="AB174" s="2" t="inlineStr"/>
+      <c r="AC174" s="2" t="inlineStr"/>
+      <c r="AD174" s="2" t="inlineStr"/>
+      <c r="AE174" s="2" t="inlineStr"/>
+      <c r="AF174" s="2" t="inlineStr"/>
+      <c r="AG174" s="2" t="inlineStr"/>
+      <c r="AH174" s="2" t="inlineStr"/>
+      <c r="AI174" s="2" t="inlineStr"/>
+      <c r="AJ174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>f95526671c784f4c</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>b14707c8a9267bdd</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>401816409</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>0.585182</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr"/>
+      <c r="N175" s="2" t="inlineStr"/>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>0.6254681647940076</t>
+        </is>
+      </c>
+      <c r="P175" s="2" t="inlineStr">
+        <is>
+          <t>0.621891</t>
+        </is>
+      </c>
+      <c r="Q175" s="2" t="inlineStr">
+        <is>
+          <t>-0.040286164794007595</t>
+        </is>
+      </c>
+      <c r="R175" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:33:51.533440Z</t>
+        </is>
+      </c>
+      <c r="S175" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:35:00-0400</t>
+        </is>
+      </c>
+      <c r="T175" s="2" t="inlineStr"/>
+      <c r="U175" s="2" t="inlineStr"/>
+      <c r="V175" s="2" t="inlineStr"/>
+      <c r="W175" s="2" t="inlineStr"/>
+      <c r="X175" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y175" s="2" t="inlineStr"/>
+      <c r="Z175" s="2" t="inlineStr"/>
+      <c r="AA175" s="2" t="inlineStr"/>
+      <c r="AB175" s="2" t="inlineStr"/>
+      <c r="AC175" s="2" t="inlineStr"/>
+      <c r="AD175" s="2" t="inlineStr"/>
+      <c r="AE175" s="2" t="inlineStr"/>
+      <c r="AF175" s="2" t="inlineStr"/>
+      <c r="AG175" s="2" t="inlineStr"/>
+      <c r="AH175" s="2" t="inlineStr"/>
+      <c r="AI175" s="2" t="inlineStr"/>
+      <c r="AJ175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>e1f3376410964fb9</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>afbdfea2d660f7f9</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>401816411</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>0.651419</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr"/>
+      <c r="N176" s="2" t="inlineStr"/>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>0.5951417004048584</t>
+        </is>
+      </c>
+      <c r="P176" s="2" t="inlineStr">
+        <is>
+          <t>0.59204</t>
+        </is>
+      </c>
+      <c r="Q176" s="2" t="inlineStr">
+        <is>
+          <t>0.056277299595141606</t>
+        </is>
+      </c>
+      <c r="R176" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:33:52.558033Z</t>
+        </is>
+      </c>
+      <c r="S176" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T15:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T176" s="2" t="inlineStr"/>
+      <c r="U176" s="2" t="inlineStr"/>
+      <c r="V176" s="2" t="inlineStr"/>
+      <c r="W176" s="2" t="inlineStr"/>
+      <c r="X176" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y176" s="2" t="inlineStr"/>
+      <c r="Z176" s="2" t="inlineStr"/>
+      <c r="AA176" s="2" t="inlineStr"/>
+      <c r="AB176" s="2" t="inlineStr"/>
+      <c r="AC176" s="2" t="inlineStr"/>
+      <c r="AD176" s="2" t="inlineStr"/>
+      <c r="AE176" s="2" t="inlineStr"/>
+      <c r="AF176" s="2" t="inlineStr"/>
+      <c r="AG176" s="2" t="inlineStr"/>
+      <c r="AH176" s="2" t="inlineStr"/>
+      <c r="AI176" s="2" t="inlineStr"/>
+      <c r="AJ176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>25ec38afa8cf41c5</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>0c5ef877e6b12160</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>401816399</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>0.620283</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr"/>
+      <c r="N177" s="2" t="inlineStr"/>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>0.5652173913043479</t>
+        </is>
+      </c>
+      <c r="P177" s="2" t="inlineStr">
+        <is>
+          <t>0.562189</t>
+        </is>
+      </c>
+      <c r="Q177" s="2" t="inlineStr">
+        <is>
+          <t>0.055065608695652135</t>
+        </is>
+      </c>
+      <c r="R177" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:33:53.451157Z</t>
+        </is>
+      </c>
+      <c r="S177" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:35:00-0400</t>
+        </is>
+      </c>
+      <c r="T177" s="2" t="inlineStr"/>
+      <c r="U177" s="2" t="inlineStr"/>
+      <c r="V177" s="2" t="inlineStr"/>
+      <c r="W177" s="2" t="inlineStr"/>
+      <c r="X177" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y177" s="2" t="inlineStr"/>
+      <c r="Z177" s="2" t="inlineStr"/>
+      <c r="AA177" s="2" t="inlineStr"/>
+      <c r="AB177" s="2" t="inlineStr"/>
+      <c r="AC177" s="2" t="inlineStr"/>
+      <c r="AD177" s="2" t="inlineStr"/>
+      <c r="AE177" s="2" t="inlineStr"/>
+      <c r="AF177" s="2" t="inlineStr"/>
+      <c r="AG177" s="2" t="inlineStr"/>
+      <c r="AH177" s="2" t="inlineStr"/>
+      <c r="AI177" s="2" t="inlineStr"/>
+      <c r="AJ177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>15b3faab042149c2</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>117cc3945a0a3429</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>401816400</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>0.531988</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr"/>
+      <c r="N178" s="2" t="inlineStr"/>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P178" s="2" t="inlineStr">
+        <is>
+          <t>0.557214</t>
+        </is>
+      </c>
+      <c r="Q178" s="2" t="inlineStr">
+        <is>
+          <t>-0.02748336563876652</t>
+        </is>
+      </c>
+      <c r="R178" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:33:56.201811Z</t>
+        </is>
+      </c>
+      <c r="S178" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T178" s="2" t="inlineStr"/>
+      <c r="U178" s="2" t="inlineStr"/>
+      <c r="V178" s="2" t="inlineStr"/>
+      <c r="W178" s="2" t="inlineStr"/>
+      <c r="X178" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y178" s="2" t="inlineStr"/>
+      <c r="Z178" s="2" t="inlineStr"/>
+      <c r="AA178" s="2" t="inlineStr"/>
+      <c r="AB178" s="2" t="inlineStr"/>
+      <c r="AC178" s="2" t="inlineStr"/>
+      <c r="AD178" s="2" t="inlineStr"/>
+      <c r="AE178" s="2" t="inlineStr"/>
+      <c r="AF178" s="2" t="inlineStr"/>
+      <c r="AG178" s="2" t="inlineStr"/>
+      <c r="AH178" s="2" t="inlineStr"/>
+      <c r="AI178" s="2" t="inlineStr"/>
+      <c r="AJ178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>4e7bf43899a74f19</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>e56570441b5f5cf2</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>401816403</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>0.570001</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr"/>
+      <c r="N179" s="2" t="inlineStr"/>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>0.4854368932038835</t>
+        </is>
+      </c>
+      <c r="P179" s="2" t="inlineStr">
+        <is>
+          <t>0.482587</t>
+        </is>
+      </c>
+      <c r="Q179" s="2" t="inlineStr">
+        <is>
+          <t>0.08456410679611648</t>
+        </is>
+      </c>
+      <c r="R179" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:33:55.141566Z</t>
+        </is>
+      </c>
+      <c r="S179" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T179" s="2" t="inlineStr"/>
+      <c r="U179" s="2" t="inlineStr"/>
+      <c r="V179" s="2" t="inlineStr"/>
+      <c r="W179" s="2" t="inlineStr"/>
+      <c r="X179" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y179" s="2" t="inlineStr"/>
+      <c r="Z179" s="2" t="inlineStr"/>
+      <c r="AA179" s="2" t="inlineStr"/>
+      <c r="AB179" s="2" t="inlineStr"/>
+      <c r="AC179" s="2" t="inlineStr"/>
+      <c r="AD179" s="2" t="inlineStr"/>
+      <c r="AE179" s="2" t="inlineStr"/>
+      <c r="AF179" s="2" t="inlineStr"/>
+      <c r="AG179" s="2" t="inlineStr"/>
+      <c r="AH179" s="2" t="inlineStr"/>
+      <c r="AI179" s="2" t="inlineStr"/>
+      <c r="AJ179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>9361e6cd2d2d4aa7</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>cc0cc1936c4cd2d0</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>401816405</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>0.568075</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr"/>
+      <c r="N180" s="2" t="inlineStr"/>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>0.6153846153846154</t>
+        </is>
+      </c>
+      <c r="P180" s="2" t="inlineStr">
+        <is>
+          <t>0.61194</t>
+        </is>
+      </c>
+      <c r="Q180" s="2" t="inlineStr">
+        <is>
+          <t>-0.04730961538461542</t>
+        </is>
+      </c>
+      <c r="R180" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:33:54.460834Z</t>
+        </is>
+      </c>
+      <c r="S180" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T180" s="2" t="inlineStr"/>
+      <c r="U180" s="2" t="inlineStr"/>
+      <c r="V180" s="2" t="inlineStr"/>
+      <c r="W180" s="2" t="inlineStr"/>
+      <c r="X180" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y180" s="2" t="inlineStr"/>
+      <c r="Z180" s="2" t="inlineStr"/>
+      <c r="AA180" s="2" t="inlineStr"/>
+      <c r="AB180" s="2" t="inlineStr"/>
+      <c r="AC180" s="2" t="inlineStr"/>
+      <c r="AD180" s="2" t="inlineStr"/>
+      <c r="AE180" s="2" t="inlineStr"/>
+      <c r="AF180" s="2" t="inlineStr"/>
+      <c r="AG180" s="2" t="inlineStr"/>
+      <c r="AH180" s="2" t="inlineStr"/>
+      <c r="AI180" s="2" t="inlineStr"/>
+      <c r="AJ180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>563b007a1fe84f4f</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>5e4023ab8bd19cc5</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>401816404</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>0.585723</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr"/>
+      <c r="N181" s="2" t="inlineStr"/>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P181" s="2" t="inlineStr">
+        <is>
+          <t>0.587065</t>
+        </is>
+      </c>
+      <c r="Q181" s="2" t="inlineStr">
+        <is>
+          <t>-0.004440934426229504</t>
+        </is>
+      </c>
+      <c r="R181" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:33:57.037353Z</t>
+        </is>
+      </c>
+      <c r="S181" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T181" s="2" t="inlineStr"/>
+      <c r="U181" s="2" t="inlineStr"/>
+      <c r="V181" s="2" t="inlineStr"/>
+      <c r="W181" s="2" t="inlineStr"/>
+      <c r="X181" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y181" s="2" t="inlineStr"/>
+      <c r="Z181" s="2" t="inlineStr"/>
+      <c r="AA181" s="2" t="inlineStr"/>
+      <c r="AB181" s="2" t="inlineStr"/>
+      <c r="AC181" s="2" t="inlineStr"/>
+      <c r="AD181" s="2" t="inlineStr"/>
+      <c r="AE181" s="2" t="inlineStr"/>
+      <c r="AF181" s="2" t="inlineStr"/>
+      <c r="AG181" s="2" t="inlineStr"/>
+      <c r="AH181" s="2" t="inlineStr"/>
+      <c r="AI181" s="2" t="inlineStr"/>
+      <c r="AJ181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>7fa39212003741d1</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>b747944f91650fd4</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>401816401</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>0.5761</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr"/>
+      <c r="N182" s="2" t="inlineStr"/>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>0.5348837209302326</t>
+        </is>
+      </c>
+      <c r="P182" s="2" t="inlineStr">
+        <is>
+          <t>0.532338</t>
+        </is>
+      </c>
+      <c r="Q182" s="2" t="inlineStr">
+        <is>
+          <t>0.041216279069767325</t>
+        </is>
+      </c>
+      <c r="R182" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:33:57.825385Z</t>
+        </is>
+      </c>
+      <c r="S182" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T182" s="2" t="inlineStr"/>
+      <c r="U182" s="2" t="inlineStr"/>
+      <c r="V182" s="2" t="inlineStr"/>
+      <c r="W182" s="2" t="inlineStr"/>
+      <c r="X182" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y182" s="2" t="inlineStr"/>
+      <c r="Z182" s="2" t="inlineStr"/>
+      <c r="AA182" s="2" t="inlineStr"/>
+      <c r="AB182" s="2" t="inlineStr"/>
+      <c r="AC182" s="2" t="inlineStr"/>
+      <c r="AD182" s="2" t="inlineStr"/>
+      <c r="AE182" s="2" t="inlineStr"/>
+      <c r="AF182" s="2" t="inlineStr"/>
+      <c r="AG182" s="2" t="inlineStr"/>
+      <c r="AH182" s="2" t="inlineStr"/>
+      <c r="AI182" s="2" t="inlineStr"/>
+      <c r="AJ182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>70f5b69f92b7401f</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>bb6f41cb5975b5bb</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>401816402</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>0.59089</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr"/>
+      <c r="N183" s="2" t="inlineStr"/>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>0.5454545454545454</t>
+        </is>
+      </c>
+      <c r="P183" s="2" t="inlineStr">
+        <is>
+          <t>0.542289</t>
+        </is>
+      </c>
+      <c r="Q183" s="2" t="inlineStr">
+        <is>
+          <t>0.04543545454545461</t>
+        </is>
+      </c>
+      <c r="R183" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:33:58.789026Z</t>
+        </is>
+      </c>
+      <c r="S183" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T183" s="2" t="inlineStr"/>
+      <c r="U183" s="2" t="inlineStr"/>
+      <c r="V183" s="2" t="inlineStr"/>
+      <c r="W183" s="2" t="inlineStr"/>
+      <c r="X183" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y183" s="2" t="inlineStr"/>
+      <c r="Z183" s="2" t="inlineStr"/>
+      <c r="AA183" s="2" t="inlineStr"/>
+      <c r="AB183" s="2" t="inlineStr"/>
+      <c r="AC183" s="2" t="inlineStr"/>
+      <c r="AD183" s="2" t="inlineStr"/>
+      <c r="AE183" s="2" t="inlineStr"/>
+      <c r="AF183" s="2" t="inlineStr"/>
+      <c r="AG183" s="2" t="inlineStr"/>
+      <c r="AH183" s="2" t="inlineStr"/>
+      <c r="AI183" s="2" t="inlineStr"/>
+      <c r="AJ183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>46933480cb254727</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>23aa584b6028ab97</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>401816408</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>0.615508</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr"/>
+      <c r="N184" s="2" t="inlineStr"/>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P184" s="2" t="inlineStr">
+        <is>
+          <t>0.547264</t>
+        </is>
+      </c>
+      <c r="Q184" s="2" t="inlineStr">
+        <is>
+          <t>0.06595845045045057</t>
+        </is>
+      </c>
+      <c r="R184" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:33:59.358107Z</t>
+        </is>
+      </c>
+      <c r="S184" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="T184" s="2" t="inlineStr"/>
+      <c r="U184" s="2" t="inlineStr"/>
+      <c r="V184" s="2" t="inlineStr"/>
+      <c r="W184" s="2" t="inlineStr"/>
+      <c r="X184" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y184" s="2" t="inlineStr"/>
+      <c r="Z184" s="2" t="inlineStr"/>
+      <c r="AA184" s="2" t="inlineStr"/>
+      <c r="AB184" s="2" t="inlineStr"/>
+      <c r="AC184" s="2" t="inlineStr"/>
+      <c r="AD184" s="2" t="inlineStr"/>
+      <c r="AE184" s="2" t="inlineStr"/>
+      <c r="AF184" s="2" t="inlineStr"/>
+      <c r="AG184" s="2" t="inlineStr"/>
+      <c r="AH184" s="2" t="inlineStr"/>
+      <c r="AI184" s="2" t="inlineStr"/>
+      <c r="AJ184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>d0ed917e58d344ad</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>f8ae77f69b137e22</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>401816407</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>0.525121</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="inlineStr"/>
+      <c r="N185" s="2" t="inlineStr"/>
+      <c r="O185" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P185" s="2" t="inlineStr">
+        <is>
+          <t>0.514851</t>
+        </is>
+      </c>
+      <c r="Q185" s="2" t="inlineStr">
+        <is>
+          <t>0.0058902307692307865</t>
+        </is>
+      </c>
+      <c r="R185" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:00.271972Z</t>
+        </is>
+      </c>
+      <c r="S185" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T185" s="2" t="inlineStr"/>
+      <c r="U185" s="2" t="inlineStr"/>
+      <c r="V185" s="2" t="inlineStr"/>
+      <c r="W185" s="2" t="inlineStr"/>
+      <c r="X185" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y185" s="2" t="inlineStr"/>
+      <c r="Z185" s="2" t="inlineStr"/>
+      <c r="AA185" s="2" t="inlineStr"/>
+      <c r="AB185" s="2" t="inlineStr"/>
+      <c r="AC185" s="2" t="inlineStr"/>
+      <c r="AD185" s="2" t="inlineStr"/>
+      <c r="AE185" s="2" t="inlineStr"/>
+      <c r="AF185" s="2" t="inlineStr"/>
+      <c r="AG185" s="2" t="inlineStr"/>
+      <c r="AH185" s="2" t="inlineStr"/>
+      <c r="AI185" s="2" t="inlineStr"/>
+      <c r="AJ185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>5fab410c78f0488b</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>1869d7c91b8ee576</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>401816412</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>0.550053</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr"/>
+      <c r="N186" s="2" t="inlineStr"/>
+      <c r="O186" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P186" s="2" t="inlineStr">
+        <is>
+          <t>0.577114</t>
+        </is>
+      </c>
+      <c r="Q186" s="2" t="inlineStr">
+        <is>
+          <t>-0.029778932773109168</t>
+        </is>
+      </c>
+      <c r="R186" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:01.074140Z</t>
+        </is>
+      </c>
+      <c r="S186" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T186" s="2" t="inlineStr"/>
+      <c r="U186" s="2" t="inlineStr"/>
+      <c r="V186" s="2" t="inlineStr"/>
+      <c r="W186" s="2" t="inlineStr"/>
+      <c r="X186" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y186" s="2" t="inlineStr"/>
+      <c r="Z186" s="2" t="inlineStr"/>
+      <c r="AA186" s="2" t="inlineStr"/>
+      <c r="AB186" s="2" t="inlineStr"/>
+      <c r="AC186" s="2" t="inlineStr"/>
+      <c r="AD186" s="2" t="inlineStr"/>
+      <c r="AE186" s="2" t="inlineStr"/>
+      <c r="AF186" s="2" t="inlineStr"/>
+      <c r="AG186" s="2" t="inlineStr"/>
+      <c r="AH186" s="2" t="inlineStr"/>
+      <c r="AI186" s="2" t="inlineStr"/>
+      <c r="AJ186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>149ecd3eee4b4310</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>f27ad71f21952264</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>401816413</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>0.512293</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="inlineStr"/>
+      <c r="N187" s="2" t="inlineStr"/>
+      <c r="O187" s="2" t="inlineStr">
+        <is>
+          <t>0.5260663507109005</t>
+        </is>
+      </c>
+      <c r="P187" s="2" t="inlineStr">
+        <is>
+          <t>0.522388</t>
+        </is>
+      </c>
+      <c r="Q187" s="2" t="inlineStr">
+        <is>
+          <t>-0.013773350710900467</t>
+        </is>
+      </c>
+      <c r="R187" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:01.895512Z</t>
+        </is>
+      </c>
+      <c r="S187" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T187" s="2" t="inlineStr"/>
+      <c r="U187" s="2" t="inlineStr"/>
+      <c r="V187" s="2" t="inlineStr"/>
+      <c r="W187" s="2" t="inlineStr"/>
+      <c r="X187" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y187" s="2" t="inlineStr"/>
+      <c r="Z187" s="2" t="inlineStr"/>
+      <c r="AA187" s="2" t="inlineStr"/>
+      <c r="AB187" s="2" t="inlineStr"/>
+      <c r="AC187" s="2" t="inlineStr"/>
+      <c r="AD187" s="2" t="inlineStr"/>
+      <c r="AE187" s="2" t="inlineStr"/>
+      <c r="AF187" s="2" t="inlineStr"/>
+      <c r="AG187" s="2" t="inlineStr"/>
+      <c r="AH187" s="2" t="inlineStr"/>
+      <c r="AI187" s="2" t="inlineStr"/>
+      <c r="AJ187" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ115"/>
+  <autoFilter ref="A1:AJ187"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/flat/model_ledgers/mlb-moneyline-elo-trend-lr.xlsx
+++ b/data/flat/model_ledgers/mlb-moneyline-elo-trend-lr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$232</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ187"/>
+  <dimension ref="A1:AJ232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -20568,8 +20568,4778 @@
       <c r="AI187" s="2" t="inlineStr"/>
       <c r="AJ187" s="2" t="inlineStr"/>
     </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>d2d6b0b6bf6d4ad6</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>7363e92b2bdde372</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>401816410</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K188" s="2" t="inlineStr"/>
+      <c r="L188" s="2" t="inlineStr">
+        <is>
+          <t>0.543314</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="inlineStr"/>
+      <c r="N188" s="2" t="inlineStr"/>
+      <c r="O188" s="2" t="inlineStr">
+        <is>
+          <t>0.6254681647940076</t>
+        </is>
+      </c>
+      <c r="P188" s="2" t="inlineStr">
+        <is>
+          <t>0.621891</t>
+        </is>
+      </c>
+      <c r="Q188" s="2" t="inlineStr">
+        <is>
+          <t>-0.08215416479400761</t>
+        </is>
+      </c>
+      <c r="R188" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:18:52.873175Z</t>
+        </is>
+      </c>
+      <c r="S188" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T188" s="2" t="inlineStr"/>
+      <c r="U188" s="2" t="inlineStr"/>
+      <c r="V188" s="2" t="inlineStr"/>
+      <c r="W188" s="2" t="inlineStr"/>
+      <c r="X188" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y188" s="2" t="inlineStr"/>
+      <c r="Z188" s="2" t="inlineStr"/>
+      <c r="AA188" s="2" t="inlineStr"/>
+      <c r="AB188" s="2" t="inlineStr"/>
+      <c r="AC188" s="2" t="inlineStr"/>
+      <c r="AD188" s="2" t="inlineStr"/>
+      <c r="AE188" s="2" t="inlineStr"/>
+      <c r="AF188" s="2" t="inlineStr"/>
+      <c r="AG188" s="2" t="inlineStr"/>
+      <c r="AH188" s="2" t="inlineStr"/>
+      <c r="AI188" s="2" t="inlineStr"/>
+      <c r="AJ188" s="2" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>4b6d0247f6d24bcd</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>757a748feb566946</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>401816406</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K189" s="2" t="inlineStr"/>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t>0.52224</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="inlineStr"/>
+      <c r="N189" s="2" t="inlineStr"/>
+      <c r="O189" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P189" s="2" t="inlineStr">
+        <is>
+          <t>0.527363</t>
+        </is>
+      </c>
+      <c r="Q189" s="2" t="inlineStr">
+        <is>
+          <t>-0.008276431924882588</t>
+        </is>
+      </c>
+      <c r="R189" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:18:53.447508Z</t>
+        </is>
+      </c>
+      <c r="S189" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:20:00-0400</t>
+        </is>
+      </c>
+      <c r="T189" s="2" t="inlineStr"/>
+      <c r="U189" s="2" t="inlineStr"/>
+      <c r="V189" s="2" t="inlineStr"/>
+      <c r="W189" s="2" t="inlineStr"/>
+      <c r="X189" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y189" s="2" t="inlineStr"/>
+      <c r="Z189" s="2" t="inlineStr"/>
+      <c r="AA189" s="2" t="inlineStr"/>
+      <c r="AB189" s="2" t="inlineStr"/>
+      <c r="AC189" s="2" t="inlineStr"/>
+      <c r="AD189" s="2" t="inlineStr"/>
+      <c r="AE189" s="2" t="inlineStr"/>
+      <c r="AF189" s="2" t="inlineStr"/>
+      <c r="AG189" s="2" t="inlineStr"/>
+      <c r="AH189" s="2" t="inlineStr"/>
+      <c r="AI189" s="2" t="inlineStr"/>
+      <c r="AJ189" s="2" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>b2d592e1318b44dd</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>b14707c8a9267bdd</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>401816409</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="2" t="inlineStr">
+        <is>
+          <t>0.585182</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="inlineStr"/>
+      <c r="N190" s="2" t="inlineStr"/>
+      <c r="O190" s="2" t="inlineStr">
+        <is>
+          <t>0.6254681647940076</t>
+        </is>
+      </c>
+      <c r="P190" s="2" t="inlineStr">
+        <is>
+          <t>0.621891</t>
+        </is>
+      </c>
+      <c r="Q190" s="2" t="inlineStr">
+        <is>
+          <t>-0.040286164794007595</t>
+        </is>
+      </c>
+      <c r="R190" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:18:53.936319Z</t>
+        </is>
+      </c>
+      <c r="S190" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:35:00-0400</t>
+        </is>
+      </c>
+      <c r="T190" s="2" t="inlineStr"/>
+      <c r="U190" s="2" t="inlineStr"/>
+      <c r="V190" s="2" t="inlineStr"/>
+      <c r="W190" s="2" t="inlineStr"/>
+      <c r="X190" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y190" s="2" t="inlineStr"/>
+      <c r="Z190" s="2" t="inlineStr"/>
+      <c r="AA190" s="2" t="inlineStr"/>
+      <c r="AB190" s="2" t="inlineStr"/>
+      <c r="AC190" s="2" t="inlineStr"/>
+      <c r="AD190" s="2" t="inlineStr"/>
+      <c r="AE190" s="2" t="inlineStr"/>
+      <c r="AF190" s="2" t="inlineStr"/>
+      <c r="AG190" s="2" t="inlineStr"/>
+      <c r="AH190" s="2" t="inlineStr"/>
+      <c r="AI190" s="2" t="inlineStr"/>
+      <c r="AJ190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>46d363d7483e43e7</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>bed62784e0e2155a</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>401816411</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="2" t="inlineStr">
+        <is>
+          <t>0.651412</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="inlineStr"/>
+      <c r="N191" s="2" t="inlineStr"/>
+      <c r="O191" s="2" t="inlineStr">
+        <is>
+          <t>0.6047430830039526</t>
+        </is>
+      </c>
+      <c r="P191" s="2" t="inlineStr">
+        <is>
+          <t>0.60199</t>
+        </is>
+      </c>
+      <c r="Q191" s="2" t="inlineStr">
+        <is>
+          <t>0.04666891699604736</t>
+        </is>
+      </c>
+      <c r="R191" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:18:54.391948Z</t>
+        </is>
+      </c>
+      <c r="S191" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T15:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T191" s="2" t="inlineStr"/>
+      <c r="U191" s="2" t="inlineStr"/>
+      <c r="V191" s="2" t="inlineStr"/>
+      <c r="W191" s="2" t="inlineStr"/>
+      <c r="X191" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y191" s="2" t="inlineStr"/>
+      <c r="Z191" s="2" t="inlineStr"/>
+      <c r="AA191" s="2" t="inlineStr"/>
+      <c r="AB191" s="2" t="inlineStr"/>
+      <c r="AC191" s="2" t="inlineStr"/>
+      <c r="AD191" s="2" t="inlineStr"/>
+      <c r="AE191" s="2" t="inlineStr"/>
+      <c r="AF191" s="2" t="inlineStr"/>
+      <c r="AG191" s="2" t="inlineStr"/>
+      <c r="AH191" s="2" t="inlineStr"/>
+      <c r="AI191" s="2" t="inlineStr"/>
+      <c r="AJ191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>2f2fdd0cb54b4f69</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>6cd4cf8afdec8c65</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>401816399</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>0.620423</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="inlineStr"/>
+      <c r="N192" s="2" t="inlineStr"/>
+      <c r="O192" s="2" t="inlineStr">
+        <is>
+          <t>0.5555555555555556</t>
+        </is>
+      </c>
+      <c r="P192" s="2" t="inlineStr">
+        <is>
+          <t>0.552239</t>
+        </is>
+      </c>
+      <c r="Q192" s="2" t="inlineStr">
+        <is>
+          <t>0.06486744444444437</t>
+        </is>
+      </c>
+      <c r="R192" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:18:54.918844Z</t>
+        </is>
+      </c>
+      <c r="S192" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:35:00-0400</t>
+        </is>
+      </c>
+      <c r="T192" s="2" t="inlineStr"/>
+      <c r="U192" s="2" t="inlineStr"/>
+      <c r="V192" s="2" t="inlineStr"/>
+      <c r="W192" s="2" t="inlineStr"/>
+      <c r="X192" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y192" s="2" t="inlineStr"/>
+      <c r="Z192" s="2" t="inlineStr"/>
+      <c r="AA192" s="2" t="inlineStr"/>
+      <c r="AB192" s="2" t="inlineStr"/>
+      <c r="AC192" s="2" t="inlineStr"/>
+      <c r="AD192" s="2" t="inlineStr"/>
+      <c r="AE192" s="2" t="inlineStr"/>
+      <c r="AF192" s="2" t="inlineStr"/>
+      <c r="AG192" s="2" t="inlineStr"/>
+      <c r="AH192" s="2" t="inlineStr"/>
+      <c r="AI192" s="2" t="inlineStr"/>
+      <c r="AJ192" s="2" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>d74978b1f7f848e4</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>38cc9b5478b87937</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>401816400</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="2" t="inlineStr">
+        <is>
+          <t>0.531973</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="inlineStr"/>
+      <c r="N193" s="2" t="inlineStr"/>
+      <c r="O193" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P193" s="2" t="inlineStr">
+        <is>
+          <t>0.557214</t>
+        </is>
+      </c>
+      <c r="Q193" s="2" t="inlineStr">
+        <is>
+          <t>-0.02749836563876651</t>
+        </is>
+      </c>
+      <c r="R193" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:18:56.327596Z</t>
+        </is>
+      </c>
+      <c r="S193" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T193" s="2" t="inlineStr"/>
+      <c r="U193" s="2" t="inlineStr"/>
+      <c r="V193" s="2" t="inlineStr"/>
+      <c r="W193" s="2" t="inlineStr"/>
+      <c r="X193" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y193" s="2" t="inlineStr"/>
+      <c r="Z193" s="2" t="inlineStr"/>
+      <c r="AA193" s="2" t="inlineStr"/>
+      <c r="AB193" s="2" t="inlineStr"/>
+      <c r="AC193" s="2" t="inlineStr"/>
+      <c r="AD193" s="2" t="inlineStr"/>
+      <c r="AE193" s="2" t="inlineStr"/>
+      <c r="AF193" s="2" t="inlineStr"/>
+      <c r="AG193" s="2" t="inlineStr"/>
+      <c r="AH193" s="2" t="inlineStr"/>
+      <c r="AI193" s="2" t="inlineStr"/>
+      <c r="AJ193" s="2" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>a333331f9d434d72</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>160edeaf9560617a</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>401816403</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t>0.570052</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="inlineStr"/>
+      <c r="N194" s="2" t="inlineStr"/>
+      <c r="O194" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P194" s="2" t="inlineStr">
+        <is>
+          <t>0.497512</t>
+        </is>
+      </c>
+      <c r="Q194" s="2" t="inlineStr">
+        <is>
+          <t>0.070052</t>
+        </is>
+      </c>
+      <c r="R194" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:18:55.718685Z</t>
+        </is>
+      </c>
+      <c r="S194" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T194" s="2" t="inlineStr"/>
+      <c r="U194" s="2" t="inlineStr"/>
+      <c r="V194" s="2" t="inlineStr"/>
+      <c r="W194" s="2" t="inlineStr"/>
+      <c r="X194" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y194" s="2" t="inlineStr"/>
+      <c r="Z194" s="2" t="inlineStr"/>
+      <c r="AA194" s="2" t="inlineStr"/>
+      <c r="AB194" s="2" t="inlineStr"/>
+      <c r="AC194" s="2" t="inlineStr"/>
+      <c r="AD194" s="2" t="inlineStr"/>
+      <c r="AE194" s="2" t="inlineStr"/>
+      <c r="AF194" s="2" t="inlineStr"/>
+      <c r="AG194" s="2" t="inlineStr"/>
+      <c r="AH194" s="2" t="inlineStr"/>
+      <c r="AI194" s="2" t="inlineStr"/>
+      <c r="AJ194" s="2" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>05f91fee065b4782</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>64c95b4d86889dd9</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>401816405</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K195" s="2" t="inlineStr"/>
+      <c r="L195" s="2" t="inlineStr">
+        <is>
+          <t>0.568185</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="inlineStr"/>
+      <c r="N195" s="2" t="inlineStr"/>
+      <c r="O195" s="2" t="inlineStr">
+        <is>
+          <t>0.6153846153846154</t>
+        </is>
+      </c>
+      <c r="P195" s="2" t="inlineStr">
+        <is>
+          <t>0.61194</t>
+        </is>
+      </c>
+      <c r="Q195" s="2" t="inlineStr">
+        <is>
+          <t>-0.04719961538461537</t>
+        </is>
+      </c>
+      <c r="R195" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:18:55.388206Z</t>
+        </is>
+      </c>
+      <c r="S195" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T195" s="2" t="inlineStr"/>
+      <c r="U195" s="2" t="inlineStr"/>
+      <c r="V195" s="2" t="inlineStr"/>
+      <c r="W195" s="2" t="inlineStr"/>
+      <c r="X195" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y195" s="2" t="inlineStr"/>
+      <c r="Z195" s="2" t="inlineStr"/>
+      <c r="AA195" s="2" t="inlineStr"/>
+      <c r="AB195" s="2" t="inlineStr"/>
+      <c r="AC195" s="2" t="inlineStr"/>
+      <c r="AD195" s="2" t="inlineStr"/>
+      <c r="AE195" s="2" t="inlineStr"/>
+      <c r="AF195" s="2" t="inlineStr"/>
+      <c r="AG195" s="2" t="inlineStr"/>
+      <c r="AH195" s="2" t="inlineStr"/>
+      <c r="AI195" s="2" t="inlineStr"/>
+      <c r="AJ195" s="2" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>5861e9a011ac42f4</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>a0beed6acc493629</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>401816404</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K196" s="2" t="inlineStr"/>
+      <c r="L196" s="2" t="inlineStr">
+        <is>
+          <t>0.585673</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="inlineStr"/>
+      <c r="N196" s="2" t="inlineStr"/>
+      <c r="O196" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P196" s="2" t="inlineStr">
+        <is>
+          <t>0.587065</t>
+        </is>
+      </c>
+      <c r="Q196" s="2" t="inlineStr">
+        <is>
+          <t>-0.004490934426229498</t>
+        </is>
+      </c>
+      <c r="R196" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:18:56.785071Z</t>
+        </is>
+      </c>
+      <c r="S196" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T196" s="2" t="inlineStr"/>
+      <c r="U196" s="2" t="inlineStr"/>
+      <c r="V196" s="2" t="inlineStr"/>
+      <c r="W196" s="2" t="inlineStr"/>
+      <c r="X196" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y196" s="2" t="inlineStr"/>
+      <c r="Z196" s="2" t="inlineStr"/>
+      <c r="AA196" s="2" t="inlineStr"/>
+      <c r="AB196" s="2" t="inlineStr"/>
+      <c r="AC196" s="2" t="inlineStr"/>
+      <c r="AD196" s="2" t="inlineStr"/>
+      <c r="AE196" s="2" t="inlineStr"/>
+      <c r="AF196" s="2" t="inlineStr"/>
+      <c r="AG196" s="2" t="inlineStr"/>
+      <c r="AH196" s="2" t="inlineStr"/>
+      <c r="AI196" s="2" t="inlineStr"/>
+      <c r="AJ196" s="2" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>cf864f6cf9544815</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>a30f963f12c48063</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>401816401</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K197" s="2" t="inlineStr"/>
+      <c r="L197" s="2" t="inlineStr">
+        <is>
+          <t>0.576304</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="inlineStr"/>
+      <c r="N197" s="2" t="inlineStr"/>
+      <c r="O197" s="2" t="inlineStr">
+        <is>
+          <t>0.5348837209302326</t>
+        </is>
+      </c>
+      <c r="P197" s="2" t="inlineStr">
+        <is>
+          <t>0.532338</t>
+        </is>
+      </c>
+      <c r="Q197" s="2" t="inlineStr">
+        <is>
+          <t>0.04142027906976742</t>
+        </is>
+      </c>
+      <c r="R197" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:18:57.294791Z</t>
+        </is>
+      </c>
+      <c r="S197" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T197" s="2" t="inlineStr"/>
+      <c r="U197" s="2" t="inlineStr"/>
+      <c r="V197" s="2" t="inlineStr"/>
+      <c r="W197" s="2" t="inlineStr"/>
+      <c r="X197" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y197" s="2" t="inlineStr"/>
+      <c r="Z197" s="2" t="inlineStr"/>
+      <c r="AA197" s="2" t="inlineStr"/>
+      <c r="AB197" s="2" t="inlineStr"/>
+      <c r="AC197" s="2" t="inlineStr"/>
+      <c r="AD197" s="2" t="inlineStr"/>
+      <c r="AE197" s="2" t="inlineStr"/>
+      <c r="AF197" s="2" t="inlineStr"/>
+      <c r="AG197" s="2" t="inlineStr"/>
+      <c r="AH197" s="2" t="inlineStr"/>
+      <c r="AI197" s="2" t="inlineStr"/>
+      <c r="AJ197" s="2" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>e4714a6056b2415c</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>14b4c447a56375f6</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>401816402</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K198" s="2" t="inlineStr"/>
+      <c r="L198" s="2" t="inlineStr">
+        <is>
+          <t>0.590631</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="inlineStr"/>
+      <c r="N198" s="2" t="inlineStr"/>
+      <c r="O198" s="2" t="inlineStr">
+        <is>
+          <t>0.5454545454545454</t>
+        </is>
+      </c>
+      <c r="P198" s="2" t="inlineStr">
+        <is>
+          <t>0.542289</t>
+        </is>
+      </c>
+      <c r="Q198" s="2" t="inlineStr">
+        <is>
+          <t>0.0451764545454546</t>
+        </is>
+      </c>
+      <c r="R198" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:18:57.738889Z</t>
+        </is>
+      </c>
+      <c r="S198" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T198" s="2" t="inlineStr"/>
+      <c r="U198" s="2" t="inlineStr"/>
+      <c r="V198" s="2" t="inlineStr"/>
+      <c r="W198" s="2" t="inlineStr"/>
+      <c r="X198" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y198" s="2" t="inlineStr"/>
+      <c r="Z198" s="2" t="inlineStr"/>
+      <c r="AA198" s="2" t="inlineStr"/>
+      <c r="AB198" s="2" t="inlineStr"/>
+      <c r="AC198" s="2" t="inlineStr"/>
+      <c r="AD198" s="2" t="inlineStr"/>
+      <c r="AE198" s="2" t="inlineStr"/>
+      <c r="AF198" s="2" t="inlineStr"/>
+      <c r="AG198" s="2" t="inlineStr"/>
+      <c r="AH198" s="2" t="inlineStr"/>
+      <c r="AI198" s="2" t="inlineStr"/>
+      <c r="AJ198" s="2" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>478d0441b8904f7a</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>23aa584b6028ab97</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>401816408</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K199" s="2" t="inlineStr"/>
+      <c r="L199" s="2" t="inlineStr">
+        <is>
+          <t>0.615508</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="inlineStr"/>
+      <c r="N199" s="2" t="inlineStr"/>
+      <c r="O199" s="2" t="inlineStr">
+        <is>
+          <t>0.5555555555555556</t>
+        </is>
+      </c>
+      <c r="P199" s="2" t="inlineStr">
+        <is>
+          <t>0.552239</t>
+        </is>
+      </c>
+      <c r="Q199" s="2" t="inlineStr">
+        <is>
+          <t>0.059952444444444475</t>
+        </is>
+      </c>
+      <c r="R199" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:18:58.222638Z</t>
+        </is>
+      </c>
+      <c r="S199" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="T199" s="2" t="inlineStr"/>
+      <c r="U199" s="2" t="inlineStr"/>
+      <c r="V199" s="2" t="inlineStr"/>
+      <c r="W199" s="2" t="inlineStr"/>
+      <c r="X199" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y199" s="2" t="inlineStr"/>
+      <c r="Z199" s="2" t="inlineStr"/>
+      <c r="AA199" s="2" t="inlineStr"/>
+      <c r="AB199" s="2" t="inlineStr"/>
+      <c r="AC199" s="2" t="inlineStr"/>
+      <c r="AD199" s="2" t="inlineStr"/>
+      <c r="AE199" s="2" t="inlineStr"/>
+      <c r="AF199" s="2" t="inlineStr"/>
+      <c r="AG199" s="2" t="inlineStr"/>
+      <c r="AH199" s="2" t="inlineStr"/>
+      <c r="AI199" s="2" t="inlineStr"/>
+      <c r="AJ199" s="2" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>777570d0e80540ec</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>5af634cf85e8d1da</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>401816407</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K200" s="2" t="inlineStr"/>
+      <c r="L200" s="2" t="inlineStr">
+        <is>
+          <t>0.524512</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="inlineStr"/>
+      <c r="N200" s="2" t="inlineStr"/>
+      <c r="O200" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P200" s="2" t="inlineStr">
+        <is>
+          <t>0.527363</t>
+        </is>
+      </c>
+      <c r="Q200" s="2" t="inlineStr">
+        <is>
+          <t>-0.006004431924882647</t>
+        </is>
+      </c>
+      <c r="R200" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:18:58.724467Z</t>
+        </is>
+      </c>
+      <c r="S200" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T200" s="2" t="inlineStr"/>
+      <c r="U200" s="2" t="inlineStr"/>
+      <c r="V200" s="2" t="inlineStr"/>
+      <c r="W200" s="2" t="inlineStr"/>
+      <c r="X200" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y200" s="2" t="inlineStr"/>
+      <c r="Z200" s="2" t="inlineStr"/>
+      <c r="AA200" s="2" t="inlineStr"/>
+      <c r="AB200" s="2" t="inlineStr"/>
+      <c r="AC200" s="2" t="inlineStr"/>
+      <c r="AD200" s="2" t="inlineStr"/>
+      <c r="AE200" s="2" t="inlineStr"/>
+      <c r="AF200" s="2" t="inlineStr"/>
+      <c r="AG200" s="2" t="inlineStr"/>
+      <c r="AH200" s="2" t="inlineStr"/>
+      <c r="AI200" s="2" t="inlineStr"/>
+      <c r="AJ200" s="2" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>9b41ea737df84810</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>1869d7c91b8ee576</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>401816412</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K201" s="2" t="inlineStr"/>
+      <c r="L201" s="2" t="inlineStr">
+        <is>
+          <t>0.550053</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="inlineStr"/>
+      <c r="N201" s="2" t="inlineStr"/>
+      <c r="O201" s="2" t="inlineStr">
+        <is>
+          <t>0.5850622406639003</t>
+        </is>
+      </c>
+      <c r="P201" s="2" t="inlineStr">
+        <is>
+          <t>0.58209</t>
+        </is>
+      </c>
+      <c r="Q201" s="2" t="inlineStr">
+        <is>
+          <t>-0.03500924066390032</t>
+        </is>
+      </c>
+      <c r="R201" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:18:59.231940Z</t>
+        </is>
+      </c>
+      <c r="S201" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T201" s="2" t="inlineStr"/>
+      <c r="U201" s="2" t="inlineStr"/>
+      <c r="V201" s="2" t="inlineStr"/>
+      <c r="W201" s="2" t="inlineStr"/>
+      <c r="X201" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y201" s="2" t="inlineStr"/>
+      <c r="Z201" s="2" t="inlineStr"/>
+      <c r="AA201" s="2" t="inlineStr"/>
+      <c r="AB201" s="2" t="inlineStr"/>
+      <c r="AC201" s="2" t="inlineStr"/>
+      <c r="AD201" s="2" t="inlineStr"/>
+      <c r="AE201" s="2" t="inlineStr"/>
+      <c r="AF201" s="2" t="inlineStr"/>
+      <c r="AG201" s="2" t="inlineStr"/>
+      <c r="AH201" s="2" t="inlineStr"/>
+      <c r="AI201" s="2" t="inlineStr"/>
+      <c r="AJ201" s="2" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>6b0a59ed319948d2</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>f27ad71f21952264</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>401816413</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K202" s="2" t="inlineStr"/>
+      <c r="L202" s="2" t="inlineStr">
+        <is>
+          <t>0.512293</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="inlineStr"/>
+      <c r="N202" s="2" t="inlineStr"/>
+      <c r="O202" s="2" t="inlineStr">
+        <is>
+          <t>0.5348837209302326</t>
+        </is>
+      </c>
+      <c r="P202" s="2" t="inlineStr">
+        <is>
+          <t>0.532338</t>
+        </is>
+      </c>
+      <c r="Q202" s="2" t="inlineStr">
+        <is>
+          <t>-0.02259072093023262</t>
+        </is>
+      </c>
+      <c r="R202" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:18:59.696395Z</t>
+        </is>
+      </c>
+      <c r="S202" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T202" s="2" t="inlineStr"/>
+      <c r="U202" s="2" t="inlineStr"/>
+      <c r="V202" s="2" t="inlineStr"/>
+      <c r="W202" s="2" t="inlineStr"/>
+      <c r="X202" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y202" s="2" t="inlineStr"/>
+      <c r="Z202" s="2" t="inlineStr"/>
+      <c r="AA202" s="2" t="inlineStr"/>
+      <c r="AB202" s="2" t="inlineStr"/>
+      <c r="AC202" s="2" t="inlineStr"/>
+      <c r="AD202" s="2" t="inlineStr"/>
+      <c r="AE202" s="2" t="inlineStr"/>
+      <c r="AF202" s="2" t="inlineStr"/>
+      <c r="AG202" s="2" t="inlineStr"/>
+      <c r="AH202" s="2" t="inlineStr"/>
+      <c r="AI202" s="2" t="inlineStr"/>
+      <c r="AJ202" s="2" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>9e9198f202904500</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>7363e92b2bdde372</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>401816410</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K203" s="2" t="inlineStr"/>
+      <c r="L203" s="2" t="inlineStr">
+        <is>
+          <t>0.543314</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="inlineStr"/>
+      <c r="N203" s="2" t="inlineStr"/>
+      <c r="O203" s="2" t="inlineStr">
+        <is>
+          <t>0.6254681647940076</t>
+        </is>
+      </c>
+      <c r="P203" s="2" t="inlineStr">
+        <is>
+          <t>0.621891</t>
+        </is>
+      </c>
+      <c r="Q203" s="2" t="inlineStr">
+        <is>
+          <t>-0.08215416479400761</t>
+        </is>
+      </c>
+      <c r="R203" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:42:21.911862Z</t>
+        </is>
+      </c>
+      <c r="S203" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T203" s="2" t="inlineStr"/>
+      <c r="U203" s="2" t="inlineStr"/>
+      <c r="V203" s="2" t="inlineStr"/>
+      <c r="W203" s="2" t="inlineStr"/>
+      <c r="X203" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y203" s="2" t="inlineStr"/>
+      <c r="Z203" s="2" t="inlineStr"/>
+      <c r="AA203" s="2" t="inlineStr"/>
+      <c r="AB203" s="2" t="inlineStr"/>
+      <c r="AC203" s="2" t="inlineStr"/>
+      <c r="AD203" s="2" t="inlineStr"/>
+      <c r="AE203" s="2" t="inlineStr"/>
+      <c r="AF203" s="2" t="inlineStr"/>
+      <c r="AG203" s="2" t="inlineStr"/>
+      <c r="AH203" s="2" t="inlineStr"/>
+      <c r="AI203" s="2" t="inlineStr"/>
+      <c r="AJ203" s="2" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>03a43ed008614955</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>757a748feb566946</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>401816406</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K204" s="2" t="inlineStr"/>
+      <c r="L204" s="2" t="inlineStr">
+        <is>
+          <t>0.52224</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="inlineStr"/>
+      <c r="N204" s="2" t="inlineStr"/>
+      <c r="O204" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P204" s="2" t="inlineStr">
+        <is>
+          <t>0.527363</t>
+        </is>
+      </c>
+      <c r="Q204" s="2" t="inlineStr">
+        <is>
+          <t>-0.008276431924882588</t>
+        </is>
+      </c>
+      <c r="R204" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:42:22.411163Z</t>
+        </is>
+      </c>
+      <c r="S204" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:20:00-0400</t>
+        </is>
+      </c>
+      <c r="T204" s="2" t="inlineStr"/>
+      <c r="U204" s="2" t="inlineStr"/>
+      <c r="V204" s="2" t="inlineStr"/>
+      <c r="W204" s="2" t="inlineStr"/>
+      <c r="X204" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y204" s="2" t="inlineStr"/>
+      <c r="Z204" s="2" t="inlineStr"/>
+      <c r="AA204" s="2" t="inlineStr"/>
+      <c r="AB204" s="2" t="inlineStr"/>
+      <c r="AC204" s="2" t="inlineStr"/>
+      <c r="AD204" s="2" t="inlineStr"/>
+      <c r="AE204" s="2" t="inlineStr"/>
+      <c r="AF204" s="2" t="inlineStr"/>
+      <c r="AG204" s="2" t="inlineStr"/>
+      <c r="AH204" s="2" t="inlineStr"/>
+      <c r="AI204" s="2" t="inlineStr"/>
+      <c r="AJ204" s="2" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>a461263d0cf84a04</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>b14707c8a9267bdd</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>401816409</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J205" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K205" s="2" t="inlineStr"/>
+      <c r="L205" s="2" t="inlineStr">
+        <is>
+          <t>0.585182</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="inlineStr"/>
+      <c r="N205" s="2" t="inlineStr"/>
+      <c r="O205" s="2" t="inlineStr">
+        <is>
+          <t>0.6254681647940076</t>
+        </is>
+      </c>
+      <c r="P205" s="2" t="inlineStr">
+        <is>
+          <t>0.621891</t>
+        </is>
+      </c>
+      <c r="Q205" s="2" t="inlineStr">
+        <is>
+          <t>-0.040286164794007595</t>
+        </is>
+      </c>
+      <c r="R205" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:42:23.036833Z</t>
+        </is>
+      </c>
+      <c r="S205" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:35:00-0400</t>
+        </is>
+      </c>
+      <c r="T205" s="2" t="inlineStr"/>
+      <c r="U205" s="2" t="inlineStr"/>
+      <c r="V205" s="2" t="inlineStr"/>
+      <c r="W205" s="2" t="inlineStr"/>
+      <c r="X205" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y205" s="2" t="inlineStr"/>
+      <c r="Z205" s="2" t="inlineStr"/>
+      <c r="AA205" s="2" t="inlineStr"/>
+      <c r="AB205" s="2" t="inlineStr"/>
+      <c r="AC205" s="2" t="inlineStr"/>
+      <c r="AD205" s="2" t="inlineStr"/>
+      <c r="AE205" s="2" t="inlineStr"/>
+      <c r="AF205" s="2" t="inlineStr"/>
+      <c r="AG205" s="2" t="inlineStr"/>
+      <c r="AH205" s="2" t="inlineStr"/>
+      <c r="AI205" s="2" t="inlineStr"/>
+      <c r="AJ205" s="2" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>74a08b084e9a4da5</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>bed62784e0e2155a</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>401816411</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K206" s="2" t="inlineStr"/>
+      <c r="L206" s="2" t="inlineStr">
+        <is>
+          <t>0.651412</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="inlineStr"/>
+      <c r="N206" s="2" t="inlineStr"/>
+      <c r="O206" s="2" t="inlineStr">
+        <is>
+          <t>0.6047430830039526</t>
+        </is>
+      </c>
+      <c r="P206" s="2" t="inlineStr">
+        <is>
+          <t>0.60199</t>
+        </is>
+      </c>
+      <c r="Q206" s="2" t="inlineStr">
+        <is>
+          <t>0.04666891699604736</t>
+        </is>
+      </c>
+      <c r="R206" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:42:23.399936Z</t>
+        </is>
+      </c>
+      <c r="S206" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T15:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T206" s="2" t="inlineStr"/>
+      <c r="U206" s="2" t="inlineStr"/>
+      <c r="V206" s="2" t="inlineStr"/>
+      <c r="W206" s="2" t="inlineStr"/>
+      <c r="X206" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y206" s="2" t="inlineStr"/>
+      <c r="Z206" s="2" t="inlineStr"/>
+      <c r="AA206" s="2" t="inlineStr"/>
+      <c r="AB206" s="2" t="inlineStr"/>
+      <c r="AC206" s="2" t="inlineStr"/>
+      <c r="AD206" s="2" t="inlineStr"/>
+      <c r="AE206" s="2" t="inlineStr"/>
+      <c r="AF206" s="2" t="inlineStr"/>
+      <c r="AG206" s="2" t="inlineStr"/>
+      <c r="AH206" s="2" t="inlineStr"/>
+      <c r="AI206" s="2" t="inlineStr"/>
+      <c r="AJ206" s="2" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>2a05e081025b4809</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>6cd4cf8afdec8c65</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>401816399</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K207" s="2" t="inlineStr"/>
+      <c r="L207" s="2" t="inlineStr">
+        <is>
+          <t>0.620423</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="inlineStr"/>
+      <c r="N207" s="2" t="inlineStr"/>
+      <c r="O207" s="2" t="inlineStr">
+        <is>
+          <t>0.5555555555555556</t>
+        </is>
+      </c>
+      <c r="P207" s="2" t="inlineStr">
+        <is>
+          <t>0.552239</t>
+        </is>
+      </c>
+      <c r="Q207" s="2" t="inlineStr">
+        <is>
+          <t>0.06486744444444437</t>
+        </is>
+      </c>
+      <c r="R207" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:42:23.917446Z</t>
+        </is>
+      </c>
+      <c r="S207" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:35:00-0400</t>
+        </is>
+      </c>
+      <c r="T207" s="2" t="inlineStr"/>
+      <c r="U207" s="2" t="inlineStr"/>
+      <c r="V207" s="2" t="inlineStr"/>
+      <c r="W207" s="2" t="inlineStr"/>
+      <c r="X207" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y207" s="2" t="inlineStr"/>
+      <c r="Z207" s="2" t="inlineStr"/>
+      <c r="AA207" s="2" t="inlineStr"/>
+      <c r="AB207" s="2" t="inlineStr"/>
+      <c r="AC207" s="2" t="inlineStr"/>
+      <c r="AD207" s="2" t="inlineStr"/>
+      <c r="AE207" s="2" t="inlineStr"/>
+      <c r="AF207" s="2" t="inlineStr"/>
+      <c r="AG207" s="2" t="inlineStr"/>
+      <c r="AH207" s="2" t="inlineStr"/>
+      <c r="AI207" s="2" t="inlineStr"/>
+      <c r="AJ207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>c8cbef1732fa426a</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>38cc9b5478b87937</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>401816400</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K208" s="2" t="inlineStr"/>
+      <c r="L208" s="2" t="inlineStr">
+        <is>
+          <t>0.531973</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="inlineStr"/>
+      <c r="N208" s="2" t="inlineStr"/>
+      <c r="O208" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P208" s="2" t="inlineStr">
+        <is>
+          <t>0.557214</t>
+        </is>
+      </c>
+      <c r="Q208" s="2" t="inlineStr">
+        <is>
+          <t>-0.02749836563876651</t>
+        </is>
+      </c>
+      <c r="R208" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:42:25.451155Z</t>
+        </is>
+      </c>
+      <c r="S208" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T208" s="2" t="inlineStr"/>
+      <c r="U208" s="2" t="inlineStr"/>
+      <c r="V208" s="2" t="inlineStr"/>
+      <c r="W208" s="2" t="inlineStr"/>
+      <c r="X208" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y208" s="2" t="inlineStr"/>
+      <c r="Z208" s="2" t="inlineStr"/>
+      <c r="AA208" s="2" t="inlineStr"/>
+      <c r="AB208" s="2" t="inlineStr"/>
+      <c r="AC208" s="2" t="inlineStr"/>
+      <c r="AD208" s="2" t="inlineStr"/>
+      <c r="AE208" s="2" t="inlineStr"/>
+      <c r="AF208" s="2" t="inlineStr"/>
+      <c r="AG208" s="2" t="inlineStr"/>
+      <c r="AH208" s="2" t="inlineStr"/>
+      <c r="AI208" s="2" t="inlineStr"/>
+      <c r="AJ208" s="2" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>c91a11b5fae741e1</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>160edeaf9560617a</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>401816403</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K209" s="2" t="inlineStr"/>
+      <c r="L209" s="2" t="inlineStr">
+        <is>
+          <t>0.570052</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="inlineStr"/>
+      <c r="N209" s="2" t="inlineStr"/>
+      <c r="O209" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P209" s="2" t="inlineStr">
+        <is>
+          <t>0.497512</t>
+        </is>
+      </c>
+      <c r="Q209" s="2" t="inlineStr">
+        <is>
+          <t>0.070052</t>
+        </is>
+      </c>
+      <c r="R209" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:42:24.902410Z</t>
+        </is>
+      </c>
+      <c r="S209" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T209" s="2" t="inlineStr"/>
+      <c r="U209" s="2" t="inlineStr"/>
+      <c r="V209" s="2" t="inlineStr"/>
+      <c r="W209" s="2" t="inlineStr"/>
+      <c r="X209" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y209" s="2" t="inlineStr"/>
+      <c r="Z209" s="2" t="inlineStr"/>
+      <c r="AA209" s="2" t="inlineStr"/>
+      <c r="AB209" s="2" t="inlineStr"/>
+      <c r="AC209" s="2" t="inlineStr"/>
+      <c r="AD209" s="2" t="inlineStr"/>
+      <c r="AE209" s="2" t="inlineStr"/>
+      <c r="AF209" s="2" t="inlineStr"/>
+      <c r="AG209" s="2" t="inlineStr"/>
+      <c r="AH209" s="2" t="inlineStr"/>
+      <c r="AI209" s="2" t="inlineStr"/>
+      <c r="AJ209" s="2" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>0885db4399514239</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>64c95b4d86889dd9</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>401816405</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J210" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K210" s="2" t="inlineStr"/>
+      <c r="L210" s="2" t="inlineStr">
+        <is>
+          <t>0.568185</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="inlineStr"/>
+      <c r="N210" s="2" t="inlineStr"/>
+      <c r="O210" s="2" t="inlineStr">
+        <is>
+          <t>0.6153846153846154</t>
+        </is>
+      </c>
+      <c r="P210" s="2" t="inlineStr">
+        <is>
+          <t>0.61194</t>
+        </is>
+      </c>
+      <c r="Q210" s="2" t="inlineStr">
+        <is>
+          <t>-0.04719961538461537</t>
+        </is>
+      </c>
+      <c r="R210" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:42:24.465488Z</t>
+        </is>
+      </c>
+      <c r="S210" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T210" s="2" t="inlineStr"/>
+      <c r="U210" s="2" t="inlineStr"/>
+      <c r="V210" s="2" t="inlineStr"/>
+      <c r="W210" s="2" t="inlineStr"/>
+      <c r="X210" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y210" s="2" t="inlineStr"/>
+      <c r="Z210" s="2" t="inlineStr"/>
+      <c r="AA210" s="2" t="inlineStr"/>
+      <c r="AB210" s="2" t="inlineStr"/>
+      <c r="AC210" s="2" t="inlineStr"/>
+      <c r="AD210" s="2" t="inlineStr"/>
+      <c r="AE210" s="2" t="inlineStr"/>
+      <c r="AF210" s="2" t="inlineStr"/>
+      <c r="AG210" s="2" t="inlineStr"/>
+      <c r="AH210" s="2" t="inlineStr"/>
+      <c r="AI210" s="2" t="inlineStr"/>
+      <c r="AJ210" s="2" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>088aebf1fe7b4a47</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>a0beed6acc493629</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>401816404</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K211" s="2" t="inlineStr"/>
+      <c r="L211" s="2" t="inlineStr">
+        <is>
+          <t>0.585673</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="inlineStr"/>
+      <c r="N211" s="2" t="inlineStr"/>
+      <c r="O211" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P211" s="2" t="inlineStr">
+        <is>
+          <t>0.587065</t>
+        </is>
+      </c>
+      <c r="Q211" s="2" t="inlineStr">
+        <is>
+          <t>-0.004490934426229498</t>
+        </is>
+      </c>
+      <c r="R211" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:42:25.946625Z</t>
+        </is>
+      </c>
+      <c r="S211" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T211" s="2" t="inlineStr"/>
+      <c r="U211" s="2" t="inlineStr"/>
+      <c r="V211" s="2" t="inlineStr"/>
+      <c r="W211" s="2" t="inlineStr"/>
+      <c r="X211" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y211" s="2" t="inlineStr"/>
+      <c r="Z211" s="2" t="inlineStr"/>
+      <c r="AA211" s="2" t="inlineStr"/>
+      <c r="AB211" s="2" t="inlineStr"/>
+      <c r="AC211" s="2" t="inlineStr"/>
+      <c r="AD211" s="2" t="inlineStr"/>
+      <c r="AE211" s="2" t="inlineStr"/>
+      <c r="AF211" s="2" t="inlineStr"/>
+      <c r="AG211" s="2" t="inlineStr"/>
+      <c r="AH211" s="2" t="inlineStr"/>
+      <c r="AI211" s="2" t="inlineStr"/>
+      <c r="AJ211" s="2" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>c13b938f5caa4542</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>a30f963f12c48063</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>401816401</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J212" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K212" s="2" t="inlineStr"/>
+      <c r="L212" s="2" t="inlineStr">
+        <is>
+          <t>0.576304</t>
+        </is>
+      </c>
+      <c r="M212" s="2" t="inlineStr"/>
+      <c r="N212" s="2" t="inlineStr"/>
+      <c r="O212" s="2" t="inlineStr">
+        <is>
+          <t>0.5348837209302326</t>
+        </is>
+      </c>
+      <c r="P212" s="2" t="inlineStr">
+        <is>
+          <t>0.532338</t>
+        </is>
+      </c>
+      <c r="Q212" s="2" t="inlineStr">
+        <is>
+          <t>0.04142027906976742</t>
+        </is>
+      </c>
+      <c r="R212" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:42:26.245041Z</t>
+        </is>
+      </c>
+      <c r="S212" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T212" s="2" t="inlineStr"/>
+      <c r="U212" s="2" t="inlineStr"/>
+      <c r="V212" s="2" t="inlineStr"/>
+      <c r="W212" s="2" t="inlineStr"/>
+      <c r="X212" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y212" s="2" t="inlineStr"/>
+      <c r="Z212" s="2" t="inlineStr"/>
+      <c r="AA212" s="2" t="inlineStr"/>
+      <c r="AB212" s="2" t="inlineStr"/>
+      <c r="AC212" s="2" t="inlineStr"/>
+      <c r="AD212" s="2" t="inlineStr"/>
+      <c r="AE212" s="2" t="inlineStr"/>
+      <c r="AF212" s="2" t="inlineStr"/>
+      <c r="AG212" s="2" t="inlineStr"/>
+      <c r="AH212" s="2" t="inlineStr"/>
+      <c r="AI212" s="2" t="inlineStr"/>
+      <c r="AJ212" s="2" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>7c0061a8c76946c6</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>14b4c447a56375f6</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>401816402</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K213" s="2" t="inlineStr"/>
+      <c r="L213" s="2" t="inlineStr">
+        <is>
+          <t>0.590631</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="inlineStr"/>
+      <c r="N213" s="2" t="inlineStr"/>
+      <c r="O213" s="2" t="inlineStr">
+        <is>
+          <t>0.5454545454545454</t>
+        </is>
+      </c>
+      <c r="P213" s="2" t="inlineStr">
+        <is>
+          <t>0.542289</t>
+        </is>
+      </c>
+      <c r="Q213" s="2" t="inlineStr">
+        <is>
+          <t>0.0451764545454546</t>
+        </is>
+      </c>
+      <c r="R213" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:42:26.805947Z</t>
+        </is>
+      </c>
+      <c r="S213" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T213" s="2" t="inlineStr"/>
+      <c r="U213" s="2" t="inlineStr"/>
+      <c r="V213" s="2" t="inlineStr"/>
+      <c r="W213" s="2" t="inlineStr"/>
+      <c r="X213" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y213" s="2" t="inlineStr"/>
+      <c r="Z213" s="2" t="inlineStr"/>
+      <c r="AA213" s="2" t="inlineStr"/>
+      <c r="AB213" s="2" t="inlineStr"/>
+      <c r="AC213" s="2" t="inlineStr"/>
+      <c r="AD213" s="2" t="inlineStr"/>
+      <c r="AE213" s="2" t="inlineStr"/>
+      <c r="AF213" s="2" t="inlineStr"/>
+      <c r="AG213" s="2" t="inlineStr"/>
+      <c r="AH213" s="2" t="inlineStr"/>
+      <c r="AI213" s="2" t="inlineStr"/>
+      <c r="AJ213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>840ffa6aae554f57</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>23aa584b6028ab97</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>401816408</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K214" s="2" t="inlineStr"/>
+      <c r="L214" s="2" t="inlineStr">
+        <is>
+          <t>0.615508</t>
+        </is>
+      </c>
+      <c r="M214" s="2" t="inlineStr"/>
+      <c r="N214" s="2" t="inlineStr"/>
+      <c r="O214" s="2" t="inlineStr">
+        <is>
+          <t>0.5555555555555556</t>
+        </is>
+      </c>
+      <c r="P214" s="2" t="inlineStr">
+        <is>
+          <t>0.552239</t>
+        </is>
+      </c>
+      <c r="Q214" s="2" t="inlineStr">
+        <is>
+          <t>0.059952444444444475</t>
+        </is>
+      </c>
+      <c r="R214" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:42:27.273802Z</t>
+        </is>
+      </c>
+      <c r="S214" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="T214" s="2" t="inlineStr"/>
+      <c r="U214" s="2" t="inlineStr"/>
+      <c r="V214" s="2" t="inlineStr"/>
+      <c r="W214" s="2" t="inlineStr"/>
+      <c r="X214" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y214" s="2" t="inlineStr"/>
+      <c r="Z214" s="2" t="inlineStr"/>
+      <c r="AA214" s="2" t="inlineStr"/>
+      <c r="AB214" s="2" t="inlineStr"/>
+      <c r="AC214" s="2" t="inlineStr"/>
+      <c r="AD214" s="2" t="inlineStr"/>
+      <c r="AE214" s="2" t="inlineStr"/>
+      <c r="AF214" s="2" t="inlineStr"/>
+      <c r="AG214" s="2" t="inlineStr"/>
+      <c r="AH214" s="2" t="inlineStr"/>
+      <c r="AI214" s="2" t="inlineStr"/>
+      <c r="AJ214" s="2" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>b03833865f1b4598</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>5af634cf85e8d1da</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>401816407</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K215" s="2" t="inlineStr"/>
+      <c r="L215" s="2" t="inlineStr">
+        <is>
+          <t>0.524512</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="inlineStr"/>
+      <c r="N215" s="2" t="inlineStr"/>
+      <c r="O215" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P215" s="2" t="inlineStr">
+        <is>
+          <t>0.527363</t>
+        </is>
+      </c>
+      <c r="Q215" s="2" t="inlineStr">
+        <is>
+          <t>-0.006004431924882647</t>
+        </is>
+      </c>
+      <c r="R215" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:42:27.782454Z</t>
+        </is>
+      </c>
+      <c r="S215" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T215" s="2" t="inlineStr"/>
+      <c r="U215" s="2" t="inlineStr"/>
+      <c r="V215" s="2" t="inlineStr"/>
+      <c r="W215" s="2" t="inlineStr"/>
+      <c r="X215" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y215" s="2" t="inlineStr"/>
+      <c r="Z215" s="2" t="inlineStr"/>
+      <c r="AA215" s="2" t="inlineStr"/>
+      <c r="AB215" s="2" t="inlineStr"/>
+      <c r="AC215" s="2" t="inlineStr"/>
+      <c r="AD215" s="2" t="inlineStr"/>
+      <c r="AE215" s="2" t="inlineStr"/>
+      <c r="AF215" s="2" t="inlineStr"/>
+      <c r="AG215" s="2" t="inlineStr"/>
+      <c r="AH215" s="2" t="inlineStr"/>
+      <c r="AI215" s="2" t="inlineStr"/>
+      <c r="AJ215" s="2" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>e2f55b06046e478e</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>1869d7c91b8ee576</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>401816412</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K216" s="2" t="inlineStr"/>
+      <c r="L216" s="2" t="inlineStr">
+        <is>
+          <t>0.550053</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="inlineStr"/>
+      <c r="N216" s="2" t="inlineStr"/>
+      <c r="O216" s="2" t="inlineStr">
+        <is>
+          <t>0.5850622406639003</t>
+        </is>
+      </c>
+      <c r="P216" s="2" t="inlineStr">
+        <is>
+          <t>0.58209</t>
+        </is>
+      </c>
+      <c r="Q216" s="2" t="inlineStr">
+        <is>
+          <t>-0.03500924066390032</t>
+        </is>
+      </c>
+      <c r="R216" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:42:29.074250Z</t>
+        </is>
+      </c>
+      <c r="S216" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T216" s="2" t="inlineStr"/>
+      <c r="U216" s="2" t="inlineStr"/>
+      <c r="V216" s="2" t="inlineStr"/>
+      <c r="W216" s="2" t="inlineStr"/>
+      <c r="X216" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y216" s="2" t="inlineStr"/>
+      <c r="Z216" s="2" t="inlineStr"/>
+      <c r="AA216" s="2" t="inlineStr"/>
+      <c r="AB216" s="2" t="inlineStr"/>
+      <c r="AC216" s="2" t="inlineStr"/>
+      <c r="AD216" s="2" t="inlineStr"/>
+      <c r="AE216" s="2" t="inlineStr"/>
+      <c r="AF216" s="2" t="inlineStr"/>
+      <c r="AG216" s="2" t="inlineStr"/>
+      <c r="AH216" s="2" t="inlineStr"/>
+      <c r="AI216" s="2" t="inlineStr"/>
+      <c r="AJ216" s="2" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>7ec7d2bd40a749b1</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>f27ad71f21952264</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>401816413</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J217" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K217" s="2" t="inlineStr"/>
+      <c r="L217" s="2" t="inlineStr">
+        <is>
+          <t>0.512293</t>
+        </is>
+      </c>
+      <c r="M217" s="2" t="inlineStr"/>
+      <c r="N217" s="2" t="inlineStr"/>
+      <c r="O217" s="2" t="inlineStr">
+        <is>
+          <t>0.5348837209302326</t>
+        </is>
+      </c>
+      <c r="P217" s="2" t="inlineStr">
+        <is>
+          <t>0.532338</t>
+        </is>
+      </c>
+      <c r="Q217" s="2" t="inlineStr">
+        <is>
+          <t>-0.02259072093023262</t>
+        </is>
+      </c>
+      <c r="R217" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:42:29.755885Z</t>
+        </is>
+      </c>
+      <c r="S217" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T217" s="2" t="inlineStr"/>
+      <c r="U217" s="2" t="inlineStr"/>
+      <c r="V217" s="2" t="inlineStr"/>
+      <c r="W217" s="2" t="inlineStr"/>
+      <c r="X217" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y217" s="2" t="inlineStr"/>
+      <c r="Z217" s="2" t="inlineStr"/>
+      <c r="AA217" s="2" t="inlineStr"/>
+      <c r="AB217" s="2" t="inlineStr"/>
+      <c r="AC217" s="2" t="inlineStr"/>
+      <c r="AD217" s="2" t="inlineStr"/>
+      <c r="AE217" s="2" t="inlineStr"/>
+      <c r="AF217" s="2" t="inlineStr"/>
+      <c r="AG217" s="2" t="inlineStr"/>
+      <c r="AH217" s="2" t="inlineStr"/>
+      <c r="AI217" s="2" t="inlineStr"/>
+      <c r="AJ217" s="2" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>f7427d9985c04d28</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>7363e92b2bdde372</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>401816410</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J218" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K218" s="2" t="inlineStr"/>
+      <c r="L218" s="2" t="inlineStr">
+        <is>
+          <t>0.543314</t>
+        </is>
+      </c>
+      <c r="M218" s="2" t="inlineStr"/>
+      <c r="N218" s="2" t="inlineStr"/>
+      <c r="O218" s="2" t="inlineStr">
+        <is>
+          <t>0.635036496350365</t>
+        </is>
+      </c>
+      <c r="P218" s="2" t="inlineStr">
+        <is>
+          <t>0.631841</t>
+        </is>
+      </c>
+      <c r="Q218" s="2" t="inlineStr">
+        <is>
+          <t>-0.091722496350365</t>
+        </is>
+      </c>
+      <c r="R218" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:24.506232Z</t>
+        </is>
+      </c>
+      <c r="S218" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T218" s="2" t="inlineStr"/>
+      <c r="U218" s="2" t="inlineStr"/>
+      <c r="V218" s="2" t="inlineStr"/>
+      <c r="W218" s="2" t="inlineStr"/>
+      <c r="X218" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y218" s="2" t="inlineStr"/>
+      <c r="Z218" s="2" t="inlineStr"/>
+      <c r="AA218" s="2" t="inlineStr"/>
+      <c r="AB218" s="2" t="inlineStr"/>
+      <c r="AC218" s="2" t="inlineStr"/>
+      <c r="AD218" s="2" t="inlineStr"/>
+      <c r="AE218" s="2" t="inlineStr"/>
+      <c r="AF218" s="2" t="inlineStr"/>
+      <c r="AG218" s="2" t="inlineStr"/>
+      <c r="AH218" s="2" t="inlineStr"/>
+      <c r="AI218" s="2" t="inlineStr"/>
+      <c r="AJ218" s="2" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>312942a108f34a8f</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>7d69706ac5e95086</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>401816406</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J219" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K219" s="2" t="inlineStr"/>
+      <c r="L219" s="2" t="inlineStr">
+        <is>
+          <t>0.522352</t>
+        </is>
+      </c>
+      <c r="M219" s="2" t="inlineStr"/>
+      <c r="N219" s="2" t="inlineStr"/>
+      <c r="O219" s="2" t="inlineStr">
+        <is>
+          <t>0.5348837209302326</t>
+        </is>
+      </c>
+      <c r="P219" s="2" t="inlineStr">
+        <is>
+          <t>0.532338</t>
+        </is>
+      </c>
+      <c r="Q219" s="2" t="inlineStr">
+        <is>
+          <t>-0.012531720930232582</t>
+        </is>
+      </c>
+      <c r="R219" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:24.994220Z</t>
+        </is>
+      </c>
+      <c r="S219" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:20:00-0400</t>
+        </is>
+      </c>
+      <c r="T219" s="2" t="inlineStr"/>
+      <c r="U219" s="2" t="inlineStr"/>
+      <c r="V219" s="2" t="inlineStr"/>
+      <c r="W219" s="2" t="inlineStr"/>
+      <c r="X219" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y219" s="2" t="inlineStr"/>
+      <c r="Z219" s="2" t="inlineStr"/>
+      <c r="AA219" s="2" t="inlineStr"/>
+      <c r="AB219" s="2" t="inlineStr"/>
+      <c r="AC219" s="2" t="inlineStr"/>
+      <c r="AD219" s="2" t="inlineStr"/>
+      <c r="AE219" s="2" t="inlineStr"/>
+      <c r="AF219" s="2" t="inlineStr"/>
+      <c r="AG219" s="2" t="inlineStr"/>
+      <c r="AH219" s="2" t="inlineStr"/>
+      <c r="AI219" s="2" t="inlineStr"/>
+      <c r="AJ219" s="2" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>b4328416dd224c55</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>b14707c8a9267bdd</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>401816409</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J220" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K220" s="2" t="inlineStr"/>
+      <c r="L220" s="2" t="inlineStr">
+        <is>
+          <t>0.585182</t>
+        </is>
+      </c>
+      <c r="M220" s="2" t="inlineStr"/>
+      <c r="N220" s="2" t="inlineStr"/>
+      <c r="O220" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P220" s="2" t="inlineStr">
+        <is>
+          <t>0.616915</t>
+        </is>
+      </c>
+      <c r="Q220" s="2" t="inlineStr">
+        <is>
+          <t>-0.03458986311787071</t>
+        </is>
+      </c>
+      <c r="R220" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:25.614756Z</t>
+        </is>
+      </c>
+      <c r="S220" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:35:00-0400</t>
+        </is>
+      </c>
+      <c r="T220" s="2" t="inlineStr"/>
+      <c r="U220" s="2" t="inlineStr"/>
+      <c r="V220" s="2" t="inlineStr"/>
+      <c r="W220" s="2" t="inlineStr"/>
+      <c r="X220" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y220" s="2" t="inlineStr"/>
+      <c r="Z220" s="2" t="inlineStr"/>
+      <c r="AA220" s="2" t="inlineStr"/>
+      <c r="AB220" s="2" t="inlineStr"/>
+      <c r="AC220" s="2" t="inlineStr"/>
+      <c r="AD220" s="2" t="inlineStr"/>
+      <c r="AE220" s="2" t="inlineStr"/>
+      <c r="AF220" s="2" t="inlineStr"/>
+      <c r="AG220" s="2" t="inlineStr"/>
+      <c r="AH220" s="2" t="inlineStr"/>
+      <c r="AI220" s="2" t="inlineStr"/>
+      <c r="AJ220" s="2" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>bb474672138540f5</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>133a0f8d2d67fce5</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>401816411</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J221" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K221" s="2" t="inlineStr"/>
+      <c r="L221" s="2" t="inlineStr">
+        <is>
+          <t>0.651358</t>
+        </is>
+      </c>
+      <c r="M221" s="2" t="inlineStr"/>
+      <c r="N221" s="2" t="inlineStr"/>
+      <c r="O221" s="2" t="inlineStr">
+        <is>
+          <t>0.6047430830039526</t>
+        </is>
+      </c>
+      <c r="P221" s="2" t="inlineStr">
+        <is>
+          <t>0.60199</t>
+        </is>
+      </c>
+      <c r="Q221" s="2" t="inlineStr">
+        <is>
+          <t>0.04661491699604736</t>
+        </is>
+      </c>
+      <c r="R221" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:26.086277Z</t>
+        </is>
+      </c>
+      <c r="S221" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T15:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T221" s="2" t="inlineStr"/>
+      <c r="U221" s="2" t="inlineStr"/>
+      <c r="V221" s="2" t="inlineStr"/>
+      <c r="W221" s="2" t="inlineStr"/>
+      <c r="X221" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y221" s="2" t="inlineStr"/>
+      <c r="Z221" s="2" t="inlineStr"/>
+      <c r="AA221" s="2" t="inlineStr"/>
+      <c r="AB221" s="2" t="inlineStr"/>
+      <c r="AC221" s="2" t="inlineStr"/>
+      <c r="AD221" s="2" t="inlineStr"/>
+      <c r="AE221" s="2" t="inlineStr"/>
+      <c r="AF221" s="2" t="inlineStr"/>
+      <c r="AG221" s="2" t="inlineStr"/>
+      <c r="AH221" s="2" t="inlineStr"/>
+      <c r="AI221" s="2" t="inlineStr"/>
+      <c r="AJ221" s="2" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>63eee1db95464f04</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>90250452b4135146</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>401816399</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J222" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K222" s="2" t="inlineStr"/>
+      <c r="L222" s="2" t="inlineStr">
+        <is>
+          <t>0.620156</t>
+        </is>
+      </c>
+      <c r="M222" s="2" t="inlineStr"/>
+      <c r="N222" s="2" t="inlineStr"/>
+      <c r="O222" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P222" s="2" t="inlineStr">
+        <is>
+          <t>0.537313</t>
+        </is>
+      </c>
+      <c r="Q222" s="2" t="inlineStr">
+        <is>
+          <t>0.08098549308755765</t>
+        </is>
+      </c>
+      <c r="R222" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:26.546603Z</t>
+        </is>
+      </c>
+      <c r="S222" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:35:00-0400</t>
+        </is>
+      </c>
+      <c r="T222" s="2" t="inlineStr"/>
+      <c r="U222" s="2" t="inlineStr"/>
+      <c r="V222" s="2" t="inlineStr"/>
+      <c r="W222" s="2" t="inlineStr"/>
+      <c r="X222" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y222" s="2" t="inlineStr"/>
+      <c r="Z222" s="2" t="inlineStr"/>
+      <c r="AA222" s="2" t="inlineStr"/>
+      <c r="AB222" s="2" t="inlineStr"/>
+      <c r="AC222" s="2" t="inlineStr"/>
+      <c r="AD222" s="2" t="inlineStr"/>
+      <c r="AE222" s="2" t="inlineStr"/>
+      <c r="AF222" s="2" t="inlineStr"/>
+      <c r="AG222" s="2" t="inlineStr"/>
+      <c r="AH222" s="2" t="inlineStr"/>
+      <c r="AI222" s="2" t="inlineStr"/>
+      <c r="AJ222" s="2" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>fcc0c52e804040db</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>b37c86ce3baa60b2</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>401816400</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J223" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K223" s="2" t="inlineStr"/>
+      <c r="L223" s="2" t="inlineStr">
+        <is>
+          <t>0.531981</t>
+        </is>
+      </c>
+      <c r="M223" s="2" t="inlineStr"/>
+      <c r="N223" s="2" t="inlineStr"/>
+      <c r="O223" s="2" t="inlineStr">
+        <is>
+          <t>0.574468085106383</t>
+        </is>
+      </c>
+      <c r="P223" s="2" t="inlineStr">
+        <is>
+          <t>0.572139</t>
+        </is>
+      </c>
+      <c r="Q223" s="2" t="inlineStr">
+        <is>
+          <t>-0.042487085106382994</t>
+        </is>
+      </c>
+      <c r="R223" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:28.221956Z</t>
+        </is>
+      </c>
+      <c r="S223" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T223" s="2" t="inlineStr"/>
+      <c r="U223" s="2" t="inlineStr"/>
+      <c r="V223" s="2" t="inlineStr"/>
+      <c r="W223" s="2" t="inlineStr"/>
+      <c r="X223" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y223" s="2" t="inlineStr"/>
+      <c r="Z223" s="2" t="inlineStr"/>
+      <c r="AA223" s="2" t="inlineStr"/>
+      <c r="AB223" s="2" t="inlineStr"/>
+      <c r="AC223" s="2" t="inlineStr"/>
+      <c r="AD223" s="2" t="inlineStr"/>
+      <c r="AE223" s="2" t="inlineStr"/>
+      <c r="AF223" s="2" t="inlineStr"/>
+      <c r="AG223" s="2" t="inlineStr"/>
+      <c r="AH223" s="2" t="inlineStr"/>
+      <c r="AI223" s="2" t="inlineStr"/>
+      <c r="AJ223" s="2" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>f72759ac4c684e66</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>a8496f0544fb49ff</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>401816403</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K224" s="2" t="inlineStr"/>
+      <c r="L224" s="2" t="inlineStr">
+        <is>
+          <t>0.570059</t>
+        </is>
+      </c>
+      <c r="M224" s="2" t="inlineStr"/>
+      <c r="N224" s="2" t="inlineStr"/>
+      <c r="O224" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P224" s="2" t="inlineStr">
+        <is>
+          <t>0.507463</t>
+        </is>
+      </c>
+      <c r="Q224" s="2" t="inlineStr">
+        <is>
+          <t>0.060255078431372566</t>
+        </is>
+      </c>
+      <c r="R224" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:27.503942Z</t>
+        </is>
+      </c>
+      <c r="S224" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T224" s="2" t="inlineStr"/>
+      <c r="U224" s="2" t="inlineStr"/>
+      <c r="V224" s="2" t="inlineStr"/>
+      <c r="W224" s="2" t="inlineStr"/>
+      <c r="X224" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y224" s="2" t="inlineStr"/>
+      <c r="Z224" s="2" t="inlineStr"/>
+      <c r="AA224" s="2" t="inlineStr"/>
+      <c r="AB224" s="2" t="inlineStr"/>
+      <c r="AC224" s="2" t="inlineStr"/>
+      <c r="AD224" s="2" t="inlineStr"/>
+      <c r="AE224" s="2" t="inlineStr"/>
+      <c r="AF224" s="2" t="inlineStr"/>
+      <c r="AG224" s="2" t="inlineStr"/>
+      <c r="AH224" s="2" t="inlineStr"/>
+      <c r="AI224" s="2" t="inlineStr"/>
+      <c r="AJ224" s="2" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>9a2e409f1c7847d0</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>28c4190bf888aff9</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>401816405</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J225" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K225" s="2" t="inlineStr"/>
+      <c r="L225" s="2" t="inlineStr">
+        <is>
+          <t>0.568112</t>
+        </is>
+      </c>
+      <c r="M225" s="2" t="inlineStr"/>
+      <c r="N225" s="2" t="inlineStr"/>
+      <c r="O225" s="2" t="inlineStr">
+        <is>
+          <t>0.635036496350365</t>
+        </is>
+      </c>
+      <c r="P225" s="2" t="inlineStr">
+        <is>
+          <t>0.631841</t>
+        </is>
+      </c>
+      <c r="Q225" s="2" t="inlineStr">
+        <is>
+          <t>-0.06692449635036501</t>
+        </is>
+      </c>
+      <c r="R225" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:27.109583Z</t>
+        </is>
+      </c>
+      <c r="S225" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T225" s="2" t="inlineStr"/>
+      <c r="U225" s="2" t="inlineStr"/>
+      <c r="V225" s="2" t="inlineStr"/>
+      <c r="W225" s="2" t="inlineStr"/>
+      <c r="X225" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y225" s="2" t="inlineStr"/>
+      <c r="Z225" s="2" t="inlineStr"/>
+      <c r="AA225" s="2" t="inlineStr"/>
+      <c r="AB225" s="2" t="inlineStr"/>
+      <c r="AC225" s="2" t="inlineStr"/>
+      <c r="AD225" s="2" t="inlineStr"/>
+      <c r="AE225" s="2" t="inlineStr"/>
+      <c r="AF225" s="2" t="inlineStr"/>
+      <c r="AG225" s="2" t="inlineStr"/>
+      <c r="AH225" s="2" t="inlineStr"/>
+      <c r="AI225" s="2" t="inlineStr"/>
+      <c r="AJ225" s="2" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>f0b3758bc7f54b04</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>f16100c8dde61330</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>401816404</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J226" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K226" s="2" t="inlineStr"/>
+      <c r="L226" s="2" t="inlineStr">
+        <is>
+          <t>0.58581</t>
+        </is>
+      </c>
+      <c r="M226" s="2" t="inlineStr"/>
+      <c r="N226" s="2" t="inlineStr"/>
+      <c r="O226" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P226" s="2" t="inlineStr">
+        <is>
+          <t>0.587065</t>
+        </is>
+      </c>
+      <c r="Q226" s="2" t="inlineStr">
+        <is>
+          <t>-0.004353934426229444</t>
+        </is>
+      </c>
+      <c r="R226" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:28.745980Z</t>
+        </is>
+      </c>
+      <c r="S226" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T226" s="2" t="inlineStr"/>
+      <c r="U226" s="2" t="inlineStr"/>
+      <c r="V226" s="2" t="inlineStr"/>
+      <c r="W226" s="2" t="inlineStr"/>
+      <c r="X226" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y226" s="2" t="inlineStr"/>
+      <c r="Z226" s="2" t="inlineStr"/>
+      <c r="AA226" s="2" t="inlineStr"/>
+      <c r="AB226" s="2" t="inlineStr"/>
+      <c r="AC226" s="2" t="inlineStr"/>
+      <c r="AD226" s="2" t="inlineStr"/>
+      <c r="AE226" s="2" t="inlineStr"/>
+      <c r="AF226" s="2" t="inlineStr"/>
+      <c r="AG226" s="2" t="inlineStr"/>
+      <c r="AH226" s="2" t="inlineStr"/>
+      <c r="AI226" s="2" t="inlineStr"/>
+      <c r="AJ226" s="2" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>ffef436e7bba4717</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>10f5b05f22dccd69</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>401816401</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J227" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K227" s="2" t="inlineStr"/>
+      <c r="L227" s="2" t="inlineStr">
+        <is>
+          <t>0.576188</t>
+        </is>
+      </c>
+      <c r="M227" s="2" t="inlineStr"/>
+      <c r="N227" s="2" t="inlineStr"/>
+      <c r="O227" s="2" t="inlineStr">
+        <is>
+          <t>0.5555555555555556</t>
+        </is>
+      </c>
+      <c r="P227" s="2" t="inlineStr">
+        <is>
+          <t>0.552239</t>
+        </is>
+      </c>
+      <c r="Q227" s="2" t="inlineStr">
+        <is>
+          <t>0.020632444444444453</t>
+        </is>
+      </c>
+      <c r="R227" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:29.150568Z</t>
+        </is>
+      </c>
+      <c r="S227" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T227" s="2" t="inlineStr"/>
+      <c r="U227" s="2" t="inlineStr"/>
+      <c r="V227" s="2" t="inlineStr"/>
+      <c r="W227" s="2" t="inlineStr"/>
+      <c r="X227" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y227" s="2" t="inlineStr"/>
+      <c r="Z227" s="2" t="inlineStr"/>
+      <c r="AA227" s="2" t="inlineStr"/>
+      <c r="AB227" s="2" t="inlineStr"/>
+      <c r="AC227" s="2" t="inlineStr"/>
+      <c r="AD227" s="2" t="inlineStr"/>
+      <c r="AE227" s="2" t="inlineStr"/>
+      <c r="AF227" s="2" t="inlineStr"/>
+      <c r="AG227" s="2" t="inlineStr"/>
+      <c r="AH227" s="2" t="inlineStr"/>
+      <c r="AI227" s="2" t="inlineStr"/>
+      <c r="AJ227" s="2" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>d3d6f064fef94039</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>06a32b1aa50e018d</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>401816402</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J228" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K228" s="2" t="inlineStr"/>
+      <c r="L228" s="2" t="inlineStr">
+        <is>
+          <t>0.590933</t>
+        </is>
+      </c>
+      <c r="M228" s="2" t="inlineStr"/>
+      <c r="N228" s="2" t="inlineStr"/>
+      <c r="O228" s="2" t="inlineStr">
+        <is>
+          <t>0.5454545454545454</t>
+        </is>
+      </c>
+      <c r="P228" s="2" t="inlineStr">
+        <is>
+          <t>0.542289</t>
+        </is>
+      </c>
+      <c r="Q228" s="2" t="inlineStr">
+        <is>
+          <t>0.04547845454545463</t>
+        </is>
+      </c>
+      <c r="R228" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:29.624655Z</t>
+        </is>
+      </c>
+      <c r="S228" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T228" s="2" t="inlineStr"/>
+      <c r="U228" s="2" t="inlineStr"/>
+      <c r="V228" s="2" t="inlineStr"/>
+      <c r="W228" s="2" t="inlineStr"/>
+      <c r="X228" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y228" s="2" t="inlineStr"/>
+      <c r="Z228" s="2" t="inlineStr"/>
+      <c r="AA228" s="2" t="inlineStr"/>
+      <c r="AB228" s="2" t="inlineStr"/>
+      <c r="AC228" s="2" t="inlineStr"/>
+      <c r="AD228" s="2" t="inlineStr"/>
+      <c r="AE228" s="2" t="inlineStr"/>
+      <c r="AF228" s="2" t="inlineStr"/>
+      <c r="AG228" s="2" t="inlineStr"/>
+      <c r="AH228" s="2" t="inlineStr"/>
+      <c r="AI228" s="2" t="inlineStr"/>
+      <c r="AJ228" s="2" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>0ded3a6119824e5b</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>23aa584b6028ab97</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>401816408</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J229" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K229" s="2" t="inlineStr"/>
+      <c r="L229" s="2" t="inlineStr">
+        <is>
+          <t>0.615508</t>
+        </is>
+      </c>
+      <c r="M229" s="2" t="inlineStr"/>
+      <c r="N229" s="2" t="inlineStr"/>
+      <c r="O229" s="2" t="inlineStr">
+        <is>
+          <t>0.5555555555555556</t>
+        </is>
+      </c>
+      <c r="P229" s="2" t="inlineStr">
+        <is>
+          <t>0.552239</t>
+        </is>
+      </c>
+      <c r="Q229" s="2" t="inlineStr">
+        <is>
+          <t>0.059952444444444475</t>
+        </is>
+      </c>
+      <c r="R229" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:30.079092Z</t>
+        </is>
+      </c>
+      <c r="S229" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="T229" s="2" t="inlineStr"/>
+      <c r="U229" s="2" t="inlineStr"/>
+      <c r="V229" s="2" t="inlineStr"/>
+      <c r="W229" s="2" t="inlineStr"/>
+      <c r="X229" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y229" s="2" t="inlineStr"/>
+      <c r="Z229" s="2" t="inlineStr"/>
+      <c r="AA229" s="2" t="inlineStr"/>
+      <c r="AB229" s="2" t="inlineStr"/>
+      <c r="AC229" s="2" t="inlineStr"/>
+      <c r="AD229" s="2" t="inlineStr"/>
+      <c r="AE229" s="2" t="inlineStr"/>
+      <c r="AF229" s="2" t="inlineStr"/>
+      <c r="AG229" s="2" t="inlineStr"/>
+      <c r="AH229" s="2" t="inlineStr"/>
+      <c r="AI229" s="2" t="inlineStr"/>
+      <c r="AJ229" s="2" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>113785b9d52f45e0</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>420793a043fef772</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>401816407</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J230" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K230" s="2" t="inlineStr"/>
+      <c r="L230" s="2" t="inlineStr">
+        <is>
+          <t>0.524802</t>
+        </is>
+      </c>
+      <c r="M230" s="2" t="inlineStr"/>
+      <c r="N230" s="2" t="inlineStr"/>
+      <c r="O230" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P230" s="2" t="inlineStr">
+        <is>
+          <t>0.527363</t>
+        </is>
+      </c>
+      <c r="Q230" s="2" t="inlineStr">
+        <is>
+          <t>-0.005714431924882635</t>
+        </is>
+      </c>
+      <c r="R230" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:30.727273Z</t>
+        </is>
+      </c>
+      <c r="S230" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T230" s="2" t="inlineStr"/>
+      <c r="U230" s="2" t="inlineStr"/>
+      <c r="V230" s="2" t="inlineStr"/>
+      <c r="W230" s="2" t="inlineStr"/>
+      <c r="X230" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y230" s="2" t="inlineStr"/>
+      <c r="Z230" s="2" t="inlineStr"/>
+      <c r="AA230" s="2" t="inlineStr"/>
+      <c r="AB230" s="2" t="inlineStr"/>
+      <c r="AC230" s="2" t="inlineStr"/>
+      <c r="AD230" s="2" t="inlineStr"/>
+      <c r="AE230" s="2" t="inlineStr"/>
+      <c r="AF230" s="2" t="inlineStr"/>
+      <c r="AG230" s="2" t="inlineStr"/>
+      <c r="AH230" s="2" t="inlineStr"/>
+      <c r="AI230" s="2" t="inlineStr"/>
+      <c r="AJ230" s="2" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>6504bbb3a7614b05</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>1869d7c91b8ee576</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>401816412</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J231" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K231" s="2" t="inlineStr"/>
+      <c r="L231" s="2" t="inlineStr">
+        <is>
+          <t>0.550053</t>
+        </is>
+      </c>
+      <c r="M231" s="2" t="inlineStr"/>
+      <c r="N231" s="2" t="inlineStr"/>
+      <c r="O231" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P231" s="2" t="inlineStr">
+        <is>
+          <t>0.587065</t>
+        </is>
+      </c>
+      <c r="Q231" s="2" t="inlineStr">
+        <is>
+          <t>-0.04011093442622948</t>
+        </is>
+      </c>
+      <c r="R231" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:31.897237Z</t>
+        </is>
+      </c>
+      <c r="S231" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T231" s="2" t="inlineStr"/>
+      <c r="U231" s="2" t="inlineStr"/>
+      <c r="V231" s="2" t="inlineStr"/>
+      <c r="W231" s="2" t="inlineStr"/>
+      <c r="X231" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y231" s="2" t="inlineStr"/>
+      <c r="Z231" s="2" t="inlineStr"/>
+      <c r="AA231" s="2" t="inlineStr"/>
+      <c r="AB231" s="2" t="inlineStr"/>
+      <c r="AC231" s="2" t="inlineStr"/>
+      <c r="AD231" s="2" t="inlineStr"/>
+      <c r="AE231" s="2" t="inlineStr"/>
+      <c r="AF231" s="2" t="inlineStr"/>
+      <c r="AG231" s="2" t="inlineStr"/>
+      <c r="AH231" s="2" t="inlineStr"/>
+      <c r="AI231" s="2" t="inlineStr"/>
+      <c r="AJ231" s="2" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>476e00aafd4347f7</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>f27ad71f21952264</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>401816413</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J232" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K232" s="2" t="inlineStr"/>
+      <c r="L232" s="2" t="inlineStr">
+        <is>
+          <t>0.512293</t>
+        </is>
+      </c>
+      <c r="M232" s="2" t="inlineStr"/>
+      <c r="N232" s="2" t="inlineStr"/>
+      <c r="O232" s="2" t="inlineStr">
+        <is>
+          <t>0.5348837209302326</t>
+        </is>
+      </c>
+      <c r="P232" s="2" t="inlineStr">
+        <is>
+          <t>0.532338</t>
+        </is>
+      </c>
+      <c r="Q232" s="2" t="inlineStr">
+        <is>
+          <t>-0.02259072093023262</t>
+        </is>
+      </c>
+      <c r="R232" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:33.047392Z</t>
+        </is>
+      </c>
+      <c r="S232" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T232" s="2" t="inlineStr"/>
+      <c r="U232" s="2" t="inlineStr"/>
+      <c r="V232" s="2" t="inlineStr"/>
+      <c r="W232" s="2" t="inlineStr"/>
+      <c r="X232" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y232" s="2" t="inlineStr"/>
+      <c r="Z232" s="2" t="inlineStr"/>
+      <c r="AA232" s="2" t="inlineStr"/>
+      <c r="AB232" s="2" t="inlineStr"/>
+      <c r="AC232" s="2" t="inlineStr"/>
+      <c r="AD232" s="2" t="inlineStr"/>
+      <c r="AE232" s="2" t="inlineStr"/>
+      <c r="AF232" s="2" t="inlineStr"/>
+      <c r="AG232" s="2" t="inlineStr"/>
+      <c r="AH232" s="2" t="inlineStr"/>
+      <c r="AI232" s="2" t="inlineStr"/>
+      <c r="AJ232" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ187"/>
+  <autoFilter ref="A1:AJ232"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/flat/model_ledgers/mlb-moneyline-elo-trend-lr.xlsx
+++ b/data/flat/model_ledgers/mlb-moneyline-elo-trend-lr.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$232</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$318</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ232"/>
+  <dimension ref="A1:AJ318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -25338,8 +25338,9544 @@
       <c r="AI232" s="2" t="inlineStr"/>
       <c r="AJ232" s="2" t="inlineStr"/>
     </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>358b9413e2b043e4</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>7363e92b2bdde372</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>401816410</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J233" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K233" s="2" t="inlineStr"/>
+      <c r="L233" s="2" t="inlineStr">
+        <is>
+          <t>0.543314</t>
+        </is>
+      </c>
+      <c r="M233" s="2" t="inlineStr"/>
+      <c r="N233" s="2" t="inlineStr"/>
+      <c r="O233" s="2" t="inlineStr">
+        <is>
+          <t>0.6753246753246753</t>
+        </is>
+      </c>
+      <c r="P233" s="2" t="inlineStr">
+        <is>
+          <t>0.671642</t>
+        </is>
+      </c>
+      <c r="Q233" s="2" t="inlineStr">
+        <is>
+          <t>-0.13201067532467536</t>
+        </is>
+      </c>
+      <c r="R233" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:01:43.592867Z</t>
+        </is>
+      </c>
+      <c r="S233" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T233" s="2" t="inlineStr"/>
+      <c r="U233" s="2" t="inlineStr"/>
+      <c r="V233" s="2" t="inlineStr"/>
+      <c r="W233" s="2" t="inlineStr"/>
+      <c r="X233" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y233" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z233" s="2" t="inlineStr">
+        <is>
+          <t>0.675000</t>
+        </is>
+      </c>
+      <c r="AA233" s="2" t="inlineStr">
+        <is>
+          <t>-0.000325</t>
+        </is>
+      </c>
+      <c r="AB233" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC233" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:20:20.421844Z</t>
+        </is>
+      </c>
+      <c r="AD233" s="2" t="inlineStr"/>
+      <c r="AE233" s="2" t="inlineStr"/>
+      <c r="AF233" s="2" t="inlineStr"/>
+      <c r="AG233" s="2" t="inlineStr"/>
+      <c r="AH233" s="2" t="inlineStr"/>
+      <c r="AI233" s="2" t="inlineStr"/>
+      <c r="AJ233" s="2" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>357c5b667c594bba</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>cd121ba990e73d6d</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>401816406</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J234" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K234" s="2" t="inlineStr"/>
+      <c r="L234" s="2" t="inlineStr">
+        <is>
+          <t>0.522292</t>
+        </is>
+      </c>
+      <c r="M234" s="2" t="inlineStr"/>
+      <c r="N234" s="2" t="inlineStr"/>
+      <c r="O234" s="2" t="inlineStr">
+        <is>
+          <t>0.5260663507109005</t>
+        </is>
+      </c>
+      <c r="P234" s="2" t="inlineStr">
+        <is>
+          <t>0.522388</t>
+        </is>
+      </c>
+      <c r="Q234" s="2" t="inlineStr">
+        <is>
+          <t>-0.003774350710900487</t>
+        </is>
+      </c>
+      <c r="R234" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:01:44.118953Z</t>
+        </is>
+      </c>
+      <c r="S234" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:20:00-0400</t>
+        </is>
+      </c>
+      <c r="T234" s="2" t="inlineStr"/>
+      <c r="U234" s="2" t="inlineStr"/>
+      <c r="V234" s="2" t="inlineStr"/>
+      <c r="W234" s="2" t="inlineStr"/>
+      <c r="X234" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y234" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z234" s="2" t="inlineStr">
+        <is>
+          <t>0.525000</t>
+        </is>
+      </c>
+      <c r="AA234" s="2" t="inlineStr">
+        <is>
+          <t>-0.001066</t>
+        </is>
+      </c>
+      <c r="AB234" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC234" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:20:21.282034Z</t>
+        </is>
+      </c>
+      <c r="AD234" s="2" t="inlineStr"/>
+      <c r="AE234" s="2" t="inlineStr"/>
+      <c r="AF234" s="2" t="inlineStr"/>
+      <c r="AG234" s="2" t="inlineStr"/>
+      <c r="AH234" s="2" t="inlineStr"/>
+      <c r="AI234" s="2" t="inlineStr"/>
+      <c r="AJ234" s="2" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>454290f2b5ff4343</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>b14707c8a9267bdd</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>401816409</t>
+        </is>
+      </c>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J235" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K235" s="2" t="inlineStr"/>
+      <c r="L235" s="2" t="inlineStr">
+        <is>
+          <t>0.585182</t>
+        </is>
+      </c>
+      <c r="M235" s="2" t="inlineStr"/>
+      <c r="N235" s="2" t="inlineStr"/>
+      <c r="O235" s="2" t="inlineStr">
+        <is>
+          <t>0.6047430830039526</t>
+        </is>
+      </c>
+      <c r="P235" s="2" t="inlineStr">
+        <is>
+          <t>0.60199</t>
+        </is>
+      </c>
+      <c r="Q235" s="2" t="inlineStr">
+        <is>
+          <t>-0.01956108300395265</t>
+        </is>
+      </c>
+      <c r="R235" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:01:44.692636Z</t>
+        </is>
+      </c>
+      <c r="S235" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:35:00-0400</t>
+        </is>
+      </c>
+      <c r="T235" s="2" t="inlineStr"/>
+      <c r="U235" s="2" t="inlineStr"/>
+      <c r="V235" s="2" t="inlineStr"/>
+      <c r="W235" s="2" t="inlineStr"/>
+      <c r="X235" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y235" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z235" s="2" t="inlineStr">
+        <is>
+          <t>0.605000</t>
+        </is>
+      </c>
+      <c r="AA235" s="2" t="inlineStr">
+        <is>
+          <t>0.000257</t>
+        </is>
+      </c>
+      <c r="AB235" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC235" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:20:22.147498Z</t>
+        </is>
+      </c>
+      <c r="AD235" s="2" t="inlineStr"/>
+      <c r="AE235" s="2" t="inlineStr"/>
+      <c r="AF235" s="2" t="inlineStr"/>
+      <c r="AG235" s="2" t="inlineStr"/>
+      <c r="AH235" s="2" t="inlineStr"/>
+      <c r="AI235" s="2" t="inlineStr"/>
+      <c r="AJ235" s="2" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>d8445e62cace4e04</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>bad8c8f6d9c491bf</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>401816411</t>
+        </is>
+      </c>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J236" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K236" s="2" t="inlineStr"/>
+      <c r="L236" s="2" t="inlineStr">
+        <is>
+          <t>0.650897</t>
+        </is>
+      </c>
+      <c r="M236" s="2" t="inlineStr"/>
+      <c r="N236" s="2" t="inlineStr"/>
+      <c r="O236" s="2" t="inlineStr">
+        <is>
+          <t>0.6047430830039526</t>
+        </is>
+      </c>
+      <c r="P236" s="2" t="inlineStr">
+        <is>
+          <t>0.60199</t>
+        </is>
+      </c>
+      <c r="Q236" s="2" t="inlineStr">
+        <is>
+          <t>0.04615391699604732</t>
+        </is>
+      </c>
+      <c r="R236" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:01:45.186103Z</t>
+        </is>
+      </c>
+      <c r="S236" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T15:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T236" s="2" t="inlineStr"/>
+      <c r="U236" s="2" t="inlineStr"/>
+      <c r="V236" s="2" t="inlineStr"/>
+      <c r="W236" s="2" t="inlineStr"/>
+      <c r="X236" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y236" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z236" s="2" t="inlineStr">
+        <is>
+          <t>0.605000</t>
+        </is>
+      </c>
+      <c r="AA236" s="2" t="inlineStr">
+        <is>
+          <t>0.000257</t>
+        </is>
+      </c>
+      <c r="AB236" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC236" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:20:23.042607Z</t>
+        </is>
+      </c>
+      <c r="AD236" s="2" t="inlineStr"/>
+      <c r="AE236" s="2" t="inlineStr"/>
+      <c r="AF236" s="2" t="inlineStr"/>
+      <c r="AG236" s="2" t="inlineStr"/>
+      <c r="AH236" s="2" t="inlineStr"/>
+      <c r="AI236" s="2" t="inlineStr"/>
+      <c r="AJ236" s="2" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>416e406b3db145cc</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>118f01d894a0812f</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>401816399</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J237" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K237" s="2" t="inlineStr"/>
+      <c r="L237" s="2" t="inlineStr">
+        <is>
+          <t>0.620086</t>
+        </is>
+      </c>
+      <c r="M237" s="2" t="inlineStr"/>
+      <c r="N237" s="2" t="inlineStr"/>
+      <c r="O237" s="2" t="inlineStr">
+        <is>
+          <t>0.5348837209302326</t>
+        </is>
+      </c>
+      <c r="P237" s="2" t="inlineStr">
+        <is>
+          <t>0.532338</t>
+        </is>
+      </c>
+      <c r="Q237" s="2" t="inlineStr">
+        <is>
+          <t>0.0852022790697674</t>
+        </is>
+      </c>
+      <c r="R237" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:01:45.667039Z</t>
+        </is>
+      </c>
+      <c r="S237" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:35:00-0400</t>
+        </is>
+      </c>
+      <c r="T237" s="2" t="inlineStr"/>
+      <c r="U237" s="2" t="inlineStr"/>
+      <c r="V237" s="2" t="inlineStr"/>
+      <c r="W237" s="2" t="inlineStr"/>
+      <c r="X237" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y237" s="2" t="inlineStr"/>
+      <c r="Z237" s="2" t="inlineStr"/>
+      <c r="AA237" s="2" t="inlineStr"/>
+      <c r="AB237" s="2" t="inlineStr"/>
+      <c r="AC237" s="2" t="inlineStr"/>
+      <c r="AD237" s="2" t="inlineStr"/>
+      <c r="AE237" s="2" t="inlineStr"/>
+      <c r="AF237" s="2" t="inlineStr"/>
+      <c r="AG237" s="2" t="inlineStr"/>
+      <c r="AH237" s="2" t="inlineStr"/>
+      <c r="AI237" s="2" t="inlineStr"/>
+      <c r="AJ237" s="2" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>79155d8d53b94454</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>8420e7560dfdc10d</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>401816400</t>
+        </is>
+      </c>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J238" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K238" s="2" t="inlineStr"/>
+      <c r="L238" s="2" t="inlineStr">
+        <is>
+          <t>0.532033</t>
+        </is>
+      </c>
+      <c r="M238" s="2" t="inlineStr"/>
+      <c r="N238" s="2" t="inlineStr"/>
+      <c r="O238" s="2" t="inlineStr">
+        <is>
+          <t>0.5850622406639003</t>
+        </is>
+      </c>
+      <c r="P238" s="2" t="inlineStr">
+        <is>
+          <t>0.58209</t>
+        </is>
+      </c>
+      <c r="Q238" s="2" t="inlineStr">
+        <is>
+          <t>-0.05302924066390036</t>
+        </is>
+      </c>
+      <c r="R238" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:01:47.554781Z</t>
+        </is>
+      </c>
+      <c r="S238" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T238" s="2" t="inlineStr"/>
+      <c r="U238" s="2" t="inlineStr"/>
+      <c r="V238" s="2" t="inlineStr"/>
+      <c r="W238" s="2" t="inlineStr"/>
+      <c r="X238" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y238" s="2" t="inlineStr"/>
+      <c r="Z238" s="2" t="inlineStr"/>
+      <c r="AA238" s="2" t="inlineStr"/>
+      <c r="AB238" s="2" t="inlineStr"/>
+      <c r="AC238" s="2" t="inlineStr"/>
+      <c r="AD238" s="2" t="inlineStr"/>
+      <c r="AE238" s="2" t="inlineStr"/>
+      <c r="AF238" s="2" t="inlineStr"/>
+      <c r="AG238" s="2" t="inlineStr"/>
+      <c r="AH238" s="2" t="inlineStr"/>
+      <c r="AI238" s="2" t="inlineStr"/>
+      <c r="AJ238" s="2" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>e2d824dd70484800</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>4e3879d5cbf1e43b</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>401816403</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J239" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K239" s="2" t="inlineStr"/>
+      <c r="L239" s="2" t="inlineStr">
+        <is>
+          <t>0.57011</t>
+        </is>
+      </c>
+      <c r="M239" s="2" t="inlineStr"/>
+      <c r="N239" s="2" t="inlineStr"/>
+      <c r="O239" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P239" s="2" t="inlineStr">
+        <is>
+          <t>0.507463</t>
+        </is>
+      </c>
+      <c r="Q239" s="2" t="inlineStr">
+        <is>
+          <t>0.06030607843137259</t>
+        </is>
+      </c>
+      <c r="R239" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:01:46.749322Z</t>
+        </is>
+      </c>
+      <c r="S239" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T239" s="2" t="inlineStr"/>
+      <c r="U239" s="2" t="inlineStr"/>
+      <c r="V239" s="2" t="inlineStr"/>
+      <c r="W239" s="2" t="inlineStr"/>
+      <c r="X239" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y239" s="2" t="inlineStr"/>
+      <c r="Z239" s="2" t="inlineStr"/>
+      <c r="AA239" s="2" t="inlineStr"/>
+      <c r="AB239" s="2" t="inlineStr"/>
+      <c r="AC239" s="2" t="inlineStr"/>
+      <c r="AD239" s="2" t="inlineStr"/>
+      <c r="AE239" s="2" t="inlineStr"/>
+      <c r="AF239" s="2" t="inlineStr"/>
+      <c r="AG239" s="2" t="inlineStr"/>
+      <c r="AH239" s="2" t="inlineStr"/>
+      <c r="AI239" s="2" t="inlineStr"/>
+      <c r="AJ239" s="2" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>907eb44c2dec429d</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>937adc1bae10792b</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>401816405</t>
+        </is>
+      </c>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J240" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K240" s="2" t="inlineStr"/>
+      <c r="L240" s="2" t="inlineStr">
+        <is>
+          <t>0.568243</t>
+        </is>
+      </c>
+      <c r="M240" s="2" t="inlineStr"/>
+      <c r="N240" s="2" t="inlineStr"/>
+      <c r="O240" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P240" s="2" t="inlineStr">
+        <is>
+          <t>0.636816</t>
+        </is>
+      </c>
+      <c r="Q240" s="2" t="inlineStr">
+        <is>
+          <t>-0.07204476978417262</t>
+        </is>
+      </c>
+      <c r="R240" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:01:46.348982Z</t>
+        </is>
+      </c>
+      <c r="S240" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T240" s="2" t="inlineStr"/>
+      <c r="U240" s="2" t="inlineStr"/>
+      <c r="V240" s="2" t="inlineStr"/>
+      <c r="W240" s="2" t="inlineStr"/>
+      <c r="X240" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y240" s="2" t="inlineStr"/>
+      <c r="Z240" s="2" t="inlineStr"/>
+      <c r="AA240" s="2" t="inlineStr"/>
+      <c r="AB240" s="2" t="inlineStr"/>
+      <c r="AC240" s="2" t="inlineStr"/>
+      <c r="AD240" s="2" t="inlineStr"/>
+      <c r="AE240" s="2" t="inlineStr"/>
+      <c r="AF240" s="2" t="inlineStr"/>
+      <c r="AG240" s="2" t="inlineStr"/>
+      <c r="AH240" s="2" t="inlineStr"/>
+      <c r="AI240" s="2" t="inlineStr"/>
+      <c r="AJ240" s="2" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>4cafbb7f1c8f48b4</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>b9323c52a9f5f53a</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>401816404</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J241" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K241" s="2" t="inlineStr"/>
+      <c r="L241" s="2" t="inlineStr">
+        <is>
+          <t>0.585694</t>
+        </is>
+      </c>
+      <c r="M241" s="2" t="inlineStr"/>
+      <c r="N241" s="2" t="inlineStr"/>
+      <c r="O241" s="2" t="inlineStr">
+        <is>
+          <t>0.5951417004048584</t>
+        </is>
+      </c>
+      <c r="P241" s="2" t="inlineStr">
+        <is>
+          <t>0.59204</t>
+        </is>
+      </c>
+      <c r="Q241" s="2" t="inlineStr">
+        <is>
+          <t>-0.009447700404858317</t>
+        </is>
+      </c>
+      <c r="R241" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:01:47.864012Z</t>
+        </is>
+      </c>
+      <c r="S241" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T241" s="2" t="inlineStr"/>
+      <c r="U241" s="2" t="inlineStr"/>
+      <c r="V241" s="2" t="inlineStr"/>
+      <c r="W241" s="2" t="inlineStr"/>
+      <c r="X241" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y241" s="2" t="inlineStr"/>
+      <c r="Z241" s="2" t="inlineStr"/>
+      <c r="AA241" s="2" t="inlineStr"/>
+      <c r="AB241" s="2" t="inlineStr"/>
+      <c r="AC241" s="2" t="inlineStr"/>
+      <c r="AD241" s="2" t="inlineStr"/>
+      <c r="AE241" s="2" t="inlineStr"/>
+      <c r="AF241" s="2" t="inlineStr"/>
+      <c r="AG241" s="2" t="inlineStr"/>
+      <c r="AH241" s="2" t="inlineStr"/>
+      <c r="AI241" s="2" t="inlineStr"/>
+      <c r="AJ241" s="2" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>1ba2b5390b504aee</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>10f5b05f22dccd69</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>401816401</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J242" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K242" s="2" t="inlineStr"/>
+      <c r="L242" s="2" t="inlineStr">
+        <is>
+          <t>0.576188</t>
+        </is>
+      </c>
+      <c r="M242" s="2" t="inlineStr"/>
+      <c r="N242" s="2" t="inlineStr"/>
+      <c r="O242" s="2" t="inlineStr">
+        <is>
+          <t>0.5555555555555556</t>
+        </is>
+      </c>
+      <c r="P242" s="2" t="inlineStr">
+        <is>
+          <t>0.552239</t>
+        </is>
+      </c>
+      <c r="Q242" s="2" t="inlineStr">
+        <is>
+          <t>0.020632444444444453</t>
+        </is>
+      </c>
+      <c r="R242" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:01:48.372889Z</t>
+        </is>
+      </c>
+      <c r="S242" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T242" s="2" t="inlineStr"/>
+      <c r="U242" s="2" t="inlineStr"/>
+      <c r="V242" s="2" t="inlineStr"/>
+      <c r="W242" s="2" t="inlineStr"/>
+      <c r="X242" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y242" s="2" t="inlineStr"/>
+      <c r="Z242" s="2" t="inlineStr"/>
+      <c r="AA242" s="2" t="inlineStr"/>
+      <c r="AB242" s="2" t="inlineStr"/>
+      <c r="AC242" s="2" t="inlineStr"/>
+      <c r="AD242" s="2" t="inlineStr"/>
+      <c r="AE242" s="2" t="inlineStr"/>
+      <c r="AF242" s="2" t="inlineStr"/>
+      <c r="AG242" s="2" t="inlineStr"/>
+      <c r="AH242" s="2" t="inlineStr"/>
+      <c r="AI242" s="2" t="inlineStr"/>
+      <c r="AJ242" s="2" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>1eab0dfb18ae4580</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>db6d6c1b1ab98d0d</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>401816402</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J243" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K243" s="2" t="inlineStr"/>
+      <c r="L243" s="2" t="inlineStr">
+        <is>
+          <t>0.590566</t>
+        </is>
+      </c>
+      <c r="M243" s="2" t="inlineStr"/>
+      <c r="N243" s="2" t="inlineStr"/>
+      <c r="O243" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P243" s="2" t="inlineStr">
+        <is>
+          <t>0.537313</t>
+        </is>
+      </c>
+      <c r="Q243" s="2" t="inlineStr">
+        <is>
+          <t>0.05139549308755764</t>
+        </is>
+      </c>
+      <c r="R243" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:01:48.928230Z</t>
+        </is>
+      </c>
+      <c r="S243" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T243" s="2" t="inlineStr"/>
+      <c r="U243" s="2" t="inlineStr"/>
+      <c r="V243" s="2" t="inlineStr"/>
+      <c r="W243" s="2" t="inlineStr"/>
+      <c r="X243" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y243" s="2" t="inlineStr"/>
+      <c r="Z243" s="2" t="inlineStr"/>
+      <c r="AA243" s="2" t="inlineStr"/>
+      <c r="AB243" s="2" t="inlineStr"/>
+      <c r="AC243" s="2" t="inlineStr"/>
+      <c r="AD243" s="2" t="inlineStr"/>
+      <c r="AE243" s="2" t="inlineStr"/>
+      <c r="AF243" s="2" t="inlineStr"/>
+      <c r="AG243" s="2" t="inlineStr"/>
+      <c r="AH243" s="2" t="inlineStr"/>
+      <c r="AI243" s="2" t="inlineStr"/>
+      <c r="AJ243" s="2" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>c7e89f39754b4fcf</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>23aa584b6028ab97</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>401816408</t>
+        </is>
+      </c>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J244" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K244" s="2" t="inlineStr"/>
+      <c r="L244" s="2" t="inlineStr">
+        <is>
+          <t>0.615508</t>
+        </is>
+      </c>
+      <c r="M244" s="2" t="inlineStr"/>
+      <c r="N244" s="2" t="inlineStr"/>
+      <c r="O244" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P244" s="2" t="inlineStr">
+        <is>
+          <t>0.547264</t>
+        </is>
+      </c>
+      <c r="Q244" s="2" t="inlineStr">
+        <is>
+          <t>0.06595845045045057</t>
+        </is>
+      </c>
+      <c r="R244" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:01:49.377801Z</t>
+        </is>
+      </c>
+      <c r="S244" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="T244" s="2" t="inlineStr"/>
+      <c r="U244" s="2" t="inlineStr"/>
+      <c r="V244" s="2" t="inlineStr"/>
+      <c r="W244" s="2" t="inlineStr"/>
+      <c r="X244" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y244" s="2" t="inlineStr"/>
+      <c r="Z244" s="2" t="inlineStr"/>
+      <c r="AA244" s="2" t="inlineStr"/>
+      <c r="AB244" s="2" t="inlineStr"/>
+      <c r="AC244" s="2" t="inlineStr"/>
+      <c r="AD244" s="2" t="inlineStr"/>
+      <c r="AE244" s="2" t="inlineStr"/>
+      <c r="AF244" s="2" t="inlineStr"/>
+      <c r="AG244" s="2" t="inlineStr"/>
+      <c r="AH244" s="2" t="inlineStr"/>
+      <c r="AI244" s="2" t="inlineStr"/>
+      <c r="AJ244" s="2" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>ebd575b2f113434b</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>7953986ab64aa910</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>401816407</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K245" s="2" t="inlineStr"/>
+      <c r="L245" s="2" t="inlineStr">
+        <is>
+          <t>0.524906</t>
+        </is>
+      </c>
+      <c r="M245" s="2" t="inlineStr"/>
+      <c r="N245" s="2" t="inlineStr"/>
+      <c r="O245" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P245" s="2" t="inlineStr">
+        <is>
+          <t>0.527363</t>
+        </is>
+      </c>
+      <c r="Q245" s="2" t="inlineStr">
+        <is>
+          <t>-0.005610431924882642</t>
+        </is>
+      </c>
+      <c r="R245" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:01:49.934563Z</t>
+        </is>
+      </c>
+      <c r="S245" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T245" s="2" t="inlineStr"/>
+      <c r="U245" s="2" t="inlineStr"/>
+      <c r="V245" s="2" t="inlineStr"/>
+      <c r="W245" s="2" t="inlineStr"/>
+      <c r="X245" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y245" s="2" t="inlineStr"/>
+      <c r="Z245" s="2" t="inlineStr"/>
+      <c r="AA245" s="2" t="inlineStr"/>
+      <c r="AB245" s="2" t="inlineStr"/>
+      <c r="AC245" s="2" t="inlineStr"/>
+      <c r="AD245" s="2" t="inlineStr"/>
+      <c r="AE245" s="2" t="inlineStr"/>
+      <c r="AF245" s="2" t="inlineStr"/>
+      <c r="AG245" s="2" t="inlineStr"/>
+      <c r="AH245" s="2" t="inlineStr"/>
+      <c r="AI245" s="2" t="inlineStr"/>
+      <c r="AJ245" s="2" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>e7fd7a42e05e4a89</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>1869d7c91b8ee576</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>401816412</t>
+        </is>
+      </c>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K246" s="2" t="inlineStr"/>
+      <c r="L246" s="2" t="inlineStr">
+        <is>
+          <t>0.550053</t>
+        </is>
+      </c>
+      <c r="M246" s="2" t="inlineStr"/>
+      <c r="N246" s="2" t="inlineStr"/>
+      <c r="O246" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P246" s="2" t="inlineStr">
+        <is>
+          <t>0.587065</t>
+        </is>
+      </c>
+      <c r="Q246" s="2" t="inlineStr">
+        <is>
+          <t>-0.04011093442622948</t>
+        </is>
+      </c>
+      <c r="R246" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:01:50.511019Z</t>
+        </is>
+      </c>
+      <c r="S246" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T246" s="2" t="inlineStr"/>
+      <c r="U246" s="2" t="inlineStr"/>
+      <c r="V246" s="2" t="inlineStr"/>
+      <c r="W246" s="2" t="inlineStr"/>
+      <c r="X246" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y246" s="2" t="inlineStr"/>
+      <c r="Z246" s="2" t="inlineStr"/>
+      <c r="AA246" s="2" t="inlineStr"/>
+      <c r="AB246" s="2" t="inlineStr"/>
+      <c r="AC246" s="2" t="inlineStr"/>
+      <c r="AD246" s="2" t="inlineStr"/>
+      <c r="AE246" s="2" t="inlineStr"/>
+      <c r="AF246" s="2" t="inlineStr"/>
+      <c r="AG246" s="2" t="inlineStr"/>
+      <c r="AH246" s="2" t="inlineStr"/>
+      <c r="AI246" s="2" t="inlineStr"/>
+      <c r="AJ246" s="2" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>db4a5c714a1c40f8</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>f27ad71f21952264</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>401816413</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J247" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K247" s="2" t="inlineStr"/>
+      <c r="L247" s="2" t="inlineStr">
+        <is>
+          <t>0.512293</t>
+        </is>
+      </c>
+      <c r="M247" s="2" t="inlineStr"/>
+      <c r="N247" s="2" t="inlineStr"/>
+      <c r="O247" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P247" s="2" t="inlineStr">
+        <is>
+          <t>0.537313</t>
+        </is>
+      </c>
+      <c r="Q247" s="2" t="inlineStr">
+        <is>
+          <t>-0.026877506912442395</t>
+        </is>
+      </c>
+      <c r="R247" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:01:51.165525Z</t>
+        </is>
+      </c>
+      <c r="S247" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T247" s="2" t="inlineStr"/>
+      <c r="U247" s="2" t="inlineStr"/>
+      <c r="V247" s="2" t="inlineStr"/>
+      <c r="W247" s="2" t="inlineStr"/>
+      <c r="X247" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y247" s="2" t="inlineStr"/>
+      <c r="Z247" s="2" t="inlineStr"/>
+      <c r="AA247" s="2" t="inlineStr"/>
+      <c r="AB247" s="2" t="inlineStr"/>
+      <c r="AC247" s="2" t="inlineStr"/>
+      <c r="AD247" s="2" t="inlineStr"/>
+      <c r="AE247" s="2" t="inlineStr"/>
+      <c r="AF247" s="2" t="inlineStr"/>
+      <c r="AG247" s="2" t="inlineStr"/>
+      <c r="AH247" s="2" t="inlineStr"/>
+      <c r="AI247" s="2" t="inlineStr"/>
+      <c r="AJ247" s="2" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>7fe00ac657aa40c3</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>733906b627a19369</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>401816399</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J248" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K248" s="2" t="inlineStr"/>
+      <c r="L248" s="2" t="inlineStr">
+        <is>
+          <t>0.620128</t>
+        </is>
+      </c>
+      <c r="M248" s="2" t="inlineStr"/>
+      <c r="N248" s="2" t="inlineStr"/>
+      <c r="O248" s="2" t="inlineStr">
+        <is>
+          <t>0.5555555555555556</t>
+        </is>
+      </c>
+      <c r="P248" s="2" t="inlineStr">
+        <is>
+          <t>0.552239</t>
+        </is>
+      </c>
+      <c r="Q248" s="2" t="inlineStr">
+        <is>
+          <t>0.06457244444444443</t>
+        </is>
+      </c>
+      <c r="R248" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:45.060709Z</t>
+        </is>
+      </c>
+      <c r="S248" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:35:00-0400</t>
+        </is>
+      </c>
+      <c r="T248" s="2" t="inlineStr"/>
+      <c r="U248" s="2" t="inlineStr"/>
+      <c r="V248" s="2" t="inlineStr"/>
+      <c r="W248" s="2" t="inlineStr"/>
+      <c r="X248" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y248" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z248" s="2" t="inlineStr">
+        <is>
+          <t>0.555000</t>
+        </is>
+      </c>
+      <c r="AA248" s="2" t="inlineStr">
+        <is>
+          <t>-0.000556</t>
+        </is>
+      </c>
+      <c r="AB248" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC248" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T03:25:39.653026Z</t>
+        </is>
+      </c>
+      <c r="AD248" s="2" t="inlineStr"/>
+      <c r="AE248" s="2" t="inlineStr"/>
+      <c r="AF248" s="2" t="inlineStr"/>
+      <c r="AG248" s="2" t="inlineStr"/>
+      <c r="AH248" s="2" t="inlineStr"/>
+      <c r="AI248" s="2" t="inlineStr"/>
+      <c r="AJ248" s="2" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>e4cb039a279a4fcf</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>2f8950260ee7a4d4</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>401816400</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J249" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K249" s="2" t="inlineStr"/>
+      <c r="L249" s="2" t="inlineStr">
+        <is>
+          <t>0.532159</t>
+        </is>
+      </c>
+      <c r="M249" s="2" t="inlineStr"/>
+      <c r="N249" s="2" t="inlineStr"/>
+      <c r="O249" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P249" s="2" t="inlineStr">
+        <is>
+          <t>0.597015</t>
+        </is>
+      </c>
+      <c r="Q249" s="2" t="inlineStr">
+        <is>
+          <t>-0.06784100000000004</t>
+        </is>
+      </c>
+      <c r="R249" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:46.705183Z</t>
+        </is>
+      </c>
+      <c r="S249" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T249" s="2" t="inlineStr"/>
+      <c r="U249" s="2" t="inlineStr"/>
+      <c r="V249" s="2" t="inlineStr"/>
+      <c r="W249" s="2" t="inlineStr"/>
+      <c r="X249" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y249" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z249" s="2" t="inlineStr">
+        <is>
+          <t>0.600000</t>
+        </is>
+      </c>
+      <c r="AA249" s="2" t="inlineStr">
+        <is>
+          <t>0.000000</t>
+        </is>
+      </c>
+      <c r="AB249" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC249" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T03:25:41.600222Z</t>
+        </is>
+      </c>
+      <c r="AD249" s="2" t="inlineStr"/>
+      <c r="AE249" s="2" t="inlineStr"/>
+      <c r="AF249" s="2" t="inlineStr"/>
+      <c r="AG249" s="2" t="inlineStr"/>
+      <c r="AH249" s="2" t="inlineStr"/>
+      <c r="AI249" s="2" t="inlineStr"/>
+      <c r="AJ249" s="2" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>fb6822915b72436c</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>1967000172c70546</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>401816403</t>
+        </is>
+      </c>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J250" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K250" s="2" t="inlineStr"/>
+      <c r="L250" s="2" t="inlineStr">
+        <is>
+          <t>0.570176</t>
+        </is>
+      </c>
+      <c r="M250" s="2" t="inlineStr"/>
+      <c r="N250" s="2" t="inlineStr"/>
+      <c r="O250" s="2" t="inlineStr">
+        <is>
+          <t>0.5145631067961165</t>
+        </is>
+      </c>
+      <c r="P250" s="2" t="inlineStr">
+        <is>
+          <t>0.512438</t>
+        </is>
+      </c>
+      <c r="Q250" s="2" t="inlineStr">
+        <is>
+          <t>0.05561289320388352</t>
+        </is>
+      </c>
+      <c r="R250" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:46.075346Z</t>
+        </is>
+      </c>
+      <c r="S250" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T250" s="2" t="inlineStr"/>
+      <c r="U250" s="2" t="inlineStr"/>
+      <c r="V250" s="2" t="inlineStr"/>
+      <c r="W250" s="2" t="inlineStr"/>
+      <c r="X250" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y250" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z250" s="2" t="inlineStr">
+        <is>
+          <t>0.515000</t>
+        </is>
+      </c>
+      <c r="AA250" s="2" t="inlineStr">
+        <is>
+          <t>0.000437</t>
+        </is>
+      </c>
+      <c r="AB250" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC250" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T03:25:43.465125Z</t>
+        </is>
+      </c>
+      <c r="AD250" s="2" t="inlineStr"/>
+      <c r="AE250" s="2" t="inlineStr"/>
+      <c r="AF250" s="2" t="inlineStr"/>
+      <c r="AG250" s="2" t="inlineStr"/>
+      <c r="AH250" s="2" t="inlineStr"/>
+      <c r="AI250" s="2" t="inlineStr"/>
+      <c r="AJ250" s="2" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>64f73ae1b62347b0</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>f438f0ddf592c10b</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>401816405</t>
+        </is>
+      </c>
+      <c r="I251" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J251" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K251" s="2" t="inlineStr"/>
+      <c r="L251" s="2" t="inlineStr">
+        <is>
+          <t>0.568061</t>
+        </is>
+      </c>
+      <c r="M251" s="2" t="inlineStr"/>
+      <c r="N251" s="2" t="inlineStr"/>
+      <c r="O251" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P251" s="2" t="inlineStr">
+        <is>
+          <t>0.646766</t>
+        </is>
+      </c>
+      <c r="Q251" s="2" t="inlineStr">
+        <is>
+          <t>-0.08228865034965027</t>
+        </is>
+      </c>
+      <c r="R251" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:45.630183Z</t>
+        </is>
+      </c>
+      <c r="S251" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T251" s="2" t="inlineStr"/>
+      <c r="U251" s="2" t="inlineStr"/>
+      <c r="V251" s="2" t="inlineStr"/>
+      <c r="W251" s="2" t="inlineStr"/>
+      <c r="X251" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y251" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z251" s="2" t="inlineStr">
+        <is>
+          <t>0.645000</t>
+        </is>
+      </c>
+      <c r="AA251" s="2" t="inlineStr">
+        <is>
+          <t>-0.005350</t>
+        </is>
+      </c>
+      <c r="AB251" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC251" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T03:25:45.321659Z</t>
+        </is>
+      </c>
+      <c r="AD251" s="2" t="inlineStr"/>
+      <c r="AE251" s="2" t="inlineStr"/>
+      <c r="AF251" s="2" t="inlineStr"/>
+      <c r="AG251" s="2" t="inlineStr"/>
+      <c r="AH251" s="2" t="inlineStr"/>
+      <c r="AI251" s="2" t="inlineStr"/>
+      <c r="AJ251" s="2" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>e838b73495b146e5</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>f0272f609cc15047</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>401816404</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J252" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K252" s="2" t="inlineStr"/>
+      <c r="L252" s="2" t="inlineStr">
+        <is>
+          <t>0.585803</t>
+        </is>
+      </c>
+      <c r="M252" s="2" t="inlineStr"/>
+      <c r="N252" s="2" t="inlineStr"/>
+      <c r="O252" s="2" t="inlineStr">
+        <is>
+          <t>0.5951417004048584</t>
+        </is>
+      </c>
+      <c r="P252" s="2" t="inlineStr">
+        <is>
+          <t>0.59204</t>
+        </is>
+      </c>
+      <c r="Q252" s="2" t="inlineStr">
+        <is>
+          <t>-0.009338700404858402</t>
+        </is>
+      </c>
+      <c r="R252" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:47.059173Z</t>
+        </is>
+      </c>
+      <c r="S252" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T252" s="2" t="inlineStr"/>
+      <c r="U252" s="2" t="inlineStr"/>
+      <c r="V252" s="2" t="inlineStr"/>
+      <c r="W252" s="2" t="inlineStr"/>
+      <c r="X252" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y252" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z252" s="2" t="inlineStr">
+        <is>
+          <t>0.595000</t>
+        </is>
+      </c>
+      <c r="AA252" s="2" t="inlineStr">
+        <is>
+          <t>-0.000142</t>
+        </is>
+      </c>
+      <c r="AB252" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC252" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:54:03.074948Z</t>
+        </is>
+      </c>
+      <c r="AD252" s="2" t="inlineStr"/>
+      <c r="AE252" s="2" t="inlineStr"/>
+      <c r="AF252" s="2" t="inlineStr"/>
+      <c r="AG252" s="2" t="inlineStr"/>
+      <c r="AH252" s="2" t="inlineStr"/>
+      <c r="AI252" s="2" t="inlineStr"/>
+      <c r="AJ252" s="2" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>c9c10ce88c704537</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>efcfcc3269a8ddbe</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>401816401</t>
+        </is>
+      </c>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J253" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K253" s="2" t="inlineStr"/>
+      <c r="L253" s="2" t="inlineStr">
+        <is>
+          <t>0.576049</t>
+        </is>
+      </c>
+      <c r="M253" s="2" t="inlineStr"/>
+      <c r="N253" s="2" t="inlineStr"/>
+      <c r="O253" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P253" s="2" t="inlineStr">
+        <is>
+          <t>0.557214</t>
+        </is>
+      </c>
+      <c r="Q253" s="2" t="inlineStr">
+        <is>
+          <t>0.016577634361233495</t>
+        </is>
+      </c>
+      <c r="R253" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:47.679094Z</t>
+        </is>
+      </c>
+      <c r="S253" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T253" s="2" t="inlineStr"/>
+      <c r="U253" s="2" t="inlineStr"/>
+      <c r="V253" s="2" t="inlineStr"/>
+      <c r="W253" s="2" t="inlineStr"/>
+      <c r="X253" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y253" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z253" s="2" t="inlineStr">
+        <is>
+          <t>0.560000</t>
+        </is>
+      </c>
+      <c r="AA253" s="2" t="inlineStr">
+        <is>
+          <t>0.000529</t>
+        </is>
+      </c>
+      <c r="AB253" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC253" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T03:25:47.380603Z</t>
+        </is>
+      </c>
+      <c r="AD253" s="2" t="inlineStr"/>
+      <c r="AE253" s="2" t="inlineStr"/>
+      <c r="AF253" s="2" t="inlineStr"/>
+      <c r="AG253" s="2" t="inlineStr"/>
+      <c r="AH253" s="2" t="inlineStr"/>
+      <c r="AI253" s="2" t="inlineStr"/>
+      <c r="AJ253" s="2" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>ac224517cb4643c3</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>15ad345ce9703e7c</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>401816402</t>
+        </is>
+      </c>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J254" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K254" s="2" t="inlineStr"/>
+      <c r="L254" s="2" t="inlineStr">
+        <is>
+          <t>0.590919</t>
+        </is>
+      </c>
+      <c r="M254" s="2" t="inlineStr"/>
+      <c r="N254" s="2" t="inlineStr"/>
+      <c r="O254" s="2" t="inlineStr">
+        <is>
+          <t>0.5454545454545454</t>
+        </is>
+      </c>
+      <c r="P254" s="2" t="inlineStr">
+        <is>
+          <t>0.542289</t>
+        </is>
+      </c>
+      <c r="Q254" s="2" t="inlineStr">
+        <is>
+          <t>0.04546445454545456</t>
+        </is>
+      </c>
+      <c r="R254" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:48.076723Z</t>
+        </is>
+      </c>
+      <c r="S254" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T254" s="2" t="inlineStr"/>
+      <c r="U254" s="2" t="inlineStr"/>
+      <c r="V254" s="2" t="inlineStr"/>
+      <c r="W254" s="2" t="inlineStr"/>
+      <c r="X254" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y254" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z254" s="2" t="inlineStr">
+        <is>
+          <t>0.545000</t>
+        </is>
+      </c>
+      <c r="AA254" s="2" t="inlineStr">
+        <is>
+          <t>-0.000455</t>
+        </is>
+      </c>
+      <c r="AB254" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC254" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T03:25:49.985859Z</t>
+        </is>
+      </c>
+      <c r="AD254" s="2" t="inlineStr"/>
+      <c r="AE254" s="2" t="inlineStr"/>
+      <c r="AF254" s="2" t="inlineStr"/>
+      <c r="AG254" s="2" t="inlineStr"/>
+      <c r="AH254" s="2" t="inlineStr"/>
+      <c r="AI254" s="2" t="inlineStr"/>
+      <c r="AJ254" s="2" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>a10473666b864c73</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>23aa584b6028ab97</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>401816408</t>
+        </is>
+      </c>
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J255" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K255" s="2" t="inlineStr"/>
+      <c r="L255" s="2" t="inlineStr">
+        <is>
+          <t>0.615508</t>
+        </is>
+      </c>
+      <c r="M255" s="2" t="inlineStr"/>
+      <c r="N255" s="2" t="inlineStr"/>
+      <c r="O255" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P255" s="2" t="inlineStr">
+        <is>
+          <t>0.547264</t>
+        </is>
+      </c>
+      <c r="Q255" s="2" t="inlineStr">
+        <is>
+          <t>0.06595845045045057</t>
+        </is>
+      </c>
+      <c r="R255" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:48.549898Z</t>
+        </is>
+      </c>
+      <c r="S255" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="T255" s="2" t="inlineStr"/>
+      <c r="U255" s="2" t="inlineStr"/>
+      <c r="V255" s="2" t="inlineStr"/>
+      <c r="W255" s="2" t="inlineStr"/>
+      <c r="X255" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y255" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z255" s="2" t="inlineStr">
+        <is>
+          <t>0.550000</t>
+        </is>
+      </c>
+      <c r="AA255" s="2" t="inlineStr">
+        <is>
+          <t>0.000450</t>
+        </is>
+      </c>
+      <c r="AB255" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC255" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T03:25:51.952665Z</t>
+        </is>
+      </c>
+      <c r="AD255" s="2" t="inlineStr"/>
+      <c r="AE255" s="2" t="inlineStr"/>
+      <c r="AF255" s="2" t="inlineStr"/>
+      <c r="AG255" s="2" t="inlineStr"/>
+      <c r="AH255" s="2" t="inlineStr"/>
+      <c r="AI255" s="2" t="inlineStr"/>
+      <c r="AJ255" s="2" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>0a810cfd047e42ab</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>f737968b03170f81</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>401816407</t>
+        </is>
+      </c>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J256" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K256" s="2" t="inlineStr"/>
+      <c r="L256" s="2" t="inlineStr">
+        <is>
+          <t>0.525738</t>
+        </is>
+      </c>
+      <c r="M256" s="2" t="inlineStr"/>
+      <c r="N256" s="2" t="inlineStr"/>
+      <c r="O256" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P256" s="2" t="inlineStr">
+        <is>
+          <t>0.527363</t>
+        </is>
+      </c>
+      <c r="Q256" s="2" t="inlineStr">
+        <is>
+          <t>-0.004778431924882587</t>
+        </is>
+      </c>
+      <c r="R256" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:49.052291Z</t>
+        </is>
+      </c>
+      <c r="S256" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T256" s="2" t="inlineStr"/>
+      <c r="U256" s="2" t="inlineStr"/>
+      <c r="V256" s="2" t="inlineStr"/>
+      <c r="W256" s="2" t="inlineStr"/>
+      <c r="X256" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y256" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z256" s="2" t="inlineStr">
+        <is>
+          <t>0.530000</t>
+        </is>
+      </c>
+      <c r="AA256" s="2" t="inlineStr">
+        <is>
+          <t>-0.000516</t>
+        </is>
+      </c>
+      <c r="AB256" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC256" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T03:25:53.782769Z</t>
+        </is>
+      </c>
+      <c r="AD256" s="2" t="inlineStr"/>
+      <c r="AE256" s="2" t="inlineStr"/>
+      <c r="AF256" s="2" t="inlineStr"/>
+      <c r="AG256" s="2" t="inlineStr"/>
+      <c r="AH256" s="2" t="inlineStr"/>
+      <c r="AI256" s="2" t="inlineStr"/>
+      <c r="AJ256" s="2" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>8c8ecb6dd0d04025</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>1869d7c91b8ee576</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>401816412</t>
+        </is>
+      </c>
+      <c r="I257" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J257" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K257" s="2" t="inlineStr"/>
+      <c r="L257" s="2" t="inlineStr">
+        <is>
+          <t>0.550053</t>
+        </is>
+      </c>
+      <c r="M257" s="2" t="inlineStr"/>
+      <c r="N257" s="2" t="inlineStr"/>
+      <c r="O257" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P257" s="2" t="inlineStr">
+        <is>
+          <t>0.587065</t>
+        </is>
+      </c>
+      <c r="Q257" s="2" t="inlineStr">
+        <is>
+          <t>-0.04011093442622948</t>
+        </is>
+      </c>
+      <c r="R257" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:49.522268Z</t>
+        </is>
+      </c>
+      <c r="S257" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T257" s="2" t="inlineStr"/>
+      <c r="U257" s="2" t="inlineStr"/>
+      <c r="V257" s="2" t="inlineStr"/>
+      <c r="W257" s="2" t="inlineStr"/>
+      <c r="X257" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y257" s="2" t="inlineStr"/>
+      <c r="Z257" s="2" t="inlineStr"/>
+      <c r="AA257" s="2" t="inlineStr"/>
+      <c r="AB257" s="2" t="inlineStr"/>
+      <c r="AC257" s="2" t="inlineStr"/>
+      <c r="AD257" s="2" t="inlineStr"/>
+      <c r="AE257" s="2" t="inlineStr"/>
+      <c r="AF257" s="2" t="inlineStr"/>
+      <c r="AG257" s="2" t="inlineStr"/>
+      <c r="AH257" s="2" t="inlineStr"/>
+      <c r="AI257" s="2" t="inlineStr"/>
+      <c r="AJ257" s="2" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>9cfcd37240114eeb</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>f27ad71f21952264</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>401816413</t>
+        </is>
+      </c>
+      <c r="I258" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J258" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K258" s="2" t="inlineStr"/>
+      <c r="L258" s="2" t="inlineStr">
+        <is>
+          <t>0.512293</t>
+        </is>
+      </c>
+      <c r="M258" s="2" t="inlineStr"/>
+      <c r="N258" s="2" t="inlineStr"/>
+      <c r="O258" s="2" t="inlineStr">
+        <is>
+          <t>0.5454545454545454</t>
+        </is>
+      </c>
+      <c r="P258" s="2" t="inlineStr">
+        <is>
+          <t>0.542289</t>
+        </is>
+      </c>
+      <c r="Q258" s="2" t="inlineStr">
+        <is>
+          <t>-0.033161545454545416</t>
+        </is>
+      </c>
+      <c r="R258" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:49.941239Z</t>
+        </is>
+      </c>
+      <c r="S258" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T258" s="2" t="inlineStr"/>
+      <c r="U258" s="2" t="inlineStr"/>
+      <c r="V258" s="2" t="inlineStr"/>
+      <c r="W258" s="2" t="inlineStr"/>
+      <c r="X258" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y258" s="2" t="inlineStr"/>
+      <c r="Z258" s="2" t="inlineStr"/>
+      <c r="AA258" s="2" t="inlineStr"/>
+      <c r="AB258" s="2" t="inlineStr"/>
+      <c r="AC258" s="2" t="inlineStr"/>
+      <c r="AD258" s="2" t="inlineStr"/>
+      <c r="AE258" s="2" t="inlineStr"/>
+      <c r="AF258" s="2" t="inlineStr"/>
+      <c r="AG258" s="2" t="inlineStr"/>
+      <c r="AH258" s="2" t="inlineStr"/>
+      <c r="AI258" s="2" t="inlineStr"/>
+      <c r="AJ258" s="2" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>55242da3a8f244e0</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>18de224cacd80118</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>401816412</t>
+        </is>
+      </c>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J259" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K259" s="2" t="inlineStr"/>
+      <c r="L259" s="2" t="inlineStr">
+        <is>
+          <t>0.549586</t>
+        </is>
+      </c>
+      <c r="M259" s="2" t="inlineStr"/>
+      <c r="N259" s="2" t="inlineStr"/>
+      <c r="O259" s="2" t="inlineStr">
+        <is>
+          <t>0.5850622406639003</t>
+        </is>
+      </c>
+      <c r="P259" s="2" t="inlineStr">
+        <is>
+          <t>0.58209</t>
+        </is>
+      </c>
+      <c r="Q259" s="2" t="inlineStr">
+        <is>
+          <t>-0.035476240663900316</t>
+        </is>
+      </c>
+      <c r="R259" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:22:57.008358Z</t>
+        </is>
+      </c>
+      <c r="S259" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T259" s="2" t="inlineStr"/>
+      <c r="U259" s="2" t="inlineStr"/>
+      <c r="V259" s="2" t="inlineStr"/>
+      <c r="W259" s="2" t="inlineStr"/>
+      <c r="X259" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y259" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z259" s="2" t="inlineStr">
+        <is>
+          <t>0.585000</t>
+        </is>
+      </c>
+      <c r="AA259" s="2" t="inlineStr">
+        <is>
+          <t>-0.000062</t>
+        </is>
+      </c>
+      <c r="AB259" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC259" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:54:08.722956Z</t>
+        </is>
+      </c>
+      <c r="AD259" s="2" t="inlineStr"/>
+      <c r="AE259" s="2" t="inlineStr"/>
+      <c r="AF259" s="2" t="inlineStr"/>
+      <c r="AG259" s="2" t="inlineStr"/>
+      <c r="AH259" s="2" t="inlineStr"/>
+      <c r="AI259" s="2" t="inlineStr"/>
+      <c r="AJ259" s="2" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>75ca86356d6644f5</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>0baa18332e487c9b</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>401816413</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J260" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K260" s="2" t="inlineStr"/>
+      <c r="L260" s="2" t="inlineStr">
+        <is>
+          <t>0.51228</t>
+        </is>
+      </c>
+      <c r="M260" s="2" t="inlineStr"/>
+      <c r="N260" s="2" t="inlineStr"/>
+      <c r="O260" s="2" t="inlineStr">
+        <is>
+          <t>0.5652173913043479</t>
+        </is>
+      </c>
+      <c r="P260" s="2" t="inlineStr">
+        <is>
+          <t>0.562189</t>
+        </is>
+      </c>
+      <c r="Q260" s="2" t="inlineStr">
+        <is>
+          <t>-0.052937391304347936</t>
+        </is>
+      </c>
+      <c r="R260" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:22:57.322907Z</t>
+        </is>
+      </c>
+      <c r="S260" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T260" s="2" t="inlineStr"/>
+      <c r="U260" s="2" t="inlineStr"/>
+      <c r="V260" s="2" t="inlineStr"/>
+      <c r="W260" s="2" t="inlineStr"/>
+      <c r="X260" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y260" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z260" s="2" t="inlineStr">
+        <is>
+          <t>0.565000</t>
+        </is>
+      </c>
+      <c r="AA260" s="2" t="inlineStr">
+        <is>
+          <t>-0.000217</t>
+        </is>
+      </c>
+      <c r="AB260" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC260" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:54:10.619052Z</t>
+        </is>
+      </c>
+      <c r="AD260" s="2" t="inlineStr"/>
+      <c r="AE260" s="2" t="inlineStr"/>
+      <c r="AF260" s="2" t="inlineStr"/>
+      <c r="AG260" s="2" t="inlineStr"/>
+      <c r="AH260" s="2" t="inlineStr"/>
+      <c r="AI260" s="2" t="inlineStr"/>
+      <c r="AJ260" s="2" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>fb4354693c82464a</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>77aa3b27790b8cf7</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>401816422</t>
+        </is>
+      </c>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J261" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K261" s="2" t="inlineStr"/>
+      <c r="L261" s="2" t="inlineStr">
+        <is>
+          <t>0.558121</t>
+        </is>
+      </c>
+      <c r="M261" s="2" t="inlineStr"/>
+      <c r="N261" s="2" t="inlineStr"/>
+      <c r="O261" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P261" s="2" t="inlineStr">
+        <is>
+          <t>0.527363</t>
+        </is>
+      </c>
+      <c r="Q261" s="2" t="inlineStr">
+        <is>
+          <t>0.027604568075117353</t>
+        </is>
+      </c>
+      <c r="R261" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:53.058009Z</t>
+        </is>
+      </c>
+      <c r="S261" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T16:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T261" s="2" t="inlineStr"/>
+      <c r="U261" s="2" t="inlineStr"/>
+      <c r="V261" s="2" t="inlineStr"/>
+      <c r="W261" s="2" t="inlineStr"/>
+      <c r="X261" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y261" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z261" s="2" t="inlineStr">
+        <is>
+          <t>0.530000</t>
+        </is>
+      </c>
+      <c r="AA261" s="2" t="inlineStr">
+        <is>
+          <t>-0.000516</t>
+        </is>
+      </c>
+      <c r="AB261" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC261" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:06:25.124523Z</t>
+        </is>
+      </c>
+      <c r="AD261" s="2" t="inlineStr"/>
+      <c r="AE261" s="2" t="inlineStr"/>
+      <c r="AF261" s="2" t="inlineStr"/>
+      <c r="AG261" s="2" t="inlineStr"/>
+      <c r="AH261" s="2" t="inlineStr"/>
+      <c r="AI261" s="2" t="inlineStr"/>
+      <c r="AJ261" s="2" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>104884fdfba04ace</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>3e52859e0e873013</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>401816419</t>
+        </is>
+      </c>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J262" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K262" s="2" t="inlineStr"/>
+      <c r="L262" s="2" t="inlineStr">
+        <is>
+          <t>0.579716</t>
+        </is>
+      </c>
+      <c r="M262" s="2" t="inlineStr"/>
+      <c r="N262" s="2" t="inlineStr"/>
+      <c r="O262" s="2" t="inlineStr">
+        <is>
+          <t>0.7549019607843137</t>
+        </is>
+      </c>
+      <c r="P262" s="2" t="inlineStr">
+        <is>
+          <t>0.751244</t>
+        </is>
+      </c>
+      <c r="Q262" s="2" t="inlineStr">
+        <is>
+          <t>-0.1751859607843137</t>
+        </is>
+      </c>
+      <c r="R262" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:53.844371Z</t>
+        </is>
+      </c>
+      <c r="S262" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T262" s="2" t="inlineStr"/>
+      <c r="U262" s="2" t="inlineStr"/>
+      <c r="V262" s="2" t="inlineStr"/>
+      <c r="W262" s="2" t="inlineStr"/>
+      <c r="X262" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y262" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z262" s="2" t="inlineStr">
+        <is>
+          <t>0.755000</t>
+        </is>
+      </c>
+      <c r="AA262" s="2" t="inlineStr">
+        <is>
+          <t>0.000098</t>
+        </is>
+      </c>
+      <c r="AB262" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC262" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:06:26.287917Z</t>
+        </is>
+      </c>
+      <c r="AD262" s="2" t="inlineStr"/>
+      <c r="AE262" s="2" t="inlineStr"/>
+      <c r="AF262" s="2" t="inlineStr"/>
+      <c r="AG262" s="2" t="inlineStr"/>
+      <c r="AH262" s="2" t="inlineStr"/>
+      <c r="AI262" s="2" t="inlineStr"/>
+      <c r="AJ262" s="2" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>a91461fa827b4048</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>848a1fa2a5c55f74</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>401816416</t>
+        </is>
+      </c>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J263" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K263" s="2" t="inlineStr"/>
+      <c r="L263" s="2" t="inlineStr">
+        <is>
+          <t>0.576121</t>
+        </is>
+      </c>
+      <c r="M263" s="2" t="inlineStr"/>
+      <c r="N263" s="2" t="inlineStr"/>
+      <c r="O263" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P263" s="2" t="inlineStr">
+        <is>
+          <t>0.636816</t>
+        </is>
+      </c>
+      <c r="Q263" s="2" t="inlineStr">
+        <is>
+          <t>-0.06416676978417268</t>
+        </is>
+      </c>
+      <c r="R263" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:54.201474Z</t>
+        </is>
+      </c>
+      <c r="S263" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T263" s="2" t="inlineStr"/>
+      <c r="U263" s="2" t="inlineStr"/>
+      <c r="V263" s="2" t="inlineStr"/>
+      <c r="W263" s="2" t="inlineStr"/>
+      <c r="X263" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y263" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z263" s="2" t="inlineStr">
+        <is>
+          <t>0.640000</t>
+        </is>
+      </c>
+      <c r="AA263" s="2" t="inlineStr">
+        <is>
+          <t>-0.000288</t>
+        </is>
+      </c>
+      <c r="AB263" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC263" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:06:27.497497Z</t>
+        </is>
+      </c>
+      <c r="AD263" s="2" t="inlineStr"/>
+      <c r="AE263" s="2" t="inlineStr"/>
+      <c r="AF263" s="2" t="inlineStr"/>
+      <c r="AG263" s="2" t="inlineStr"/>
+      <c r="AH263" s="2" t="inlineStr"/>
+      <c r="AI263" s="2" t="inlineStr"/>
+      <c r="AJ263" s="2" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>d495543645144977</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>f529e3d523db2fe0</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>401816417</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J264" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K264" s="2" t="inlineStr"/>
+      <c r="L264" s="2" t="inlineStr">
+        <is>
+          <t>0.594958</t>
+        </is>
+      </c>
+      <c r="M264" s="2" t="inlineStr"/>
+      <c r="N264" s="2" t="inlineStr"/>
+      <c r="O264" s="2" t="inlineStr">
+        <is>
+          <t>0.574468085106383</t>
+        </is>
+      </c>
+      <c r="P264" s="2" t="inlineStr">
+        <is>
+          <t>0.572139</t>
+        </is>
+      </c>
+      <c r="Q264" s="2" t="inlineStr">
+        <is>
+          <t>0.020489914893616956</t>
+        </is>
+      </c>
+      <c r="R264" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:54.768966Z</t>
+        </is>
+      </c>
+      <c r="S264" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T19:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T264" s="2" t="inlineStr"/>
+      <c r="U264" s="2" t="inlineStr"/>
+      <c r="V264" s="2" t="inlineStr"/>
+      <c r="W264" s="2" t="inlineStr"/>
+      <c r="X264" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y264" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z264" s="2" t="inlineStr">
+        <is>
+          <t>0.575000</t>
+        </is>
+      </c>
+      <c r="AA264" s="2" t="inlineStr">
+        <is>
+          <t>0.000532</t>
+        </is>
+      </c>
+      <c r="AB264" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC264" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:06:28.618329Z</t>
+        </is>
+      </c>
+      <c r="AD264" s="2" t="inlineStr"/>
+      <c r="AE264" s="2" t="inlineStr"/>
+      <c r="AF264" s="2" t="inlineStr"/>
+      <c r="AG264" s="2" t="inlineStr"/>
+      <c r="AH264" s="2" t="inlineStr"/>
+      <c r="AI264" s="2" t="inlineStr"/>
+      <c r="AJ264" s="2" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>fef3759ec32b41f5</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>e72f25a204594f46</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>401816420</t>
+        </is>
+      </c>
+      <c r="I265" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J265" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K265" s="2" t="inlineStr"/>
+      <c r="L265" s="2" t="inlineStr">
+        <is>
+          <t>0.55965</t>
+        </is>
+      </c>
+      <c r="M265" s="2" t="inlineStr"/>
+      <c r="N265" s="2" t="inlineStr"/>
+      <c r="O265" s="2" t="inlineStr">
+        <is>
+          <t>0.5348837209302326</t>
+        </is>
+      </c>
+      <c r="P265" s="2" t="inlineStr">
+        <is>
+          <t>0.532338</t>
+        </is>
+      </c>
+      <c r="Q265" s="2" t="inlineStr">
+        <is>
+          <t>0.02476627906976736</t>
+        </is>
+      </c>
+      <c r="R265" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:55.278501Z</t>
+        </is>
+      </c>
+      <c r="S265" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="T265" s="2" t="inlineStr"/>
+      <c r="U265" s="2" t="inlineStr"/>
+      <c r="V265" s="2" t="inlineStr"/>
+      <c r="W265" s="2" t="inlineStr"/>
+      <c r="X265" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y265" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z265" s="2" t="inlineStr">
+        <is>
+          <t>0.535000</t>
+        </is>
+      </c>
+      <c r="AA265" s="2" t="inlineStr">
+        <is>
+          <t>0.000116</t>
+        </is>
+      </c>
+      <c r="AB265" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC265" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:06:29.809663Z</t>
+        </is>
+      </c>
+      <c r="AD265" s="2" t="inlineStr"/>
+      <c r="AE265" s="2" t="inlineStr"/>
+      <c r="AF265" s="2" t="inlineStr"/>
+      <c r="AG265" s="2" t="inlineStr"/>
+      <c r="AH265" s="2" t="inlineStr"/>
+      <c r="AI265" s="2" t="inlineStr"/>
+      <c r="AJ265" s="2" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>c414c5f8dbe3416b</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>6d072d85bcbb15af</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>401816423</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J266" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K266" s="2" t="inlineStr"/>
+      <c r="L266" s="2" t="inlineStr">
+        <is>
+          <t>0.508065</t>
+        </is>
+      </c>
+      <c r="M266" s="2" t="inlineStr"/>
+      <c r="N266" s="2" t="inlineStr"/>
+      <c r="O266" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P266" s="2" t="inlineStr">
+        <is>
+          <t>0.497512</t>
+        </is>
+      </c>
+      <c r="Q266" s="2" t="inlineStr">
+        <is>
+          <t>0.008064999999999989</t>
+        </is>
+      </c>
+      <c r="R266" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:55.802850Z</t>
+        </is>
+      </c>
+      <c r="S266" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T266" s="2" t="inlineStr"/>
+      <c r="U266" s="2" t="inlineStr"/>
+      <c r="V266" s="2" t="inlineStr"/>
+      <c r="W266" s="2" t="inlineStr"/>
+      <c r="X266" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y266" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z266" s="2" t="inlineStr">
+        <is>
+          <t>0.500000</t>
+        </is>
+      </c>
+      <c r="AA266" s="2" t="inlineStr">
+        <is>
+          <t>0.000000</t>
+        </is>
+      </c>
+      <c r="AB266" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC266" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:06:30.941094Z</t>
+        </is>
+      </c>
+      <c r="AD266" s="2" t="inlineStr"/>
+      <c r="AE266" s="2" t="inlineStr"/>
+      <c r="AF266" s="2" t="inlineStr"/>
+      <c r="AG266" s="2" t="inlineStr"/>
+      <c r="AH266" s="2" t="inlineStr"/>
+      <c r="AI266" s="2" t="inlineStr"/>
+      <c r="AJ266" s="2" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>e09a88b69a7943cd</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>567600f080a90fdc</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>401816428</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K267" s="2" t="inlineStr"/>
+      <c r="L267" s="2" t="inlineStr">
+        <is>
+          <t>0.581948</t>
+        </is>
+      </c>
+      <c r="M267" s="2" t="inlineStr"/>
+      <c r="N267" s="2" t="inlineStr"/>
+      <c r="O267" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P267" s="2" t="inlineStr">
+        <is>
+          <t>0.567164</t>
+        </is>
+      </c>
+      <c r="Q267" s="2" t="inlineStr">
+        <is>
+          <t>0.01113254935622321</t>
+        </is>
+      </c>
+      <c r="R267" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:02:21.161553Z</t>
+        </is>
+      </c>
+      <c r="S267" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T267" s="2" t="inlineStr"/>
+      <c r="U267" s="2" t="inlineStr"/>
+      <c r="V267" s="2" t="inlineStr"/>
+      <c r="W267" s="2" t="inlineStr"/>
+      <c r="X267" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y267" s="2" t="inlineStr"/>
+      <c r="Z267" s="2" t="inlineStr"/>
+      <c r="AA267" s="2" t="inlineStr"/>
+      <c r="AB267" s="2" t="inlineStr"/>
+      <c r="AC267" s="2" t="inlineStr"/>
+      <c r="AD267" s="2" t="inlineStr"/>
+      <c r="AE267" s="2" t="inlineStr"/>
+      <c r="AF267" s="2" t="inlineStr"/>
+      <c r="AG267" s="2" t="inlineStr"/>
+      <c r="AH267" s="2" t="inlineStr"/>
+      <c r="AI267" s="2" t="inlineStr"/>
+      <c r="AJ267" s="2" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>d593f46de68f4f36</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>399cd11dc6c6f93d</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>401816429</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J268" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K268" s="2" t="inlineStr"/>
+      <c r="L268" s="2" t="inlineStr">
+        <is>
+          <t>0.56257</t>
+        </is>
+      </c>
+      <c r="M268" s="2" t="inlineStr"/>
+      <c r="N268" s="2" t="inlineStr"/>
+      <c r="O268" s="2" t="inlineStr">
+        <is>
+          <t>0.6753246753246753</t>
+        </is>
+      </c>
+      <c r="P268" s="2" t="inlineStr">
+        <is>
+          <t>0.671642</t>
+        </is>
+      </c>
+      <c r="Q268" s="2" t="inlineStr">
+        <is>
+          <t>-0.11275467532467531</t>
+        </is>
+      </c>
+      <c r="R268" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:02:20.630977Z</t>
+        </is>
+      </c>
+      <c r="S268" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T268" s="2" t="inlineStr"/>
+      <c r="U268" s="2" t="inlineStr"/>
+      <c r="V268" s="2" t="inlineStr"/>
+      <c r="W268" s="2" t="inlineStr"/>
+      <c r="X268" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y268" s="2" t="inlineStr"/>
+      <c r="Z268" s="2" t="inlineStr"/>
+      <c r="AA268" s="2" t="inlineStr"/>
+      <c r="AB268" s="2" t="inlineStr"/>
+      <c r="AC268" s="2" t="inlineStr"/>
+      <c r="AD268" s="2" t="inlineStr"/>
+      <c r="AE268" s="2" t="inlineStr"/>
+      <c r="AF268" s="2" t="inlineStr"/>
+      <c r="AG268" s="2" t="inlineStr"/>
+      <c r="AH268" s="2" t="inlineStr"/>
+      <c r="AI268" s="2" t="inlineStr"/>
+      <c r="AJ268" s="2" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>154fd375ee8e4299</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>d10b15dc92074c26</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>401816426</t>
+        </is>
+      </c>
+      <c r="I269" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J269" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K269" s="2" t="inlineStr"/>
+      <c r="L269" s="2" t="inlineStr">
+        <is>
+          <t>0.530881</t>
+        </is>
+      </c>
+      <c r="M269" s="2" t="inlineStr"/>
+      <c r="N269" s="2" t="inlineStr"/>
+      <c r="O269" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P269" s="2" t="inlineStr">
+        <is>
+          <t>0.577114</t>
+        </is>
+      </c>
+      <c r="Q269" s="2" t="inlineStr">
+        <is>
+          <t>-0.048950932773109135</t>
+        </is>
+      </c>
+      <c r="R269" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:02:22.193578Z</t>
+        </is>
+      </c>
+      <c r="S269" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T269" s="2" t="inlineStr"/>
+      <c r="U269" s="2" t="inlineStr"/>
+      <c r="V269" s="2" t="inlineStr"/>
+      <c r="W269" s="2" t="inlineStr"/>
+      <c r="X269" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y269" s="2" t="inlineStr"/>
+      <c r="Z269" s="2" t="inlineStr"/>
+      <c r="AA269" s="2" t="inlineStr"/>
+      <c r="AB269" s="2" t="inlineStr"/>
+      <c r="AC269" s="2" t="inlineStr"/>
+      <c r="AD269" s="2" t="inlineStr"/>
+      <c r="AE269" s="2" t="inlineStr"/>
+      <c r="AF269" s="2" t="inlineStr"/>
+      <c r="AG269" s="2" t="inlineStr"/>
+      <c r="AH269" s="2" t="inlineStr"/>
+      <c r="AI269" s="2" t="inlineStr"/>
+      <c r="AJ269" s="2" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>5bab2f7ee5414960</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>8bd990e177da70c3</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>401816424</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J270" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K270" s="2" t="inlineStr"/>
+      <c r="L270" s="2" t="inlineStr">
+        <is>
+          <t>0.641185</t>
+        </is>
+      </c>
+      <c r="M270" s="2" t="inlineStr"/>
+      <c r="N270" s="2" t="inlineStr"/>
+      <c r="O270" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P270" s="2" t="inlineStr">
+        <is>
+          <t>0.606965</t>
+        </is>
+      </c>
+      <c r="Q270" s="2" t="inlineStr">
+        <is>
+          <t>0.031810000000000005</t>
+        </is>
+      </c>
+      <c r="R270" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:02:23.266659Z</t>
+        </is>
+      </c>
+      <c r="S270" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T270" s="2" t="inlineStr"/>
+      <c r="U270" s="2" t="inlineStr"/>
+      <c r="V270" s="2" t="inlineStr"/>
+      <c r="W270" s="2" t="inlineStr"/>
+      <c r="X270" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y270" s="2" t="inlineStr"/>
+      <c r="Z270" s="2" t="inlineStr"/>
+      <c r="AA270" s="2" t="inlineStr"/>
+      <c r="AB270" s="2" t="inlineStr"/>
+      <c r="AC270" s="2" t="inlineStr"/>
+      <c r="AD270" s="2" t="inlineStr"/>
+      <c r="AE270" s="2" t="inlineStr"/>
+      <c r="AF270" s="2" t="inlineStr"/>
+      <c r="AG270" s="2" t="inlineStr"/>
+      <c r="AH270" s="2" t="inlineStr"/>
+      <c r="AI270" s="2" t="inlineStr"/>
+      <c r="AJ270" s="2" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>0f524b24af7d4853</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>0ff3d2b2c501e1c6</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>401816425</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J271" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K271" s="2" t="inlineStr"/>
+      <c r="L271" s="2" t="inlineStr">
+        <is>
+          <t>0.633595</t>
+        </is>
+      </c>
+      <c r="M271" s="2" t="inlineStr"/>
+      <c r="N271" s="2" t="inlineStr"/>
+      <c r="O271" s="2" t="inlineStr">
+        <is>
+          <t>0.7101449275362319</t>
+        </is>
+      </c>
+      <c r="P271" s="2" t="inlineStr">
+        <is>
+          <t>0.706468</t>
+        </is>
+      </c>
+      <c r="Q271" s="2" t="inlineStr">
+        <is>
+          <t>-0.07654992753623191</t>
+        </is>
+      </c>
+      <c r="R271" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:02:22.786514Z</t>
+        </is>
+      </c>
+      <c r="S271" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T271" s="2" t="inlineStr"/>
+      <c r="U271" s="2" t="inlineStr"/>
+      <c r="V271" s="2" t="inlineStr"/>
+      <c r="W271" s="2" t="inlineStr"/>
+      <c r="X271" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y271" s="2" t="inlineStr"/>
+      <c r="Z271" s="2" t="inlineStr"/>
+      <c r="AA271" s="2" t="inlineStr"/>
+      <c r="AB271" s="2" t="inlineStr"/>
+      <c r="AC271" s="2" t="inlineStr"/>
+      <c r="AD271" s="2" t="inlineStr"/>
+      <c r="AE271" s="2" t="inlineStr"/>
+      <c r="AF271" s="2" t="inlineStr"/>
+      <c r="AG271" s="2" t="inlineStr"/>
+      <c r="AH271" s="2" t="inlineStr"/>
+      <c r="AI271" s="2" t="inlineStr"/>
+      <c r="AJ271" s="2" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>5b12fd6890884f96</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>fe46ee6a1fc3c45e</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>401816432</t>
+        </is>
+      </c>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J272" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K272" s="2" t="inlineStr"/>
+      <c r="L272" s="2" t="inlineStr">
+        <is>
+          <t>0.522138</t>
+        </is>
+      </c>
+      <c r="M272" s="2" t="inlineStr"/>
+      <c r="N272" s="2" t="inlineStr"/>
+      <c r="O272" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P272" s="2" t="inlineStr">
+        <is>
+          <t>0.437811</t>
+        </is>
+      </c>
+      <c r="Q272" s="2" t="inlineStr">
+        <is>
+          <t>0.08160936563876653</t>
+        </is>
+      </c>
+      <c r="R272" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:02:24.244086Z</t>
+        </is>
+      </c>
+      <c r="S272" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T272" s="2" t="inlineStr"/>
+      <c r="U272" s="2" t="inlineStr"/>
+      <c r="V272" s="2" t="inlineStr"/>
+      <c r="W272" s="2" t="inlineStr"/>
+      <c r="X272" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y272" s="2" t="inlineStr"/>
+      <c r="Z272" s="2" t="inlineStr"/>
+      <c r="AA272" s="2" t="inlineStr"/>
+      <c r="AB272" s="2" t="inlineStr"/>
+      <c r="AC272" s="2" t="inlineStr"/>
+      <c r="AD272" s="2" t="inlineStr"/>
+      <c r="AE272" s="2" t="inlineStr"/>
+      <c r="AF272" s="2" t="inlineStr"/>
+      <c r="AG272" s="2" t="inlineStr"/>
+      <c r="AH272" s="2" t="inlineStr"/>
+      <c r="AI272" s="2" t="inlineStr"/>
+      <c r="AJ272" s="2" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>69645f863066498c</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>6930bf181d0a558c</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>401816434</t>
+        </is>
+      </c>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J273" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K273" s="2" t="inlineStr"/>
+      <c r="L273" s="2" t="inlineStr">
+        <is>
+          <t>0.651659</t>
+        </is>
+      </c>
+      <c r="M273" s="2" t="inlineStr"/>
+      <c r="N273" s="2" t="inlineStr"/>
+      <c r="O273" s="2" t="inlineStr">
+        <is>
+          <t>0.6254681647940076</t>
+        </is>
+      </c>
+      <c r="P273" s="2" t="inlineStr">
+        <is>
+          <t>0.621891</t>
+        </is>
+      </c>
+      <c r="Q273" s="2" t="inlineStr">
+        <is>
+          <t>0.026190835205992413</t>
+        </is>
+      </c>
+      <c r="R273" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:02:23.778848Z</t>
+        </is>
+      </c>
+      <c r="S273" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T273" s="2" t="inlineStr"/>
+      <c r="U273" s="2" t="inlineStr"/>
+      <c r="V273" s="2" t="inlineStr"/>
+      <c r="W273" s="2" t="inlineStr"/>
+      <c r="X273" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y273" s="2" t="inlineStr"/>
+      <c r="Z273" s="2" t="inlineStr"/>
+      <c r="AA273" s="2" t="inlineStr"/>
+      <c r="AB273" s="2" t="inlineStr"/>
+      <c r="AC273" s="2" t="inlineStr"/>
+      <c r="AD273" s="2" t="inlineStr"/>
+      <c r="AE273" s="2" t="inlineStr"/>
+      <c r="AF273" s="2" t="inlineStr"/>
+      <c r="AG273" s="2" t="inlineStr"/>
+      <c r="AH273" s="2" t="inlineStr"/>
+      <c r="AI273" s="2" t="inlineStr"/>
+      <c r="AJ273" s="2" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>ab0e23b101814acf</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>af44fd94b4c3d055</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>401816431</t>
+        </is>
+      </c>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J274" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K274" s="2" t="inlineStr"/>
+      <c r="L274" s="2" t="inlineStr">
+        <is>
+          <t>0.532837</t>
+        </is>
+      </c>
+      <c r="M274" s="2" t="inlineStr"/>
+      <c r="N274" s="2" t="inlineStr"/>
+      <c r="O274" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P274" s="2" t="inlineStr">
+        <is>
+          <t>0.616915</t>
+        </is>
+      </c>
+      <c r="Q274" s="2" t="inlineStr">
+        <is>
+          <t>-0.08693486311787069</t>
+        </is>
+      </c>
+      <c r="R274" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:02:24.909108Z</t>
+        </is>
+      </c>
+      <c r="S274" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T20:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T274" s="2" t="inlineStr"/>
+      <c r="U274" s="2" t="inlineStr"/>
+      <c r="V274" s="2" t="inlineStr"/>
+      <c r="W274" s="2" t="inlineStr"/>
+      <c r="X274" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y274" s="2" t="inlineStr"/>
+      <c r="Z274" s="2" t="inlineStr"/>
+      <c r="AA274" s="2" t="inlineStr"/>
+      <c r="AB274" s="2" t="inlineStr"/>
+      <c r="AC274" s="2" t="inlineStr"/>
+      <c r="AD274" s="2" t="inlineStr"/>
+      <c r="AE274" s="2" t="inlineStr"/>
+      <c r="AF274" s="2" t="inlineStr"/>
+      <c r="AG274" s="2" t="inlineStr"/>
+      <c r="AH274" s="2" t="inlineStr"/>
+      <c r="AI274" s="2" t="inlineStr"/>
+      <c r="AJ274" s="2" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>19fe44623cc340de</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>a94431fcc113fab7</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>401816430</t>
+        </is>
+      </c>
+      <c r="I275" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J275" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K275" s="2" t="inlineStr"/>
+      <c r="L275" s="2" t="inlineStr">
+        <is>
+          <t>0.550403</t>
+        </is>
+      </c>
+      <c r="M275" s="2" t="inlineStr"/>
+      <c r="N275" s="2" t="inlineStr"/>
+      <c r="O275" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P275" s="2" t="inlineStr">
+        <is>
+          <t>0.577114</t>
+        </is>
+      </c>
+      <c r="Q275" s="2" t="inlineStr">
+        <is>
+          <t>-0.029428932773109207</t>
+        </is>
+      </c>
+      <c r="R275" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:02:25.412794Z</t>
+        </is>
+      </c>
+      <c r="S275" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T20:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T275" s="2" t="inlineStr"/>
+      <c r="U275" s="2" t="inlineStr"/>
+      <c r="V275" s="2" t="inlineStr"/>
+      <c r="W275" s="2" t="inlineStr"/>
+      <c r="X275" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y275" s="2" t="inlineStr"/>
+      <c r="Z275" s="2" t="inlineStr"/>
+      <c r="AA275" s="2" t="inlineStr"/>
+      <c r="AB275" s="2" t="inlineStr"/>
+      <c r="AC275" s="2" t="inlineStr"/>
+      <c r="AD275" s="2" t="inlineStr"/>
+      <c r="AE275" s="2" t="inlineStr"/>
+      <c r="AF275" s="2" t="inlineStr"/>
+      <c r="AG275" s="2" t="inlineStr"/>
+      <c r="AH275" s="2" t="inlineStr"/>
+      <c r="AI275" s="2" t="inlineStr"/>
+      <c r="AJ275" s="2" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>5c718dd3c7714116</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>79ee549a481a811e</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>401816433</t>
+        </is>
+      </c>
+      <c r="I276" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J276" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K276" s="2" t="inlineStr"/>
+      <c r="L276" s="2" t="inlineStr">
+        <is>
+          <t>0.667152</t>
+        </is>
+      </c>
+      <c r="M276" s="2" t="inlineStr"/>
+      <c r="N276" s="2" t="inlineStr"/>
+      <c r="O276" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P276" s="2" t="inlineStr">
+        <is>
+          <t>0.597015</t>
+        </is>
+      </c>
+      <c r="Q276" s="2" t="inlineStr">
+        <is>
+          <t>0.06715199999999988</t>
+        </is>
+      </c>
+      <c r="R276" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:02:26.057808Z</t>
+        </is>
+      </c>
+      <c r="S276" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T20:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T276" s="2" t="inlineStr"/>
+      <c r="U276" s="2" t="inlineStr"/>
+      <c r="V276" s="2" t="inlineStr"/>
+      <c r="W276" s="2" t="inlineStr"/>
+      <c r="X276" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y276" s="2" t="inlineStr"/>
+      <c r="Z276" s="2" t="inlineStr"/>
+      <c r="AA276" s="2" t="inlineStr"/>
+      <c r="AB276" s="2" t="inlineStr"/>
+      <c r="AC276" s="2" t="inlineStr"/>
+      <c r="AD276" s="2" t="inlineStr"/>
+      <c r="AE276" s="2" t="inlineStr"/>
+      <c r="AF276" s="2" t="inlineStr"/>
+      <c r="AG276" s="2" t="inlineStr"/>
+      <c r="AH276" s="2" t="inlineStr"/>
+      <c r="AI276" s="2" t="inlineStr"/>
+      <c r="AJ276" s="2" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>42a22c50cb1b4db8</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>be698cf16bd0db8f</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>401816436</t>
+        </is>
+      </c>
+      <c r="I277" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J277" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K277" s="2" t="inlineStr"/>
+      <c r="L277" s="2" t="inlineStr">
+        <is>
+          <t>0.586465</t>
+        </is>
+      </c>
+      <c r="M277" s="2" t="inlineStr"/>
+      <c r="N277" s="2" t="inlineStr"/>
+      <c r="O277" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P277" s="2" t="inlineStr">
+        <is>
+          <t>0.527363</t>
+        </is>
+      </c>
+      <c r="Q277" s="2" t="inlineStr">
+        <is>
+          <t>0.05594856807511739</t>
+        </is>
+      </c>
+      <c r="R277" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:02:26.430863Z</t>
+        </is>
+      </c>
+      <c r="S277" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T277" s="2" t="inlineStr"/>
+      <c r="U277" s="2" t="inlineStr"/>
+      <c r="V277" s="2" t="inlineStr"/>
+      <c r="W277" s="2" t="inlineStr"/>
+      <c r="X277" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y277" s="2" t="inlineStr"/>
+      <c r="Z277" s="2" t="inlineStr"/>
+      <c r="AA277" s="2" t="inlineStr"/>
+      <c r="AB277" s="2" t="inlineStr"/>
+      <c r="AC277" s="2" t="inlineStr"/>
+      <c r="AD277" s="2" t="inlineStr"/>
+      <c r="AE277" s="2" t="inlineStr"/>
+      <c r="AF277" s="2" t="inlineStr"/>
+      <c r="AG277" s="2" t="inlineStr"/>
+      <c r="AH277" s="2" t="inlineStr"/>
+      <c r="AI277" s="2" t="inlineStr"/>
+      <c r="AJ277" s="2" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>935c3e23343f44eb</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>807bfd9a83666e43</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>401816437</t>
+        </is>
+      </c>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J278" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K278" s="2" t="inlineStr"/>
+      <c r="L278" s="2" t="inlineStr">
+        <is>
+          <t>0.527996</t>
+        </is>
+      </c>
+      <c r="M278" s="2" t="inlineStr"/>
+      <c r="N278" s="2" t="inlineStr"/>
+      <c r="O278" s="2" t="inlineStr">
+        <is>
+          <t>0.6254681647940076</t>
+        </is>
+      </c>
+      <c r="P278" s="2" t="inlineStr">
+        <is>
+          <t>0.621891</t>
+        </is>
+      </c>
+      <c r="Q278" s="2" t="inlineStr">
+        <is>
+          <t>-0.09747216479400755</t>
+        </is>
+      </c>
+      <c r="R278" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:02:26.947932Z</t>
+        </is>
+      </c>
+      <c r="S278" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T278" s="2" t="inlineStr"/>
+      <c r="U278" s="2" t="inlineStr"/>
+      <c r="V278" s="2" t="inlineStr"/>
+      <c r="W278" s="2" t="inlineStr"/>
+      <c r="X278" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y278" s="2" t="inlineStr"/>
+      <c r="Z278" s="2" t="inlineStr"/>
+      <c r="AA278" s="2" t="inlineStr"/>
+      <c r="AB278" s="2" t="inlineStr"/>
+      <c r="AC278" s="2" t="inlineStr"/>
+      <c r="AD278" s="2" t="inlineStr"/>
+      <c r="AE278" s="2" t="inlineStr"/>
+      <c r="AF278" s="2" t="inlineStr"/>
+      <c r="AG278" s="2" t="inlineStr"/>
+      <c r="AH278" s="2" t="inlineStr"/>
+      <c r="AI278" s="2" t="inlineStr"/>
+      <c r="AJ278" s="2" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>98ace618115c41e4</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>cf9d26fcd493bc83</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>401816438</t>
+        </is>
+      </c>
+      <c r="I279" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J279" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K279" s="2" t="inlineStr"/>
+      <c r="L279" s="2" t="inlineStr">
+        <is>
+          <t>0.556751</t>
+        </is>
+      </c>
+      <c r="M279" s="2" t="inlineStr"/>
+      <c r="N279" s="2" t="inlineStr"/>
+      <c r="O279" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P279" s="2" t="inlineStr">
+        <is>
+          <t>0.507463</t>
+        </is>
+      </c>
+      <c r="Q279" s="2" t="inlineStr">
+        <is>
+          <t>0.04694707843137258</t>
+        </is>
+      </c>
+      <c r="R279" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:02:27.524669Z</t>
+        </is>
+      </c>
+      <c r="S279" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:45:00-0400</t>
+        </is>
+      </c>
+      <c r="T279" s="2" t="inlineStr"/>
+      <c r="U279" s="2" t="inlineStr"/>
+      <c r="V279" s="2" t="inlineStr"/>
+      <c r="W279" s="2" t="inlineStr"/>
+      <c r="X279" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y279" s="2" t="inlineStr"/>
+      <c r="Z279" s="2" t="inlineStr"/>
+      <c r="AA279" s="2" t="inlineStr"/>
+      <c r="AB279" s="2" t="inlineStr"/>
+      <c r="AC279" s="2" t="inlineStr"/>
+      <c r="AD279" s="2" t="inlineStr"/>
+      <c r="AE279" s="2" t="inlineStr"/>
+      <c r="AF279" s="2" t="inlineStr"/>
+      <c r="AG279" s="2" t="inlineStr"/>
+      <c r="AH279" s="2" t="inlineStr"/>
+      <c r="AI279" s="2" t="inlineStr"/>
+      <c r="AJ279" s="2" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>e32ed80a3b514d6e</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>810d5d0b370cbcab</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>401816428</t>
+        </is>
+      </c>
+      <c r="I280" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J280" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K280" s="2" t="inlineStr"/>
+      <c r="L280" s="2" t="inlineStr">
+        <is>
+          <t>0.581767</t>
+        </is>
+      </c>
+      <c r="M280" s="2" t="inlineStr"/>
+      <c r="N280" s="2" t="inlineStr"/>
+      <c r="O280" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P280" s="2" t="inlineStr">
+        <is>
+          <t>0.557214</t>
+        </is>
+      </c>
+      <c r="Q280" s="2" t="inlineStr">
+        <is>
+          <t>0.022295634361233496</t>
+        </is>
+      </c>
+      <c r="R280" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:08:36.623292Z</t>
+        </is>
+      </c>
+      <c r="S280" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T280" s="2" t="inlineStr"/>
+      <c r="U280" s="2" t="inlineStr"/>
+      <c r="V280" s="2" t="inlineStr"/>
+      <c r="W280" s="2" t="inlineStr"/>
+      <c r="X280" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y280" s="2" t="inlineStr"/>
+      <c r="Z280" s="2" t="inlineStr"/>
+      <c r="AA280" s="2" t="inlineStr"/>
+      <c r="AB280" s="2" t="inlineStr"/>
+      <c r="AC280" s="2" t="inlineStr"/>
+      <c r="AD280" s="2" t="inlineStr"/>
+      <c r="AE280" s="2" t="inlineStr"/>
+      <c r="AF280" s="2" t="inlineStr"/>
+      <c r="AG280" s="2" t="inlineStr"/>
+      <c r="AH280" s="2" t="inlineStr"/>
+      <c r="AI280" s="2" t="inlineStr"/>
+      <c r="AJ280" s="2" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>ad5eed4daf9e43f7</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>62011a9ddda6a041</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>401816429</t>
+        </is>
+      </c>
+      <c r="I281" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J281" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K281" s="2" t="inlineStr"/>
+      <c r="L281" s="2" t="inlineStr">
+        <is>
+          <t>0.56249</t>
+        </is>
+      </c>
+      <c r="M281" s="2" t="inlineStr"/>
+      <c r="N281" s="2" t="inlineStr"/>
+      <c r="O281" s="2" t="inlineStr">
+        <is>
+          <t>0.6753246753246753</t>
+        </is>
+      </c>
+      <c r="P281" s="2" t="inlineStr">
+        <is>
+          <t>0.671642</t>
+        </is>
+      </c>
+      <c r="Q281" s="2" t="inlineStr">
+        <is>
+          <t>-0.11283467532467528</t>
+        </is>
+      </c>
+      <c r="R281" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:08:35.856368Z</t>
+        </is>
+      </c>
+      <c r="S281" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T281" s="2" t="inlineStr"/>
+      <c r="U281" s="2" t="inlineStr"/>
+      <c r="V281" s="2" t="inlineStr"/>
+      <c r="W281" s="2" t="inlineStr"/>
+      <c r="X281" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y281" s="2" t="inlineStr"/>
+      <c r="Z281" s="2" t="inlineStr"/>
+      <c r="AA281" s="2" t="inlineStr"/>
+      <c r="AB281" s="2" t="inlineStr"/>
+      <c r="AC281" s="2" t="inlineStr"/>
+      <c r="AD281" s="2" t="inlineStr"/>
+      <c r="AE281" s="2" t="inlineStr"/>
+      <c r="AF281" s="2" t="inlineStr"/>
+      <c r="AG281" s="2" t="inlineStr"/>
+      <c r="AH281" s="2" t="inlineStr"/>
+      <c r="AI281" s="2" t="inlineStr"/>
+      <c r="AJ281" s="2" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>0fb2a24152e74143</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>ae43d83e4e087496</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>401816426</t>
+        </is>
+      </c>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J282" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K282" s="2" t="inlineStr"/>
+      <c r="L282" s="2" t="inlineStr">
+        <is>
+          <t>0.531341</t>
+        </is>
+      </c>
+      <c r="M282" s="2" t="inlineStr"/>
+      <c r="N282" s="2" t="inlineStr"/>
+      <c r="O282" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P282" s="2" t="inlineStr">
+        <is>
+          <t>0.577114</t>
+        </is>
+      </c>
+      <c r="Q282" s="2" t="inlineStr">
+        <is>
+          <t>-0.04849093277310923</t>
+        </is>
+      </c>
+      <c r="R282" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:08:37.679474Z</t>
+        </is>
+      </c>
+      <c r="S282" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T282" s="2" t="inlineStr"/>
+      <c r="U282" s="2" t="inlineStr"/>
+      <c r="V282" s="2" t="inlineStr"/>
+      <c r="W282" s="2" t="inlineStr"/>
+      <c r="X282" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y282" s="2" t="inlineStr"/>
+      <c r="Z282" s="2" t="inlineStr"/>
+      <c r="AA282" s="2" t="inlineStr"/>
+      <c r="AB282" s="2" t="inlineStr"/>
+      <c r="AC282" s="2" t="inlineStr"/>
+      <c r="AD282" s="2" t="inlineStr"/>
+      <c r="AE282" s="2" t="inlineStr"/>
+      <c r="AF282" s="2" t="inlineStr"/>
+      <c r="AG282" s="2" t="inlineStr"/>
+      <c r="AH282" s="2" t="inlineStr"/>
+      <c r="AI282" s="2" t="inlineStr"/>
+      <c r="AJ282" s="2" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>2a0f74a36dc7471a</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>8bd990e177da70c3</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>401816424</t>
+        </is>
+      </c>
+      <c r="I283" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J283" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K283" s="2" t="inlineStr"/>
+      <c r="L283" s="2" t="inlineStr">
+        <is>
+          <t>0.641185</t>
+        </is>
+      </c>
+      <c r="M283" s="2" t="inlineStr"/>
+      <c r="N283" s="2" t="inlineStr"/>
+      <c r="O283" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P283" s="2" t="inlineStr">
+        <is>
+          <t>0.606965</t>
+        </is>
+      </c>
+      <c r="Q283" s="2" t="inlineStr">
+        <is>
+          <t>0.031810000000000005</t>
+        </is>
+      </c>
+      <c r="R283" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:08:38.816301Z</t>
+        </is>
+      </c>
+      <c r="S283" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T283" s="2" t="inlineStr"/>
+      <c r="U283" s="2" t="inlineStr"/>
+      <c r="V283" s="2" t="inlineStr"/>
+      <c r="W283" s="2" t="inlineStr"/>
+      <c r="X283" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y283" s="2" t="inlineStr"/>
+      <c r="Z283" s="2" t="inlineStr"/>
+      <c r="AA283" s="2" t="inlineStr"/>
+      <c r="AB283" s="2" t="inlineStr"/>
+      <c r="AC283" s="2" t="inlineStr"/>
+      <c r="AD283" s="2" t="inlineStr"/>
+      <c r="AE283" s="2" t="inlineStr"/>
+      <c r="AF283" s="2" t="inlineStr"/>
+      <c r="AG283" s="2" t="inlineStr"/>
+      <c r="AH283" s="2" t="inlineStr"/>
+      <c r="AI283" s="2" t="inlineStr"/>
+      <c r="AJ283" s="2" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>82272a7439e44591</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>b3968e53078ac1c8</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>401816425</t>
+        </is>
+      </c>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J284" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K284" s="2" t="inlineStr"/>
+      <c r="L284" s="2" t="inlineStr">
+        <is>
+          <t>0.63363</t>
+        </is>
+      </c>
+      <c r="M284" s="2" t="inlineStr"/>
+      <c r="N284" s="2" t="inlineStr"/>
+      <c r="O284" s="2" t="inlineStr">
+        <is>
+          <t>0.715099715099715</t>
+        </is>
+      </c>
+      <c r="P284" s="2" t="inlineStr">
+        <is>
+          <t>0.711443</t>
+        </is>
+      </c>
+      <c r="Q284" s="2" t="inlineStr">
+        <is>
+          <t>-0.08146971509971501</t>
+        </is>
+      </c>
+      <c r="R284" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:08:38.326505Z</t>
+        </is>
+      </c>
+      <c r="S284" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T284" s="2" t="inlineStr"/>
+      <c r="U284" s="2" t="inlineStr"/>
+      <c r="V284" s="2" t="inlineStr"/>
+      <c r="W284" s="2" t="inlineStr"/>
+      <c r="X284" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y284" s="2" t="inlineStr"/>
+      <c r="Z284" s="2" t="inlineStr"/>
+      <c r="AA284" s="2" t="inlineStr"/>
+      <c r="AB284" s="2" t="inlineStr"/>
+      <c r="AC284" s="2" t="inlineStr"/>
+      <c r="AD284" s="2" t="inlineStr"/>
+      <c r="AE284" s="2" t="inlineStr"/>
+      <c r="AF284" s="2" t="inlineStr"/>
+      <c r="AG284" s="2" t="inlineStr"/>
+      <c r="AH284" s="2" t="inlineStr"/>
+      <c r="AI284" s="2" t="inlineStr"/>
+      <c r="AJ284" s="2" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>0213d8b6798e445b</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>6e78198b9918239f</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>401816432</t>
+        </is>
+      </c>
+      <c r="I285" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J285" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K285" s="2" t="inlineStr"/>
+      <c r="L285" s="2" t="inlineStr">
+        <is>
+          <t>0.522071</t>
+        </is>
+      </c>
+      <c r="M285" s="2" t="inlineStr"/>
+      <c r="N285" s="2" t="inlineStr"/>
+      <c r="O285" s="2" t="inlineStr">
+        <is>
+          <t>0.4347826086956522</t>
+        </is>
+      </c>
+      <c r="P285" s="2" t="inlineStr">
+        <is>
+          <t>0.432836</t>
+        </is>
+      </c>
+      <c r="Q285" s="2" t="inlineStr">
+        <is>
+          <t>0.08728839130434773</t>
+        </is>
+      </c>
+      <c r="R285" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:08:39.555140Z</t>
+        </is>
+      </c>
+      <c r="S285" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T285" s="2" t="inlineStr"/>
+      <c r="U285" s="2" t="inlineStr"/>
+      <c r="V285" s="2" t="inlineStr"/>
+      <c r="W285" s="2" t="inlineStr"/>
+      <c r="X285" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y285" s="2" t="inlineStr"/>
+      <c r="Z285" s="2" t="inlineStr"/>
+      <c r="AA285" s="2" t="inlineStr"/>
+      <c r="AB285" s="2" t="inlineStr"/>
+      <c r="AC285" s="2" t="inlineStr"/>
+      <c r="AD285" s="2" t="inlineStr"/>
+      <c r="AE285" s="2" t="inlineStr"/>
+      <c r="AF285" s="2" t="inlineStr"/>
+      <c r="AG285" s="2" t="inlineStr"/>
+      <c r="AH285" s="2" t="inlineStr"/>
+      <c r="AI285" s="2" t="inlineStr"/>
+      <c r="AJ285" s="2" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>2c330daaa6e04c0f</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>6930bf181d0a558c</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>401816434</t>
+        </is>
+      </c>
+      <c r="I286" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J286" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K286" s="2" t="inlineStr"/>
+      <c r="L286" s="2" t="inlineStr">
+        <is>
+          <t>0.651659</t>
+        </is>
+      </c>
+      <c r="M286" s="2" t="inlineStr"/>
+      <c r="N286" s="2" t="inlineStr"/>
+      <c r="O286" s="2" t="inlineStr">
+        <is>
+          <t>0.6254681647940076</t>
+        </is>
+      </c>
+      <c r="P286" s="2" t="inlineStr">
+        <is>
+          <t>0.621891</t>
+        </is>
+      </c>
+      <c r="Q286" s="2" t="inlineStr">
+        <is>
+          <t>0.026190835205992413</t>
+        </is>
+      </c>
+      <c r="R286" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:08:39.327107Z</t>
+        </is>
+      </c>
+      <c r="S286" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T286" s="2" t="inlineStr"/>
+      <c r="U286" s="2" t="inlineStr"/>
+      <c r="V286" s="2" t="inlineStr"/>
+      <c r="W286" s="2" t="inlineStr"/>
+      <c r="X286" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y286" s="2" t="inlineStr"/>
+      <c r="Z286" s="2" t="inlineStr"/>
+      <c r="AA286" s="2" t="inlineStr"/>
+      <c r="AB286" s="2" t="inlineStr"/>
+      <c r="AC286" s="2" t="inlineStr"/>
+      <c r="AD286" s="2" t="inlineStr"/>
+      <c r="AE286" s="2" t="inlineStr"/>
+      <c r="AF286" s="2" t="inlineStr"/>
+      <c r="AG286" s="2" t="inlineStr"/>
+      <c r="AH286" s="2" t="inlineStr"/>
+      <c r="AI286" s="2" t="inlineStr"/>
+      <c r="AJ286" s="2" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>ad42073443dd4874</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>e68db64c45e76e22</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>401816431</t>
+        </is>
+      </c>
+      <c r="I287" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J287" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K287" s="2" t="inlineStr"/>
+      <c r="L287" s="2" t="inlineStr">
+        <is>
+          <t>0.533008</t>
+        </is>
+      </c>
+      <c r="M287" s="2" t="inlineStr"/>
+      <c r="N287" s="2" t="inlineStr"/>
+      <c r="O287" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P287" s="2" t="inlineStr">
+        <is>
+          <t>0.616915</t>
+        </is>
+      </c>
+      <c r="Q287" s="2" t="inlineStr">
+        <is>
+          <t>-0.08676386311787065</t>
+        </is>
+      </c>
+      <c r="R287" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:08:40.056917Z</t>
+        </is>
+      </c>
+      <c r="S287" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T20:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T287" s="2" t="inlineStr"/>
+      <c r="U287" s="2" t="inlineStr"/>
+      <c r="V287" s="2" t="inlineStr"/>
+      <c r="W287" s="2" t="inlineStr"/>
+      <c r="X287" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y287" s="2" t="inlineStr"/>
+      <c r="Z287" s="2" t="inlineStr"/>
+      <c r="AA287" s="2" t="inlineStr"/>
+      <c r="AB287" s="2" t="inlineStr"/>
+      <c r="AC287" s="2" t="inlineStr"/>
+      <c r="AD287" s="2" t="inlineStr"/>
+      <c r="AE287" s="2" t="inlineStr"/>
+      <c r="AF287" s="2" t="inlineStr"/>
+      <c r="AG287" s="2" t="inlineStr"/>
+      <c r="AH287" s="2" t="inlineStr"/>
+      <c r="AI287" s="2" t="inlineStr"/>
+      <c r="AJ287" s="2" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>934dbeb0f6e646fe</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>a94431fcc113fab7</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>401816430</t>
+        </is>
+      </c>
+      <c r="I288" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J288" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K288" s="2" t="inlineStr"/>
+      <c r="L288" s="2" t="inlineStr">
+        <is>
+          <t>0.550403</t>
+        </is>
+      </c>
+      <c r="M288" s="2" t="inlineStr"/>
+      <c r="N288" s="2" t="inlineStr"/>
+      <c r="O288" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P288" s="2" t="inlineStr">
+        <is>
+          <t>0.577114</t>
+        </is>
+      </c>
+      <c r="Q288" s="2" t="inlineStr">
+        <is>
+          <t>-0.029428932773109207</t>
+        </is>
+      </c>
+      <c r="R288" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:08:40.734373Z</t>
+        </is>
+      </c>
+      <c r="S288" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T20:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T288" s="2" t="inlineStr"/>
+      <c r="U288" s="2" t="inlineStr"/>
+      <c r="V288" s="2" t="inlineStr"/>
+      <c r="W288" s="2" t="inlineStr"/>
+      <c r="X288" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y288" s="2" t="inlineStr"/>
+      <c r="Z288" s="2" t="inlineStr"/>
+      <c r="AA288" s="2" t="inlineStr"/>
+      <c r="AB288" s="2" t="inlineStr"/>
+      <c r="AC288" s="2" t="inlineStr"/>
+      <c r="AD288" s="2" t="inlineStr"/>
+      <c r="AE288" s="2" t="inlineStr"/>
+      <c r="AF288" s="2" t="inlineStr"/>
+      <c r="AG288" s="2" t="inlineStr"/>
+      <c r="AH288" s="2" t="inlineStr"/>
+      <c r="AI288" s="2" t="inlineStr"/>
+      <c r="AJ288" s="2" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>64dd0a08040a4a93</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>5254a477eb5f5067</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>401816433</t>
+        </is>
+      </c>
+      <c r="I289" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J289" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K289" s="2" t="inlineStr"/>
+      <c r="L289" s="2" t="inlineStr">
+        <is>
+          <t>0.667092</t>
+        </is>
+      </c>
+      <c r="M289" s="2" t="inlineStr"/>
+      <c r="N289" s="2" t="inlineStr"/>
+      <c r="O289" s="2" t="inlineStr">
+        <is>
+          <t>0.6047430830039526</t>
+        </is>
+      </c>
+      <c r="P289" s="2" t="inlineStr">
+        <is>
+          <t>0.60199</t>
+        </is>
+      </c>
+      <c r="Q289" s="2" t="inlineStr">
+        <is>
+          <t>0.06234891699604739</t>
+        </is>
+      </c>
+      <c r="R289" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:08:41.534907Z</t>
+        </is>
+      </c>
+      <c r="S289" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T20:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T289" s="2" t="inlineStr"/>
+      <c r="U289" s="2" t="inlineStr"/>
+      <c r="V289" s="2" t="inlineStr"/>
+      <c r="W289" s="2" t="inlineStr"/>
+      <c r="X289" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y289" s="2" t="inlineStr"/>
+      <c r="Z289" s="2" t="inlineStr"/>
+      <c r="AA289" s="2" t="inlineStr"/>
+      <c r="AB289" s="2" t="inlineStr"/>
+      <c r="AC289" s="2" t="inlineStr"/>
+      <c r="AD289" s="2" t="inlineStr"/>
+      <c r="AE289" s="2" t="inlineStr"/>
+      <c r="AF289" s="2" t="inlineStr"/>
+      <c r="AG289" s="2" t="inlineStr"/>
+      <c r="AH289" s="2" t="inlineStr"/>
+      <c r="AI289" s="2" t="inlineStr"/>
+      <c r="AJ289" s="2" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>0d843a94a3c54966</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>f9f4fbc27e74d366</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>401816436</t>
+        </is>
+      </c>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J290" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K290" s="2" t="inlineStr"/>
+      <c r="L290" s="2" t="inlineStr">
+        <is>
+          <t>0.586458</t>
+        </is>
+      </c>
+      <c r="M290" s="2" t="inlineStr"/>
+      <c r="N290" s="2" t="inlineStr"/>
+      <c r="O290" s="2" t="inlineStr">
+        <is>
+          <t>0.5348837209302326</t>
+        </is>
+      </c>
+      <c r="P290" s="2" t="inlineStr">
+        <is>
+          <t>0.532338</t>
+        </is>
+      </c>
+      <c r="Q290" s="2" t="inlineStr">
+        <is>
+          <t>0.051574279069767415</t>
+        </is>
+      </c>
+      <c r="R290" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:08:41.878795Z</t>
+        </is>
+      </c>
+      <c r="S290" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T290" s="2" t="inlineStr"/>
+      <c r="U290" s="2" t="inlineStr"/>
+      <c r="V290" s="2" t="inlineStr"/>
+      <c r="W290" s="2" t="inlineStr"/>
+      <c r="X290" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y290" s="2" t="inlineStr"/>
+      <c r="Z290" s="2" t="inlineStr"/>
+      <c r="AA290" s="2" t="inlineStr"/>
+      <c r="AB290" s="2" t="inlineStr"/>
+      <c r="AC290" s="2" t="inlineStr"/>
+      <c r="AD290" s="2" t="inlineStr"/>
+      <c r="AE290" s="2" t="inlineStr"/>
+      <c r="AF290" s="2" t="inlineStr"/>
+      <c r="AG290" s="2" t="inlineStr"/>
+      <c r="AH290" s="2" t="inlineStr"/>
+      <c r="AI290" s="2" t="inlineStr"/>
+      <c r="AJ290" s="2" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>bdf78d7b1dd04f7e</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>807bfd9a83666e43</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>401816437</t>
+        </is>
+      </c>
+      <c r="I291" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J291" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K291" s="2" t="inlineStr"/>
+      <c r="L291" s="2" t="inlineStr">
+        <is>
+          <t>0.527996</t>
+        </is>
+      </c>
+      <c r="M291" s="2" t="inlineStr"/>
+      <c r="N291" s="2" t="inlineStr"/>
+      <c r="O291" s="2" t="inlineStr">
+        <is>
+          <t>0.6254681647940076</t>
+        </is>
+      </c>
+      <c r="P291" s="2" t="inlineStr">
+        <is>
+          <t>0.621891</t>
+        </is>
+      </c>
+      <c r="Q291" s="2" t="inlineStr">
+        <is>
+          <t>-0.09747216479400755</t>
+        </is>
+      </c>
+      <c r="R291" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:08:42.416305Z</t>
+        </is>
+      </c>
+      <c r="S291" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T291" s="2" t="inlineStr"/>
+      <c r="U291" s="2" t="inlineStr"/>
+      <c r="V291" s="2" t="inlineStr"/>
+      <c r="W291" s="2" t="inlineStr"/>
+      <c r="X291" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y291" s="2" t="inlineStr"/>
+      <c r="Z291" s="2" t="inlineStr"/>
+      <c r="AA291" s="2" t="inlineStr"/>
+      <c r="AB291" s="2" t="inlineStr"/>
+      <c r="AC291" s="2" t="inlineStr"/>
+      <c r="AD291" s="2" t="inlineStr"/>
+      <c r="AE291" s="2" t="inlineStr"/>
+      <c r="AF291" s="2" t="inlineStr"/>
+      <c r="AG291" s="2" t="inlineStr"/>
+      <c r="AH291" s="2" t="inlineStr"/>
+      <c r="AI291" s="2" t="inlineStr"/>
+      <c r="AJ291" s="2" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>e817393c4fa04acb</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>cf9d26fcd493bc83</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>401816438</t>
+        </is>
+      </c>
+      <c r="I292" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J292" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K292" s="2" t="inlineStr"/>
+      <c r="L292" s="2" t="inlineStr">
+        <is>
+          <t>0.556751</t>
+        </is>
+      </c>
+      <c r="M292" s="2" t="inlineStr"/>
+      <c r="N292" s="2" t="inlineStr"/>
+      <c r="O292" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P292" s="2" t="inlineStr">
+        <is>
+          <t>0.507463</t>
+        </is>
+      </c>
+      <c r="Q292" s="2" t="inlineStr">
+        <is>
+          <t>0.04694707843137258</t>
+        </is>
+      </c>
+      <c r="R292" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:08:43.010411Z</t>
+        </is>
+      </c>
+      <c r="S292" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:45:00-0400</t>
+        </is>
+      </c>
+      <c r="T292" s="2" t="inlineStr"/>
+      <c r="U292" s="2" t="inlineStr"/>
+      <c r="V292" s="2" t="inlineStr"/>
+      <c r="W292" s="2" t="inlineStr"/>
+      <c r="X292" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y292" s="2" t="inlineStr"/>
+      <c r="Z292" s="2" t="inlineStr"/>
+      <c r="AA292" s="2" t="inlineStr"/>
+      <c r="AB292" s="2" t="inlineStr"/>
+      <c r="AC292" s="2" t="inlineStr"/>
+      <c r="AD292" s="2" t="inlineStr"/>
+      <c r="AE292" s="2" t="inlineStr"/>
+      <c r="AF292" s="2" t="inlineStr"/>
+      <c r="AG292" s="2" t="inlineStr"/>
+      <c r="AH292" s="2" t="inlineStr"/>
+      <c r="AI292" s="2" t="inlineStr"/>
+      <c r="AJ292" s="2" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>f30039ce7a2e4f2b</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>d25085d32ebd899a</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>401816428</t>
+        </is>
+      </c>
+      <c r="I293" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J293" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K293" s="2" t="inlineStr"/>
+      <c r="L293" s="2" t="inlineStr">
+        <is>
+          <t>0.581839</t>
+        </is>
+      </c>
+      <c r="M293" s="2" t="inlineStr"/>
+      <c r="N293" s="2" t="inlineStr"/>
+      <c r="O293" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P293" s="2" t="inlineStr">
+        <is>
+          <t>0.557214</t>
+        </is>
+      </c>
+      <c r="Q293" s="2" t="inlineStr">
+        <is>
+          <t>0.022367634361233457</t>
+        </is>
+      </c>
+      <c r="R293" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:14:37.487946Z</t>
+        </is>
+      </c>
+      <c r="S293" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T293" s="2" t="inlineStr"/>
+      <c r="U293" s="2" t="inlineStr"/>
+      <c r="V293" s="2" t="inlineStr"/>
+      <c r="W293" s="2" t="inlineStr"/>
+      <c r="X293" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y293" s="2" t="inlineStr"/>
+      <c r="Z293" s="2" t="inlineStr"/>
+      <c r="AA293" s="2" t="inlineStr"/>
+      <c r="AB293" s="2" t="inlineStr"/>
+      <c r="AC293" s="2" t="inlineStr"/>
+      <c r="AD293" s="2" t="inlineStr"/>
+      <c r="AE293" s="2" t="inlineStr"/>
+      <c r="AF293" s="2" t="inlineStr"/>
+      <c r="AG293" s="2" t="inlineStr"/>
+      <c r="AH293" s="2" t="inlineStr"/>
+      <c r="AI293" s="2" t="inlineStr"/>
+      <c r="AJ293" s="2" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>0d86a6dabd9c4d89</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>f899e3dda89e964b</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>401816429</t>
+        </is>
+      </c>
+      <c r="I294" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J294" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K294" s="2" t="inlineStr"/>
+      <c r="L294" s="2" t="inlineStr">
+        <is>
+          <t>0.56224</t>
+        </is>
+      </c>
+      <c r="M294" s="2" t="inlineStr"/>
+      <c r="N294" s="2" t="inlineStr"/>
+      <c r="O294" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P294" s="2" t="inlineStr">
+        <is>
+          <t>0.666667</t>
+        </is>
+      </c>
+      <c r="Q294" s="2" t="inlineStr">
+        <is>
+          <t>-0.10772699669967001</t>
+        </is>
+      </c>
+      <c r="R294" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:14:36.895250Z</t>
+        </is>
+      </c>
+      <c r="S294" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T294" s="2" t="inlineStr"/>
+      <c r="U294" s="2" t="inlineStr"/>
+      <c r="V294" s="2" t="inlineStr"/>
+      <c r="W294" s="2" t="inlineStr"/>
+      <c r="X294" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y294" s="2" t="inlineStr"/>
+      <c r="Z294" s="2" t="inlineStr"/>
+      <c r="AA294" s="2" t="inlineStr"/>
+      <c r="AB294" s="2" t="inlineStr"/>
+      <c r="AC294" s="2" t="inlineStr"/>
+      <c r="AD294" s="2" t="inlineStr"/>
+      <c r="AE294" s="2" t="inlineStr"/>
+      <c r="AF294" s="2" t="inlineStr"/>
+      <c r="AG294" s="2" t="inlineStr"/>
+      <c r="AH294" s="2" t="inlineStr"/>
+      <c r="AI294" s="2" t="inlineStr"/>
+      <c r="AJ294" s="2" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>b5e1a84c55f74df7</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
+          <t>832b08de30adc878</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>401816426</t>
+        </is>
+      </c>
+      <c r="I295" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J295" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K295" s="2" t="inlineStr"/>
+      <c r="L295" s="2" t="inlineStr">
+        <is>
+          <t>0.530725</t>
+        </is>
+      </c>
+      <c r="M295" s="2" t="inlineStr"/>
+      <c r="N295" s="2" t="inlineStr"/>
+      <c r="O295" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P295" s="2" t="inlineStr">
+        <is>
+          <t>0.577114</t>
+        </is>
+      </c>
+      <c r="Q295" s="2" t="inlineStr">
+        <is>
+          <t>-0.04910693277310918</t>
+        </is>
+      </c>
+      <c r="R295" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:14:38.752496Z</t>
+        </is>
+      </c>
+      <c r="S295" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T295" s="2" t="inlineStr"/>
+      <c r="U295" s="2" t="inlineStr"/>
+      <c r="V295" s="2" t="inlineStr"/>
+      <c r="W295" s="2" t="inlineStr"/>
+      <c r="X295" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y295" s="2" t="inlineStr"/>
+      <c r="Z295" s="2" t="inlineStr"/>
+      <c r="AA295" s="2" t="inlineStr"/>
+      <c r="AB295" s="2" t="inlineStr"/>
+      <c r="AC295" s="2" t="inlineStr"/>
+      <c r="AD295" s="2" t="inlineStr"/>
+      <c r="AE295" s="2" t="inlineStr"/>
+      <c r="AF295" s="2" t="inlineStr"/>
+      <c r="AG295" s="2" t="inlineStr"/>
+      <c r="AH295" s="2" t="inlineStr"/>
+      <c r="AI295" s="2" t="inlineStr"/>
+      <c r="AJ295" s="2" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>8383d3f30b8c4470</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>8bd990e177da70c3</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="inlineStr">
+        <is>
+          <t>401816424</t>
+        </is>
+      </c>
+      <c r="I296" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J296" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K296" s="2" t="inlineStr"/>
+      <c r="L296" s="2" t="inlineStr">
+        <is>
+          <t>0.641185</t>
+        </is>
+      </c>
+      <c r="M296" s="2" t="inlineStr"/>
+      <c r="N296" s="2" t="inlineStr"/>
+      <c r="O296" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P296" s="2" t="inlineStr">
+        <is>
+          <t>0.606965</t>
+        </is>
+      </c>
+      <c r="Q296" s="2" t="inlineStr">
+        <is>
+          <t>0.031810000000000005</t>
+        </is>
+      </c>
+      <c r="R296" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:14:39.776408Z</t>
+        </is>
+      </c>
+      <c r="S296" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T296" s="2" t="inlineStr"/>
+      <c r="U296" s="2" t="inlineStr"/>
+      <c r="V296" s="2" t="inlineStr"/>
+      <c r="W296" s="2" t="inlineStr"/>
+      <c r="X296" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y296" s="2" t="inlineStr"/>
+      <c r="Z296" s="2" t="inlineStr"/>
+      <c r="AA296" s="2" t="inlineStr"/>
+      <c r="AB296" s="2" t="inlineStr"/>
+      <c r="AC296" s="2" t="inlineStr"/>
+      <c r="AD296" s="2" t="inlineStr"/>
+      <c r="AE296" s="2" t="inlineStr"/>
+      <c r="AF296" s="2" t="inlineStr"/>
+      <c r="AG296" s="2" t="inlineStr"/>
+      <c r="AH296" s="2" t="inlineStr"/>
+      <c r="AI296" s="2" t="inlineStr"/>
+      <c r="AJ296" s="2" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>94e2c1f20218445c</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G297" s="2" t="inlineStr">
+        <is>
+          <t>0ff3d2b2c501e1c6</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>401816425</t>
+        </is>
+      </c>
+      <c r="I297" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J297" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K297" s="2" t="inlineStr"/>
+      <c r="L297" s="2" t="inlineStr">
+        <is>
+          <t>0.633595</t>
+        </is>
+      </c>
+      <c r="M297" s="2" t="inlineStr"/>
+      <c r="N297" s="2" t="inlineStr"/>
+      <c r="O297" s="2" t="inlineStr">
+        <is>
+          <t>0.715099715099715</t>
+        </is>
+      </c>
+      <c r="P297" s="2" t="inlineStr">
+        <is>
+          <t>0.711443</t>
+        </is>
+      </c>
+      <c r="Q297" s="2" t="inlineStr">
+        <is>
+          <t>-0.08150471509971502</t>
+        </is>
+      </c>
+      <c r="R297" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:14:39.283883Z</t>
+        </is>
+      </c>
+      <c r="S297" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T297" s="2" t="inlineStr"/>
+      <c r="U297" s="2" t="inlineStr"/>
+      <c r="V297" s="2" t="inlineStr"/>
+      <c r="W297" s="2" t="inlineStr"/>
+      <c r="X297" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y297" s="2" t="inlineStr"/>
+      <c r="Z297" s="2" t="inlineStr"/>
+      <c r="AA297" s="2" t="inlineStr"/>
+      <c r="AB297" s="2" t="inlineStr"/>
+      <c r="AC297" s="2" t="inlineStr"/>
+      <c r="AD297" s="2" t="inlineStr"/>
+      <c r="AE297" s="2" t="inlineStr"/>
+      <c r="AF297" s="2" t="inlineStr"/>
+      <c r="AG297" s="2" t="inlineStr"/>
+      <c r="AH297" s="2" t="inlineStr"/>
+      <c r="AI297" s="2" t="inlineStr"/>
+      <c r="AJ297" s="2" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>3606666cdf254d2d</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>6e78198b9918239f</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>401816432</t>
+        </is>
+      </c>
+      <c r="I298" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J298" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K298" s="2" t="inlineStr"/>
+      <c r="L298" s="2" t="inlineStr">
+        <is>
+          <t>0.522071</t>
+        </is>
+      </c>
+      <c r="M298" s="2" t="inlineStr"/>
+      <c r="N298" s="2" t="inlineStr"/>
+      <c r="O298" s="2" t="inlineStr">
+        <is>
+          <t>0.4347826086956522</t>
+        </is>
+      </c>
+      <c r="P298" s="2" t="inlineStr">
+        <is>
+          <t>0.432836</t>
+        </is>
+      </c>
+      <c r="Q298" s="2" t="inlineStr">
+        <is>
+          <t>0.08728839130434773</t>
+        </is>
+      </c>
+      <c r="R298" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:14:40.477952Z</t>
+        </is>
+      </c>
+      <c r="S298" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T298" s="2" t="inlineStr"/>
+      <c r="U298" s="2" t="inlineStr"/>
+      <c r="V298" s="2" t="inlineStr"/>
+      <c r="W298" s="2" t="inlineStr"/>
+      <c r="X298" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y298" s="2" t="inlineStr"/>
+      <c r="Z298" s="2" t="inlineStr"/>
+      <c r="AA298" s="2" t="inlineStr"/>
+      <c r="AB298" s="2" t="inlineStr"/>
+      <c r="AC298" s="2" t="inlineStr"/>
+      <c r="AD298" s="2" t="inlineStr"/>
+      <c r="AE298" s="2" t="inlineStr"/>
+      <c r="AF298" s="2" t="inlineStr"/>
+      <c r="AG298" s="2" t="inlineStr"/>
+      <c r="AH298" s="2" t="inlineStr"/>
+      <c r="AI298" s="2" t="inlineStr"/>
+      <c r="AJ298" s="2" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>08fbfbd260b0425b</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>6930bf181d0a558c</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>401816434</t>
+        </is>
+      </c>
+      <c r="I299" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J299" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K299" s="2" t="inlineStr"/>
+      <c r="L299" s="2" t="inlineStr">
+        <is>
+          <t>0.651659</t>
+        </is>
+      </c>
+      <c r="M299" s="2" t="inlineStr"/>
+      <c r="N299" s="2" t="inlineStr"/>
+      <c r="O299" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P299" s="2" t="inlineStr">
+        <is>
+          <t>0.626866</t>
+        </is>
+      </c>
+      <c r="Q299" s="2" t="inlineStr">
+        <is>
+          <t>0.02202937037037045</t>
+        </is>
+      </c>
+      <c r="R299" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:14:40.330217Z</t>
+        </is>
+      </c>
+      <c r="S299" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T299" s="2" t="inlineStr"/>
+      <c r="U299" s="2" t="inlineStr"/>
+      <c r="V299" s="2" t="inlineStr"/>
+      <c r="W299" s="2" t="inlineStr"/>
+      <c r="X299" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y299" s="2" t="inlineStr"/>
+      <c r="Z299" s="2" t="inlineStr"/>
+      <c r="AA299" s="2" t="inlineStr"/>
+      <c r="AB299" s="2" t="inlineStr"/>
+      <c r="AC299" s="2" t="inlineStr"/>
+      <c r="AD299" s="2" t="inlineStr"/>
+      <c r="AE299" s="2" t="inlineStr"/>
+      <c r="AF299" s="2" t="inlineStr"/>
+      <c r="AG299" s="2" t="inlineStr"/>
+      <c r="AH299" s="2" t="inlineStr"/>
+      <c r="AI299" s="2" t="inlineStr"/>
+      <c r="AJ299" s="2" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>ac4ef554be264634</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>b3f98c9129b9e2d8</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="inlineStr">
+        <is>
+          <t>401816431</t>
+        </is>
+      </c>
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J300" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K300" s="2" t="inlineStr"/>
+      <c r="L300" s="2" t="inlineStr">
+        <is>
+          <t>0.53277</t>
+        </is>
+      </c>
+      <c r="M300" s="2" t="inlineStr"/>
+      <c r="N300" s="2" t="inlineStr"/>
+      <c r="O300" s="2" t="inlineStr">
+        <is>
+          <t>0.6153846153846154</t>
+        </is>
+      </c>
+      <c r="P300" s="2" t="inlineStr">
+        <is>
+          <t>0.61194</t>
+        </is>
+      </c>
+      <c r="Q300" s="2" t="inlineStr">
+        <is>
+          <t>-0.08261461538461545</t>
+        </is>
+      </c>
+      <c r="R300" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:14:41.124231Z</t>
+        </is>
+      </c>
+      <c r="S300" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T20:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T300" s="2" t="inlineStr"/>
+      <c r="U300" s="2" t="inlineStr"/>
+      <c r="V300" s="2" t="inlineStr"/>
+      <c r="W300" s="2" t="inlineStr"/>
+      <c r="X300" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y300" s="2" t="inlineStr"/>
+      <c r="Z300" s="2" t="inlineStr"/>
+      <c r="AA300" s="2" t="inlineStr"/>
+      <c r="AB300" s="2" t="inlineStr"/>
+      <c r="AC300" s="2" t="inlineStr"/>
+      <c r="AD300" s="2" t="inlineStr"/>
+      <c r="AE300" s="2" t="inlineStr"/>
+      <c r="AF300" s="2" t="inlineStr"/>
+      <c r="AG300" s="2" t="inlineStr"/>
+      <c r="AH300" s="2" t="inlineStr"/>
+      <c r="AI300" s="2" t="inlineStr"/>
+      <c r="AJ300" s="2" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>7c8a6279a4bd4b5c</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>a94431fcc113fab7</t>
+        </is>
+      </c>
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>401816430</t>
+        </is>
+      </c>
+      <c r="I301" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J301" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K301" s="2" t="inlineStr"/>
+      <c r="L301" s="2" t="inlineStr">
+        <is>
+          <t>0.550403</t>
+        </is>
+      </c>
+      <c r="M301" s="2" t="inlineStr"/>
+      <c r="N301" s="2" t="inlineStr"/>
+      <c r="O301" s="2" t="inlineStr">
+        <is>
+          <t>0.5850622406639003</t>
+        </is>
+      </c>
+      <c r="P301" s="2" t="inlineStr">
+        <is>
+          <t>0.58209</t>
+        </is>
+      </c>
+      <c r="Q301" s="2" t="inlineStr">
+        <is>
+          <t>-0.03465924066390036</t>
+        </is>
+      </c>
+      <c r="R301" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:14:41.725200Z</t>
+        </is>
+      </c>
+      <c r="S301" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T20:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T301" s="2" t="inlineStr"/>
+      <c r="U301" s="2" t="inlineStr"/>
+      <c r="V301" s="2" t="inlineStr"/>
+      <c r="W301" s="2" t="inlineStr"/>
+      <c r="X301" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y301" s="2" t="inlineStr"/>
+      <c r="Z301" s="2" t="inlineStr"/>
+      <c r="AA301" s="2" t="inlineStr"/>
+      <c r="AB301" s="2" t="inlineStr"/>
+      <c r="AC301" s="2" t="inlineStr"/>
+      <c r="AD301" s="2" t="inlineStr"/>
+      <c r="AE301" s="2" t="inlineStr"/>
+      <c r="AF301" s="2" t="inlineStr"/>
+      <c r="AG301" s="2" t="inlineStr"/>
+      <c r="AH301" s="2" t="inlineStr"/>
+      <c r="AI301" s="2" t="inlineStr"/>
+      <c r="AJ301" s="2" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>46e24fcf6e634106</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>afcfaab14f1642bd</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>401816433</t>
+        </is>
+      </c>
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J302" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K302" s="2" t="inlineStr"/>
+      <c r="L302" s="2" t="inlineStr">
+        <is>
+          <t>0.667139</t>
+        </is>
+      </c>
+      <c r="M302" s="2" t="inlineStr"/>
+      <c r="N302" s="2" t="inlineStr"/>
+      <c r="O302" s="2" t="inlineStr">
+        <is>
+          <t>0.6153846153846154</t>
+        </is>
+      </c>
+      <c r="P302" s="2" t="inlineStr">
+        <is>
+          <t>0.61194</t>
+        </is>
+      </c>
+      <c r="Q302" s="2" t="inlineStr">
+        <is>
+          <t>0.05175438461538462</t>
+        </is>
+      </c>
+      <c r="R302" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:14:42.254426Z</t>
+        </is>
+      </c>
+      <c r="S302" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T20:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T302" s="2" t="inlineStr"/>
+      <c r="U302" s="2" t="inlineStr"/>
+      <c r="V302" s="2" t="inlineStr"/>
+      <c r="W302" s="2" t="inlineStr"/>
+      <c r="X302" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y302" s="2" t="inlineStr"/>
+      <c r="Z302" s="2" t="inlineStr"/>
+      <c r="AA302" s="2" t="inlineStr"/>
+      <c r="AB302" s="2" t="inlineStr"/>
+      <c r="AC302" s="2" t="inlineStr"/>
+      <c r="AD302" s="2" t="inlineStr"/>
+      <c r="AE302" s="2" t="inlineStr"/>
+      <c r="AF302" s="2" t="inlineStr"/>
+      <c r="AG302" s="2" t="inlineStr"/>
+      <c r="AH302" s="2" t="inlineStr"/>
+      <c r="AI302" s="2" t="inlineStr"/>
+      <c r="AJ302" s="2" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>d6bcb970a7584f93</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>3576be583da63691</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t>401816436</t>
+        </is>
+      </c>
+      <c r="I303" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J303" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K303" s="2" t="inlineStr"/>
+      <c r="L303" s="2" t="inlineStr">
+        <is>
+          <t>0.586451</t>
+        </is>
+      </c>
+      <c r="M303" s="2" t="inlineStr"/>
+      <c r="N303" s="2" t="inlineStr"/>
+      <c r="O303" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P303" s="2" t="inlineStr">
+        <is>
+          <t>0.537313</t>
+        </is>
+      </c>
+      <c r="Q303" s="2" t="inlineStr">
+        <is>
+          <t>0.04728049308755755</t>
+        </is>
+      </c>
+      <c r="R303" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:14:42.707346Z</t>
+        </is>
+      </c>
+      <c r="S303" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T303" s="2" t="inlineStr"/>
+      <c r="U303" s="2" t="inlineStr"/>
+      <c r="V303" s="2" t="inlineStr"/>
+      <c r="W303" s="2" t="inlineStr"/>
+      <c r="X303" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y303" s="2" t="inlineStr"/>
+      <c r="Z303" s="2" t="inlineStr"/>
+      <c r="AA303" s="2" t="inlineStr"/>
+      <c r="AB303" s="2" t="inlineStr"/>
+      <c r="AC303" s="2" t="inlineStr"/>
+      <c r="AD303" s="2" t="inlineStr"/>
+      <c r="AE303" s="2" t="inlineStr"/>
+      <c r="AF303" s="2" t="inlineStr"/>
+      <c r="AG303" s="2" t="inlineStr"/>
+      <c r="AH303" s="2" t="inlineStr"/>
+      <c r="AI303" s="2" t="inlineStr"/>
+      <c r="AJ303" s="2" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>1417117ffa20411c</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>807bfd9a83666e43</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>401816437</t>
+        </is>
+      </c>
+      <c r="I304" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J304" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K304" s="2" t="inlineStr"/>
+      <c r="L304" s="2" t="inlineStr">
+        <is>
+          <t>0.527996</t>
+        </is>
+      </c>
+      <c r="M304" s="2" t="inlineStr"/>
+      <c r="N304" s="2" t="inlineStr"/>
+      <c r="O304" s="2" t="inlineStr">
+        <is>
+          <t>0.6254681647940076</t>
+        </is>
+      </c>
+      <c r="P304" s="2" t="inlineStr">
+        <is>
+          <t>0.621891</t>
+        </is>
+      </c>
+      <c r="Q304" s="2" t="inlineStr">
+        <is>
+          <t>-0.09747216479400755</t>
+        </is>
+      </c>
+      <c r="R304" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:14:43.208239Z</t>
+        </is>
+      </c>
+      <c r="S304" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T304" s="2" t="inlineStr"/>
+      <c r="U304" s="2" t="inlineStr"/>
+      <c r="V304" s="2" t="inlineStr"/>
+      <c r="W304" s="2" t="inlineStr"/>
+      <c r="X304" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y304" s="2" t="inlineStr"/>
+      <c r="Z304" s="2" t="inlineStr"/>
+      <c r="AA304" s="2" t="inlineStr"/>
+      <c r="AB304" s="2" t="inlineStr"/>
+      <c r="AC304" s="2" t="inlineStr"/>
+      <c r="AD304" s="2" t="inlineStr"/>
+      <c r="AE304" s="2" t="inlineStr"/>
+      <c r="AF304" s="2" t="inlineStr"/>
+      <c r="AG304" s="2" t="inlineStr"/>
+      <c r="AH304" s="2" t="inlineStr"/>
+      <c r="AI304" s="2" t="inlineStr"/>
+      <c r="AJ304" s="2" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>95b7f4629e8a4cac</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>cf9d26fcd493bc83</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>401816438</t>
+        </is>
+      </c>
+      <c r="I305" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J305" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K305" s="2" t="inlineStr"/>
+      <c r="L305" s="2" t="inlineStr">
+        <is>
+          <t>0.556751</t>
+        </is>
+      </c>
+      <c r="M305" s="2" t="inlineStr"/>
+      <c r="N305" s="2" t="inlineStr"/>
+      <c r="O305" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P305" s="2" t="inlineStr">
+        <is>
+          <t>0.507463</t>
+        </is>
+      </c>
+      <c r="Q305" s="2" t="inlineStr">
+        <is>
+          <t>0.04694707843137258</t>
+        </is>
+      </c>
+      <c r="R305" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:14:44.174152Z</t>
+        </is>
+      </c>
+      <c r="S305" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:45:00-0400</t>
+        </is>
+      </c>
+      <c r="T305" s="2" t="inlineStr"/>
+      <c r="U305" s="2" t="inlineStr"/>
+      <c r="V305" s="2" t="inlineStr"/>
+      <c r="W305" s="2" t="inlineStr"/>
+      <c r="X305" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y305" s="2" t="inlineStr"/>
+      <c r="Z305" s="2" t="inlineStr"/>
+      <c r="AA305" s="2" t="inlineStr"/>
+      <c r="AB305" s="2" t="inlineStr"/>
+      <c r="AC305" s="2" t="inlineStr"/>
+      <c r="AD305" s="2" t="inlineStr"/>
+      <c r="AE305" s="2" t="inlineStr"/>
+      <c r="AF305" s="2" t="inlineStr"/>
+      <c r="AG305" s="2" t="inlineStr"/>
+      <c r="AH305" s="2" t="inlineStr"/>
+      <c r="AI305" s="2" t="inlineStr"/>
+      <c r="AJ305" s="2" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>e0c8b9046c2e49df</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>e12a127ae2be75e7</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>401816428</t>
+        </is>
+      </c>
+      <c r="I306" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J306" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K306" s="2" t="inlineStr"/>
+      <c r="L306" s="2" t="inlineStr">
+        <is>
+          <t>0.582115</t>
+        </is>
+      </c>
+      <c r="M306" s="2" t="inlineStr"/>
+      <c r="N306" s="2" t="inlineStr"/>
+      <c r="O306" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P306" s="2" t="inlineStr">
+        <is>
+          <t>0.557214</t>
+        </is>
+      </c>
+      <c r="Q306" s="2" t="inlineStr">
+        <is>
+          <t>0.02264363436123351</t>
+        </is>
+      </c>
+      <c r="R306" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:30.212391Z</t>
+        </is>
+      </c>
+      <c r="S306" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T306" s="2" t="inlineStr"/>
+      <c r="U306" s="2" t="inlineStr"/>
+      <c r="V306" s="2" t="inlineStr"/>
+      <c r="W306" s="2" t="inlineStr"/>
+      <c r="X306" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y306" s="2" t="inlineStr"/>
+      <c r="Z306" s="2" t="inlineStr"/>
+      <c r="AA306" s="2" t="inlineStr"/>
+      <c r="AB306" s="2" t="inlineStr"/>
+      <c r="AC306" s="2" t="inlineStr"/>
+      <c r="AD306" s="2" t="inlineStr"/>
+      <c r="AE306" s="2" t="inlineStr"/>
+      <c r="AF306" s="2" t="inlineStr"/>
+      <c r="AG306" s="2" t="inlineStr"/>
+      <c r="AH306" s="2" t="inlineStr"/>
+      <c r="AI306" s="2" t="inlineStr"/>
+      <c r="AJ306" s="2" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>8f5ea850073348c2</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>b673147bebc07f1b</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>401816429</t>
+        </is>
+      </c>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J307" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K307" s="2" t="inlineStr"/>
+      <c r="L307" s="2" t="inlineStr">
+        <is>
+          <t>0.562548</t>
+        </is>
+      </c>
+      <c r="M307" s="2" t="inlineStr"/>
+      <c r="N307" s="2" t="inlineStr"/>
+      <c r="O307" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P307" s="2" t="inlineStr">
+        <is>
+          <t>0.666667</t>
+        </is>
+      </c>
+      <c r="Q307" s="2" t="inlineStr">
+        <is>
+          <t>-0.10741899669966992</t>
+        </is>
+      </c>
+      <c r="R307" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:29.485983Z</t>
+        </is>
+      </c>
+      <c r="S307" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T307" s="2" t="inlineStr"/>
+      <c r="U307" s="2" t="inlineStr"/>
+      <c r="V307" s="2" t="inlineStr"/>
+      <c r="W307" s="2" t="inlineStr"/>
+      <c r="X307" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y307" s="2" t="inlineStr"/>
+      <c r="Z307" s="2" t="inlineStr"/>
+      <c r="AA307" s="2" t="inlineStr"/>
+      <c r="AB307" s="2" t="inlineStr"/>
+      <c r="AC307" s="2" t="inlineStr"/>
+      <c r="AD307" s="2" t="inlineStr"/>
+      <c r="AE307" s="2" t="inlineStr"/>
+      <c r="AF307" s="2" t="inlineStr"/>
+      <c r="AG307" s="2" t="inlineStr"/>
+      <c r="AH307" s="2" t="inlineStr"/>
+      <c r="AI307" s="2" t="inlineStr"/>
+      <c r="AJ307" s="2" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>01e47054d6184de7</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>6d71e1aa1aca3674</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>401816426</t>
+        </is>
+      </c>
+      <c r="I308" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J308" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K308" s="2" t="inlineStr"/>
+      <c r="L308" s="2" t="inlineStr">
+        <is>
+          <t>0.531474</t>
+        </is>
+      </c>
+      <c r="M308" s="2" t="inlineStr"/>
+      <c r="N308" s="2" t="inlineStr"/>
+      <c r="O308" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P308" s="2" t="inlineStr">
+        <is>
+          <t>0.557214</t>
+        </is>
+      </c>
+      <c r="Q308" s="2" t="inlineStr">
+        <is>
+          <t>-0.027997365638766536</t>
+        </is>
+      </c>
+      <c r="R308" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:31.729374Z</t>
+        </is>
+      </c>
+      <c r="S308" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T308" s="2" t="inlineStr"/>
+      <c r="U308" s="2" t="inlineStr"/>
+      <c r="V308" s="2" t="inlineStr"/>
+      <c r="W308" s="2" t="inlineStr"/>
+      <c r="X308" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y308" s="2" t="inlineStr"/>
+      <c r="Z308" s="2" t="inlineStr"/>
+      <c r="AA308" s="2" t="inlineStr"/>
+      <c r="AB308" s="2" t="inlineStr"/>
+      <c r="AC308" s="2" t="inlineStr"/>
+      <c r="AD308" s="2" t="inlineStr"/>
+      <c r="AE308" s="2" t="inlineStr"/>
+      <c r="AF308" s="2" t="inlineStr"/>
+      <c r="AG308" s="2" t="inlineStr"/>
+      <c r="AH308" s="2" t="inlineStr"/>
+      <c r="AI308" s="2" t="inlineStr"/>
+      <c r="AJ308" s="2" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>337c7fa88b2e4366</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>8bd990e177da70c3</t>
+        </is>
+      </c>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>401816424</t>
+        </is>
+      </c>
+      <c r="I309" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J309" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K309" s="2" t="inlineStr"/>
+      <c r="L309" s="2" t="inlineStr">
+        <is>
+          <t>0.641185</t>
+        </is>
+      </c>
+      <c r="M309" s="2" t="inlineStr"/>
+      <c r="N309" s="2" t="inlineStr"/>
+      <c r="O309" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P309" s="2" t="inlineStr">
+        <is>
+          <t>0.587065</t>
+        </is>
+      </c>
+      <c r="Q309" s="2" t="inlineStr">
+        <is>
+          <t>0.05102106557377051</t>
+        </is>
+      </c>
+      <c r="R309" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:32.539307Z</t>
+        </is>
+      </c>
+      <c r="S309" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T309" s="2" t="inlineStr"/>
+      <c r="U309" s="2" t="inlineStr"/>
+      <c r="V309" s="2" t="inlineStr"/>
+      <c r="W309" s="2" t="inlineStr"/>
+      <c r="X309" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y309" s="2" t="inlineStr"/>
+      <c r="Z309" s="2" t="inlineStr"/>
+      <c r="AA309" s="2" t="inlineStr"/>
+      <c r="AB309" s="2" t="inlineStr"/>
+      <c r="AC309" s="2" t="inlineStr"/>
+      <c r="AD309" s="2" t="inlineStr"/>
+      <c r="AE309" s="2" t="inlineStr"/>
+      <c r="AF309" s="2" t="inlineStr"/>
+      <c r="AG309" s="2" t="inlineStr"/>
+      <c r="AH309" s="2" t="inlineStr"/>
+      <c r="AI309" s="2" t="inlineStr"/>
+      <c r="AJ309" s="2" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>9d7b165a0e7d407e</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>0ff3d2b2c501e1c6</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>401816425</t>
+        </is>
+      </c>
+      <c r="I310" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J310" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K310" s="2" t="inlineStr"/>
+      <c r="L310" s="2" t="inlineStr">
+        <is>
+          <t>0.633595</t>
+        </is>
+      </c>
+      <c r="M310" s="2" t="inlineStr"/>
+      <c r="N310" s="2" t="inlineStr"/>
+      <c r="O310" s="2" t="inlineStr">
+        <is>
+          <t>0.715099715099715</t>
+        </is>
+      </c>
+      <c r="P310" s="2" t="inlineStr">
+        <is>
+          <t>0.711443</t>
+        </is>
+      </c>
+      <c r="Q310" s="2" t="inlineStr">
+        <is>
+          <t>-0.08150471509971502</t>
+        </is>
+      </c>
+      <c r="R310" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:32.009937Z</t>
+        </is>
+      </c>
+      <c r="S310" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T310" s="2" t="inlineStr"/>
+      <c r="U310" s="2" t="inlineStr"/>
+      <c r="V310" s="2" t="inlineStr"/>
+      <c r="W310" s="2" t="inlineStr"/>
+      <c r="X310" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y310" s="2" t="inlineStr"/>
+      <c r="Z310" s="2" t="inlineStr"/>
+      <c r="AA310" s="2" t="inlineStr"/>
+      <c r="AB310" s="2" t="inlineStr"/>
+      <c r="AC310" s="2" t="inlineStr"/>
+      <c r="AD310" s="2" t="inlineStr"/>
+      <c r="AE310" s="2" t="inlineStr"/>
+      <c r="AF310" s="2" t="inlineStr"/>
+      <c r="AG310" s="2" t="inlineStr"/>
+      <c r="AH310" s="2" t="inlineStr"/>
+      <c r="AI310" s="2" t="inlineStr"/>
+      <c r="AJ310" s="2" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>a49df2d8c6394ea2</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>2efd36b960d60e32</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>401816432</t>
+        </is>
+      </c>
+      <c r="I311" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J311" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K311" s="2" t="inlineStr"/>
+      <c r="L311" s="2" t="inlineStr">
+        <is>
+          <t>0.522019</t>
+        </is>
+      </c>
+      <c r="M311" s="2" t="inlineStr"/>
+      <c r="N311" s="2" t="inlineStr"/>
+      <c r="O311" s="2" t="inlineStr">
+        <is>
+          <t>0.4347826086956522</t>
+        </is>
+      </c>
+      <c r="P311" s="2" t="inlineStr">
+        <is>
+          <t>0.432836</t>
+        </is>
+      </c>
+      <c r="Q311" s="2" t="inlineStr">
+        <is>
+          <t>0.0872363913043478</t>
+        </is>
+      </c>
+      <c r="R311" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:33.568333Z</t>
+        </is>
+      </c>
+      <c r="S311" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T311" s="2" t="inlineStr"/>
+      <c r="U311" s="2" t="inlineStr"/>
+      <c r="V311" s="2" t="inlineStr"/>
+      <c r="W311" s="2" t="inlineStr"/>
+      <c r="X311" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y311" s="2" t="inlineStr"/>
+      <c r="Z311" s="2" t="inlineStr"/>
+      <c r="AA311" s="2" t="inlineStr"/>
+      <c r="AB311" s="2" t="inlineStr"/>
+      <c r="AC311" s="2" t="inlineStr"/>
+      <c r="AD311" s="2" t="inlineStr"/>
+      <c r="AE311" s="2" t="inlineStr"/>
+      <c r="AF311" s="2" t="inlineStr"/>
+      <c r="AG311" s="2" t="inlineStr"/>
+      <c r="AH311" s="2" t="inlineStr"/>
+      <c r="AI311" s="2" t="inlineStr"/>
+      <c r="AJ311" s="2" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>be38a6d02d8a494e</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>6930bf181d0a558c</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>401816434</t>
+        </is>
+      </c>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J312" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K312" s="2" t="inlineStr"/>
+      <c r="L312" s="2" t="inlineStr">
+        <is>
+          <t>0.651659</t>
+        </is>
+      </c>
+      <c r="M312" s="2" t="inlineStr"/>
+      <c r="N312" s="2" t="inlineStr"/>
+      <c r="O312" s="2" t="inlineStr">
+        <is>
+          <t>0.6254681647940076</t>
+        </is>
+      </c>
+      <c r="P312" s="2" t="inlineStr">
+        <is>
+          <t>0.621891</t>
+        </is>
+      </c>
+      <c r="Q312" s="2" t="inlineStr">
+        <is>
+          <t>0.026190835205992413</t>
+        </is>
+      </c>
+      <c r="R312" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:33.201063Z</t>
+        </is>
+      </c>
+      <c r="S312" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T312" s="2" t="inlineStr"/>
+      <c r="U312" s="2" t="inlineStr"/>
+      <c r="V312" s="2" t="inlineStr"/>
+      <c r="W312" s="2" t="inlineStr"/>
+      <c r="X312" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y312" s="2" t="inlineStr"/>
+      <c r="Z312" s="2" t="inlineStr"/>
+      <c r="AA312" s="2" t="inlineStr"/>
+      <c r="AB312" s="2" t="inlineStr"/>
+      <c r="AC312" s="2" t="inlineStr"/>
+      <c r="AD312" s="2" t="inlineStr"/>
+      <c r="AE312" s="2" t="inlineStr"/>
+      <c r="AF312" s="2" t="inlineStr"/>
+      <c r="AG312" s="2" t="inlineStr"/>
+      <c r="AH312" s="2" t="inlineStr"/>
+      <c r="AI312" s="2" t="inlineStr"/>
+      <c r="AJ312" s="2" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>89e4715535df4e54</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>4aaa53f1128b4c90</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>401816431</t>
+        </is>
+      </c>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J313" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K313" s="2" t="inlineStr"/>
+      <c r="L313" s="2" t="inlineStr">
+        <is>
+          <t>0.532599</t>
+        </is>
+      </c>
+      <c r="M313" s="2" t="inlineStr"/>
+      <c r="N313" s="2" t="inlineStr"/>
+      <c r="O313" s="2" t="inlineStr">
+        <is>
+          <t>0.6153846153846154</t>
+        </is>
+      </c>
+      <c r="P313" s="2" t="inlineStr">
+        <is>
+          <t>0.61194</t>
+        </is>
+      </c>
+      <c r="Q313" s="2" t="inlineStr">
+        <is>
+          <t>-0.08278561538461537</t>
+        </is>
+      </c>
+      <c r="R313" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:34.170354Z</t>
+        </is>
+      </c>
+      <c r="S313" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T20:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T313" s="2" t="inlineStr"/>
+      <c r="U313" s="2" t="inlineStr"/>
+      <c r="V313" s="2" t="inlineStr"/>
+      <c r="W313" s="2" t="inlineStr"/>
+      <c r="X313" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y313" s="2" t="inlineStr"/>
+      <c r="Z313" s="2" t="inlineStr"/>
+      <c r="AA313" s="2" t="inlineStr"/>
+      <c r="AB313" s="2" t="inlineStr"/>
+      <c r="AC313" s="2" t="inlineStr"/>
+      <c r="AD313" s="2" t="inlineStr"/>
+      <c r="AE313" s="2" t="inlineStr"/>
+      <c r="AF313" s="2" t="inlineStr"/>
+      <c r="AG313" s="2" t="inlineStr"/>
+      <c r="AH313" s="2" t="inlineStr"/>
+      <c r="AI313" s="2" t="inlineStr"/>
+      <c r="AJ313" s="2" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>c7492ed1925f41d5</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>014888ea3e3e3318</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>401816430</t>
+        </is>
+      </c>
+      <c r="I314" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J314" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K314" s="2" t="inlineStr"/>
+      <c r="L314" s="2" t="inlineStr">
+        <is>
+          <t>0.551691</t>
+        </is>
+      </c>
+      <c r="M314" s="2" t="inlineStr"/>
+      <c r="N314" s="2" t="inlineStr"/>
+      <c r="O314" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P314" s="2" t="inlineStr">
+        <is>
+          <t>0.577114</t>
+        </is>
+      </c>
+      <c r="Q314" s="2" t="inlineStr">
+        <is>
+          <t>-0.02814093277310914</t>
+        </is>
+      </c>
+      <c r="R314" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:34.716538Z</t>
+        </is>
+      </c>
+      <c r="S314" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T20:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T314" s="2" t="inlineStr"/>
+      <c r="U314" s="2" t="inlineStr"/>
+      <c r="V314" s="2" t="inlineStr"/>
+      <c r="W314" s="2" t="inlineStr"/>
+      <c r="X314" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y314" s="2" t="inlineStr"/>
+      <c r="Z314" s="2" t="inlineStr"/>
+      <c r="AA314" s="2" t="inlineStr"/>
+      <c r="AB314" s="2" t="inlineStr"/>
+      <c r="AC314" s="2" t="inlineStr"/>
+      <c r="AD314" s="2" t="inlineStr"/>
+      <c r="AE314" s="2" t="inlineStr"/>
+      <c r="AF314" s="2" t="inlineStr"/>
+      <c r="AG314" s="2" t="inlineStr"/>
+      <c r="AH314" s="2" t="inlineStr"/>
+      <c r="AI314" s="2" t="inlineStr"/>
+      <c r="AJ314" s="2" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>2b79471837f646c9</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>1feab342954b6f1c</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>401816433</t>
+        </is>
+      </c>
+      <c r="I315" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J315" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K315" s="2" t="inlineStr"/>
+      <c r="L315" s="2" t="inlineStr">
+        <is>
+          <t>0.667231</t>
+        </is>
+      </c>
+      <c r="M315" s="2" t="inlineStr"/>
+      <c r="N315" s="2" t="inlineStr"/>
+      <c r="O315" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P315" s="2" t="inlineStr">
+        <is>
+          <t>0.606965</t>
+        </is>
+      </c>
+      <c r="Q315" s="2" t="inlineStr">
+        <is>
+          <t>0.05785600000000002</t>
+        </is>
+      </c>
+      <c r="R315" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:35.292740Z</t>
+        </is>
+      </c>
+      <c r="S315" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T20:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T315" s="2" t="inlineStr"/>
+      <c r="U315" s="2" t="inlineStr"/>
+      <c r="V315" s="2" t="inlineStr"/>
+      <c r="W315" s="2" t="inlineStr"/>
+      <c r="X315" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y315" s="2" t="inlineStr"/>
+      <c r="Z315" s="2" t="inlineStr"/>
+      <c r="AA315" s="2" t="inlineStr"/>
+      <c r="AB315" s="2" t="inlineStr"/>
+      <c r="AC315" s="2" t="inlineStr"/>
+      <c r="AD315" s="2" t="inlineStr"/>
+      <c r="AE315" s="2" t="inlineStr"/>
+      <c r="AF315" s="2" t="inlineStr"/>
+      <c r="AG315" s="2" t="inlineStr"/>
+      <c r="AH315" s="2" t="inlineStr"/>
+      <c r="AI315" s="2" t="inlineStr"/>
+      <c r="AJ315" s="2" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>9f6f2dd8f45d4b22</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>7d222b05e34d512d</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>401816436</t>
+        </is>
+      </c>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J316" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K316" s="2" t="inlineStr"/>
+      <c r="L316" s="2" t="inlineStr">
+        <is>
+          <t>0.586429</t>
+        </is>
+      </c>
+      <c r="M316" s="2" t="inlineStr"/>
+      <c r="N316" s="2" t="inlineStr"/>
+      <c r="O316" s="2" t="inlineStr">
+        <is>
+          <t>0.5348837209302326</t>
+        </is>
+      </c>
+      <c r="P316" s="2" t="inlineStr">
+        <is>
+          <t>0.532338</t>
+        </is>
+      </c>
+      <c r="Q316" s="2" t="inlineStr">
+        <is>
+          <t>0.05154527906976736</t>
+        </is>
+      </c>
+      <c r="R316" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:35.802686Z</t>
+        </is>
+      </c>
+      <c r="S316" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T316" s="2" t="inlineStr"/>
+      <c r="U316" s="2" t="inlineStr"/>
+      <c r="V316" s="2" t="inlineStr"/>
+      <c r="W316" s="2" t="inlineStr"/>
+      <c r="X316" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y316" s="2" t="inlineStr"/>
+      <c r="Z316" s="2" t="inlineStr"/>
+      <c r="AA316" s="2" t="inlineStr"/>
+      <c r="AB316" s="2" t="inlineStr"/>
+      <c r="AC316" s="2" t="inlineStr"/>
+      <c r="AD316" s="2" t="inlineStr"/>
+      <c r="AE316" s="2" t="inlineStr"/>
+      <c r="AF316" s="2" t="inlineStr"/>
+      <c r="AG316" s="2" t="inlineStr"/>
+      <c r="AH316" s="2" t="inlineStr"/>
+      <c r="AI316" s="2" t="inlineStr"/>
+      <c r="AJ316" s="2" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>fcd7a7fcdd7d4a97</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F317" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>807bfd9a83666e43</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>401816437</t>
+        </is>
+      </c>
+      <c r="I317" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J317" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K317" s="2" t="inlineStr"/>
+      <c r="L317" s="2" t="inlineStr">
+        <is>
+          <t>0.527996</t>
+        </is>
+      </c>
+      <c r="M317" s="2" t="inlineStr"/>
+      <c r="N317" s="2" t="inlineStr"/>
+      <c r="O317" s="2" t="inlineStr">
+        <is>
+          <t>0.6254681647940076</t>
+        </is>
+      </c>
+      <c r="P317" s="2" t="inlineStr">
+        <is>
+          <t>0.621891</t>
+        </is>
+      </c>
+      <c r="Q317" s="2" t="inlineStr">
+        <is>
+          <t>-0.09747216479400755</t>
+        </is>
+      </c>
+      <c r="R317" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:36.331607Z</t>
+        </is>
+      </c>
+      <c r="S317" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T317" s="2" t="inlineStr"/>
+      <c r="U317" s="2" t="inlineStr"/>
+      <c r="V317" s="2" t="inlineStr"/>
+      <c r="W317" s="2" t="inlineStr"/>
+      <c r="X317" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y317" s="2" t="inlineStr"/>
+      <c r="Z317" s="2" t="inlineStr"/>
+      <c r="AA317" s="2" t="inlineStr"/>
+      <c r="AB317" s="2" t="inlineStr"/>
+      <c r="AC317" s="2" t="inlineStr"/>
+      <c r="AD317" s="2" t="inlineStr"/>
+      <c r="AE317" s="2" t="inlineStr"/>
+      <c r="AF317" s="2" t="inlineStr"/>
+      <c r="AG317" s="2" t="inlineStr"/>
+      <c r="AH317" s="2" t="inlineStr"/>
+      <c r="AI317" s="2" t="inlineStr"/>
+      <c r="AJ317" s="2" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>053d0a6cdd144b05</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>cf9d26fcd493bc83</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>401816438</t>
+        </is>
+      </c>
+      <c r="I318" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J318" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K318" s="2" t="inlineStr"/>
+      <c r="L318" s="2" t="inlineStr">
+        <is>
+          <t>0.556751</t>
+        </is>
+      </c>
+      <c r="M318" s="2" t="inlineStr"/>
+      <c r="N318" s="2" t="inlineStr"/>
+      <c r="O318" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P318" s="2" t="inlineStr">
+        <is>
+          <t>0.517413</t>
+        </is>
+      </c>
+      <c r="Q318" s="2" t="inlineStr">
+        <is>
+          <t>0.03752023076923083</t>
+        </is>
+      </c>
+      <c r="R318" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:37.028130Z</t>
+        </is>
+      </c>
+      <c r="S318" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:45:00-0400</t>
+        </is>
+      </c>
+      <c r="T318" s="2" t="inlineStr"/>
+      <c r="U318" s="2" t="inlineStr"/>
+      <c r="V318" s="2" t="inlineStr"/>
+      <c r="W318" s="2" t="inlineStr"/>
+      <c r="X318" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y318" s="2" t="inlineStr"/>
+      <c r="Z318" s="2" t="inlineStr"/>
+      <c r="AA318" s="2" t="inlineStr"/>
+      <c r="AB318" s="2" t="inlineStr"/>
+      <c r="AC318" s="2" t="inlineStr"/>
+      <c r="AD318" s="2" t="inlineStr"/>
+      <c r="AE318" s="2" t="inlineStr"/>
+      <c r="AF318" s="2" t="inlineStr"/>
+      <c r="AG318" s="2" t="inlineStr"/>
+      <c r="AH318" s="2" t="inlineStr"/>
+      <c r="AI318" s="2" t="inlineStr"/>
+      <c r="AJ318" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ232"/>
+  <autoFilter ref="A1:AJ318"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/flat/model_ledgers/mlb-moneyline-elo-trend-lr.xlsx
+++ b/data/flat/model_ledgers/mlb-moneyline-elo-trend-lr.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$318</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$331</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ318"/>
+  <dimension ref="A1:AJ331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -34874,8 +34874,1386 @@
       <c r="AI318" s="2" t="inlineStr"/>
       <c r="AJ318" s="2" t="inlineStr"/>
     </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>f8c9ab98bc8643df</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>36b77e0a89c00685</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t>401816428</t>
+        </is>
+      </c>
+      <c r="I319" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J319" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K319" s="2" t="inlineStr"/>
+      <c r="L319" s="2" t="inlineStr">
+        <is>
+          <t>0.581752</t>
+        </is>
+      </c>
+      <c r="M319" s="2" t="inlineStr"/>
+      <c r="N319" s="2" t="inlineStr"/>
+      <c r="O319" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P319" s="2" t="inlineStr">
+        <is>
+          <t>0.557214</t>
+        </is>
+      </c>
+      <c r="Q319" s="2" t="inlineStr">
+        <is>
+          <t>0.02228063436123351</t>
+        </is>
+      </c>
+      <c r="R319" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:53.881975Z</t>
+        </is>
+      </c>
+      <c r="S319" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T319" s="2" t="inlineStr"/>
+      <c r="U319" s="2" t="inlineStr"/>
+      <c r="V319" s="2" t="inlineStr"/>
+      <c r="W319" s="2" t="inlineStr"/>
+      <c r="X319" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y319" s="2" t="inlineStr"/>
+      <c r="Z319" s="2" t="inlineStr"/>
+      <c r="AA319" s="2" t="inlineStr"/>
+      <c r="AB319" s="2" t="inlineStr"/>
+      <c r="AC319" s="2" t="inlineStr"/>
+      <c r="AD319" s="2" t="inlineStr"/>
+      <c r="AE319" s="2" t="inlineStr"/>
+      <c r="AF319" s="2" t="inlineStr"/>
+      <c r="AG319" s="2" t="inlineStr"/>
+      <c r="AH319" s="2" t="inlineStr"/>
+      <c r="AI319" s="2" t="inlineStr"/>
+      <c r="AJ319" s="2" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>a8bcd75548df43b0</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="inlineStr">
+        <is>
+          <t>8e2973a0813de9d2</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="inlineStr">
+        <is>
+          <t>401816429</t>
+        </is>
+      </c>
+      <c r="I320" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J320" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K320" s="2" t="inlineStr"/>
+      <c r="L320" s="2" t="inlineStr">
+        <is>
+          <t>0.562475</t>
+        </is>
+      </c>
+      <c r="M320" s="2" t="inlineStr"/>
+      <c r="N320" s="2" t="inlineStr"/>
+      <c r="O320" s="2" t="inlineStr">
+        <is>
+          <t>0.6655518394648829</t>
+        </is>
+      </c>
+      <c r="P320" s="2" t="inlineStr">
+        <is>
+          <t>0.661692</t>
+        </is>
+      </c>
+      <c r="Q320" s="2" t="inlineStr">
+        <is>
+          <t>-0.103076839464883</t>
+        </is>
+      </c>
+      <c r="R320" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:53.313564Z</t>
+        </is>
+      </c>
+      <c r="S320" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T320" s="2" t="inlineStr"/>
+      <c r="U320" s="2" t="inlineStr"/>
+      <c r="V320" s="2" t="inlineStr"/>
+      <c r="W320" s="2" t="inlineStr"/>
+      <c r="X320" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y320" s="2" t="inlineStr"/>
+      <c r="Z320" s="2" t="inlineStr"/>
+      <c r="AA320" s="2" t="inlineStr"/>
+      <c r="AB320" s="2" t="inlineStr"/>
+      <c r="AC320" s="2" t="inlineStr"/>
+      <c r="AD320" s="2" t="inlineStr"/>
+      <c r="AE320" s="2" t="inlineStr"/>
+      <c r="AF320" s="2" t="inlineStr"/>
+      <c r="AG320" s="2" t="inlineStr"/>
+      <c r="AH320" s="2" t="inlineStr"/>
+      <c r="AI320" s="2" t="inlineStr"/>
+      <c r="AJ320" s="2" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>0369358d03204a0b</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F321" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G321" s="2" t="inlineStr">
+        <is>
+          <t>b382714397f85937</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="inlineStr">
+        <is>
+          <t>401816426</t>
+        </is>
+      </c>
+      <c r="I321" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J321" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K321" s="2" t="inlineStr"/>
+      <c r="L321" s="2" t="inlineStr">
+        <is>
+          <t>0.531118</t>
+        </is>
+      </c>
+      <c r="M321" s="2" t="inlineStr"/>
+      <c r="N321" s="2" t="inlineStr"/>
+      <c r="O321" s="2" t="inlineStr">
+        <is>
+          <t>0.5555555555555556</t>
+        </is>
+      </c>
+      <c r="P321" s="2" t="inlineStr">
+        <is>
+          <t>0.552239</t>
+        </is>
+      </c>
+      <c r="Q321" s="2" t="inlineStr">
+        <is>
+          <t>-0.0244375555555556</t>
+        </is>
+      </c>
+      <c r="R321" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:54.963458Z</t>
+        </is>
+      </c>
+      <c r="S321" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="T321" s="2" t="inlineStr"/>
+      <c r="U321" s="2" t="inlineStr"/>
+      <c r="V321" s="2" t="inlineStr"/>
+      <c r="W321" s="2" t="inlineStr"/>
+      <c r="X321" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y321" s="2" t="inlineStr"/>
+      <c r="Z321" s="2" t="inlineStr"/>
+      <c r="AA321" s="2" t="inlineStr"/>
+      <c r="AB321" s="2" t="inlineStr"/>
+      <c r="AC321" s="2" t="inlineStr"/>
+      <c r="AD321" s="2" t="inlineStr"/>
+      <c r="AE321" s="2" t="inlineStr"/>
+      <c r="AF321" s="2" t="inlineStr"/>
+      <c r="AG321" s="2" t="inlineStr"/>
+      <c r="AH321" s="2" t="inlineStr"/>
+      <c r="AI321" s="2" t="inlineStr"/>
+      <c r="AJ321" s="2" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>0d57dfbb286a409d</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>8bd990e177da70c3</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t>401816424</t>
+        </is>
+      </c>
+      <c r="I322" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J322" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K322" s="2" t="inlineStr"/>
+      <c r="L322" s="2" t="inlineStr">
+        <is>
+          <t>0.641185</t>
+        </is>
+      </c>
+      <c r="M322" s="2" t="inlineStr"/>
+      <c r="N322" s="2" t="inlineStr"/>
+      <c r="O322" s="2" t="inlineStr">
+        <is>
+          <t>0.5850622406639003</t>
+        </is>
+      </c>
+      <c r="P322" s="2" t="inlineStr">
+        <is>
+          <t>0.58209</t>
+        </is>
+      </c>
+      <c r="Q322" s="2" t="inlineStr">
+        <is>
+          <t>0.05612275933609967</t>
+        </is>
+      </c>
+      <c r="R322" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:55.953169Z</t>
+        </is>
+      </c>
+      <c r="S322" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T322" s="2" t="inlineStr"/>
+      <c r="U322" s="2" t="inlineStr"/>
+      <c r="V322" s="2" t="inlineStr"/>
+      <c r="W322" s="2" t="inlineStr"/>
+      <c r="X322" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y322" s="2" t="inlineStr"/>
+      <c r="Z322" s="2" t="inlineStr"/>
+      <c r="AA322" s="2" t="inlineStr"/>
+      <c r="AB322" s="2" t="inlineStr"/>
+      <c r="AC322" s="2" t="inlineStr"/>
+      <c r="AD322" s="2" t="inlineStr"/>
+      <c r="AE322" s="2" t="inlineStr"/>
+      <c r="AF322" s="2" t="inlineStr"/>
+      <c r="AG322" s="2" t="inlineStr"/>
+      <c r="AH322" s="2" t="inlineStr"/>
+      <c r="AI322" s="2" t="inlineStr"/>
+      <c r="AJ322" s="2" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>8df16023b5cd4f26</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G323" s="2" t="inlineStr">
+        <is>
+          <t>e1b75023630563d1</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="inlineStr">
+        <is>
+          <t>401816425</t>
+        </is>
+      </c>
+      <c r="I323" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J323" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K323" s="2" t="inlineStr"/>
+      <c r="L323" s="2" t="inlineStr">
+        <is>
+          <t>0.633651</t>
+        </is>
+      </c>
+      <c r="M323" s="2" t="inlineStr"/>
+      <c r="N323" s="2" t="inlineStr"/>
+      <c r="O323" s="2" t="inlineStr">
+        <is>
+          <t>0.715099715099715</t>
+        </is>
+      </c>
+      <c r="P323" s="2" t="inlineStr">
+        <is>
+          <t>0.711443</t>
+        </is>
+      </c>
+      <c r="Q323" s="2" t="inlineStr">
+        <is>
+          <t>-0.08144871509971507</t>
+        </is>
+      </c>
+      <c r="R323" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:55.473435Z</t>
+        </is>
+      </c>
+      <c r="S323" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T323" s="2" t="inlineStr"/>
+      <c r="U323" s="2" t="inlineStr"/>
+      <c r="V323" s="2" t="inlineStr"/>
+      <c r="W323" s="2" t="inlineStr"/>
+      <c r="X323" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y323" s="2" t="inlineStr"/>
+      <c r="Z323" s="2" t="inlineStr"/>
+      <c r="AA323" s="2" t="inlineStr"/>
+      <c r="AB323" s="2" t="inlineStr"/>
+      <c r="AC323" s="2" t="inlineStr"/>
+      <c r="AD323" s="2" t="inlineStr"/>
+      <c r="AE323" s="2" t="inlineStr"/>
+      <c r="AF323" s="2" t="inlineStr"/>
+      <c r="AG323" s="2" t="inlineStr"/>
+      <c r="AH323" s="2" t="inlineStr"/>
+      <c r="AI323" s="2" t="inlineStr"/>
+      <c r="AJ323" s="2" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>55626f9b1cc84979</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>53df13bab12c4582</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t>401816432</t>
+        </is>
+      </c>
+      <c r="I324" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J324" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K324" s="2" t="inlineStr"/>
+      <c r="L324" s="2" t="inlineStr">
+        <is>
+          <t>0.522033</t>
+        </is>
+      </c>
+      <c r="M324" s="2" t="inlineStr"/>
+      <c r="N324" s="2" t="inlineStr"/>
+      <c r="O324" s="2" t="inlineStr">
+        <is>
+          <t>0.4291845493562232</t>
+        </is>
+      </c>
+      <c r="P324" s="2" t="inlineStr">
+        <is>
+          <t>0.427861</t>
+        </is>
+      </c>
+      <c r="Q324" s="2" t="inlineStr">
+        <is>
+          <t>0.09284845064377678</t>
+        </is>
+      </c>
+      <c r="R324" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:57.437825Z</t>
+        </is>
+      </c>
+      <c r="S324" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T324" s="2" t="inlineStr"/>
+      <c r="U324" s="2" t="inlineStr"/>
+      <c r="V324" s="2" t="inlineStr"/>
+      <c r="W324" s="2" t="inlineStr"/>
+      <c r="X324" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y324" s="2" t="inlineStr"/>
+      <c r="Z324" s="2" t="inlineStr"/>
+      <c r="AA324" s="2" t="inlineStr"/>
+      <c r="AB324" s="2" t="inlineStr"/>
+      <c r="AC324" s="2" t="inlineStr"/>
+      <c r="AD324" s="2" t="inlineStr"/>
+      <c r="AE324" s="2" t="inlineStr"/>
+      <c r="AF324" s="2" t="inlineStr"/>
+      <c r="AG324" s="2" t="inlineStr"/>
+      <c r="AH324" s="2" t="inlineStr"/>
+      <c r="AI324" s="2" t="inlineStr"/>
+      <c r="AJ324" s="2" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>b216031ab5ef493b</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G325" s="2" t="inlineStr">
+        <is>
+          <t>6930bf181d0a558c</t>
+        </is>
+      </c>
+      <c r="H325" s="2" t="inlineStr">
+        <is>
+          <t>401816434</t>
+        </is>
+      </c>
+      <c r="I325" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J325" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K325" s="2" t="inlineStr"/>
+      <c r="L325" s="2" t="inlineStr">
+        <is>
+          <t>0.651659</t>
+        </is>
+      </c>
+      <c r="M325" s="2" t="inlineStr"/>
+      <c r="N325" s="2" t="inlineStr"/>
+      <c r="O325" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P325" s="2" t="inlineStr">
+        <is>
+          <t>0.616915</t>
+        </is>
+      </c>
+      <c r="Q325" s="2" t="inlineStr">
+        <is>
+          <t>0.0318871368821293</t>
+        </is>
+      </c>
+      <c r="R325" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:56.444164Z</t>
+        </is>
+      </c>
+      <c r="S325" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T325" s="2" t="inlineStr"/>
+      <c r="U325" s="2" t="inlineStr"/>
+      <c r="V325" s="2" t="inlineStr"/>
+      <c r="W325" s="2" t="inlineStr"/>
+      <c r="X325" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y325" s="2" t="inlineStr"/>
+      <c r="Z325" s="2" t="inlineStr"/>
+      <c r="AA325" s="2" t="inlineStr"/>
+      <c r="AB325" s="2" t="inlineStr"/>
+      <c r="AC325" s="2" t="inlineStr"/>
+      <c r="AD325" s="2" t="inlineStr"/>
+      <c r="AE325" s="2" t="inlineStr"/>
+      <c r="AF325" s="2" t="inlineStr"/>
+      <c r="AG325" s="2" t="inlineStr"/>
+      <c r="AH325" s="2" t="inlineStr"/>
+      <c r="AI325" s="2" t="inlineStr"/>
+      <c r="AJ325" s="2" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>0a05673eba8c47ba</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>db25d2479efd20e9</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t>401816431</t>
+        </is>
+      </c>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J326" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K326" s="2" t="inlineStr"/>
+      <c r="L326" s="2" t="inlineStr">
+        <is>
+          <t>0.532629</t>
+        </is>
+      </c>
+      <c r="M326" s="2" t="inlineStr"/>
+      <c r="N326" s="2" t="inlineStr"/>
+      <c r="O326" s="2" t="inlineStr">
+        <is>
+          <t>0.6153846153846154</t>
+        </is>
+      </c>
+      <c r="P326" s="2" t="inlineStr">
+        <is>
+          <t>0.61194</t>
+        </is>
+      </c>
+      <c r="Q326" s="2" t="inlineStr">
+        <is>
+          <t>-0.0827556153846154</t>
+        </is>
+      </c>
+      <c r="R326" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:57.775453Z</t>
+        </is>
+      </c>
+      <c r="S326" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T20:10:00-0400</t>
+        </is>
+      </c>
+      <c r="T326" s="2" t="inlineStr"/>
+      <c r="U326" s="2" t="inlineStr"/>
+      <c r="V326" s="2" t="inlineStr"/>
+      <c r="W326" s="2" t="inlineStr"/>
+      <c r="X326" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y326" s="2" t="inlineStr"/>
+      <c r="Z326" s="2" t="inlineStr"/>
+      <c r="AA326" s="2" t="inlineStr"/>
+      <c r="AB326" s="2" t="inlineStr"/>
+      <c r="AC326" s="2" t="inlineStr"/>
+      <c r="AD326" s="2" t="inlineStr"/>
+      <c r="AE326" s="2" t="inlineStr"/>
+      <c r="AF326" s="2" t="inlineStr"/>
+      <c r="AG326" s="2" t="inlineStr"/>
+      <c r="AH326" s="2" t="inlineStr"/>
+      <c r="AI326" s="2" t="inlineStr"/>
+      <c r="AJ326" s="2" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>128b0e95c10545ac</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>014888ea3e3e3318</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t>401816430</t>
+        </is>
+      </c>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J327" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K327" s="2" t="inlineStr"/>
+      <c r="L327" s="2" t="inlineStr">
+        <is>
+          <t>0.551691</t>
+        </is>
+      </c>
+      <c r="M327" s="2" t="inlineStr"/>
+      <c r="N327" s="2" t="inlineStr"/>
+      <c r="O327" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P327" s="2" t="inlineStr">
+        <is>
+          <t>0.577114</t>
+        </is>
+      </c>
+      <c r="Q327" s="2" t="inlineStr">
+        <is>
+          <t>-0.02814093277310914</t>
+        </is>
+      </c>
+      <c r="R327" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:58.624050Z</t>
+        </is>
+      </c>
+      <c r="S327" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T20:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T327" s="2" t="inlineStr"/>
+      <c r="U327" s="2" t="inlineStr"/>
+      <c r="V327" s="2" t="inlineStr"/>
+      <c r="W327" s="2" t="inlineStr"/>
+      <c r="X327" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y327" s="2" t="inlineStr"/>
+      <c r="Z327" s="2" t="inlineStr"/>
+      <c r="AA327" s="2" t="inlineStr"/>
+      <c r="AB327" s="2" t="inlineStr"/>
+      <c r="AC327" s="2" t="inlineStr"/>
+      <c r="AD327" s="2" t="inlineStr"/>
+      <c r="AE327" s="2" t="inlineStr"/>
+      <c r="AF327" s="2" t="inlineStr"/>
+      <c r="AG327" s="2" t="inlineStr"/>
+      <c r="AH327" s="2" t="inlineStr"/>
+      <c r="AI327" s="2" t="inlineStr"/>
+      <c r="AJ327" s="2" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>955a1482baa548b2</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>cf5d809f58d18264</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t>401816433</t>
+        </is>
+      </c>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J328" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K328" s="2" t="inlineStr"/>
+      <c r="L328" s="2" t="inlineStr">
+        <is>
+          <t>0.667145</t>
+        </is>
+      </c>
+      <c r="M328" s="2" t="inlineStr"/>
+      <c r="N328" s="2" t="inlineStr"/>
+      <c r="O328" s="2" t="inlineStr">
+        <is>
+          <t>0.6153846153846154</t>
+        </is>
+      </c>
+      <c r="P328" s="2" t="inlineStr">
+        <is>
+          <t>0.61194</t>
+        </is>
+      </c>
+      <c r="Q328" s="2" t="inlineStr">
+        <is>
+          <t>0.05176038461538457</t>
+        </is>
+      </c>
+      <c r="R328" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:59.237881Z</t>
+        </is>
+      </c>
+      <c r="S328" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T20:15:00-0400</t>
+        </is>
+      </c>
+      <c r="T328" s="2" t="inlineStr"/>
+      <c r="U328" s="2" t="inlineStr"/>
+      <c r="V328" s="2" t="inlineStr"/>
+      <c r="W328" s="2" t="inlineStr"/>
+      <c r="X328" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y328" s="2" t="inlineStr"/>
+      <c r="Z328" s="2" t="inlineStr"/>
+      <c r="AA328" s="2" t="inlineStr"/>
+      <c r="AB328" s="2" t="inlineStr"/>
+      <c r="AC328" s="2" t="inlineStr"/>
+      <c r="AD328" s="2" t="inlineStr"/>
+      <c r="AE328" s="2" t="inlineStr"/>
+      <c r="AF328" s="2" t="inlineStr"/>
+      <c r="AG328" s="2" t="inlineStr"/>
+      <c r="AH328" s="2" t="inlineStr"/>
+      <c r="AI328" s="2" t="inlineStr"/>
+      <c r="AJ328" s="2" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>75f5ed3c3c2647f1</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G329" s="2" t="inlineStr">
+        <is>
+          <t>f41cdedf84b1bab8</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="inlineStr">
+        <is>
+          <t>401816436</t>
+        </is>
+      </c>
+      <c r="I329" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J329" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K329" s="2" t="inlineStr"/>
+      <c r="L329" s="2" t="inlineStr">
+        <is>
+          <t>0.586422</t>
+        </is>
+      </c>
+      <c r="M329" s="2" t="inlineStr"/>
+      <c r="N329" s="2" t="inlineStr"/>
+      <c r="O329" s="2" t="inlineStr">
+        <is>
+          <t>0.5260663507109005</t>
+        </is>
+      </c>
+      <c r="P329" s="2" t="inlineStr">
+        <is>
+          <t>0.522388</t>
+        </is>
+      </c>
+      <c r="Q329" s="2" t="inlineStr">
+        <is>
+          <t>0.06035564928909953</t>
+        </is>
+      </c>
+      <c r="R329" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:59.634473Z</t>
+        </is>
+      </c>
+      <c r="S329" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T329" s="2" t="inlineStr"/>
+      <c r="U329" s="2" t="inlineStr"/>
+      <c r="V329" s="2" t="inlineStr"/>
+      <c r="W329" s="2" t="inlineStr"/>
+      <c r="X329" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y329" s="2" t="inlineStr"/>
+      <c r="Z329" s="2" t="inlineStr"/>
+      <c r="AA329" s="2" t="inlineStr"/>
+      <c r="AB329" s="2" t="inlineStr"/>
+      <c r="AC329" s="2" t="inlineStr"/>
+      <c r="AD329" s="2" t="inlineStr"/>
+      <c r="AE329" s="2" t="inlineStr"/>
+      <c r="AF329" s="2" t="inlineStr"/>
+      <c r="AG329" s="2" t="inlineStr"/>
+      <c r="AH329" s="2" t="inlineStr"/>
+      <c r="AI329" s="2" t="inlineStr"/>
+      <c r="AJ329" s="2" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>f493f2e498264692</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>807bfd9a83666e43</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="inlineStr">
+        <is>
+          <t>401816437</t>
+        </is>
+      </c>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J330" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K330" s="2" t="inlineStr"/>
+      <c r="L330" s="2" t="inlineStr">
+        <is>
+          <t>0.527996</t>
+        </is>
+      </c>
+      <c r="M330" s="2" t="inlineStr"/>
+      <c r="N330" s="2" t="inlineStr"/>
+      <c r="O330" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P330" s="2" t="inlineStr">
+        <is>
+          <t>0.616915</t>
+        </is>
+      </c>
+      <c r="Q330" s="2" t="inlineStr">
+        <is>
+          <t>-0.09177586311787067</t>
+        </is>
+      </c>
+      <c r="R330" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:28:00.536930Z</t>
+        </is>
+      </c>
+      <c r="S330" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="T330" s="2" t="inlineStr"/>
+      <c r="U330" s="2" t="inlineStr"/>
+      <c r="V330" s="2" t="inlineStr"/>
+      <c r="W330" s="2" t="inlineStr"/>
+      <c r="X330" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y330" s="2" t="inlineStr"/>
+      <c r="Z330" s="2" t="inlineStr"/>
+      <c r="AA330" s="2" t="inlineStr"/>
+      <c r="AB330" s="2" t="inlineStr"/>
+      <c r="AC330" s="2" t="inlineStr"/>
+      <c r="AD330" s="2" t="inlineStr"/>
+      <c r="AE330" s="2" t="inlineStr"/>
+      <c r="AF330" s="2" t="inlineStr"/>
+      <c r="AG330" s="2" t="inlineStr"/>
+      <c r="AH330" s="2" t="inlineStr"/>
+      <c r="AI330" s="2" t="inlineStr"/>
+      <c r="AJ330" s="2" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>9978fb6eb7ea49aa</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>mlb-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="G331" s="2" t="inlineStr">
+        <is>
+          <t>cf9d26fcd493bc83</t>
+        </is>
+      </c>
+      <c r="H331" s="2" t="inlineStr">
+        <is>
+          <t>401816438</t>
+        </is>
+      </c>
+      <c r="I331" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J331" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K331" s="2" t="inlineStr"/>
+      <c r="L331" s="2" t="inlineStr">
+        <is>
+          <t>0.556751</t>
+        </is>
+      </c>
+      <c r="M331" s="2" t="inlineStr"/>
+      <c r="N331" s="2" t="inlineStr"/>
+      <c r="O331" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P331" s="2" t="inlineStr">
+        <is>
+          <t>0.517413</t>
+        </is>
+      </c>
+      <c r="Q331" s="2" t="inlineStr">
+        <is>
+          <t>0.03752023076923083</t>
+        </is>
+      </c>
+      <c r="R331" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:28:01.370150Z</t>
+        </is>
+      </c>
+      <c r="S331" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:45:00-0400</t>
+        </is>
+      </c>
+      <c r="T331" s="2" t="inlineStr"/>
+      <c r="U331" s="2" t="inlineStr"/>
+      <c r="V331" s="2" t="inlineStr"/>
+      <c r="W331" s="2" t="inlineStr"/>
+      <c r="X331" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y331" s="2" t="inlineStr"/>
+      <c r="Z331" s="2" t="inlineStr"/>
+      <c r="AA331" s="2" t="inlineStr"/>
+      <c r="AB331" s="2" t="inlineStr"/>
+      <c r="AC331" s="2" t="inlineStr"/>
+      <c r="AD331" s="2" t="inlineStr"/>
+      <c r="AE331" s="2" t="inlineStr"/>
+      <c r="AF331" s="2" t="inlineStr"/>
+      <c r="AG331" s="2" t="inlineStr"/>
+      <c r="AH331" s="2" t="inlineStr"/>
+      <c r="AI331" s="2" t="inlineStr"/>
+      <c r="AJ331" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ318"/>
+  <autoFilter ref="A1:AJ331"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>